--- a/BaoCao_BGD_TimViec123.xlsx
+++ b/BaoCao_BGD_TimViec123.xlsx
@@ -35,7 +35,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -215,13 +215,25 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="9"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -313,7 +325,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -540,57 +552,102 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="27" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="27" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -599,13 +656,13 @@
     <xf numFmtId="3" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2476,13 +2533,13 @@
     </row>
     <row r="64">
       <c r="A64" s="79">
-        <f>IFERROR(QUERY('z_TrangFull'!$A$1:$R$65,"select B, I, E where P &gt;= date '"&amp;TEXT($N$4,"yyyy-mm-dd")&amp;"' and P &lt;= date '"&amp;TEXT($O$4,"yyyy-mm-dd")&amp;"' and (E = 'Hoàn thành' or E = 'Kiểm tra lại') order by I desc label B '', I '', E '' format I '#,##0'",1),"(không có trang test trong kỳ)")</f>
+        <f>IFERROR(QUERY('z_TrangFull'!$A$1:$R$197,"select B, I, E where P &gt;= date '"&amp;TEXT($N$4,"yyyy-mm-dd")&amp;"' and P &lt;= date '"&amp;TEXT($O$4,"yyyy-mm-dd")&amp;"' and (E = 'Hoàn thành' or E = 'Kiểm tra lại') order by I desc label B '', I '', E '' format I '#,##0'",1),"(không có trang test trong kỳ)")</f>
         <v/>
       </c>
       <c r="B64" s="80" t="n"/>
       <c r="C64" s="14" t="n"/>
       <c r="F64" s="79">
-        <f>IFERROR(QUERY('z_TNFull'!$A$1:$T$89,"select B, K, J where R &gt;= date '"&amp;TEXT($N$4,"yyyy-mm-dd")&amp;"' and R &lt;= date '"&amp;TEXT($O$4,"yyyy-mm-dd")&amp;"' and (J = 'Hoàn thành' or J = 'Kiểm tra lại') order by K desc label B '', K '', J '' format K '#,##0'",1),"(không có tính năng test trong kỳ)")</f>
+        <f>IFERROR(QUERY('z_TNFull'!$A$1:$T$197,"select B, K, J where R &gt;= date '"&amp;TEXT($N$4,"yyyy-mm-dd")&amp;"' and R &lt;= date '"&amp;TEXT($O$4,"yyyy-mm-dd")&amp;"' and (J = 'Hoàn thành' or J = 'Kiểm tra lại') order by K desc label B '', K '', J '' format K '#,##0'",1),"(không có tính năng test trong kỳ)")</f>
         <v/>
       </c>
       <c r="G64" s="80" t="n"/>
@@ -4160,13 +4217,13 @@
     </row>
     <row r="65">
       <c r="A65" s="79">
-        <f>IFERROR(QUERY('z_TrangFull'!$A$1:$R$65,"select B, I, P where P &gt;= date '"&amp;TEXT($N$4,"yyyy-mm-dd")&amp;"' and P &lt;= date '"&amp;TEXT($O$4,"yyyy-mm-dd")&amp;"' and (E = 'Hoàn thành' or E = 'Kiểm tra lại') order by P desc label B '', I '', P '' format I '#,##0', P 'dd/mm/yyyy'",1),"(không có trang test trong kỳ)")</f>
+        <f>IFERROR(QUERY('z_TrangFull'!$A$1:$R$197,"select B, I, P where P &gt;= date '"&amp;TEXT($N$4,"yyyy-mm-dd")&amp;"' and P &lt;= date '"&amp;TEXT($O$4,"yyyy-mm-dd")&amp;"' and (E = 'Hoàn thành' or E = 'Kiểm tra lại') order by P desc label B '', I '', P '' format I '#,##0', P 'dd/mm/yyyy'",1),"(không có trang test trong kỳ)")</f>
         <v/>
       </c>
       <c r="B65" s="80" t="n"/>
       <c r="C65" s="85" t="n"/>
       <c r="F65" s="79">
-        <f>IFERROR(QUERY('z_TNFull'!$A$1:$T$89,"select B, K, R where R &gt;= date '"&amp;TEXT($N$4,"yyyy-mm-dd")&amp;"' and R &lt;= date '"&amp;TEXT($O$4,"yyyy-mm-dd")&amp;"' and (J = 'Hoàn thành' or J = 'Kiểm tra lại') order by R desc label B '', K '', R '' format K '#,##0', R 'dd/mm/yyyy'",1),"(không có tính năng test trong kỳ)")</f>
+        <f>IFERROR(QUERY('z_TNFull'!$A$1:$T$197,"select B, K, R where R &gt;= date '"&amp;TEXT($N$4,"yyyy-mm-dd")&amp;"' and R &lt;= date '"&amp;TEXT($O$4,"yyyy-mm-dd")&amp;"' and (J = 'Hoàn thành' or J = 'Kiểm tra lại') order by R desc label B '', K '', R '' format K '#,##0', R 'dd/mm/yyyy'",1),"(không có tính năng test trong kỳ)")</f>
         <v/>
       </c>
       <c r="G65" s="80" t="n"/>
@@ -4737,23 +4794,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>BIÊN BẢN / CHECKLIST NGHIỆM THU</t>
+          <t>BIÊN BẢN NGHIỆM THU WEBSITE TIMVIEC123</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -4763,11 +4821,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="22" t="inlineStr">
-        <is>
-          <t>Cột Kết luận &amp; Người duyệt do người duyệt điền.</t>
+      <c r="I1" s="3" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>Ô nền VÀNG = nhập tay. Ô nền trắng/xám có công thức = tự động lấy từ dữ liệu QA (02_UI_UX, 03_Tính_năng, 05_Lỗi_Tester) — không sửa tay. Phần nào chưa có dữ liệu nguồn thì để trống và ghi rõ trong mục 'Thông tin còn thiếu'.</t>
         </is>
       </c>
       <c r="B2" s="5" t="n"/>
@@ -4777,258 +4836,4438 @@
       <c r="F2" s="5" t="n"/>
       <c r="G2" s="5" t="n"/>
       <c r="H2" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="43" t="inlineStr">
-        <is>
-          <t>Kỳ nghiệm thu</t>
-        </is>
-      </c>
-      <c r="B4" s="86" t="inlineStr">
-        <is>
-          <t>Tháng 8</t>
-        </is>
-      </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="I2" s="5" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>I. THÔNG TIN CHUNG</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="86" t="inlineStr">
+        <is>
+          <t>Số biên bản</t>
+        </is>
+      </c>
+      <c r="B5" s="87" t="n"/>
+      <c r="C5" s="88" t="n"/>
+      <c r="D5" s="86" t="inlineStr">
         <is>
           <t>Ngày lập</t>
         </is>
       </c>
-      <c r="D4" s="87">
+      <c r="E5" s="89">
         <f>TODAY()</f>
         <v/>
       </c>
-      <c r="E4" s="88" t="n"/>
-      <c r="F4" s="43" t="inlineStr">
-        <is>
-          <t>Người lập</t>
-        </is>
-      </c>
-      <c r="G4" s="89" t="inlineStr"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="90" t="inlineStr">
+      <c r="F5" s="88" t="n"/>
+      <c r="G5" s="86" t="inlineStr">
+        <is>
+          <t>Địa điểm lập</t>
+        </is>
+      </c>
+      <c r="H5" s="87" t="n"/>
+      <c r="I5" s="88" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="86" t="inlineStr">
+        <is>
+          <t>Tên dự án</t>
+        </is>
+      </c>
+      <c r="B6" s="87" t="inlineStr">
+        <is>
+          <t>Website TimViec123</t>
+        </is>
+      </c>
+      <c r="C6" s="88" t="n"/>
+      <c r="D6" s="86" t="inlineStr">
+        <is>
+          <t>Tên miền / URL</t>
+        </is>
+      </c>
+      <c r="E6" s="87" t="n"/>
+      <c r="F6" s="88" t="n"/>
+      <c r="G6" s="86" t="inlineStr">
+        <is>
+          <t>Môi trường nghiệm thu</t>
+        </is>
+      </c>
+      <c r="H6" s="87" t="n"/>
+      <c r="I6" s="88" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="86" t="inlineStr">
+        <is>
+          <t>Giai đoạn nghiệm thu</t>
+        </is>
+      </c>
+      <c r="B7" s="87" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1</t>
+        </is>
+      </c>
+      <c r="C7" s="88" t="n"/>
+      <c r="D7" s="86" t="inlineStr">
+        <is>
+          <t>Phiên bản / Release</t>
+        </is>
+      </c>
+      <c r="E7" s="87" t="n"/>
+      <c r="F7" s="88" t="n"/>
+      <c r="G7" s="86" t="inlineStr">
+        <is>
+          <t>Kỳ kiểm thử (từ)</t>
+        </is>
+      </c>
+      <c r="H7" s="89" t="n"/>
+      <c r="I7" s="88" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="86" t="inlineStr">
+        <is>
+          <t>Kỳ kiểm thử (đến)</t>
+        </is>
+      </c>
+      <c r="B8" s="89" t="n"/>
+      <c r="C8" s="88" t="n"/>
+      <c r="D8" s="86" t="inlineStr">
+        <is>
+          <t>Hợp đồng số</t>
+        </is>
+      </c>
+      <c r="E8" s="87" t="n"/>
+      <c r="F8" s="88" t="n"/>
+      <c r="G8" s="86" t="inlineStr">
+        <is>
+          <t>Ngày hợp đồng</t>
+        </is>
+      </c>
+      <c r="H8" s="89" t="n"/>
+      <c r="I8" s="88" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="86" t="inlineStr">
+        <is>
+          <t>Tài liệu yêu cầu (SRS/BRD)</t>
+        </is>
+      </c>
+      <c r="B9" s="87" t="n"/>
+      <c r="C9" s="88" t="n"/>
+      <c r="D9" s="86" t="inlineStr">
+        <is>
+          <t>Kế hoạch kiểm thử</t>
+        </is>
+      </c>
+      <c r="E9" s="87" t="n"/>
+      <c r="F9" s="88" t="n"/>
+      <c r="G9" s="86" t="inlineStr">
+        <is>
+          <t>Lần nghiệm thu thứ</t>
+        </is>
+      </c>
+      <c r="H9" s="87" t="n"/>
+      <c r="I9" s="88" t="n"/>
+    </row>
+    <row r="10" ht="8" customHeight="1"/>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>II. CÁC BÊN THAM GIA</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="90" t="inlineStr">
+        <is>
+          <t>Vai trò</t>
+        </is>
+      </c>
+      <c r="B12" s="90" t="inlineStr">
+        <is>
+          <t>Đơn vị / Bộ phận</t>
+        </is>
+      </c>
+      <c r="C12" s="90" t="inlineStr">
+        <is>
+          <t>Họ và tên</t>
+        </is>
+      </c>
+      <c r="D12" s="90" t="inlineStr">
+        <is>
+          <t>Chức vụ</t>
+        </is>
+      </c>
+      <c r="E12" s="90" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="F12" s="90" t="inlineStr">
+        <is>
+          <t>Điện thoại</t>
+        </is>
+      </c>
+      <c r="G12" s="90" t="inlineStr">
+        <is>
+          <t>Trách nhiệm</t>
+        </is>
+      </c>
+      <c r="H12" s="90" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+      <c r="I12" s="90" t="inlineStr"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="91" t="inlineStr">
+        <is>
+          <t>Bên A — Chủ đầu tư</t>
+        </is>
+      </c>
+      <c r="B13" s="92" t="n"/>
+      <c r="C13" s="92" t="n"/>
+      <c r="D13" s="93" t="n"/>
+      <c r="E13" s="93" t="n"/>
+      <c r="F13" s="93" t="n"/>
+      <c r="G13" s="91" t="inlineStr">
+        <is>
+          <t>Phê duyệt &amp; ký nghiệm thu</t>
+        </is>
+      </c>
+      <c r="H13" s="91" t="n"/>
+      <c r="I13" s="94" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="95" t="inlineStr">
+        <is>
+          <t>Bên B — Đơn vị thực hiện</t>
+        </is>
+      </c>
+      <c r="B14" s="92" t="n"/>
+      <c r="C14" s="92" t="n"/>
+      <c r="D14" s="93" t="n"/>
+      <c r="E14" s="93" t="n"/>
+      <c r="F14" s="93" t="n"/>
+      <c r="G14" s="95" t="inlineStr">
+        <is>
+          <t>Bàn giao sản phẩm, xử lý lỗi</t>
+        </is>
+      </c>
+      <c r="H14" s="95" t="n"/>
+      <c r="I14" s="96" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="91" t="inlineStr">
+        <is>
+          <t>Quản lý dự án (PM)</t>
+        </is>
+      </c>
+      <c r="B15" s="92" t="n"/>
+      <c r="C15" s="92" t="n"/>
+      <c r="D15" s="93" t="n"/>
+      <c r="E15" s="93" t="n"/>
+      <c r="F15" s="93" t="n"/>
+      <c r="G15" s="91" t="inlineStr">
+        <is>
+          <t>Điều phối, chốt phạm vi</t>
+        </is>
+      </c>
+      <c r="H15" s="91" t="n"/>
+      <c r="I15" s="94" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="95" t="inlineStr">
+        <is>
+          <t>QA / Tester</t>
+        </is>
+      </c>
+      <c r="B16" s="92" t="n"/>
+      <c r="C16" s="92" t="inlineStr">
+        <is>
+          <t>Mr. Ẩn</t>
+        </is>
+      </c>
+      <c r="D16" s="93" t="n"/>
+      <c r="E16" s="93" t="n"/>
+      <c r="F16" s="93" t="n"/>
+      <c r="G16" s="95" t="inlineStr">
+        <is>
+          <t>Thực hiện kiểm thử, lập hồ sơ lỗi</t>
+        </is>
+      </c>
+      <c r="H16" s="95" t="n"/>
+      <c r="I16" s="96" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="91" t="inlineStr">
+        <is>
+          <t>Đại diện Dev</t>
+        </is>
+      </c>
+      <c r="B17" s="92" t="n"/>
+      <c r="C17" s="92" t="n"/>
+      <c r="D17" s="93" t="n"/>
+      <c r="E17" s="93" t="n"/>
+      <c r="F17" s="93" t="n"/>
+      <c r="G17" s="91" t="inlineStr">
+        <is>
+          <t>Sửa lỗi, xác nhận kỹ thuật</t>
+        </is>
+      </c>
+      <c r="H17" s="91" t="n"/>
+      <c r="I17" s="94" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="95" t="inlineStr">
+        <is>
+          <t>Người duyệt cuối</t>
+        </is>
+      </c>
+      <c r="B18" s="92" t="n"/>
+      <c r="C18" s="92" t="n"/>
+      <c r="D18" s="93" t="n"/>
+      <c r="E18" s="93" t="n"/>
+      <c r="F18" s="93" t="n"/>
+      <c r="G18" s="95" t="inlineStr">
+        <is>
+          <t>Ra kết luận nghiệm thu</t>
+        </is>
+      </c>
+      <c r="H18" s="95" t="n"/>
+      <c r="I18" s="96" t="n"/>
+    </row>
+    <row r="19" ht="8" customHeight="1"/>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>III. PHẠM VI NGHIỆM THU</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="7" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>Nghiệm thu chỉ xét đúng các hạng mục liệt kê trong phạm vi. Hạng mục ngoài phạm vi không dùng làm lý do từ chối nghiệm thu.</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="90" t="inlineStr">
+        <is>
+          <t>Nhóm</t>
+        </is>
+      </c>
+      <c r="B22" s="90" t="inlineStr">
+        <is>
+          <t>Nội dung trong phạm vi</t>
+        </is>
+      </c>
+      <c r="C22" s="90" t="inlineStr">
+        <is>
+          <t>Số lượng trong phạm vi</t>
+        </is>
+      </c>
+      <c r="D22" s="90" t="inlineStr">
+        <is>
+          <t>Tổng trên hệ thống</t>
+        </is>
+      </c>
+      <c r="E22" s="90" t="inlineStr">
+        <is>
+          <t>Tỷ lệ phạm vi</t>
+        </is>
+      </c>
+      <c r="F22" s="90" t="inlineStr">
+        <is>
+          <t>Tài liệu tham chiếu</t>
+        </is>
+      </c>
+      <c r="G22" s="90" t="inlineStr">
+        <is>
+          <t>Ngoài phạm vi (loại trừ)</t>
+        </is>
+      </c>
+      <c r="H22" s="90" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+      <c r="I22" s="90" t="inlineStr"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="91" t="inlineStr">
+        <is>
+          <t>Trang (DS)</t>
+        </is>
+      </c>
+      <c r="B23" s="91" t="inlineStr">
+        <is>
+          <t>Danh sách DS được chốt nghiệm thu</t>
+        </is>
+      </c>
+      <c r="C23" s="93" t="n"/>
+      <c r="D23" s="97">
+        <f>'z_Trang'!$B$1</f>
+        <v/>
+      </c>
+      <c r="E23" s="98">
+        <f>IFERROR(C23/D23,"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="92" t="n"/>
+      <c r="G23" s="92" t="n"/>
+      <c r="H23" s="92" t="n"/>
+      <c r="I23" s="94" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="95" t="inlineStr">
+        <is>
+          <t>Tính năng (YC)</t>
+        </is>
+      </c>
+      <c r="B24" s="95" t="inlineStr">
+        <is>
+          <t>Danh sách YC được chốt nghiệm thu</t>
+        </is>
+      </c>
+      <c r="C24" s="93" t="n"/>
+      <c r="D24" s="99">
+        <f>'z_TinhNang'!$B$1</f>
+        <v/>
+      </c>
+      <c r="E24" s="100">
+        <f>IFERROR(C24/D24,"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="92" t="n"/>
+      <c r="G24" s="92" t="n"/>
+      <c r="H24" s="92" t="n"/>
+      <c r="I24" s="96" t="n"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="91" t="inlineStr">
+        <is>
+          <t>Vai trò người dùng</t>
+        </is>
+      </c>
+      <c r="B25" s="91" t="inlineStr">
+        <is>
+          <t>Khách / Ứng viên / Nhà tuyển dụng / Admin</t>
+        </is>
+      </c>
+      <c r="C25" s="93" t="n"/>
+      <c r="D25" s="93" t="n"/>
+      <c r="E25" s="94" t="n"/>
+      <c r="F25" s="92" t="n"/>
+      <c r="G25" s="92" t="n"/>
+      <c r="H25" s="92" t="n"/>
+      <c r="I25" s="94" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="95" t="inlineStr">
+        <is>
+          <t>Tích hợp / API</t>
+        </is>
+      </c>
+      <c r="B26" s="95" t="inlineStr">
+        <is>
+          <t>Danh sách tích hợp bên thứ ba</t>
+        </is>
+      </c>
+      <c r="C26" s="93" t="n"/>
+      <c r="D26" s="93" t="n"/>
+      <c r="E26" s="96" t="n"/>
+      <c r="F26" s="92" t="n"/>
+      <c r="G26" s="92" t="n"/>
+      <c r="H26" s="92" t="n"/>
+      <c r="I26" s="96" t="n"/>
+    </row>
+    <row r="27" ht="8" customHeight="1"/>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>IV. MÔI TRƯỜNG KIỂM THỬ</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
+      <c r="I28" s="7" t="n"/>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="90" t="inlineStr">
         <is>
           <t>Hạng mục</t>
         </is>
       </c>
-      <c r="B6" s="90" t="inlineStr">
+      <c r="B29" s="90" t="inlineStr">
+        <is>
+          <t>Cấu hình / danh sách cụ thể</t>
+        </is>
+      </c>
+      <c r="C29" s="90" t="inlineStr">
+        <is>
+          <t>Phiên bản</t>
+        </is>
+      </c>
+      <c r="D29" s="90" t="inlineStr">
+        <is>
+          <t>Đã kiểm thử</t>
+        </is>
+      </c>
+      <c r="E29" s="90" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+      <c r="F29" s="90" t="inlineStr"/>
+      <c r="G29" s="90" t="inlineStr"/>
+      <c r="H29" s="90" t="inlineStr"/>
+      <c r="I29" s="90" t="inlineStr"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="91" t="inlineStr">
+        <is>
+          <t>Trình duyệt Desktop</t>
+        </is>
+      </c>
+      <c r="B30" s="92" t="n"/>
+      <c r="C30" s="93" t="n"/>
+      <c r="D30" s="93" t="n"/>
+      <c r="E30" s="92" t="n"/>
+      <c r="F30" s="94" t="n"/>
+      <c r="G30" s="94" t="n"/>
+      <c r="H30" s="94" t="n"/>
+      <c r="I30" s="94" t="n"/>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="95" t="inlineStr">
+        <is>
+          <t>Trình duyệt Mobile</t>
+        </is>
+      </c>
+      <c r="B31" s="92" t="n"/>
+      <c r="C31" s="93" t="n"/>
+      <c r="D31" s="93" t="n"/>
+      <c r="E31" s="92" t="n"/>
+      <c r="F31" s="96" t="n"/>
+      <c r="G31" s="96" t="n"/>
+      <c r="H31" s="96" t="n"/>
+      <c r="I31" s="96" t="n"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="91" t="inlineStr">
+        <is>
+          <t>Thiết bị di động</t>
+        </is>
+      </c>
+      <c r="B32" s="92" t="n"/>
+      <c r="C32" s="93" t="n"/>
+      <c r="D32" s="93" t="n"/>
+      <c r="E32" s="92" t="n"/>
+      <c r="F32" s="94" t="n"/>
+      <c r="G32" s="94" t="n"/>
+      <c r="H32" s="94" t="n"/>
+      <c r="I32" s="94" t="n"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="95" t="inlineStr">
+        <is>
+          <t>Máy tính bảng</t>
+        </is>
+      </c>
+      <c r="B33" s="92" t="n"/>
+      <c r="C33" s="93" t="n"/>
+      <c r="D33" s="93" t="n"/>
+      <c r="E33" s="92" t="n"/>
+      <c r="F33" s="96" t="n"/>
+      <c r="G33" s="96" t="n"/>
+      <c r="H33" s="96" t="n"/>
+      <c r="I33" s="96" t="n"/>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="91" t="inlineStr">
+        <is>
+          <t>Độ phân giải chuẩn</t>
+        </is>
+      </c>
+      <c r="B34" s="92" t="n"/>
+      <c r="C34" s="93" t="n"/>
+      <c r="D34" s="93" t="n"/>
+      <c r="E34" s="92" t="n"/>
+      <c r="F34" s="94" t="n"/>
+      <c r="G34" s="94" t="n"/>
+      <c r="H34" s="94" t="n"/>
+      <c r="I34" s="94" t="n"/>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="95" t="inlineStr">
+        <is>
+          <t>Hệ điều hành</t>
+        </is>
+      </c>
+      <c r="B35" s="92" t="n"/>
+      <c r="C35" s="93" t="n"/>
+      <c r="D35" s="93" t="n"/>
+      <c r="E35" s="92" t="n"/>
+      <c r="F35" s="96" t="n"/>
+      <c r="G35" s="96" t="n"/>
+      <c r="H35" s="96" t="n"/>
+      <c r="I35" s="96" t="n"/>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="91" t="inlineStr">
+        <is>
+          <t>Tài khoản kiểm thử</t>
+        </is>
+      </c>
+      <c r="B36" s="92" t="n"/>
+      <c r="C36" s="93" t="n"/>
+      <c r="D36" s="93" t="n"/>
+      <c r="E36" s="92" t="n"/>
+      <c r="F36" s="94" t="n"/>
+      <c r="G36" s="94" t="n"/>
+      <c r="H36" s="94" t="n"/>
+      <c r="I36" s="94" t="n"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="95" t="inlineStr">
+        <is>
+          <t>Dữ liệu kiểm thử</t>
+        </is>
+      </c>
+      <c r="B37" s="92" t="n"/>
+      <c r="C37" s="93" t="n"/>
+      <c r="D37" s="93" t="n"/>
+      <c r="E37" s="92" t="n"/>
+      <c r="F37" s="96" t="n"/>
+      <c r="G37" s="96" t="n"/>
+      <c r="H37" s="96" t="n"/>
+      <c r="I37" s="96" t="n"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="91" t="inlineStr">
+        <is>
+          <t>Đường truyền / mạng</t>
+        </is>
+      </c>
+      <c r="B38" s="92" t="n"/>
+      <c r="C38" s="93" t="n"/>
+      <c r="D38" s="93" t="n"/>
+      <c r="E38" s="92" t="n"/>
+      <c r="F38" s="94" t="n"/>
+      <c r="G38" s="94" t="n"/>
+      <c r="H38" s="94" t="n"/>
+      <c r="I38" s="94" t="n"/>
+    </row>
+    <row r="39" ht="8" customHeight="1"/>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>V. TIÊU CHÍ NGHIỆM THU (ACCEPTANCE / EXIT CRITERIA)</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
+      <c r="G40" s="7" t="n"/>
+      <c r="H40" s="7" t="n"/>
+      <c r="I40" s="7" t="n"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>Ngưỡng bắt buộc do hai bên chốt trước khi kiểm thử. Kết quả thực tế tự động tính; đánh giá tự so sánh với ngưỡng.</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="90" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="B42" s="90" t="inlineStr">
+        <is>
+          <t>Tiêu chí</t>
+        </is>
+      </c>
+      <c r="C42" s="90" t="inlineStr">
+        <is>
+          <t>Ngưỡng bắt buộc</t>
+        </is>
+      </c>
+      <c r="D42" s="90" t="inlineStr">
+        <is>
+          <t>Kết quả thực tế</t>
+        </is>
+      </c>
+      <c r="E42" s="90" t="inlineStr">
+        <is>
+          <t>Đánh giá</t>
+        </is>
+      </c>
+      <c r="F42" s="90" t="inlineStr">
+        <is>
+          <t>Bắt buộc?</t>
+        </is>
+      </c>
+      <c r="G42" s="90" t="inlineStr">
+        <is>
+          <t>Nguồn số liệu</t>
+        </is>
+      </c>
+      <c r="H42" s="90" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+      <c r="I42" s="90" t="inlineStr"/>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="91" t="inlineStr">
+        <is>
+          <t>TC01</t>
+        </is>
+      </c>
+      <c r="B43" s="91" t="inlineStr">
+        <is>
+          <t>Lỗi Critical đang mở</t>
+        </is>
+      </c>
+      <c r="C43" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="97">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"Critical"))</f>
+        <v/>
+      </c>
+      <c r="E43" s="102">
+        <f>IF(C43="","Chưa chốt ngưỡng",IF(D43&lt;=C43,"Đạt","Chưa đạt"))</f>
+        <v/>
+      </c>
+      <c r="F43" s="94" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="G43" s="91" t="inlineStr">
+        <is>
+          <t>05_Lỗi_Tester (L, U)</t>
+        </is>
+      </c>
+      <c r="H43" s="92" t="n"/>
+      <c r="I43" s="94" t="n"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="95" t="inlineStr">
+        <is>
+          <t>TC02</t>
+        </is>
+      </c>
+      <c r="B44" s="95" t="inlineStr">
+        <is>
+          <t>Lỗi High đang mở</t>
+        </is>
+      </c>
+      <c r="C44" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="99">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"High")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"High"))</f>
+        <v/>
+      </c>
+      <c r="E44" s="103">
+        <f>IF(C44="","Chưa chốt ngưỡng",IF(D44&lt;=C44,"Đạt","Chưa đạt"))</f>
+        <v/>
+      </c>
+      <c r="F44" s="96" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="G44" s="95" t="inlineStr">
+        <is>
+          <t>05_Lỗi_Tester (L, U)</t>
+        </is>
+      </c>
+      <c r="H44" s="92" t="n"/>
+      <c r="I44" s="96" t="n"/>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="91" t="inlineStr">
+        <is>
+          <t>TC03</t>
+        </is>
+      </c>
+      <c r="B45" s="91" t="inlineStr">
+        <is>
+          <t>Lỗi Medium đang mở</t>
+        </is>
+      </c>
+      <c r="C45" s="101" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" s="97">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"Medium")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"Medium"))</f>
+        <v/>
+      </c>
+      <c r="E45" s="102">
+        <f>IF(C45="","Chưa chốt ngưỡng",IF(D45&lt;=C45,"Đạt","Chưa đạt"))</f>
+        <v/>
+      </c>
+      <c r="F45" s="94" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="G45" s="91" t="inlineStr">
+        <is>
+          <t>05_Lỗi_Tester (L, U)</t>
+        </is>
+      </c>
+      <c r="H45" s="92" t="n"/>
+      <c r="I45" s="94" t="n"/>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="95" t="inlineStr">
+        <is>
+          <t>TC04</t>
+        </is>
+      </c>
+      <c r="B46" s="95" t="inlineStr">
+        <is>
+          <t>Lỗi Low đang mở</t>
+        </is>
+      </c>
+      <c r="C46" s="101" t="n"/>
+      <c r="D46" s="99">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"Low")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"Low"))</f>
+        <v/>
+      </c>
+      <c r="E46" s="103">
+        <f>IF(C46="","Chưa chốt ngưỡng",IF(D46&lt;=C46,"Đạt","Chưa đạt"))</f>
+        <v/>
+      </c>
+      <c r="F46" s="96" t="inlineStr">
+        <is>
+          <t>Khuyến nghị</t>
+        </is>
+      </c>
+      <c r="G46" s="95" t="inlineStr">
+        <is>
+          <t>05_Lỗi_Tester (L, U)</t>
+        </is>
+      </c>
+      <c r="H46" s="92" t="n"/>
+      <c r="I46" s="96" t="n"/>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="91" t="inlineStr">
+        <is>
+          <t>TC05</t>
+        </is>
+      </c>
+      <c r="B47" s="91" t="inlineStr">
+        <is>
+          <t>Tỷ lệ trang hoàn thành kiểm thử</t>
+        </is>
+      </c>
+      <c r="C47" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="98">
+        <f>'z_Trang'!$F$1</f>
+        <v/>
+      </c>
+      <c r="E47" s="102">
+        <f>IF(C47="","Chưa chốt ngưỡng",IF(D47&gt;=C47,"Đạt","Chưa đạt"))</f>
+        <v/>
+      </c>
+      <c r="F47" s="94" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="G47" s="91" t="inlineStr">
+        <is>
+          <t>02_UI_UX</t>
+        </is>
+      </c>
+      <c r="H47" s="92" t="n"/>
+      <c r="I47" s="94" t="n"/>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="95" t="inlineStr">
+        <is>
+          <t>TC06</t>
+        </is>
+      </c>
+      <c r="B48" s="95" t="inlineStr">
+        <is>
+          <t>Tỷ lệ tính năng hoàn thành kiểm thử</t>
+        </is>
+      </c>
+      <c r="C48" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="100">
+        <f>'z_TinhNang'!$F$1</f>
+        <v/>
+      </c>
+      <c r="E48" s="103">
+        <f>IF(C48="","Chưa chốt ngưỡng",IF(D48&gt;=C48,"Đạt","Chưa đạt"))</f>
+        <v/>
+      </c>
+      <c r="F48" s="96" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="G48" s="95" t="inlineStr">
+        <is>
+          <t>03_Tính_năng</t>
+        </is>
+      </c>
+      <c r="H48" s="92" t="n"/>
+      <c r="I48" s="96" t="n"/>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="91" t="inlineStr">
+        <is>
+          <t>TC07</t>
+        </is>
+      </c>
+      <c r="B49" s="91" t="inlineStr">
+        <is>
+          <t>Tỷ lệ lỗi đã xử lý (Fixed/Verified/Closed)</t>
+        </is>
+      </c>
+      <c r="C49" s="104" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D49" s="98">
+        <f>IFERROR((COUNTIF('z_Loi'!$U:$U,"Fixed")+COUNTIF('z_Loi'!$U:$U,"Verified")+COUNTIF('z_Loi'!$U:$U,"Closed"))/(COUNTA('z_Loi'!$E:$E)-1),0)</f>
+        <v/>
+      </c>
+      <c r="E49" s="102">
+        <f>IF(C49="","Chưa chốt ngưỡng",IF(D49&gt;=C49,"Đạt","Chưa đạt"))</f>
+        <v/>
+      </c>
+      <c r="F49" s="94" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="G49" s="91" t="inlineStr">
+        <is>
+          <t>05_Lỗi_Tester (U)</t>
+        </is>
+      </c>
+      <c r="H49" s="92" t="n"/>
+      <c r="I49" s="94" t="n"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="95" t="inlineStr">
+        <is>
+          <t>TC08</t>
+        </is>
+      </c>
+      <c r="B50" s="95" t="inlineStr">
+        <is>
+          <t>Tỷ lệ lỗi đã retest đạt (Verified/Closed)</t>
+        </is>
+      </c>
+      <c r="C50" s="104" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D50" s="100">
+        <f>IFERROR((COUNTIF('z_Loi'!$U:$U,"Verified")+COUNTIF('z_Loi'!$U:$U,"Closed"))/(COUNTA('z_Loi'!$E:$E)-1),0)</f>
+        <v/>
+      </c>
+      <c r="E50" s="103">
+        <f>IF(C50="","Chưa chốt ngưỡng",IF(D50&gt;=C50,"Đạt","Chưa đạt"))</f>
+        <v/>
+      </c>
+      <c r="F50" s="96" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="G50" s="95" t="inlineStr">
+        <is>
+          <t>05_Lỗi_Tester (U)</t>
+        </is>
+      </c>
+      <c r="H50" s="92" t="n"/>
+      <c r="I50" s="96" t="n"/>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="91" t="inlineStr">
+        <is>
+          <t>TC09</t>
+        </is>
+      </c>
+      <c r="B51" s="91" t="inlineStr">
+        <is>
+          <t>Tỷ lệ Test Case Pass</t>
+        </is>
+      </c>
+      <c r="C51" s="104" t="n"/>
+      <c r="D51" s="104" t="n"/>
+      <c r="E51" s="102">
+        <f>IF(C51="","Chưa chốt ngưỡng",IF(D51&gt;=C51,"Đạt","Chưa đạt"))</f>
+        <v/>
+      </c>
+      <c r="F51" s="94" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="G51" s="91" t="inlineStr">
+        <is>
+          <t>06_RTM_Dev_Test — CHƯA CÓ SỐ</t>
+        </is>
+      </c>
+      <c r="H51" s="92" t="n"/>
+      <c r="I51" s="94" t="n"/>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="95" t="inlineStr">
+        <is>
+          <t>TC10</t>
+        </is>
+      </c>
+      <c r="B52" s="95" t="inlineStr">
+        <is>
+          <t>Độ phủ yêu cầu (RTM: YC có Test Case)</t>
+        </is>
+      </c>
+      <c r="C52" s="104" t="n"/>
+      <c r="D52" s="104" t="n"/>
+      <c r="E52" s="103">
+        <f>IF(C52="","Chưa chốt ngưỡng",IF(D52&gt;=C52,"Đạt","Chưa đạt"))</f>
+        <v/>
+      </c>
+      <c r="F52" s="96" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="G52" s="95" t="inlineStr">
+        <is>
+          <t>06_RTM_Dev_Test — CHƯA CÓ SỐ</t>
+        </is>
+      </c>
+      <c r="H52" s="92" t="n"/>
+      <c r="I52" s="96" t="n"/>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="91" t="inlineStr">
+        <is>
+          <t>TC11</t>
+        </is>
+      </c>
+      <c r="B53" s="91" t="inlineStr">
+        <is>
+          <t>Lỗi bảo mật Critical/High đang mở</t>
+        </is>
+      </c>
+      <c r="C53" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="97">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*Security*",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*Security*",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*Security*",'z_Loi'!$L:$L,"High")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*Security*",'z_Loi'!$L:$L,"High"))</f>
+        <v/>
+      </c>
+      <c r="E53" s="102">
+        <f>IF(C53="","Chưa chốt ngưỡng",IF(D53&lt;=C53,"Đạt","Chưa đạt"))</f>
+        <v/>
+      </c>
+      <c r="F53" s="94" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="G53" s="91" t="inlineStr">
+        <is>
+          <t>05_Lỗi_Tester (K, L, U)</t>
+        </is>
+      </c>
+      <c r="H53" s="92" t="n"/>
+      <c r="I53" s="94" t="n"/>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="95" t="inlineStr">
+        <is>
+          <t>TC12</t>
+        </is>
+      </c>
+      <c r="B54" s="95" t="inlineStr">
+        <is>
+          <t>Lỗi Responsive Critical/High đang mở</t>
+        </is>
+      </c>
+      <c r="C54" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="99">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*Responsive*",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*Responsive*",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*Responsive*",'z_Loi'!$L:$L,"High")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*Responsive*",'z_Loi'!$L:$L,"High"))</f>
+        <v/>
+      </c>
+      <c r="E54" s="103">
+        <f>IF(C54="","Chưa chốt ngưỡng",IF(D54&lt;=C54,"Đạt","Chưa đạt"))</f>
+        <v/>
+      </c>
+      <c r="F54" s="96" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="G54" s="95" t="inlineStr">
+        <is>
+          <t>05_Lỗi_Tester (K, L, U)</t>
+        </is>
+      </c>
+      <c r="H54" s="92" t="n"/>
+      <c r="I54" s="96" t="n"/>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="91" t="inlineStr">
+        <is>
+          <t>TC13</t>
+        </is>
+      </c>
+      <c r="B55" s="91" t="inlineStr">
+        <is>
+          <t>Hiệu năng trang chủ (điểm PageSpeed / LCP)</t>
+        </is>
+      </c>
+      <c r="C55" s="101" t="n"/>
+      <c r="D55" s="101" t="n"/>
+      <c r="E55" s="105" t="n"/>
+      <c r="F55" s="94" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="G55" s="91" t="inlineStr">
+        <is>
+          <t>Đo bằng công cụ — CHƯA CÓ SỐ</t>
+        </is>
+      </c>
+      <c r="H55" s="92" t="n"/>
+      <c r="I55" s="94" t="n"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="95" t="inlineStr">
+        <is>
+          <t>TC14</t>
+        </is>
+      </c>
+      <c r="B56" s="95" t="inlineStr">
+        <is>
+          <t>Tương thích đủ danh mục trình duyệt/thiết bị đã chốt</t>
+        </is>
+      </c>
+      <c r="C56" s="101" t="n"/>
+      <c r="D56" s="101" t="n"/>
+      <c r="E56" s="105" t="n"/>
+      <c r="F56" s="96" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="G56" s="95" t="inlineStr">
+        <is>
+          <t>Mục IV — CHƯA CÓ SỐ</t>
+        </is>
+      </c>
+      <c r="H56" s="92" t="n"/>
+      <c r="I56" s="96" t="n"/>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="91" t="inlineStr">
+        <is>
+          <t>TC15</t>
+        </is>
+      </c>
+      <c r="B57" s="91" t="inlineStr">
+        <is>
+          <t>Bằng chứng kiểm thử đầy đủ (ảnh/video/link retest)</t>
+        </is>
+      </c>
+      <c r="C57" s="101" t="n"/>
+      <c r="D57" s="101" t="n"/>
+      <c r="E57" s="105" t="n"/>
+      <c r="F57" s="94" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="G57" s="91" t="inlineStr">
+        <is>
+          <t>05_Lỗi_Tester (O, P)</t>
+        </is>
+      </c>
+      <c r="H57" s="92" t="n"/>
+      <c r="I57" s="94" t="n"/>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="95" t="inlineStr">
+        <is>
+          <t>TC16</t>
+        </is>
+      </c>
+      <c r="B58" s="95" t="inlineStr">
+        <is>
+          <t>Không còn lỗi hồi quy (regression) đang mở</t>
+        </is>
+      </c>
+      <c r="C58" s="101" t="n"/>
+      <c r="D58" s="101" t="n"/>
+      <c r="E58" s="105" t="n"/>
+      <c r="F58" s="96" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="G58" s="95" t="inlineStr">
+        <is>
+          <t>Kết quả retest — CHƯA CÓ SỐ</t>
+        </is>
+      </c>
+      <c r="H58" s="92" t="n"/>
+      <c r="I58" s="96" t="n"/>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="91" t="inlineStr">
+        <is>
+          <t>TC17</t>
+        </is>
+      </c>
+      <c r="B59" s="91" t="inlineStr">
+        <is>
+          <t>Tài liệu bàn giao đầy đủ</t>
+        </is>
+      </c>
+      <c r="C59" s="101" t="n"/>
+      <c r="D59" s="101" t="n"/>
+      <c r="E59" s="105" t="n"/>
+      <c r="F59" s="94" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="G59" s="91" t="inlineStr">
+        <is>
+          <t>Mục XII</t>
+        </is>
+      </c>
+      <c r="H59" s="92" t="n"/>
+      <c r="I59" s="94" t="n"/>
+    </row>
+    <row r="60" ht="8" customHeight="1"/>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>VI. ĐỊNH NGHĨA MỨC ĐỘ LỖI VÀ SLA XỬ LÝ</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="n"/>
+      <c r="C61" s="7" t="n"/>
+      <c r="D61" s="7" t="n"/>
+      <c r="E61" s="7" t="n"/>
+      <c r="F61" s="7" t="n"/>
+      <c r="G61" s="7" t="n"/>
+      <c r="H61" s="7" t="n"/>
+      <c r="I61" s="7" t="n"/>
+    </row>
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="90" t="inlineStr">
+        <is>
+          <t>Mức độ</t>
+        </is>
+      </c>
+      <c r="B62" s="90" t="inlineStr">
+        <is>
+          <t>Định nghĩa</t>
+        </is>
+      </c>
+      <c r="C62" s="90" t="inlineStr">
+        <is>
+          <t>Ảnh hưởng</t>
+        </is>
+      </c>
+      <c r="D62" s="90" t="inlineStr">
+        <is>
+          <t>SLA xử lý (giờ/ngày)</t>
+        </is>
+      </c>
+      <c r="E62" s="90" t="inlineStr">
+        <is>
+          <t>Chặn nghiệm thu?</t>
+        </is>
+      </c>
+      <c r="F62" s="90" t="inlineStr">
+        <is>
+          <t>Số lỗi hiện có</t>
+        </is>
+      </c>
+      <c r="G62" s="90" t="inlineStr">
+        <is>
+          <t>Đang mở</t>
+        </is>
+      </c>
+      <c r="H62" s="90" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+      <c r="I62" s="90" t="inlineStr"/>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="91" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="B63" s="91" t="inlineStr">
+        <is>
+          <t>Chặn luồng nghiệp vụ chính, mất dữ liệu, lỗ hổng bảo mật nghiêm trọng</t>
+        </is>
+      </c>
+      <c r="C63" s="91" t="inlineStr">
+        <is>
+          <t>Không thể sử dụng</t>
+        </is>
+      </c>
+      <c r="D63" s="93" t="n"/>
+      <c r="E63" s="94" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F63" s="97">
+        <f>COUNTIF('z_Loi'!$L:$L,"Critical")</f>
+        <v/>
+      </c>
+      <c r="G63" s="97">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"Critical"))</f>
+        <v/>
+      </c>
+      <c r="H63" s="92" t="n"/>
+      <c r="I63" s="94" t="n"/>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="95" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B64" s="95" t="inlineStr">
+        <is>
+          <t>Sai nghiệp vụ, tính năng chính không hoạt động đúng</t>
+        </is>
+      </c>
+      <c r="C64" s="95" t="inlineStr">
+        <is>
+          <t>Ảnh hưởng lớn</t>
+        </is>
+      </c>
+      <c r="D64" s="93" t="n"/>
+      <c r="E64" s="96" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F64" s="99">
+        <f>COUNTIF('z_Loi'!$L:$L,"High")</f>
+        <v/>
+      </c>
+      <c r="G64" s="99">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"High")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"High"))</f>
+        <v/>
+      </c>
+      <c r="H64" s="92" t="n"/>
+      <c r="I64" s="96" t="n"/>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="91" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B65" s="91" t="inlineStr">
+        <is>
+          <t>Sai lệch hiển thị/nghiệp vụ phụ, có cách làm thay thế</t>
+        </is>
+      </c>
+      <c r="C65" s="91" t="inlineStr">
+        <is>
+          <t>Ảnh hưởng vừa</t>
+        </is>
+      </c>
+      <c r="D65" s="93" t="n"/>
+      <c r="E65" s="94" t="inlineStr">
+        <is>
+          <t>Theo ngưỡng TC03</t>
+        </is>
+      </c>
+      <c r="F65" s="97">
+        <f>COUNTIF('z_Loi'!$L:$L,"Medium")</f>
+        <v/>
+      </c>
+      <c r="G65" s="97">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"Medium")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"Medium"))</f>
+        <v/>
+      </c>
+      <c r="H65" s="92" t="n"/>
+      <c r="I65" s="94" t="n"/>
+    </row>
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" s="95" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B66" s="95" t="inlineStr">
+        <is>
+          <t>Lỗi nhỏ về giao diện, chính tả, trải nghiệm</t>
+        </is>
+      </c>
+      <c r="C66" s="95" t="inlineStr">
+        <is>
+          <t>Ảnh hưởng thấp</t>
+        </is>
+      </c>
+      <c r="D66" s="93" t="n"/>
+      <c r="E66" s="96" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="F66" s="99">
+        <f>COUNTIF('z_Loi'!$L:$L,"Low")</f>
+        <v/>
+      </c>
+      <c r="G66" s="99">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"Low")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"Low"))</f>
+        <v/>
+      </c>
+      <c r="H66" s="92" t="n"/>
+      <c r="I66" s="96" t="n"/>
+    </row>
+    <row r="67" ht="8" customHeight="1"/>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>VII. KẾT QUẢ KIỂM THỬ — TỔNG HỢP (tự động)</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="n"/>
+      <c r="C68" s="7" t="n"/>
+      <c r="D68" s="7" t="n"/>
+      <c r="E68" s="7" t="n"/>
+      <c r="F68" s="7" t="n"/>
+      <c r="G68" s="7" t="n"/>
+      <c r="H68" s="7" t="n"/>
+      <c r="I68" s="7" t="n"/>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="90" t="inlineStr">
+        <is>
+          <t>Chỉ số</t>
+        </is>
+      </c>
+      <c r="B69" s="90" t="inlineStr">
+        <is>
+          <t>Diễn giải</t>
+        </is>
+      </c>
+      <c r="C69" s="90" t="inlineStr">
+        <is>
+          <t>Số lượng</t>
+        </is>
+      </c>
+      <c r="D69" s="90" t="inlineStr">
+        <is>
+          <t>Tổng</t>
+        </is>
+      </c>
+      <c r="E69" s="90" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="F69" s="90" t="inlineStr">
+        <is>
+          <t>Chỉ số</t>
+        </is>
+      </c>
+      <c r="G69" s="90" t="inlineStr">
+        <is>
+          <t>Diễn giải</t>
+        </is>
+      </c>
+      <c r="H69" s="90" t="inlineStr">
+        <is>
+          <t>Số lượng</t>
+        </is>
+      </c>
+      <c r="I69" s="90" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="24" customHeight="1">
+      <c r="A70" s="91" t="inlineStr">
+        <is>
+          <t>Trang hoàn thành</t>
+        </is>
+      </c>
+      <c r="B70" s="91" t="inlineStr">
+        <is>
+          <t>Đã test xong, không còn lỗi chặn</t>
+        </is>
+      </c>
+      <c r="C70" s="97">
+        <f>'z_Trang'!$D$1</f>
+        <v/>
+      </c>
+      <c r="D70" s="97">
+        <f>'z_Trang'!$B$1</f>
+        <v/>
+      </c>
+      <c r="E70" s="98">
+        <f>'z_Trang'!$F$1</f>
+        <v/>
+      </c>
+      <c r="F70" s="91" t="inlineStr">
+        <is>
+          <t>Tổng lỗi ghi nhận</t>
+        </is>
+      </c>
+      <c r="G70" s="91" t="inlineStr">
+        <is>
+          <t>Số dòng có BUG_ID</t>
+        </is>
+      </c>
+      <c r="H70" s="97">
+        <f>COUNTA('z_Loi'!$E:$E)-1</f>
+        <v/>
+      </c>
+      <c r="I70" s="98" t="n"/>
+    </row>
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" s="95" t="inlineStr">
+        <is>
+          <t>Trang cần kiểm tra lại</t>
+        </is>
+      </c>
+      <c r="B71" s="95" t="inlineStr">
+        <is>
+          <t>Đã test, còn lỗi phải retest</t>
+        </is>
+      </c>
+      <c r="C71" s="99">
+        <f>'z_Trang'!$J$1</f>
+        <v/>
+      </c>
+      <c r="D71" s="99">
+        <f>'z_Trang'!$B$1</f>
+        <v/>
+      </c>
+      <c r="E71" s="100">
+        <f>IFERROR(C71/D71,"")</f>
+        <v/>
+      </c>
+      <c r="F71" s="95" t="inlineStr">
+        <is>
+          <t>Lỗi đang mở</t>
+        </is>
+      </c>
+      <c r="G71" s="95" t="inlineStr">
+        <is>
+          <t>Open + Chưa gửi Dev</t>
+        </is>
+      </c>
+      <c r="H71" s="99">
+        <f>(COUNTIF('z_Loi'!$U:$U,"Open")+COUNTIF('z_Loi'!$U:$U,"Chưa gửi Dev"))</f>
+        <v/>
+      </c>
+      <c r="I71" s="100">
+        <f>IFERROR(H71/(COUNTA('z_Loi'!$E:$E)-1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="24" customHeight="1">
+      <c r="A72" s="91" t="inlineStr">
+        <is>
+          <t>Trang chưa kiểm tra</t>
+        </is>
+      </c>
+      <c r="B72" s="91" t="inlineStr">
+        <is>
+          <t>Chưa bắt đầu kiểm thử</t>
+        </is>
+      </c>
+      <c r="C72" s="97">
+        <f>'z_Trang'!$L$1</f>
+        <v/>
+      </c>
+      <c r="D72" s="97">
+        <f>'z_Trang'!$B$1</f>
+        <v/>
+      </c>
+      <c r="E72" s="98">
+        <f>IFERROR(C72/D72,"")</f>
+        <v/>
+      </c>
+      <c r="F72" s="91" t="inlineStr">
+        <is>
+          <t>Lỗi đã xử lý</t>
+        </is>
+      </c>
+      <c r="G72" s="91" t="inlineStr">
+        <is>
+          <t>Fixed + Verified + Closed</t>
+        </is>
+      </c>
+      <c r="H72" s="97">
+        <f>(COUNTIF('z_Loi'!$U:$U,"Fixed")+COUNTIF('z_Loi'!$U:$U,"Verified")+COUNTIF('z_Loi'!$U:$U,"Closed"))</f>
+        <v/>
+      </c>
+      <c r="I72" s="98">
+        <f>IFERROR(H72/(COUNTA('z_Loi'!$E:$E)-1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="95" t="inlineStr">
+        <is>
+          <t>Tính năng hoàn thành</t>
+        </is>
+      </c>
+      <c r="B73" s="95" t="inlineStr">
+        <is>
+          <t>Đã test xong</t>
+        </is>
+      </c>
+      <c r="C73" s="99">
+        <f>'z_TinhNang'!$D$1</f>
+        <v/>
+      </c>
+      <c r="D73" s="99">
+        <f>'z_TinhNang'!$B$1</f>
+        <v/>
+      </c>
+      <c r="E73" s="100">
+        <f>'z_TinhNang'!$F$1</f>
+        <v/>
+      </c>
+      <c r="F73" s="95" t="inlineStr">
+        <is>
+          <t>Lỗi Critical/High đang mở</t>
+        </is>
+      </c>
+      <c r="G73" s="95" t="inlineStr">
+        <is>
+          <t>Chặn nghiệm thu</t>
+        </is>
+      </c>
+      <c r="H73" s="99">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"High")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"High"))</f>
+        <v/>
+      </c>
+      <c r="I73" s="100">
+        <f>IFERROR(H73/(COUNTA('z_Loi'!$E:$E)-1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" s="91" t="inlineStr">
+        <is>
+          <t>Tính năng cần kiểm tra lại</t>
+        </is>
+      </c>
+      <c r="B74" s="91" t="inlineStr">
+        <is>
+          <t>Còn lỗi phải retest</t>
+        </is>
+      </c>
+      <c r="C74" s="97">
+        <f>'z_TinhNang'!$J$1</f>
+        <v/>
+      </c>
+      <c r="D74" s="97">
+        <f>'z_TinhNang'!$B$1</f>
+        <v/>
+      </c>
+      <c r="E74" s="98">
+        <f>IFERROR(C74/D74,"")</f>
+        <v/>
+      </c>
+      <c r="F74" s="91" t="inlineStr">
+        <is>
+          <t>Lỗi tạm hoãn (Deferred)</t>
+        </is>
+      </c>
+      <c r="G74" s="91" t="inlineStr">
+        <is>
+          <t>Cần ghi nhận ngoại lệ</t>
+        </is>
+      </c>
+      <c r="H74" s="97">
+        <f>COUNTIF('z_Loi'!$U:$U,"Deferred")</f>
+        <v/>
+      </c>
+      <c r="I74" s="98">
+        <f>IFERROR(H74/(COUNTA('z_Loi'!$E:$E)-1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" ht="24" customHeight="1">
+      <c r="A75" s="95" t="inlineStr">
+        <is>
+          <t>Tính năng chưa kiểm tra</t>
+        </is>
+      </c>
+      <c r="B75" s="95" t="inlineStr">
+        <is>
+          <t>Chưa bắt đầu kiểm thử</t>
+        </is>
+      </c>
+      <c r="C75" s="99">
+        <f>'z_TinhNang'!$L$1</f>
+        <v/>
+      </c>
+      <c r="D75" s="99">
+        <f>'z_TinhNang'!$B$1</f>
+        <v/>
+      </c>
+      <c r="E75" s="100">
+        <f>IFERROR(C75/D75,"")</f>
+        <v/>
+      </c>
+      <c r="F75" s="95" t="inlineStr">
+        <is>
+          <t>Lỗi đã retest đạt</t>
+        </is>
+      </c>
+      <c r="G75" s="95" t="inlineStr">
+        <is>
+          <t>Verified + Closed</t>
+        </is>
+      </c>
+      <c r="H75" s="99">
+        <f>(COUNTIF('z_Loi'!$U:$U,"Verified")+COUNTIF('z_Loi'!$U:$U,"Closed"))</f>
+        <v/>
+      </c>
+      <c r="I75" s="100">
+        <f>IFERROR(H75/(COUNTA('z_Loi'!$E:$E)-1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" ht="8" customHeight="1"/>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>VIII. THỐNG KÊ LỖI (tự động)</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="n"/>
+      <c r="C77" s="7" t="n"/>
+      <c r="D77" s="7" t="n"/>
+      <c r="E77" s="7" t="n"/>
+      <c r="F77" s="7" t="n"/>
+      <c r="G77" s="7" t="n"/>
+      <c r="H77" s="7" t="n"/>
+      <c r="I77" s="7" t="n"/>
+    </row>
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="90" t="inlineStr">
+        <is>
+          <t>Theo trạng thái</t>
+        </is>
+      </c>
+      <c r="B78" s="90" t="inlineStr">
+        <is>
+          <t>Số lỗi</t>
+        </is>
+      </c>
+      <c r="C78" s="90" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="D78" s="90" t="inlineStr">
+        <is>
+          <t>Theo mức độ</t>
+        </is>
+      </c>
+      <c r="E78" s="90" t="inlineStr">
+        <is>
+          <t>Tổng</t>
+        </is>
+      </c>
+      <c r="F78" s="90" t="inlineStr">
+        <is>
+          <t>Đang mở</t>
+        </is>
+      </c>
+      <c r="G78" s="90" t="inlineStr">
+        <is>
+          <t>Theo thiết bị / loại</t>
+        </is>
+      </c>
+      <c r="H78" s="90" t="inlineStr">
+        <is>
+          <t>Tổng</t>
+        </is>
+      </c>
+      <c r="I78" s="90" t="inlineStr">
+        <is>
+          <t>Đang mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" s="91" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="B79" s="97">
+        <f>COUNTIF('z_Loi'!$U:$U,"Open")</f>
+        <v/>
+      </c>
+      <c r="C79" s="98">
+        <f>IFERROR(B79/(COUNTA('z_Loi'!$E:$E)-1),"")</f>
+        <v/>
+      </c>
+      <c r="D79" s="91" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E79" s="97">
+        <f>COUNTIF('z_Loi'!$L:$L,"Critical")</f>
+        <v/>
+      </c>
+      <c r="F79" s="97">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"Critical"))</f>
+        <v/>
+      </c>
+      <c r="G79" s="91" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="H79" s="97">
+        <f>COUNTIF('z_Loi'!$M:$M,"*Desktop*")</f>
+        <v/>
+      </c>
+      <c r="I79" s="97">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$M:$M,"*Desktop*")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$M:$M,"*Desktop*"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="95" t="inlineStr">
+        <is>
+          <t>Chưa gửi Dev</t>
+        </is>
+      </c>
+      <c r="B80" s="99">
+        <f>COUNTIF('z_Loi'!$U:$U,"Chưa gửi Dev")</f>
+        <v/>
+      </c>
+      <c r="C80" s="100">
+        <f>IFERROR(B80/(COUNTA('z_Loi'!$E:$E)-1),"")</f>
+        <v/>
+      </c>
+      <c r="D80" s="95" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E80" s="99">
+        <f>COUNTIF('z_Loi'!$L:$L,"High")</f>
+        <v/>
+      </c>
+      <c r="F80" s="99">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"High")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"High"))</f>
+        <v/>
+      </c>
+      <c r="G80" s="95" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="H80" s="99">
+        <f>COUNTIF('z_Loi'!$M:$M,"*Mobile*")</f>
+        <v/>
+      </c>
+      <c r="I80" s="99">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$M:$M,"*Mobile*")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$M:$M,"*Mobile*"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" s="91" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="B81" s="97">
+        <f>COUNTIF('z_Loi'!$U:$U,"Fixed")</f>
+        <v/>
+      </c>
+      <c r="C81" s="98">
+        <f>IFERROR(B81/(COUNTA('z_Loi'!$E:$E)-1),"")</f>
+        <v/>
+      </c>
+      <c r="D81" s="91" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E81" s="97">
+        <f>COUNTIF('z_Loi'!$L:$L,"Medium")</f>
+        <v/>
+      </c>
+      <c r="F81" s="97">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"Medium")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"Medium"))</f>
+        <v/>
+      </c>
+      <c r="G81" s="91" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="H81" s="97">
+        <f>COUNTIF('z_Loi'!$M:$M,"*Tablet*")</f>
+        <v/>
+      </c>
+      <c r="I81" s="97">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$M:$M,"*Tablet*")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$M:$M,"*Tablet*"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="24" customHeight="1">
+      <c r="A82" s="95" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="B82" s="99">
+        <f>COUNTIF('z_Loi'!$U:$U,"Verified")</f>
+        <v/>
+      </c>
+      <c r="C82" s="100">
+        <f>IFERROR(B82/(COUNTA('z_Loi'!$E:$E)-1),"")</f>
+        <v/>
+      </c>
+      <c r="D82" s="95" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E82" s="99">
+        <f>COUNTIF('z_Loi'!$L:$L,"Low")</f>
+        <v/>
+      </c>
+      <c r="F82" s="99">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"Low")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"Low"))</f>
+        <v/>
+      </c>
+      <c r="G82" s="95" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="H82" s="99">
+        <f>COUNTIF('z_Loi'!$K:$K,"*UI/UX*")</f>
+        <v/>
+      </c>
+      <c r="I82" s="99">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*UI/UX*")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*UI/UX*"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" s="91" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="B83" s="97">
+        <f>COUNTIF('z_Loi'!$U:$U,"Closed")</f>
+        <v/>
+      </c>
+      <c r="C83" s="98">
+        <f>IFERROR(B83/(COUNTA('z_Loi'!$E:$E)-1),"")</f>
+        <v/>
+      </c>
+      <c r="D83" s="91" t="n"/>
+      <c r="E83" s="97" t="n"/>
+      <c r="F83" s="97" t="n"/>
+      <c r="G83" s="91" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H83" s="97">
+        <f>COUNTIF('z_Loi'!$K:$K,"*Functional*")</f>
+        <v/>
+      </c>
+      <c r="I83" s="97">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*Functional*")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*Functional*"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="24" customHeight="1">
+      <c r="A84" s="95" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="B84" s="99">
+        <f>COUNTIF('z_Loi'!$U:$U,"Deferred")</f>
+        <v/>
+      </c>
+      <c r="C84" s="100">
+        <f>IFERROR(B84/(COUNTA('z_Loi'!$E:$E)-1),"")</f>
+        <v/>
+      </c>
+      <c r="D84" s="95" t="n"/>
+      <c r="E84" s="99" t="n"/>
+      <c r="F84" s="99" t="n"/>
+      <c r="G84" s="95" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="H84" s="99">
+        <f>COUNTIF('z_Loi'!$K:$K,"*Security*")</f>
+        <v/>
+      </c>
+      <c r="I84" s="99">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*Security*")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*Security*"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="8" customHeight="1"/>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t>IX. KẾT QUẢ NGHIỆM THU THEO HẠNG MỤC</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="n"/>
+      <c r="C86" s="7" t="n"/>
+      <c r="D86" s="7" t="n"/>
+      <c r="E86" s="7" t="n"/>
+      <c r="F86" s="7" t="n"/>
+      <c r="G86" s="7" t="n"/>
+      <c r="H86" s="7" t="n"/>
+      <c r="I86" s="7" t="n"/>
+    </row>
+    <row r="87" ht="32" customHeight="1">
+      <c r="A87" s="90" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="B87" s="90" t="inlineStr">
         <is>
           <t>Phạm vi</t>
         </is>
       </c>
-      <c r="C6" s="90" t="inlineStr">
+      <c r="C87" s="90" t="inlineStr">
         <is>
           <t>Tổng</t>
         </is>
       </c>
-      <c r="D6" s="90" t="inlineStr">
+      <c r="D87" s="90" t="inlineStr">
         <is>
           <t>Hoàn thành</t>
         </is>
       </c>
-      <c r="E6" s="90" t="inlineStr">
+      <c r="E87" s="90" t="inlineStr">
         <is>
           <t>Tỷ lệ</t>
         </is>
       </c>
-      <c r="F6" s="90" t="inlineStr">
+      <c r="F87" s="90" t="inlineStr">
+        <is>
+          <t>Lỗi đang mở</t>
+        </is>
+      </c>
+      <c r="G87" s="90" t="inlineStr">
         <is>
           <t>Critical/High mở</t>
         </is>
       </c>
-      <c r="G6" s="90" t="inlineStr">
+      <c r="H87" s="90" t="inlineStr">
         <is>
           <t>Kết luận</t>
         </is>
       </c>
-      <c r="H6" s="90" t="inlineStr">
+      <c r="I87" s="90" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="74" t="inlineStr">
-        <is>
-          <t>UI/UX</t>
-        </is>
-      </c>
-      <c r="B7" s="91" t="inlineStr">
+    <row r="88" ht="26" customHeight="1">
+      <c r="A88" s="91" t="inlineStr">
+        <is>
+          <t>Giao diện &amp; trải nghiệm (UI/UX)</t>
+        </is>
+      </c>
+      <c r="B88" s="91" t="inlineStr">
         <is>
           <t>Trang website</t>
         </is>
       </c>
-      <c r="C7" s="52">
+      <c r="C88" s="97">
         <f>'z_Trang'!$B$1</f>
         <v/>
       </c>
-      <c r="D7" s="92">
+      <c r="D88" s="97">
         <f>'z_Trang'!$D$1</f>
         <v/>
       </c>
-      <c r="E7" s="33">
+      <c r="E88" s="98">
         <f>'z_Trang'!$F$1</f>
         <v/>
       </c>
-      <c r="F7" s="93">
-        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"High")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"High"))</f>
-        <v/>
-      </c>
-      <c r="G7" s="94" t="inlineStr">
-        <is>
-          <t>Chưa nghiệm thu</t>
-        </is>
-      </c>
-      <c r="H7" s="79" t="inlineStr"/>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="76" t="inlineStr">
-        <is>
-          <t>Chức năng</t>
-        </is>
-      </c>
-      <c r="B8" s="95" t="inlineStr">
-        <is>
-          <t>88 tính năng</t>
-        </is>
-      </c>
-      <c r="C8" s="49">
+      <c r="F88" s="97">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*UI/UX*")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*UI/UX*"))</f>
+        <v/>
+      </c>
+      <c r="G88" s="97">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*UI/UX*",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*UI/UX*",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*UI/UX*",'z_Loi'!$L:$L,"High")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*UI/UX*",'z_Loi'!$L:$L,"High"))</f>
+        <v/>
+      </c>
+      <c r="H88" s="102">
+        <f>IF(G88&gt;0,"Không đạt",IF(F88&gt;0,"Đạt có điều kiện","Đạt"))</f>
+        <v/>
+      </c>
+      <c r="I88" s="92" t="n"/>
+    </row>
+    <row r="89" ht="26" customHeight="1">
+      <c r="A89" s="95" t="inlineStr">
+        <is>
+          <t>Chức năng nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="B89" s="95" t="inlineStr">
+        <is>
+          <t>Tính năng theo yêu cầu</t>
+        </is>
+      </c>
+      <c r="C89" s="99">
         <f>'z_TinhNang'!$B$1</f>
         <v/>
       </c>
-      <c r="D8" s="96">
+      <c r="D89" s="99">
         <f>'z_TinhNang'!$D$1</f>
         <v/>
       </c>
-      <c r="E8" s="39">
+      <c r="E89" s="100">
         <f>'z_TinhNang'!$F$1</f>
         <v/>
       </c>
-      <c r="F8" s="97">
-        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"High")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"High"))</f>
-        <v/>
-      </c>
-      <c r="G8" s="98" t="inlineStr">
-        <is>
-          <t>Chưa nghiệm thu</t>
-        </is>
-      </c>
-      <c r="H8" s="99" t="inlineStr"/>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="74" t="inlineStr">
-        <is>
-          <t>Responsive</t>
-        </is>
-      </c>
-      <c r="B9" s="91" t="inlineStr">
-        <is>
-          <t>YC_87 + lỗi responsive</t>
-        </is>
-      </c>
-      <c r="C9" s="52" t="inlineStr"/>
-      <c r="D9" s="92" t="inlineStr"/>
-      <c r="E9" s="59" t="inlineStr"/>
-      <c r="F9" s="93">
-        <f>COUNTIF('z_Loi'!$K:$K,"*Responsive*")</f>
-        <v/>
-      </c>
-      <c r="G9" s="94" t="inlineStr">
-        <is>
-          <t>Chưa nghiệm thu</t>
-        </is>
-      </c>
-      <c r="H9" s="79" t="inlineStr"/>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="76" t="inlineStr">
+      <c r="F89" s="99">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*Functional*")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*Functional*"))</f>
+        <v/>
+      </c>
+      <c r="G89" s="99">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*Functional*",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*Functional*",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*Functional*",'z_Loi'!$L:$L,"High")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*Functional*",'z_Loi'!$L:$L,"High"))</f>
+        <v/>
+      </c>
+      <c r="H89" s="103">
+        <f>IF(G89&gt;0,"Không đạt",IF(F89&gt;0,"Đạt có điều kiện","Đạt"))</f>
+        <v/>
+      </c>
+      <c r="I89" s="92" t="n"/>
+    </row>
+    <row r="90" ht="26" customHeight="1">
+      <c r="A90" s="91" t="inlineStr">
+        <is>
+          <t>Tương thích &amp; Responsive</t>
+        </is>
+      </c>
+      <c r="B90" s="91" t="inlineStr">
+        <is>
+          <t>Desktop / Mobile / Tablet</t>
+        </is>
+      </c>
+      <c r="C90" s="97" t="n"/>
+      <c r="D90" s="97" t="n"/>
+      <c r="E90" s="98" t="n"/>
+      <c r="F90" s="97">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*Responsive*")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*Responsive*"))</f>
+        <v/>
+      </c>
+      <c r="G90" s="97">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*Responsive*",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*Responsive*",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*Responsive*",'z_Loi'!$L:$L,"High")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*Responsive*",'z_Loi'!$L:$L,"High"))</f>
+        <v/>
+      </c>
+      <c r="H90" s="102">
+        <f>IF(G90&gt;0,"Không đạt",IF(F90&gt;0,"Đạt có điều kiện","Đạt"))</f>
+        <v/>
+      </c>
+      <c r="I90" s="92" t="n"/>
+    </row>
+    <row r="91" ht="26" customHeight="1">
+      <c r="A91" s="95" t="inlineStr">
         <is>
           <t>Bảo mật</t>
         </is>
       </c>
-      <c r="B10" s="95" t="inlineStr">
-        <is>
-          <t>Test Case Security</t>
-        </is>
-      </c>
-      <c r="C10" s="49" t="inlineStr"/>
-      <c r="D10" s="96" t="inlineStr"/>
-      <c r="E10" s="54" t="inlineStr"/>
-      <c r="F10" s="97">
-        <f>COUNTIF('z_Loi'!$K:$K,"*Security*")</f>
-        <v/>
-      </c>
-      <c r="G10" s="98" t="inlineStr">
-        <is>
-          <t>Chưa nghiệm thu</t>
-        </is>
-      </c>
-      <c r="H10" s="99" t="inlineStr"/>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="74" t="inlineStr">
-        <is>
-          <t>Dữ liệu</t>
-        </is>
-      </c>
-      <c r="B11" s="91" t="inlineStr">
-        <is>
-          <t>Test Case API/Database</t>
-        </is>
-      </c>
-      <c r="C11" s="52" t="inlineStr"/>
-      <c r="D11" s="92" t="inlineStr"/>
-      <c r="E11" s="59" t="inlineStr"/>
-      <c r="F11" s="100" t="inlineStr"/>
-      <c r="G11" s="94" t="inlineStr">
-        <is>
-          <t>Chưa nghiệm thu</t>
-        </is>
-      </c>
-      <c r="H11" s="79" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="73" t="inlineStr">
-        <is>
-          <t>KẾT LUẬN CHUNG</t>
-        </is>
-      </c>
-      <c r="B13" s="60" t="n"/>
-      <c r="C13" s="101" t="inlineStr">
-        <is>
-          <t>Chưa nghiệm thu</t>
-        </is>
-      </c>
-      <c r="D13" s="63" t="n"/>
-      <c r="E13" s="63" t="n"/>
-      <c r="F13" s="63" t="n"/>
-      <c r="G13" s="63" t="n"/>
-      <c r="H13" s="63" t="n"/>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="102" t="inlineStr">
-        <is>
-          <t>Điều kiện khuyến nghị: không còn Critical/High chưa được phê duyệt; phạm vi và bằng chứng đầy đủ; ngoại lệ phải có người duyệt và lý do rõ ràng.</t>
-        </is>
-      </c>
-      <c r="B14" s="103" t="n"/>
-      <c r="C14" s="103" t="n"/>
-      <c r="D14" s="103" t="n"/>
-      <c r="E14" s="103" t="n"/>
-      <c r="F14" s="103" t="n"/>
-      <c r="G14" s="103" t="n"/>
-      <c r="H14" s="103" t="n"/>
+      <c r="B91" s="95" t="inlineStr">
+        <is>
+          <t>Test case Security, phân quyền, dữ liệu</t>
+        </is>
+      </c>
+      <c r="C91" s="99" t="n"/>
+      <c r="D91" s="99" t="n"/>
+      <c r="E91" s="100" t="n"/>
+      <c r="F91" s="99">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*Security*")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*Security*"))</f>
+        <v/>
+      </c>
+      <c r="G91" s="99">
+        <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*Security*",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*Security*",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$K:$K,"*Security*",'z_Loi'!$L:$L,"High")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$K:$K,"*Security*",'z_Loi'!$L:$L,"High"))</f>
+        <v/>
+      </c>
+      <c r="H91" s="103">
+        <f>IF(G91&gt;0,"Không đạt",IF(F91&gt;0,"Đạt có điều kiện","Đạt"))</f>
+        <v/>
+      </c>
+      <c r="I91" s="92" t="n"/>
+    </row>
+    <row r="92" ht="26" customHeight="1">
+      <c r="A92" s="91" t="inlineStr">
+        <is>
+          <t>Dữ liệu &amp; tích hợp (API/DB)</t>
+        </is>
+      </c>
+      <c r="B92" s="91" t="inlineStr">
+        <is>
+          <t>Luồng dữ liệu, API bên thứ ba</t>
+        </is>
+      </c>
+      <c r="C92" s="101" t="n"/>
+      <c r="D92" s="101" t="n"/>
+      <c r="E92" s="104" t="n"/>
+      <c r="F92" s="101" t="n"/>
+      <c r="G92" s="101" t="n"/>
+      <c r="H92" s="105" t="n"/>
+      <c r="I92" s="92" t="n"/>
+    </row>
+    <row r="93" ht="26" customHeight="1">
+      <c r="A93" s="95" t="inlineStr">
+        <is>
+          <t>Hiệu năng</t>
+        </is>
+      </c>
+      <c r="B93" s="95" t="inlineStr">
+        <is>
+          <t>Tốc độ tải, chịu tải</t>
+        </is>
+      </c>
+      <c r="C93" s="101" t="n"/>
+      <c r="D93" s="101" t="n"/>
+      <c r="E93" s="104" t="n"/>
+      <c r="F93" s="101" t="n"/>
+      <c r="G93" s="101" t="n"/>
+      <c r="H93" s="105" t="n"/>
+      <c r="I93" s="92" t="n"/>
+    </row>
+    <row r="94" ht="26" customHeight="1">
+      <c r="A94" s="91" t="inlineStr">
+        <is>
+          <t>SEO &amp; chuẩn nội dung</t>
+        </is>
+      </c>
+      <c r="B94" s="91" t="inlineStr">
+        <is>
+          <t>Meta, sitemap, robots, URL</t>
+        </is>
+      </c>
+      <c r="C94" s="101" t="n"/>
+      <c r="D94" s="101" t="n"/>
+      <c r="E94" s="104" t="n"/>
+      <c r="F94" s="101" t="n"/>
+      <c r="G94" s="101" t="n"/>
+      <c r="H94" s="105" t="n"/>
+      <c r="I94" s="92" t="n"/>
+    </row>
+    <row r="95" ht="26" customHeight="1">
+      <c r="A95" s="95" t="inlineStr">
+        <is>
+          <t>Khả năng truy cập (Accessibility)</t>
+        </is>
+      </c>
+      <c r="B95" s="95" t="inlineStr">
+        <is>
+          <t>Chuẩn WCAG cơ bản</t>
+        </is>
+      </c>
+      <c r="C95" s="101" t="n"/>
+      <c r="D95" s="101" t="n"/>
+      <c r="E95" s="104" t="n"/>
+      <c r="F95" s="101" t="n"/>
+      <c r="G95" s="101" t="n"/>
+      <c r="H95" s="105" t="n"/>
+      <c r="I95" s="92" t="n"/>
+    </row>
+    <row r="96" ht="26" customHeight="1">
+      <c r="A96" s="91" t="inlineStr">
+        <is>
+          <t>Vận hành &amp; bàn giao</t>
+        </is>
+      </c>
+      <c r="B96" s="91" t="inlineStr">
+        <is>
+          <t>Tài liệu, tài khoản, hướng dẫn</t>
+        </is>
+      </c>
+      <c r="C96" s="101" t="n"/>
+      <c r="D96" s="101" t="n"/>
+      <c r="E96" s="104" t="n"/>
+      <c r="F96" s="101" t="n"/>
+      <c r="G96" s="101" t="n"/>
+      <c r="H96" s="105" t="n"/>
+      <c r="I96" s="92" t="n"/>
+    </row>
+    <row r="97" ht="8" customHeight="1"/>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>X. KẾT QUẢ KIỂM THỬ PHI CHỨC NĂNG (nhập tay — cần bổ sung số đo)</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="n"/>
+      <c r="C98" s="7" t="n"/>
+      <c r="D98" s="7" t="n"/>
+      <c r="E98" s="7" t="n"/>
+      <c r="F98" s="7" t="n"/>
+      <c r="G98" s="7" t="n"/>
+      <c r="H98" s="7" t="n"/>
+      <c r="I98" s="7" t="n"/>
+    </row>
+    <row r="99" ht="32" customHeight="1">
+      <c r="A99" s="90" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="B99" s="90" t="inlineStr">
+        <is>
+          <t>Chỉ số đo</t>
+        </is>
+      </c>
+      <c r="C99" s="90" t="inlineStr">
+        <is>
+          <t>Công cụ đo</t>
+        </is>
+      </c>
+      <c r="D99" s="90" t="inlineStr">
+        <is>
+          <t>Ngưỡng yêu cầu</t>
+        </is>
+      </c>
+      <c r="E99" s="90" t="inlineStr">
+        <is>
+          <t>Kết quả đo</t>
+        </is>
+      </c>
+      <c r="F99" s="90" t="inlineStr">
+        <is>
+          <t>Ngày đo</t>
+        </is>
+      </c>
+      <c r="G99" s="90" t="inlineStr">
+        <is>
+          <t>Đánh giá</t>
+        </is>
+      </c>
+      <c r="H99" s="90" t="inlineStr">
+        <is>
+          <t>Bằng chứng / link</t>
+        </is>
+      </c>
+      <c r="I99" s="90" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="24" customHeight="1">
+      <c r="A100" s="91" t="inlineStr">
+        <is>
+          <t>Hiệu năng</t>
+        </is>
+      </c>
+      <c r="B100" s="91" t="inlineStr">
+        <is>
+          <t>Điểm PageSpeed Desktop</t>
+        </is>
+      </c>
+      <c r="C100" s="93" t="n"/>
+      <c r="D100" s="93" t="n"/>
+      <c r="E100" s="93" t="n"/>
+      <c r="F100" s="106" t="n"/>
+      <c r="G100" s="93" t="n"/>
+      <c r="H100" s="92" t="n"/>
+      <c r="I100" s="92" t="n"/>
+    </row>
+    <row r="101" ht="24" customHeight="1">
+      <c r="A101" s="95" t="inlineStr">
+        <is>
+          <t>Hiệu năng</t>
+        </is>
+      </c>
+      <c r="B101" s="95" t="inlineStr">
+        <is>
+          <t>Điểm PageSpeed Mobile</t>
+        </is>
+      </c>
+      <c r="C101" s="93" t="n"/>
+      <c r="D101" s="93" t="n"/>
+      <c r="E101" s="93" t="n"/>
+      <c r="F101" s="106" t="n"/>
+      <c r="G101" s="93" t="n"/>
+      <c r="H101" s="92" t="n"/>
+      <c r="I101" s="92" t="n"/>
+    </row>
+    <row r="102" ht="24" customHeight="1">
+      <c r="A102" s="91" t="inlineStr">
+        <is>
+          <t>Hiệu năng</t>
+        </is>
+      </c>
+      <c r="B102" s="91" t="inlineStr">
+        <is>
+          <t>LCP (giây)</t>
+        </is>
+      </c>
+      <c r="C102" s="93" t="n"/>
+      <c r="D102" s="93" t="n"/>
+      <c r="E102" s="93" t="n"/>
+      <c r="F102" s="106" t="n"/>
+      <c r="G102" s="93" t="n"/>
+      <c r="H102" s="92" t="n"/>
+      <c r="I102" s="92" t="n"/>
+    </row>
+    <row r="103" ht="24" customHeight="1">
+      <c r="A103" s="95" t="inlineStr">
+        <is>
+          <t>Hiệu năng</t>
+        </is>
+      </c>
+      <c r="B103" s="95" t="inlineStr">
+        <is>
+          <t>Thời gian tải trang chủ (giây)</t>
+        </is>
+      </c>
+      <c r="C103" s="93" t="n"/>
+      <c r="D103" s="93" t="n"/>
+      <c r="E103" s="93" t="n"/>
+      <c r="F103" s="106" t="n"/>
+      <c r="G103" s="93" t="n"/>
+      <c r="H103" s="92" t="n"/>
+      <c r="I103" s="92" t="n"/>
+    </row>
+    <row r="104" ht="24" customHeight="1">
+      <c r="A104" s="91" t="inlineStr">
+        <is>
+          <t>Chịu tải</t>
+        </is>
+      </c>
+      <c r="B104" s="91" t="inlineStr">
+        <is>
+          <t>Số người dùng đồng thời</t>
+        </is>
+      </c>
+      <c r="C104" s="93" t="n"/>
+      <c r="D104" s="93" t="n"/>
+      <c r="E104" s="93" t="n"/>
+      <c r="F104" s="106" t="n"/>
+      <c r="G104" s="93" t="n"/>
+      <c r="H104" s="92" t="n"/>
+      <c r="I104" s="92" t="n"/>
+    </row>
+    <row r="105" ht="24" customHeight="1">
+      <c r="A105" s="95" t="inlineStr">
+        <is>
+          <t>Bảo mật</t>
+        </is>
+      </c>
+      <c r="B105" s="95" t="inlineStr">
+        <is>
+          <t>Quét lỗ hổng (OWASP Top 10)</t>
+        </is>
+      </c>
+      <c r="C105" s="93" t="n"/>
+      <c r="D105" s="93" t="n"/>
+      <c r="E105" s="93" t="n"/>
+      <c r="F105" s="106" t="n"/>
+      <c r="G105" s="93" t="n"/>
+      <c r="H105" s="92" t="n"/>
+      <c r="I105" s="92" t="n"/>
+    </row>
+    <row r="106" ht="24" customHeight="1">
+      <c r="A106" s="91" t="inlineStr">
+        <is>
+          <t>Bảo mật</t>
+        </is>
+      </c>
+      <c r="B106" s="91" t="inlineStr">
+        <is>
+          <t>HTTPS / chứng chỉ SSL</t>
+        </is>
+      </c>
+      <c r="C106" s="93" t="n"/>
+      <c r="D106" s="93" t="n"/>
+      <c r="E106" s="93" t="n"/>
+      <c r="F106" s="106" t="n"/>
+      <c r="G106" s="93" t="n"/>
+      <c r="H106" s="92" t="n"/>
+      <c r="I106" s="92" t="n"/>
+    </row>
+    <row r="107" ht="24" customHeight="1">
+      <c r="A107" s="95" t="inlineStr">
+        <is>
+          <t>Bảo mật</t>
+        </is>
+      </c>
+      <c r="B107" s="95" t="inlineStr">
+        <is>
+          <t>Phân quyền theo vai trò</t>
+        </is>
+      </c>
+      <c r="C107" s="93" t="n"/>
+      <c r="D107" s="93" t="n"/>
+      <c r="E107" s="93" t="n"/>
+      <c r="F107" s="106" t="n"/>
+      <c r="G107" s="93" t="n"/>
+      <c r="H107" s="92" t="n"/>
+      <c r="I107" s="92" t="n"/>
+    </row>
+    <row r="108" ht="24" customHeight="1">
+      <c r="A108" s="91" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="B108" s="91" t="inlineStr">
+        <is>
+          <t>Sitemap / robots.txt / meta</t>
+        </is>
+      </c>
+      <c r="C108" s="93" t="n"/>
+      <c r="D108" s="93" t="n"/>
+      <c r="E108" s="93" t="n"/>
+      <c r="F108" s="106" t="n"/>
+      <c r="G108" s="93" t="n"/>
+      <c r="H108" s="92" t="n"/>
+      <c r="I108" s="92" t="n"/>
+    </row>
+    <row r="109" ht="24" customHeight="1">
+      <c r="A109" s="95" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="B109" s="95" t="inlineStr">
+        <is>
+          <t>Tương phản &amp; thao tác bàn phím</t>
+        </is>
+      </c>
+      <c r="C109" s="93" t="n"/>
+      <c r="D109" s="93" t="n"/>
+      <c r="E109" s="93" t="n"/>
+      <c r="F109" s="106" t="n"/>
+      <c r="G109" s="93" t="n"/>
+      <c r="H109" s="92" t="n"/>
+      <c r="I109" s="92" t="n"/>
+    </row>
+    <row r="110" ht="24" customHeight="1">
+      <c r="A110" s="91" t="inlineStr">
+        <is>
+          <t>Sao lưu</t>
+        </is>
+      </c>
+      <c r="B110" s="91" t="inlineStr">
+        <is>
+          <t>Cơ chế backup &amp; phục hồi</t>
+        </is>
+      </c>
+      <c r="C110" s="93" t="n"/>
+      <c r="D110" s="93" t="n"/>
+      <c r="E110" s="93" t="n"/>
+      <c r="F110" s="106" t="n"/>
+      <c r="G110" s="93" t="n"/>
+      <c r="H110" s="92" t="n"/>
+      <c r="I110" s="92" t="n"/>
+    </row>
+    <row r="111" ht="8" customHeight="1"/>
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>XI. LỖI TỒN ĐỌNG ĐANG CHẶN NGHIỆM THU (Critical/High còn mở)</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="n"/>
+      <c r="C112" s="7" t="n"/>
+      <c r="D112" s="7" t="n"/>
+      <c r="E112" s="7" t="n"/>
+      <c r="F112" s="7" t="n"/>
+      <c r="G112" s="7" t="n"/>
+      <c r="H112" s="7" t="n"/>
+      <c r="I112" s="7" t="n"/>
+    </row>
+    <row r="113" ht="26" customHeight="1">
+      <c r="A113" s="18" t="inlineStr">
+        <is>
+          <t>Danh sách tự động, hiển thị tối đa 30 lỗi ưu tiên. Danh sách đầy đủ xem sheet 05_Lỗi_Tester của file QA. Không nhập gì vào vùng bảng bên dưới (công thức sẽ tự đổ dữ liệu).</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="n"/>
+      <c r="C113" s="5" t="n"/>
+      <c r="D113" s="5" t="n"/>
+      <c r="E113" s="5" t="n"/>
+      <c r="F113" s="5" t="n"/>
+      <c r="G113" s="5" t="n"/>
+      <c r="H113" s="5" t="n"/>
+      <c r="I113" s="5" t="n"/>
+    </row>
+    <row r="114" ht="32" customHeight="1">
+      <c r="A114" s="90" t="inlineStr">
+        <is>
+          <t>BUG_ID</t>
+        </is>
+      </c>
+      <c r="B114" s="90" t="inlineStr">
+        <is>
+          <t>Trang</t>
+        </is>
+      </c>
+      <c r="C114" s="90" t="inlineStr">
+        <is>
+          <t>Tính năng</t>
+        </is>
+      </c>
+      <c r="D114" s="90" t="inlineStr">
+        <is>
+          <t>Mức độ</t>
+        </is>
+      </c>
+      <c r="E114" s="90" t="inlineStr">
+        <is>
+          <t>Loại lỗi</t>
+        </is>
+      </c>
+      <c r="F114" s="90" t="inlineStr">
+        <is>
+          <t>Ngày phát hiện</t>
+        </is>
+      </c>
+      <c r="G114" s="90" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+      <c r="H114" s="90" t="inlineStr">
+        <is>
+          <t>Người xử lý</t>
+        </is>
+      </c>
+      <c r="I114" s="90" t="inlineStr">
+        <is>
+          <t>Hạn xử lý</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="79">
+        <f>IFERROR(QUERY('z_Loi'!$A:$V,"select E,B,C,L,K,Q,U where (L = 'Critical' or L = 'High') and (U = 'Open' or U = 'Chưa gửi Dev') order by L asc, Q desc limit 30 label E '', B '', C '', L '', K '', Q '', U '' format Q 'dd/mm/yyyy'",1),"Không còn lỗi Critical/High đang mở — đủ điều kiện về lỗi chặn")</f>
+        <v/>
+      </c>
+      <c r="B115" s="14" t="n"/>
+      <c r="C115" s="14" t="n"/>
+      <c r="D115" s="14" t="n"/>
+      <c r="E115" s="14" t="n"/>
+      <c r="F115" s="14" t="n"/>
+      <c r="G115" s="14" t="n"/>
+      <c r="H115" s="14" t="n"/>
+      <c r="I115" s="14" t="n"/>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="14" t="n"/>
+      <c r="B116" s="14" t="n"/>
+      <c r="C116" s="14" t="n"/>
+      <c r="D116" s="14" t="n"/>
+      <c r="E116" s="14" t="n"/>
+      <c r="F116" s="14" t="n"/>
+      <c r="G116" s="14" t="n"/>
+      <c r="H116" s="14" t="n"/>
+      <c r="I116" s="14" t="n"/>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="14" t="n"/>
+      <c r="B117" s="14" t="n"/>
+      <c r="C117" s="14" t="n"/>
+      <c r="D117" s="14" t="n"/>
+      <c r="E117" s="14" t="n"/>
+      <c r="F117" s="14" t="n"/>
+      <c r="G117" s="14" t="n"/>
+      <c r="H117" s="14" t="n"/>
+      <c r="I117" s="14" t="n"/>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="14" t="n"/>
+      <c r="B118" s="14" t="n"/>
+      <c r="C118" s="14" t="n"/>
+      <c r="D118" s="14" t="n"/>
+      <c r="E118" s="14" t="n"/>
+      <c r="F118" s="14" t="n"/>
+      <c r="G118" s="14" t="n"/>
+      <c r="H118" s="14" t="n"/>
+      <c r="I118" s="14" t="n"/>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="14" t="n"/>
+      <c r="B119" s="14" t="n"/>
+      <c r="C119" s="14" t="n"/>
+      <c r="D119" s="14" t="n"/>
+      <c r="E119" s="14" t="n"/>
+      <c r="F119" s="14" t="n"/>
+      <c r="G119" s="14" t="n"/>
+      <c r="H119" s="14" t="n"/>
+      <c r="I119" s="14" t="n"/>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="14" t="n"/>
+      <c r="B120" s="14" t="n"/>
+      <c r="C120" s="14" t="n"/>
+      <c r="D120" s="14" t="n"/>
+      <c r="E120" s="14" t="n"/>
+      <c r="F120" s="14" t="n"/>
+      <c r="G120" s="14" t="n"/>
+      <c r="H120" s="14" t="n"/>
+      <c r="I120" s="14" t="n"/>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="14" t="n"/>
+      <c r="B121" s="14" t="n"/>
+      <c r="C121" s="14" t="n"/>
+      <c r="D121" s="14" t="n"/>
+      <c r="E121" s="14" t="n"/>
+      <c r="F121" s="14" t="n"/>
+      <c r="G121" s="14" t="n"/>
+      <c r="H121" s="14" t="n"/>
+      <c r="I121" s="14" t="n"/>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="14" t="n"/>
+      <c r="B122" s="14" t="n"/>
+      <c r="C122" s="14" t="n"/>
+      <c r="D122" s="14" t="n"/>
+      <c r="E122" s="14" t="n"/>
+      <c r="F122" s="14" t="n"/>
+      <c r="G122" s="14" t="n"/>
+      <c r="H122" s="14" t="n"/>
+      <c r="I122" s="14" t="n"/>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="14" t="n"/>
+      <c r="B123" s="14" t="n"/>
+      <c r="C123" s="14" t="n"/>
+      <c r="D123" s="14" t="n"/>
+      <c r="E123" s="14" t="n"/>
+      <c r="F123" s="14" t="n"/>
+      <c r="G123" s="14" t="n"/>
+      <c r="H123" s="14" t="n"/>
+      <c r="I123" s="14" t="n"/>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="14" t="n"/>
+      <c r="B124" s="14" t="n"/>
+      <c r="C124" s="14" t="n"/>
+      <c r="D124" s="14" t="n"/>
+      <c r="E124" s="14" t="n"/>
+      <c r="F124" s="14" t="n"/>
+      <c r="G124" s="14" t="n"/>
+      <c r="H124" s="14" t="n"/>
+      <c r="I124" s="14" t="n"/>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="14" t="n"/>
+      <c r="B125" s="14" t="n"/>
+      <c r="C125" s="14" t="n"/>
+      <c r="D125" s="14" t="n"/>
+      <c r="E125" s="14" t="n"/>
+      <c r="F125" s="14" t="n"/>
+      <c r="G125" s="14" t="n"/>
+      <c r="H125" s="14" t="n"/>
+      <c r="I125" s="14" t="n"/>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="14" t="n"/>
+      <c r="B126" s="14" t="n"/>
+      <c r="C126" s="14" t="n"/>
+      <c r="D126" s="14" t="n"/>
+      <c r="E126" s="14" t="n"/>
+      <c r="F126" s="14" t="n"/>
+      <c r="G126" s="14" t="n"/>
+      <c r="H126" s="14" t="n"/>
+      <c r="I126" s="14" t="n"/>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="14" t="n"/>
+      <c r="B127" s="14" t="n"/>
+      <c r="C127" s="14" t="n"/>
+      <c r="D127" s="14" t="n"/>
+      <c r="E127" s="14" t="n"/>
+      <c r="F127" s="14" t="n"/>
+      <c r="G127" s="14" t="n"/>
+      <c r="H127" s="14" t="n"/>
+      <c r="I127" s="14" t="n"/>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="14" t="n"/>
+      <c r="B128" s="14" t="n"/>
+      <c r="C128" s="14" t="n"/>
+      <c r="D128" s="14" t="n"/>
+      <c r="E128" s="14" t="n"/>
+      <c r="F128" s="14" t="n"/>
+      <c r="G128" s="14" t="n"/>
+      <c r="H128" s="14" t="n"/>
+      <c r="I128" s="14" t="n"/>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="14" t="n"/>
+      <c r="B129" s="14" t="n"/>
+      <c r="C129" s="14" t="n"/>
+      <c r="D129" s="14" t="n"/>
+      <c r="E129" s="14" t="n"/>
+      <c r="F129" s="14" t="n"/>
+      <c r="G129" s="14" t="n"/>
+      <c r="H129" s="14" t="n"/>
+      <c r="I129" s="14" t="n"/>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="14" t="n"/>
+      <c r="B130" s="14" t="n"/>
+      <c r="C130" s="14" t="n"/>
+      <c r="D130" s="14" t="n"/>
+      <c r="E130" s="14" t="n"/>
+      <c r="F130" s="14" t="n"/>
+      <c r="G130" s="14" t="n"/>
+      <c r="H130" s="14" t="n"/>
+      <c r="I130" s="14" t="n"/>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="14" t="n"/>
+      <c r="B131" s="14" t="n"/>
+      <c r="C131" s="14" t="n"/>
+      <c r="D131" s="14" t="n"/>
+      <c r="E131" s="14" t="n"/>
+      <c r="F131" s="14" t="n"/>
+      <c r="G131" s="14" t="n"/>
+      <c r="H131" s="14" t="n"/>
+      <c r="I131" s="14" t="n"/>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="14" t="n"/>
+      <c r="B132" s="14" t="n"/>
+      <c r="C132" s="14" t="n"/>
+      <c r="D132" s="14" t="n"/>
+      <c r="E132" s="14" t="n"/>
+      <c r="F132" s="14" t="n"/>
+      <c r="G132" s="14" t="n"/>
+      <c r="H132" s="14" t="n"/>
+      <c r="I132" s="14" t="n"/>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="14" t="n"/>
+      <c r="B133" s="14" t="n"/>
+      <c r="C133" s="14" t="n"/>
+      <c r="D133" s="14" t="n"/>
+      <c r="E133" s="14" t="n"/>
+      <c r="F133" s="14" t="n"/>
+      <c r="G133" s="14" t="n"/>
+      <c r="H133" s="14" t="n"/>
+      <c r="I133" s="14" t="n"/>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="14" t="n"/>
+      <c r="B134" s="14" t="n"/>
+      <c r="C134" s="14" t="n"/>
+      <c r="D134" s="14" t="n"/>
+      <c r="E134" s="14" t="n"/>
+      <c r="F134" s="14" t="n"/>
+      <c r="G134" s="14" t="n"/>
+      <c r="H134" s="14" t="n"/>
+      <c r="I134" s="14" t="n"/>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="14" t="n"/>
+      <c r="B135" s="14" t="n"/>
+      <c r="C135" s="14" t="n"/>
+      <c r="D135" s="14" t="n"/>
+      <c r="E135" s="14" t="n"/>
+      <c r="F135" s="14" t="n"/>
+      <c r="G135" s="14" t="n"/>
+      <c r="H135" s="14" t="n"/>
+      <c r="I135" s="14" t="n"/>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="14" t="n"/>
+      <c r="B136" s="14" t="n"/>
+      <c r="C136" s="14" t="n"/>
+      <c r="D136" s="14" t="n"/>
+      <c r="E136" s="14" t="n"/>
+      <c r="F136" s="14" t="n"/>
+      <c r="G136" s="14" t="n"/>
+      <c r="H136" s="14" t="n"/>
+      <c r="I136" s="14" t="n"/>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="14" t="n"/>
+      <c r="B137" s="14" t="n"/>
+      <c r="C137" s="14" t="n"/>
+      <c r="D137" s="14" t="n"/>
+      <c r="E137" s="14" t="n"/>
+      <c r="F137" s="14" t="n"/>
+      <c r="G137" s="14" t="n"/>
+      <c r="H137" s="14" t="n"/>
+      <c r="I137" s="14" t="n"/>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="14" t="n"/>
+      <c r="B138" s="14" t="n"/>
+      <c r="C138" s="14" t="n"/>
+      <c r="D138" s="14" t="n"/>
+      <c r="E138" s="14" t="n"/>
+      <c r="F138" s="14" t="n"/>
+      <c r="G138" s="14" t="n"/>
+      <c r="H138" s="14" t="n"/>
+      <c r="I138" s="14" t="n"/>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="14" t="n"/>
+      <c r="B139" s="14" t="n"/>
+      <c r="C139" s="14" t="n"/>
+      <c r="D139" s="14" t="n"/>
+      <c r="E139" s="14" t="n"/>
+      <c r="F139" s="14" t="n"/>
+      <c r="G139" s="14" t="n"/>
+      <c r="H139" s="14" t="n"/>
+      <c r="I139" s="14" t="n"/>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="14" t="n"/>
+      <c r="B140" s="14" t="n"/>
+      <c r="C140" s="14" t="n"/>
+      <c r="D140" s="14" t="n"/>
+      <c r="E140" s="14" t="n"/>
+      <c r="F140" s="14" t="n"/>
+      <c r="G140" s="14" t="n"/>
+      <c r="H140" s="14" t="n"/>
+      <c r="I140" s="14" t="n"/>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="14" t="n"/>
+      <c r="B141" s="14" t="n"/>
+      <c r="C141" s="14" t="n"/>
+      <c r="D141" s="14" t="n"/>
+      <c r="E141" s="14" t="n"/>
+      <c r="F141" s="14" t="n"/>
+      <c r="G141" s="14" t="n"/>
+      <c r="H141" s="14" t="n"/>
+      <c r="I141" s="14" t="n"/>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="14" t="n"/>
+      <c r="B142" s="14" t="n"/>
+      <c r="C142" s="14" t="n"/>
+      <c r="D142" s="14" t="n"/>
+      <c r="E142" s="14" t="n"/>
+      <c r="F142" s="14" t="n"/>
+      <c r="G142" s="14" t="n"/>
+      <c r="H142" s="14" t="n"/>
+      <c r="I142" s="14" t="n"/>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="14" t="n"/>
+      <c r="B143" s="14" t="n"/>
+      <c r="C143" s="14" t="n"/>
+      <c r="D143" s="14" t="n"/>
+      <c r="E143" s="14" t="n"/>
+      <c r="F143" s="14" t="n"/>
+      <c r="G143" s="14" t="n"/>
+      <c r="H143" s="14" t="n"/>
+      <c r="I143" s="14" t="n"/>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="14" t="n"/>
+      <c r="B144" s="14" t="n"/>
+      <c r="C144" s="14" t="n"/>
+      <c r="D144" s="14" t="n"/>
+      <c r="E144" s="14" t="n"/>
+      <c r="F144" s="14" t="n"/>
+      <c r="G144" s="14" t="n"/>
+      <c r="H144" s="14" t="n"/>
+      <c r="I144" s="14" t="n"/>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="14" t="n"/>
+      <c r="B145" s="14" t="n"/>
+      <c r="C145" s="14" t="n"/>
+      <c r="D145" s="14" t="n"/>
+      <c r="E145" s="14" t="n"/>
+      <c r="F145" s="14" t="n"/>
+      <c r="G145" s="14" t="n"/>
+      <c r="H145" s="14" t="n"/>
+      <c r="I145" s="14" t="n"/>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="14" t="n"/>
+      <c r="B146" s="14" t="n"/>
+      <c r="C146" s="14" t="n"/>
+      <c r="D146" s="14" t="n"/>
+      <c r="E146" s="14" t="n"/>
+      <c r="F146" s="14" t="n"/>
+      <c r="G146" s="14" t="n"/>
+      <c r="H146" s="14" t="n"/>
+      <c r="I146" s="14" t="n"/>
+    </row>
+    <row r="147" ht="8" customHeight="1"/>
+    <row r="148" ht="22" customHeight="1">
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t>XII. NGOẠI LỆ / LỖI ĐƯỢC CHẤP NHẬN BỎ QUA (WAIVER)</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="n"/>
+      <c r="C148" s="7" t="n"/>
+      <c r="D148" s="7" t="n"/>
+      <c r="E148" s="7" t="n"/>
+      <c r="F148" s="7" t="n"/>
+      <c r="G148" s="7" t="n"/>
+      <c r="H148" s="7" t="n"/>
+      <c r="I148" s="7" t="n"/>
+    </row>
+    <row r="149" ht="22" customHeight="1">
+      <c r="A149" s="18" t="inlineStr">
+        <is>
+          <t>Mọi lỗi Critical/High không xử lý trước nghiệm thu phải có ngoại lệ được người duyệt của Bên A ký chấp nhận.</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="n"/>
+      <c r="C149" s="5" t="n"/>
+      <c r="D149" s="5" t="n"/>
+      <c r="E149" s="5" t="n"/>
+      <c r="F149" s="5" t="n"/>
+      <c r="G149" s="5" t="n"/>
+      <c r="H149" s="5" t="n"/>
+      <c r="I149" s="5" t="n"/>
+    </row>
+    <row r="150" ht="32" customHeight="1">
+      <c r="A150" s="90" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B150" s="90" t="inlineStr">
+        <is>
+          <t>BUG_ID / Hạng mục</t>
+        </is>
+      </c>
+      <c r="C150" s="90" t="inlineStr">
+        <is>
+          <t>Mức độ</t>
+        </is>
+      </c>
+      <c r="D150" s="90" t="inlineStr">
+        <is>
+          <t>Lý do chấp nhận</t>
+        </is>
+      </c>
+      <c r="E150" s="90" t="inlineStr">
+        <is>
+          <t>Ảnh hưởng còn lại</t>
+        </is>
+      </c>
+      <c r="F150" s="90" t="inlineStr">
+        <is>
+          <t>Phương án tạm thời</t>
+        </is>
+      </c>
+      <c r="G150" s="90" t="inlineStr">
+        <is>
+          <t>Hạn xử lý dứt điểm</t>
+        </is>
+      </c>
+      <c r="H150" s="90" t="inlineStr">
+        <is>
+          <t>Người duyệt</t>
+        </is>
+      </c>
+      <c r="I150" s="90" t="inlineStr">
+        <is>
+          <t>Ngày duyệt</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="24" customHeight="1">
+      <c r="A151" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="B151" s="92" t="n"/>
+      <c r="C151" s="93" t="n"/>
+      <c r="D151" s="92" t="n"/>
+      <c r="E151" s="92" t="n"/>
+      <c r="F151" s="92" t="n"/>
+      <c r="G151" s="106" t="n"/>
+      <c r="H151" s="93" t="n"/>
+      <c r="I151" s="106" t="n"/>
+    </row>
+    <row r="152" ht="24" customHeight="1">
+      <c r="A152" s="96" t="n">
+        <v>2</v>
+      </c>
+      <c r="B152" s="92" t="n"/>
+      <c r="C152" s="93" t="n"/>
+      <c r="D152" s="92" t="n"/>
+      <c r="E152" s="92" t="n"/>
+      <c r="F152" s="92" t="n"/>
+      <c r="G152" s="106" t="n"/>
+      <c r="H152" s="93" t="n"/>
+      <c r="I152" s="106" t="n"/>
+    </row>
+    <row r="153" ht="24" customHeight="1">
+      <c r="A153" s="94" t="n">
+        <v>3</v>
+      </c>
+      <c r="B153" s="92" t="n"/>
+      <c r="C153" s="93" t="n"/>
+      <c r="D153" s="92" t="n"/>
+      <c r="E153" s="92" t="n"/>
+      <c r="F153" s="92" t="n"/>
+      <c r="G153" s="106" t="n"/>
+      <c r="H153" s="93" t="n"/>
+      <c r="I153" s="106" t="n"/>
+    </row>
+    <row r="154" ht="24" customHeight="1">
+      <c r="A154" s="96" t="n">
+        <v>4</v>
+      </c>
+      <c r="B154" s="92" t="n"/>
+      <c r="C154" s="93" t="n"/>
+      <c r="D154" s="92" t="n"/>
+      <c r="E154" s="92" t="n"/>
+      <c r="F154" s="92" t="n"/>
+      <c r="G154" s="106" t="n"/>
+      <c r="H154" s="93" t="n"/>
+      <c r="I154" s="106" t="n"/>
+    </row>
+    <row r="155" ht="24" customHeight="1">
+      <c r="A155" s="94" t="n">
+        <v>5</v>
+      </c>
+      <c r="B155" s="92" t="n"/>
+      <c r="C155" s="93" t="n"/>
+      <c r="D155" s="92" t="n"/>
+      <c r="E155" s="92" t="n"/>
+      <c r="F155" s="92" t="n"/>
+      <c r="G155" s="106" t="n"/>
+      <c r="H155" s="93" t="n"/>
+      <c r="I155" s="106" t="n"/>
+    </row>
+    <row r="156" ht="24" customHeight="1">
+      <c r="A156" s="96" t="n">
+        <v>6</v>
+      </c>
+      <c r="B156" s="92" t="n"/>
+      <c r="C156" s="93" t="n"/>
+      <c r="D156" s="92" t="n"/>
+      <c r="E156" s="92" t="n"/>
+      <c r="F156" s="92" t="n"/>
+      <c r="G156" s="106" t="n"/>
+      <c r="H156" s="93" t="n"/>
+      <c r="I156" s="106" t="n"/>
+    </row>
+    <row r="157" ht="8" customHeight="1"/>
+    <row r="158" ht="22" customHeight="1">
+      <c r="A158" s="11" t="inlineStr">
+        <is>
+          <t>XIII. RỦI RO VÀ HẠN CHẾ ĐÃ BIẾT</t>
+        </is>
+      </c>
+      <c r="B158" s="7" t="n"/>
+      <c r="C158" s="7" t="n"/>
+      <c r="D158" s="7" t="n"/>
+      <c r="E158" s="7" t="n"/>
+      <c r="F158" s="7" t="n"/>
+      <c r="G158" s="7" t="n"/>
+      <c r="H158" s="7" t="n"/>
+      <c r="I158" s="7" t="n"/>
+    </row>
+    <row r="159" ht="32" customHeight="1">
+      <c r="A159" s="90" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B159" s="90" t="inlineStr">
+        <is>
+          <t>Rủi ro / hạn chế</t>
+        </is>
+      </c>
+      <c r="C159" s="90" t="inlineStr">
+        <is>
+          <t>Khả năng xảy ra</t>
+        </is>
+      </c>
+      <c r="D159" s="90" t="inlineStr">
+        <is>
+          <t>Mức ảnh hưởng</t>
+        </is>
+      </c>
+      <c r="E159" s="90" t="inlineStr">
+        <is>
+          <t>Biện pháp giảm thiểu</t>
+        </is>
+      </c>
+      <c r="F159" s="90" t="inlineStr">
+        <is>
+          <t>Người theo dõi</t>
+        </is>
+      </c>
+      <c r="G159" s="90" t="inlineStr">
+        <is>
+          <t>Hạn xử lý</t>
+        </is>
+      </c>
+      <c r="H159" s="90" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+      <c r="I159" s="90" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="24" customHeight="1">
+      <c r="A160" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="B160" s="92" t="n"/>
+      <c r="C160" s="93" t="n"/>
+      <c r="D160" s="93" t="n"/>
+      <c r="E160" s="92" t="n"/>
+      <c r="F160" s="93" t="n"/>
+      <c r="G160" s="106" t="n"/>
+      <c r="H160" s="93" t="n"/>
+      <c r="I160" s="92" t="n"/>
+    </row>
+    <row r="161" ht="24" customHeight="1">
+      <c r="A161" s="96" t="n">
+        <v>2</v>
+      </c>
+      <c r="B161" s="92" t="n"/>
+      <c r="C161" s="93" t="n"/>
+      <c r="D161" s="93" t="n"/>
+      <c r="E161" s="92" t="n"/>
+      <c r="F161" s="93" t="n"/>
+      <c r="G161" s="106" t="n"/>
+      <c r="H161" s="93" t="n"/>
+      <c r="I161" s="92" t="n"/>
+    </row>
+    <row r="162" ht="24" customHeight="1">
+      <c r="A162" s="94" t="n">
+        <v>3</v>
+      </c>
+      <c r="B162" s="92" t="n"/>
+      <c r="C162" s="93" t="n"/>
+      <c r="D162" s="93" t="n"/>
+      <c r="E162" s="92" t="n"/>
+      <c r="F162" s="93" t="n"/>
+      <c r="G162" s="106" t="n"/>
+      <c r="H162" s="93" t="n"/>
+      <c r="I162" s="92" t="n"/>
+    </row>
+    <row r="163" ht="24" customHeight="1">
+      <c r="A163" s="96" t="n">
+        <v>4</v>
+      </c>
+      <c r="B163" s="92" t="n"/>
+      <c r="C163" s="93" t="n"/>
+      <c r="D163" s="93" t="n"/>
+      <c r="E163" s="92" t="n"/>
+      <c r="F163" s="93" t="n"/>
+      <c r="G163" s="106" t="n"/>
+      <c r="H163" s="93" t="n"/>
+      <c r="I163" s="92" t="n"/>
+    </row>
+    <row r="164" ht="24" customHeight="1">
+      <c r="A164" s="94" t="n">
+        <v>5</v>
+      </c>
+      <c r="B164" s="92" t="n"/>
+      <c r="C164" s="93" t="n"/>
+      <c r="D164" s="93" t="n"/>
+      <c r="E164" s="92" t="n"/>
+      <c r="F164" s="93" t="n"/>
+      <c r="G164" s="106" t="n"/>
+      <c r="H164" s="93" t="n"/>
+      <c r="I164" s="92" t="n"/>
+    </row>
+    <row r="165" ht="8" customHeight="1"/>
+    <row r="166" ht="22" customHeight="1">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t>XIV. HẠNG MỤC BÀN GIAO</t>
+        </is>
+      </c>
+      <c r="B166" s="7" t="n"/>
+      <c r="C166" s="7" t="n"/>
+      <c r="D166" s="7" t="n"/>
+      <c r="E166" s="7" t="n"/>
+      <c r="F166" s="7" t="n"/>
+      <c r="G166" s="7" t="n"/>
+      <c r="H166" s="7" t="n"/>
+      <c r="I166" s="7" t="n"/>
+    </row>
+    <row r="167" ht="32" customHeight="1">
+      <c r="A167" s="90" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B167" s="90" t="inlineStr">
+        <is>
+          <t>Hạng mục bàn giao</t>
+        </is>
+      </c>
+      <c r="C167" s="90" t="inlineStr">
+        <is>
+          <t>Định dạng / nơi lưu</t>
+        </is>
+      </c>
+      <c r="D167" s="90" t="inlineStr">
+        <is>
+          <t>Số lượng</t>
+        </is>
+      </c>
+      <c r="E167" s="90" t="inlineStr">
+        <is>
+          <t>Tình trạng</t>
+        </is>
+      </c>
+      <c r="F167" s="90" t="inlineStr">
+        <is>
+          <t>Ngày bàn giao</t>
+        </is>
+      </c>
+      <c r="G167" s="90" t="inlineStr">
+        <is>
+          <t>Người bàn giao</t>
+        </is>
+      </c>
+      <c r="H167" s="90" t="inlineStr">
+        <is>
+          <t>Người nhận</t>
+        </is>
+      </c>
+      <c r="I167" s="90" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="24" customHeight="1">
+      <c r="A168" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="B168" s="91" t="inlineStr">
+        <is>
+          <t>Mã nguồn website (repository)</t>
+        </is>
+      </c>
+      <c r="C168" s="92" t="n"/>
+      <c r="D168" s="93" t="n"/>
+      <c r="E168" s="93" t="n"/>
+      <c r="F168" s="106" t="n"/>
+      <c r="G168" s="93" t="n"/>
+      <c r="H168" s="93" t="n"/>
+      <c r="I168" s="92" t="n"/>
+    </row>
+    <row r="169" ht="24" customHeight="1">
+      <c r="A169" s="96" t="n">
+        <v>2</v>
+      </c>
+      <c r="B169" s="95" t="inlineStr">
+        <is>
+          <t>Cơ sở dữ liệu (dump/backup)</t>
+        </is>
+      </c>
+      <c r="C169" s="92" t="n"/>
+      <c r="D169" s="93" t="n"/>
+      <c r="E169" s="93" t="n"/>
+      <c r="F169" s="106" t="n"/>
+      <c r="G169" s="93" t="n"/>
+      <c r="H169" s="93" t="n"/>
+      <c r="I169" s="92" t="n"/>
+    </row>
+    <row r="170" ht="24" customHeight="1">
+      <c r="A170" s="94" t="n">
+        <v>3</v>
+      </c>
+      <c r="B170" s="91" t="inlineStr">
+        <is>
+          <t>Tài khoản quản trị hệ thống</t>
+        </is>
+      </c>
+      <c r="C170" s="92" t="n"/>
+      <c r="D170" s="93" t="n"/>
+      <c r="E170" s="93" t="n"/>
+      <c r="F170" s="106" t="n"/>
+      <c r="G170" s="93" t="n"/>
+      <c r="H170" s="93" t="n"/>
+      <c r="I170" s="92" t="n"/>
+    </row>
+    <row r="171" ht="24" customHeight="1">
+      <c r="A171" s="96" t="n">
+        <v>4</v>
+      </c>
+      <c r="B171" s="95" t="inlineStr">
+        <is>
+          <t>Tài liệu hướng dẫn sử dụng</t>
+        </is>
+      </c>
+      <c r="C171" s="92" t="n"/>
+      <c r="D171" s="93" t="n"/>
+      <c r="E171" s="93" t="n"/>
+      <c r="F171" s="106" t="n"/>
+      <c r="G171" s="93" t="n"/>
+      <c r="H171" s="93" t="n"/>
+      <c r="I171" s="92" t="n"/>
+    </row>
+    <row r="172" ht="24" customHeight="1">
+      <c r="A172" s="94" t="n">
+        <v>5</v>
+      </c>
+      <c r="B172" s="91" t="inlineStr">
+        <is>
+          <t>Tài liệu kỹ thuật / triển khai</t>
+        </is>
+      </c>
+      <c r="C172" s="92" t="n"/>
+      <c r="D172" s="93" t="n"/>
+      <c r="E172" s="93" t="n"/>
+      <c r="F172" s="106" t="n"/>
+      <c r="G172" s="93" t="n"/>
+      <c r="H172" s="93" t="n"/>
+      <c r="I172" s="92" t="n"/>
+    </row>
+    <row r="173" ht="24" customHeight="1">
+      <c r="A173" s="96" t="n">
+        <v>6</v>
+      </c>
+      <c r="B173" s="95" t="inlineStr">
+        <is>
+          <t>Bộ Test Case (RTM)</t>
+        </is>
+      </c>
+      <c r="C173" s="92" t="n"/>
+      <c r="D173" s="93" t="n"/>
+      <c r="E173" s="93" t="n"/>
+      <c r="F173" s="106" t="n"/>
+      <c r="G173" s="93" t="n"/>
+      <c r="H173" s="93" t="n"/>
+      <c r="I173" s="92" t="n"/>
+    </row>
+    <row r="174" ht="24" customHeight="1">
+      <c r="A174" s="94" t="n">
+        <v>7</v>
+      </c>
+      <c r="B174" s="91" t="inlineStr">
+        <is>
+          <t>Bộ hồ sơ lỗi + bằng chứng</t>
+        </is>
+      </c>
+      <c r="C174" s="92" t="n"/>
+      <c r="D174" s="93" t="n"/>
+      <c r="E174" s="93" t="n"/>
+      <c r="F174" s="106" t="n"/>
+      <c r="G174" s="93" t="n"/>
+      <c r="H174" s="93" t="n"/>
+      <c r="I174" s="92" t="n"/>
+    </row>
+    <row r="175" ht="24" customHeight="1">
+      <c r="A175" s="96" t="n">
+        <v>8</v>
+      </c>
+      <c r="B175" s="95" t="inlineStr">
+        <is>
+          <t>Bộ thiết kế (Figma/ảnh)</t>
+        </is>
+      </c>
+      <c r="C175" s="92" t="n"/>
+      <c r="D175" s="93" t="n"/>
+      <c r="E175" s="93" t="n"/>
+      <c r="F175" s="106" t="n"/>
+      <c r="G175" s="93" t="n"/>
+      <c r="H175" s="93" t="n"/>
+      <c r="I175" s="92" t="n"/>
+    </row>
+    <row r="176" ht="24" customHeight="1">
+      <c r="A176" s="94" t="n">
+        <v>9</v>
+      </c>
+      <c r="B176" s="91" t="inlineStr">
+        <is>
+          <t>Tên miền, hosting, chứng chỉ SSL</t>
+        </is>
+      </c>
+      <c r="C176" s="92" t="n"/>
+      <c r="D176" s="93" t="n"/>
+      <c r="E176" s="93" t="n"/>
+      <c r="F176" s="106" t="n"/>
+      <c r="G176" s="93" t="n"/>
+      <c r="H176" s="93" t="n"/>
+      <c r="I176" s="92" t="n"/>
+    </row>
+    <row r="177" ht="24" customHeight="1">
+      <c r="A177" s="96" t="n">
+        <v>10</v>
+      </c>
+      <c r="B177" s="95" t="inlineStr">
+        <is>
+          <t>Tài khoản dịch vụ bên thứ ba</t>
+        </is>
+      </c>
+      <c r="C177" s="92" t="n"/>
+      <c r="D177" s="93" t="n"/>
+      <c r="E177" s="93" t="n"/>
+      <c r="F177" s="106" t="n"/>
+      <c r="G177" s="93" t="n"/>
+      <c r="H177" s="93" t="n"/>
+      <c r="I177" s="92" t="n"/>
+    </row>
+    <row r="178" ht="8" customHeight="1"/>
+    <row r="179" ht="22" customHeight="1">
+      <c r="A179" s="11" t="inlineStr">
+        <is>
+          <t>XV. BẢO HÀNH VÀ HỖ TRỢ SAU NGHIỆM THU</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="n"/>
+      <c r="C179" s="7" t="n"/>
+      <c r="D179" s="7" t="n"/>
+      <c r="E179" s="7" t="n"/>
+      <c r="F179" s="7" t="n"/>
+      <c r="G179" s="7" t="n"/>
+      <c r="H179" s="7" t="n"/>
+      <c r="I179" s="7" t="n"/>
+    </row>
+    <row r="180" ht="24" customHeight="1">
+      <c r="A180" s="86" t="inlineStr">
+        <is>
+          <t>Thời gian bảo hành</t>
+        </is>
+      </c>
+      <c r="B180" s="87" t="n"/>
+      <c r="C180" s="88" t="n"/>
+      <c r="D180" s="86" t="inlineStr">
+        <is>
+          <t>Từ ngày</t>
+        </is>
+      </c>
+      <c r="E180" s="89" t="n"/>
+      <c r="F180" s="88" t="n"/>
+      <c r="G180" s="86" t="inlineStr">
+        <is>
+          <t>Đến ngày</t>
+        </is>
+      </c>
+      <c r="H180" s="89" t="n"/>
+      <c r="I180" s="88" t="n"/>
+    </row>
+    <row r="181" ht="24" customHeight="1">
+      <c r="A181" s="86" t="inlineStr">
+        <is>
+          <t>Phạm vi bảo hành</t>
+        </is>
+      </c>
+      <c r="B181" s="87" t="n"/>
+      <c r="C181" s="88" t="n"/>
+      <c r="D181" s="86" t="inlineStr">
+        <is>
+          <t>Kênh tiếp nhận lỗi</t>
+        </is>
+      </c>
+      <c r="E181" s="87" t="n"/>
+      <c r="F181" s="88" t="n"/>
+      <c r="G181" s="86" t="inlineStr">
+        <is>
+          <t>Thời gian phản hồi (SLA)</t>
+        </is>
+      </c>
+      <c r="H181" s="87" t="n"/>
+      <c r="I181" s="88" t="n"/>
+    </row>
+    <row r="182" ht="24" customHeight="1">
+      <c r="A182" s="86" t="inlineStr">
+        <is>
+          <t>Thời gian khắc phục Critical</t>
+        </is>
+      </c>
+      <c r="B182" s="87" t="n"/>
+      <c r="C182" s="88" t="n"/>
+      <c r="D182" s="86" t="inlineStr">
+        <is>
+          <t>Thời gian khắc phục High</t>
+        </is>
+      </c>
+      <c r="E182" s="87" t="n"/>
+      <c r="F182" s="88" t="n"/>
+      <c r="G182" s="86" t="inlineStr">
+        <is>
+          <t>Chi phí ngoài bảo hành</t>
+        </is>
+      </c>
+      <c r="H182" s="87" t="n"/>
+      <c r="I182" s="88" t="n"/>
+    </row>
+    <row r="183" ht="8" customHeight="1"/>
+    <row r="184" ht="22" customHeight="1">
+      <c r="A184" s="11" t="inlineStr">
+        <is>
+          <t>XVI. KẾT LUẬN NGHIỆM THU</t>
+        </is>
+      </c>
+      <c r="B184" s="7" t="n"/>
+      <c r="C184" s="7" t="n"/>
+      <c r="D184" s="7" t="n"/>
+      <c r="E184" s="7" t="n"/>
+      <c r="F184" s="7" t="n"/>
+      <c r="G184" s="7" t="n"/>
+      <c r="H184" s="7" t="n"/>
+      <c r="I184" s="7" t="n"/>
+    </row>
+    <row r="185" ht="32" customHeight="1">
+      <c r="A185" s="90" t="inlineStr">
+        <is>
+          <t>Nội dung</t>
+        </is>
+      </c>
+      <c r="B185" s="90" t="inlineStr">
+        <is>
+          <t>Kết quả</t>
+        </is>
+      </c>
+      <c r="C185" s="90" t="inlineStr"/>
+      <c r="D185" s="90" t="inlineStr">
+        <is>
+          <t>Diễn giải</t>
+        </is>
+      </c>
+      <c r="E185" s="90" t="inlineStr"/>
+      <c r="F185" s="90" t="inlineStr"/>
+      <c r="G185" s="90" t="inlineStr"/>
+      <c r="H185" s="90" t="inlineStr"/>
+      <c r="I185" s="90" t="inlineStr"/>
+    </row>
+    <row r="186" ht="28" customHeight="1">
+      <c r="A186" s="107" t="inlineStr">
+        <is>
+          <t>Đề xuất tự động (theo tiêu chí mục V)</t>
+        </is>
+      </c>
+      <c r="B186" s="108">
+        <f>IF(COUNTIF(E43:E59,"Chưa đạt")&gt;0,"KHÔNG ĐẠT — còn "&amp;COUNTIF(E43:E59,"Chưa đạt")&amp;" tiêu chí chưa đạt",IF(COUNTIF(E43:E59,"Chưa chốt ngưỡng")+COUNTBLANK(E43:E59)&gt;0,"CHƯA ĐỦ CĂN CỨ — còn tiêu chí chưa có ngưỡng hoặc chưa đánh giá","ĐẠT — toàn bộ tiêu chí bắt buộc đã thỏa mãn"))</f>
+        <v/>
+      </c>
+      <c r="C186" s="109" t="n"/>
+      <c r="D186" s="109" t="n"/>
+      <c r="E186" s="109" t="n"/>
+      <c r="F186" s="109" t="n"/>
+      <c r="G186" s="109" t="n"/>
+      <c r="H186" s="109" t="n"/>
+      <c r="I186" s="109" t="n"/>
+    </row>
+    <row r="187" ht="24" customHeight="1">
+      <c r="A187" s="107" t="inlineStr">
+        <is>
+          <t>Số hạng mục Đạt / Không đạt (mục IX)</t>
+        </is>
+      </c>
+      <c r="B187" s="51">
+        <f>"Đạt: "&amp;COUNTIF(H88:H96,"Đạt")&amp;"  |  Đạt có điều kiện: "&amp;COUNTIF(H88:H96,"Đạt có điều kiện")&amp;"  |  Không đạt: "&amp;COUNTIF(H88:H96,"Không đạt")&amp;"  |  Chưa kết luận: "&amp;COUNTBLANK(H88:H96)</f>
+        <v/>
+      </c>
+      <c r="C187" s="63" t="n"/>
+      <c r="D187" s="63" t="n"/>
+      <c r="E187" s="63" t="n"/>
+      <c r="F187" s="63" t="n"/>
+      <c r="G187" s="63" t="n"/>
+      <c r="H187" s="63" t="n"/>
+      <c r="I187" s="63" t="n"/>
+    </row>
+    <row r="188" ht="30" customHeight="1">
+      <c r="A188" s="26" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN CHÍNH THỨC (người duyệt chọn)</t>
+        </is>
+      </c>
+      <c r="B188" s="110" t="inlineStr"/>
+      <c r="C188" s="88" t="n"/>
+      <c r="D188" s="88" t="n"/>
+      <c r="E188" s="111" t="inlineStr">
+        <is>
+          <t>Ngày kết luận</t>
+        </is>
+      </c>
+      <c r="F188" s="112" t="inlineStr"/>
+      <c r="G188" s="88" t="n"/>
+      <c r="H188" s="111" t="inlineStr">
+        <is>
+          <t>Hiệu lực từ</t>
+        </is>
+      </c>
+      <c r="I188" s="112" t="inlineStr"/>
+    </row>
+    <row r="189" ht="46" customHeight="1">
+      <c r="A189" s="107" t="inlineStr">
+        <is>
+          <t>Lý do / điều kiện kèm theo</t>
+        </is>
+      </c>
+      <c r="B189" s="92" t="inlineStr"/>
+      <c r="C189" s="88" t="n"/>
+      <c r="D189" s="88" t="n"/>
+      <c r="E189" s="88" t="n"/>
+      <c r="F189" s="88" t="n"/>
+      <c r="G189" s="88" t="n"/>
+      <c r="H189" s="88" t="n"/>
+      <c r="I189" s="88" t="n"/>
+    </row>
+    <row r="190" ht="8" customHeight="1"/>
+    <row r="191" ht="22" customHeight="1">
+      <c r="A191" s="11" t="inlineStr">
+        <is>
+          <t>XVII. VIỆC CẦN LÀM ĐỂ HOÀN TẤT NGHIỆM THU</t>
+        </is>
+      </c>
+      <c r="B191" s="7" t="n"/>
+      <c r="C191" s="7" t="n"/>
+      <c r="D191" s="7" t="n"/>
+      <c r="E191" s="7" t="n"/>
+      <c r="F191" s="7" t="n"/>
+      <c r="G191" s="7" t="n"/>
+      <c r="H191" s="7" t="n"/>
+      <c r="I191" s="7" t="n"/>
+    </row>
+    <row r="192" ht="32" customHeight="1">
+      <c r="A192" s="90" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B192" s="90" t="inlineStr">
+        <is>
+          <t>Việc cần làm</t>
+        </is>
+      </c>
+      <c r="C192" s="90" t="inlineStr">
+        <is>
+          <t>Đầu ra / điều kiện xong</t>
+        </is>
+      </c>
+      <c r="D192" s="90" t="inlineStr">
+        <is>
+          <t>Người phụ trách</t>
+        </is>
+      </c>
+      <c r="E192" s="90" t="inlineStr">
+        <is>
+          <t>Hạn hoàn thành</t>
+        </is>
+      </c>
+      <c r="F192" s="90" t="inlineStr">
+        <is>
+          <t>Mức ưu tiên</t>
+        </is>
+      </c>
+      <c r="G192" s="90" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+      <c r="H192" s="90" t="inlineStr">
+        <is>
+          <t>Bằng chứng</t>
+        </is>
+      </c>
+      <c r="I192" s="90" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="24" customHeight="1">
+      <c r="A193" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="B193" s="91" t="inlineStr">
+        <is>
+          <t>Dev sửa dứt điểm toàn bộ lỗi Critical/High đang mở</t>
+        </is>
+      </c>
+      <c r="C193" s="92" t="n"/>
+      <c r="D193" s="93" t="n"/>
+      <c r="E193" s="106" t="n"/>
+      <c r="F193" s="93" t="n"/>
+      <c r="G193" s="93" t="n"/>
+      <c r="H193" s="92" t="n"/>
+      <c r="I193" s="92" t="n"/>
+    </row>
+    <row r="194" ht="24" customHeight="1">
+      <c r="A194" s="96" t="n">
+        <v>2</v>
+      </c>
+      <c r="B194" s="95" t="inlineStr">
+        <is>
+          <t>QA retest và chuyển trạng thái lỗi sang Verified/Closed</t>
+        </is>
+      </c>
+      <c r="C194" s="92" t="n"/>
+      <c r="D194" s="93" t="n"/>
+      <c r="E194" s="106" t="n"/>
+      <c r="F194" s="93" t="n"/>
+      <c r="G194" s="93" t="n"/>
+      <c r="H194" s="92" t="n"/>
+      <c r="I194" s="92" t="n"/>
+    </row>
+    <row r="195" ht="24" customHeight="1">
+      <c r="A195" s="94" t="n">
+        <v>3</v>
+      </c>
+      <c r="B195" s="91" t="inlineStr">
+        <is>
+          <t>Bổ sung link bằng chứng (ảnh/video) cho các mục còn thiếu</t>
+        </is>
+      </c>
+      <c r="C195" s="92" t="n"/>
+      <c r="D195" s="93" t="n"/>
+      <c r="E195" s="106" t="n"/>
+      <c r="F195" s="93" t="n"/>
+      <c r="G195" s="93" t="n"/>
+      <c r="H195" s="92" t="n"/>
+      <c r="I195" s="92" t="n"/>
+    </row>
+    <row r="196" ht="24" customHeight="1">
+      <c r="A196" s="96" t="n">
+        <v>4</v>
+      </c>
+      <c r="B196" s="95" t="inlineStr">
+        <is>
+          <t>Chốt danh sách DS/YC thuộc phạm vi nghiệm thu giai đoạn này</t>
+        </is>
+      </c>
+      <c r="C196" s="92" t="n"/>
+      <c r="D196" s="93" t="n"/>
+      <c r="E196" s="106" t="n"/>
+      <c r="F196" s="93" t="n"/>
+      <c r="G196" s="93" t="n"/>
+      <c r="H196" s="92" t="n"/>
+      <c r="I196" s="92" t="n"/>
+    </row>
+    <row r="197" ht="24" customHeight="1">
+      <c r="A197" s="94" t="n">
+        <v>5</v>
+      </c>
+      <c r="B197" s="91" t="inlineStr">
+        <is>
+          <t>Chốt ngưỡng tiêu chí nghiệm thu tại mục V với Bên A</t>
+        </is>
+      </c>
+      <c r="C197" s="92" t="n"/>
+      <c r="D197" s="93" t="n"/>
+      <c r="E197" s="106" t="n"/>
+      <c r="F197" s="93" t="n"/>
+      <c r="G197" s="93" t="n"/>
+      <c r="H197" s="92" t="n"/>
+      <c r="I197" s="92" t="n"/>
+    </row>
+    <row r="198" ht="24" customHeight="1">
+      <c r="A198" s="96" t="n">
+        <v>6</v>
+      </c>
+      <c r="B198" s="95" t="inlineStr">
+        <is>
+          <t>Đo và điền kết quả kiểm thử phi chức năng (mục X)</t>
+        </is>
+      </c>
+      <c r="C198" s="92" t="n"/>
+      <c r="D198" s="93" t="n"/>
+      <c r="E198" s="106" t="n"/>
+      <c r="F198" s="93" t="n"/>
+      <c r="G198" s="93" t="n"/>
+      <c r="H198" s="92" t="n"/>
+      <c r="I198" s="92" t="n"/>
+    </row>
+    <row r="199" ht="24" customHeight="1">
+      <c r="A199" s="94" t="n">
+        <v>7</v>
+      </c>
+      <c r="B199" s="91" t="inlineStr">
+        <is>
+          <t>Hoàn tất bàn giao tài liệu và tài khoản (mục XIV)</t>
+        </is>
+      </c>
+      <c r="C199" s="92" t="n"/>
+      <c r="D199" s="93" t="n"/>
+      <c r="E199" s="106" t="n"/>
+      <c r="F199" s="93" t="n"/>
+      <c r="G199" s="93" t="n"/>
+      <c r="H199" s="92" t="n"/>
+      <c r="I199" s="92" t="n"/>
+    </row>
+    <row r="200" ht="24" customHeight="1">
+      <c r="A200" s="96" t="n">
+        <v>8</v>
+      </c>
+      <c r="B200" s="95" t="inlineStr">
+        <is>
+          <t>Người duyệt ký kết luận nghiệm thu (mục XVI, XVIII)</t>
+        </is>
+      </c>
+      <c r="C200" s="92" t="n"/>
+      <c r="D200" s="93" t="n"/>
+      <c r="E200" s="106" t="n"/>
+      <c r="F200" s="93" t="n"/>
+      <c r="G200" s="93" t="n"/>
+      <c r="H200" s="92" t="n"/>
+      <c r="I200" s="92" t="n"/>
+    </row>
+    <row r="201" ht="8" customHeight="1"/>
+    <row r="202" ht="22" customHeight="1">
+      <c r="A202" s="11" t="inlineStr">
+        <is>
+          <t>XVIII. XÁC NHẬN CỦA CÁC BÊN</t>
+        </is>
+      </c>
+      <c r="B202" s="7" t="n"/>
+      <c r="C202" s="7" t="n"/>
+      <c r="D202" s="7" t="n"/>
+      <c r="E202" s="7" t="n"/>
+      <c r="F202" s="7" t="n"/>
+      <c r="G202" s="7" t="n"/>
+      <c r="H202" s="7" t="n"/>
+      <c r="I202" s="7" t="n"/>
+    </row>
+    <row r="203" ht="20" customHeight="1">
+      <c r="A203" s="18" t="inlineStr">
+        <is>
+          <t>Biên bản được lập thành 02 bản có giá trị pháp lý như nhau, mỗi bên giữ 01 bản.</t>
+        </is>
+      </c>
+      <c r="B203" s="5" t="n"/>
+      <c r="C203" s="5" t="n"/>
+      <c r="D203" s="5" t="n"/>
+      <c r="E203" s="5" t="n"/>
+      <c r="F203" s="5" t="n"/>
+      <c r="G203" s="5" t="n"/>
+      <c r="H203" s="5" t="n"/>
+      <c r="I203" s="5" t="n"/>
+    </row>
+    <row r="204" ht="26" customHeight="1">
+      <c r="A204" s="90" t="inlineStr">
+        <is>
+          <t>Vai trò</t>
+        </is>
+      </c>
+      <c r="B204" s="90" t="inlineStr">
+        <is>
+          <t>Họ và tên</t>
+        </is>
+      </c>
+      <c r="C204" s="90" t="inlineStr">
+        <is>
+          <t>Chức vụ</t>
+        </is>
+      </c>
+      <c r="D204" s="90" t="inlineStr">
+        <is>
+          <t>Ý kiến / ghi chú</t>
+        </is>
+      </c>
+      <c r="E204" s="90" t="inlineStr"/>
+      <c r="F204" s="90" t="inlineStr">
+        <is>
+          <t>Ngày ký</t>
+        </is>
+      </c>
+      <c r="G204" s="90" t="inlineStr">
+        <is>
+          <t>Chữ ký</t>
+        </is>
+      </c>
+      <c r="H204" s="90" t="inlineStr"/>
+      <c r="I204" s="90" t="inlineStr"/>
+    </row>
+    <row r="205" ht="56" customHeight="1">
+      <c r="A205" s="113" t="inlineStr">
+        <is>
+          <t>ĐẠI DIỆN BÊN A (Chủ đầu tư)</t>
+        </is>
+      </c>
+      <c r="B205" s="114" t="inlineStr"/>
+      <c r="C205" s="114" t="inlineStr"/>
+      <c r="D205" s="92" t="inlineStr"/>
+      <c r="E205" s="88" t="n"/>
+      <c r="F205" s="115" t="inlineStr"/>
+      <c r="G205" s="116" t="inlineStr"/>
+      <c r="H205" s="63" t="n"/>
+      <c r="I205" s="63" t="n"/>
+    </row>
+    <row r="206" ht="56" customHeight="1">
+      <c r="A206" s="117" t="inlineStr">
+        <is>
+          <t>ĐẠI DIỆN BÊN B (Đơn vị thực hiện)</t>
+        </is>
+      </c>
+      <c r="B206" s="114" t="inlineStr"/>
+      <c r="C206" s="114" t="inlineStr"/>
+      <c r="D206" s="92" t="inlineStr"/>
+      <c r="E206" s="88" t="n"/>
+      <c r="F206" s="115" t="inlineStr"/>
+      <c r="G206" s="116" t="inlineStr"/>
+      <c r="H206" s="63" t="n"/>
+      <c r="I206" s="63" t="n"/>
+    </row>
+    <row r="207" ht="56" customHeight="1">
+      <c r="A207" s="113" t="inlineStr">
+        <is>
+          <t>QUẢN LÝ DỰ ÁN</t>
+        </is>
+      </c>
+      <c r="B207" s="114" t="inlineStr"/>
+      <c r="C207" s="114" t="inlineStr"/>
+      <c r="D207" s="92" t="inlineStr"/>
+      <c r="E207" s="88" t="n"/>
+      <c r="F207" s="115" t="inlineStr"/>
+      <c r="G207" s="116" t="inlineStr"/>
+      <c r="H207" s="63" t="n"/>
+      <c r="I207" s="63" t="n"/>
+    </row>
+    <row r="208" ht="56" customHeight="1">
+      <c r="A208" s="117" t="inlineStr">
+        <is>
+          <t>QA / TESTER</t>
+        </is>
+      </c>
+      <c r="B208" s="114" t="inlineStr"/>
+      <c r="C208" s="114" t="inlineStr"/>
+      <c r="D208" s="92" t="inlineStr"/>
+      <c r="E208" s="88" t="n"/>
+      <c r="F208" s="115" t="inlineStr"/>
+      <c r="G208" s="116" t="inlineStr"/>
+      <c r="H208" s="63" t="n"/>
+      <c r="I208" s="63" t="n"/>
+    </row>
+    <row r="209" ht="56" customHeight="1">
+      <c r="A209" s="113" t="inlineStr">
+        <is>
+          <t>NGƯỜI DUYỆT NGHIỆM THU</t>
+        </is>
+      </c>
+      <c r="B209" s="114" t="inlineStr"/>
+      <c r="C209" s="114" t="inlineStr"/>
+      <c r="D209" s="92" t="inlineStr"/>
+      <c r="E209" s="88" t="n"/>
+      <c r="F209" s="115" t="inlineStr"/>
+      <c r="G209" s="116" t="inlineStr"/>
+      <c r="H209" s="63" t="n"/>
+      <c r="I209" s="63" t="n"/>
+    </row>
+    <row r="210" ht="8" customHeight="1"/>
+    <row r="211" ht="22" customHeight="1">
+      <c r="A211" s="11" t="inlineStr">
+        <is>
+          <t>PHỤ LỤC KÈM THEO</t>
+        </is>
+      </c>
+      <c r="B211" s="7" t="n"/>
+      <c r="C211" s="7" t="n"/>
+      <c r="D211" s="7" t="n"/>
+      <c r="E211" s="7" t="n"/>
+      <c r="F211" s="7" t="n"/>
+      <c r="G211" s="7" t="n"/>
+      <c r="H211" s="7" t="n"/>
+      <c r="I211" s="7" t="n"/>
+    </row>
+    <row r="212" ht="32" customHeight="1">
+      <c r="A212" s="90" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="B212" s="90" t="inlineStr">
+        <is>
+          <t>Tên phụ lục</t>
+        </is>
+      </c>
+      <c r="C212" s="90" t="inlineStr">
+        <is>
+          <t>Nguồn / đường dẫn</t>
+        </is>
+      </c>
+      <c r="D212" s="90" t="inlineStr">
+        <is>
+          <t>Đính kèm?</t>
+        </is>
+      </c>
+      <c r="E212" s="90" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+      <c r="F212" s="90" t="inlineStr"/>
+      <c r="G212" s="90" t="inlineStr"/>
+      <c r="H212" s="90" t="inlineStr"/>
+      <c r="I212" s="90" t="inlineStr"/>
+    </row>
+    <row r="213" ht="24" customHeight="1">
+      <c r="A213" s="91" t="inlineStr">
+        <is>
+          <t>PL-01</t>
+        </is>
+      </c>
+      <c r="B213" s="91" t="inlineStr">
+        <is>
+          <t>Danh sách trang (DS) và trạng thái kiểm thử</t>
+        </is>
+      </c>
+      <c r="C213" s="91" t="inlineStr">
+        <is>
+          <t>File QA — sheet 02_UI_UX</t>
+        </is>
+      </c>
+      <c r="D213" s="93" t="n"/>
+      <c r="E213" s="92" t="n"/>
+      <c r="F213" s="94" t="n"/>
+      <c r="G213" s="94" t="n"/>
+      <c r="H213" s="94" t="n"/>
+      <c r="I213" s="94" t="n"/>
+    </row>
+    <row r="214" ht="24" customHeight="1">
+      <c r="A214" s="95" t="inlineStr">
+        <is>
+          <t>PL-02</t>
+        </is>
+      </c>
+      <c r="B214" s="95" t="inlineStr">
+        <is>
+          <t>Danh sách tính năng (YC) và trạng thái kiểm thử</t>
+        </is>
+      </c>
+      <c r="C214" s="95" t="inlineStr">
+        <is>
+          <t>File QA — sheet 03_Tính_năng</t>
+        </is>
+      </c>
+      <c r="D214" s="93" t="n"/>
+      <c r="E214" s="92" t="n"/>
+      <c r="F214" s="96" t="n"/>
+      <c r="G214" s="96" t="n"/>
+      <c r="H214" s="96" t="n"/>
+      <c r="I214" s="96" t="n"/>
+    </row>
+    <row r="215" ht="24" customHeight="1">
+      <c r="A215" s="91" t="inlineStr">
+        <is>
+          <t>PL-03</t>
+        </is>
+      </c>
+      <c r="B215" s="91" t="inlineStr">
+        <is>
+          <t>Danh sách lỗi đầy đủ kèm bằng chứng</t>
+        </is>
+      </c>
+      <c r="C215" s="91" t="inlineStr">
+        <is>
+          <t>File QA — sheet 05_Lỗi_Tester</t>
+        </is>
+      </c>
+      <c r="D215" s="93" t="n"/>
+      <c r="E215" s="92" t="n"/>
+      <c r="F215" s="94" t="n"/>
+      <c r="G215" s="94" t="n"/>
+      <c r="H215" s="94" t="n"/>
+      <c r="I215" s="94" t="n"/>
+    </row>
+    <row r="216" ht="24" customHeight="1">
+      <c r="A216" s="95" t="inlineStr">
+        <is>
+          <t>PL-04</t>
+        </is>
+      </c>
+      <c r="B216" s="95" t="inlineStr">
+        <is>
+          <t>Ma trận truy vết yêu cầu — Test Case (RTM)</t>
+        </is>
+      </c>
+      <c r="C216" s="95" t="inlineStr">
+        <is>
+          <t>File QA — sheet 06_RTM_Dev_Test</t>
+        </is>
+      </c>
+      <c r="D216" s="93" t="n"/>
+      <c r="E216" s="92" t="n"/>
+      <c r="F216" s="96" t="n"/>
+      <c r="G216" s="96" t="n"/>
+      <c r="H216" s="96" t="n"/>
+      <c r="I216" s="96" t="n"/>
+    </row>
+    <row r="217" ht="24" customHeight="1">
+      <c r="A217" s="91" t="inlineStr">
+        <is>
+          <t>PL-05</t>
+        </is>
+      </c>
+      <c r="B217" s="91" t="inlineStr">
+        <is>
+          <t>Nhật ký công việc kiểm thử theo ngày</t>
+        </is>
+      </c>
+      <c r="C217" s="91" t="inlineStr">
+        <is>
+          <t>File QA — sheet 01_Cong_viec_ngay</t>
+        </is>
+      </c>
+      <c r="D217" s="93" t="n"/>
+      <c r="E217" s="92" t="n"/>
+      <c r="F217" s="94" t="n"/>
+      <c r="G217" s="94" t="n"/>
+      <c r="H217" s="94" t="n"/>
+      <c r="I217" s="94" t="n"/>
+    </row>
+    <row r="218" ht="24" customHeight="1">
+      <c r="A218" s="95" t="inlineStr">
+        <is>
+          <t>PL-06</t>
+        </is>
+      </c>
+      <c r="B218" s="95" t="inlineStr">
+        <is>
+          <t>Báo cáo tiến độ theo tháng / tuần</t>
+        </is>
+      </c>
+      <c r="C218" s="95" t="inlineStr">
+        <is>
+          <t>File này — sheet 01, 02</t>
+        </is>
+      </c>
+      <c r="D218" s="93" t="n"/>
+      <c r="E218" s="92" t="n"/>
+      <c r="F218" s="96" t="n"/>
+      <c r="G218" s="96" t="n"/>
+      <c r="H218" s="96" t="n"/>
+      <c r="I218" s="96" t="n"/>
+    </row>
+    <row r="219" ht="24" customHeight="1">
+      <c r="A219" s="91" t="inlineStr">
+        <is>
+          <t>PL-07</t>
+        </is>
+      </c>
+      <c r="B219" s="91" t="inlineStr">
+        <is>
+          <t>Kết quả đo hiệu năng và bảo mật</t>
+        </is>
+      </c>
+      <c r="C219" s="91" t="inlineStr">
+        <is>
+          <t>Cần bổ sung</t>
+        </is>
+      </c>
+      <c r="D219" s="93" t="n"/>
+      <c r="E219" s="92" t="n"/>
+      <c r="F219" s="94" t="n"/>
+      <c r="G219" s="94" t="n"/>
+      <c r="H219" s="94" t="n"/>
+      <c r="I219" s="94" t="n"/>
+    </row>
+    <row r="220" ht="24" customHeight="1">
+      <c r="A220" s="95" t="inlineStr">
+        <is>
+          <t>PL-08</t>
+        </is>
+      </c>
+      <c r="B220" s="95" t="inlineStr">
+        <is>
+          <t>Biên bản họp chốt phạm vi và tiêu chí</t>
+        </is>
+      </c>
+      <c r="C220" s="95" t="inlineStr">
+        <is>
+          <t>Cần bổ sung</t>
+        </is>
+      </c>
+      <c r="D220" s="93" t="n"/>
+      <c r="E220" s="92" t="n"/>
+      <c r="F220" s="96" t="n"/>
+      <c r="G220" s="96" t="n"/>
+      <c r="H220" s="96" t="n"/>
+      <c r="I220" s="96" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="65">
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="H181:I181"/>
+    <mergeCell ref="A149:I149"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="D208:E208"/>
+    <mergeCell ref="A158:I158"/>
+    <mergeCell ref="E181:F181"/>
+    <mergeCell ref="G205:I205"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A86:I86"/>
+    <mergeCell ref="A179:I179"/>
+    <mergeCell ref="B180:C180"/>
+    <mergeCell ref="E180:F180"/>
+    <mergeCell ref="H180:I180"/>
+    <mergeCell ref="A113:I113"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="G207:I207"/>
+    <mergeCell ref="A203:I203"/>
+    <mergeCell ref="G206:I206"/>
+    <mergeCell ref="B181:C181"/>
+    <mergeCell ref="E182:F182"/>
+    <mergeCell ref="A184:I184"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="F188:G188"/>
+    <mergeCell ref="B182:C182"/>
+    <mergeCell ref="H182:I182"/>
+    <mergeCell ref="A112:I112"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="D206:E206"/>
+    <mergeCell ref="D209:E209"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="D205:E205"/>
+    <mergeCell ref="A202:I202"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A211:I211"/>
+    <mergeCell ref="B188:D188"/>
+    <mergeCell ref="B186:I186"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="G208:I208"/>
+    <mergeCell ref="A148:I148"/>
+    <mergeCell ref="A166:I166"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A98:I98"/>
+    <mergeCell ref="B187:I187"/>
+    <mergeCell ref="A191:I191"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="D207:E207"/>
+    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="B189:I189"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="G209:I209"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B188 H92 H93 H94 H95 H96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Đạt,Đạt có điều kiện,Không đạt,Chưa nghiệm thu"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E55 E56 E57 E58 E59 G100 G101 G102 G103 G104 G105 G106 G107 G108 G109 G110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Đạt,Chưa đạt,Không áp dụng,Chưa đo"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E168 E169 E170 E171 E172 E173 E174 E175 E176 E177" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Đã bàn giao,Chưa bàn giao,Không áp dụng"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5100,258 +9339,258 @@
       <c r="N3" s="7" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="90" t="inlineStr">
+      <c r="A4" s="118" t="inlineStr">
         <is>
           <t>Tháng</t>
         </is>
       </c>
-      <c r="B4" s="104" t="inlineStr">
+      <c r="B4" s="119" t="inlineStr">
         <is>
           <t>Trang hoàn thành</t>
         </is>
       </c>
-      <c r="C4" s="104" t="inlineStr">
+      <c r="C4" s="119" t="inlineStr">
         <is>
           <t>Tính năng hoàn thành</t>
         </is>
       </c>
-      <c r="D4" s="104" t="inlineStr">
+      <c r="D4" s="119" t="inlineStr">
         <is>
           <t>Công việc HT trong kỳ</t>
         </is>
       </c>
-      <c r="E4" s="104" t="inlineStr">
+      <c r="E4" s="119" t="inlineStr">
         <is>
           <t>Lỗi phát hiện trong kỳ</t>
         </is>
       </c>
-      <c r="F4" s="104" t="inlineStr">
+      <c r="F4" s="119" t="inlineStr">
         <is>
           <t>Lỗi đã xử lý (lũy kế)</t>
         </is>
       </c>
-      <c r="G4" s="104" t="inlineStr">
+      <c r="G4" s="119" t="inlineStr">
         <is>
           <t>Số Trang đã xử lý</t>
         </is>
       </c>
-      <c r="H4" s="104" t="inlineStr">
+      <c r="H4" s="119" t="inlineStr">
         <is>
           <t>Số Tính năng đã xử lý</t>
         </is>
       </c>
-      <c r="I4" s="104" t="inlineStr">
+      <c r="I4" s="119" t="inlineStr">
         <is>
           <t>DB Doanh nghiệp</t>
         </is>
       </c>
-      <c r="J4" s="104" t="inlineStr">
+      <c r="J4" s="119" t="inlineStr">
         <is>
           <t>DB HR</t>
         </is>
       </c>
-      <c r="K4" s="104" t="inlineStr">
+      <c r="K4" s="119" t="inlineStr">
         <is>
           <t>DB Ứng viên</t>
         </is>
       </c>
-      <c r="L4" s="104" t="inlineStr">
+      <c r="L4" s="119" t="inlineStr">
         <is>
           <t>Tin tuyển dụng</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="105" t="n">
+      <c r="A5" s="120" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="106" t="n"/>
-      <c r="C5" s="106" t="n"/>
-      <c r="D5" s="106" t="n"/>
-      <c r="E5" s="106" t="n"/>
-      <c r="F5" s="106" t="n"/>
-      <c r="G5" s="106" t="n"/>
-      <c r="H5" s="106" t="n"/>
-      <c r="I5" s="106" t="n"/>
-      <c r="J5" s="106" t="n"/>
-      <c r="K5" s="106" t="n"/>
-      <c r="L5" s="106" t="n"/>
+      <c r="B5" s="121" t="n"/>
+      <c r="C5" s="121" t="n"/>
+      <c r="D5" s="121" t="n"/>
+      <c r="E5" s="121" t="n"/>
+      <c r="F5" s="121" t="n"/>
+      <c r="G5" s="121" t="n"/>
+      <c r="H5" s="121" t="n"/>
+      <c r="I5" s="121" t="n"/>
+      <c r="J5" s="121" t="n"/>
+      <c r="K5" s="121" t="n"/>
+      <c r="L5" s="121" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="105" t="n">
+      <c r="A6" s="120" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="106" t="n"/>
-      <c r="C6" s="106" t="n"/>
-      <c r="D6" s="106" t="n"/>
-      <c r="E6" s="106" t="n"/>
-      <c r="F6" s="106" t="n"/>
-      <c r="G6" s="106" t="n"/>
-      <c r="H6" s="106" t="n"/>
-      <c r="I6" s="106" t="n"/>
-      <c r="J6" s="106" t="n"/>
-      <c r="K6" s="106" t="n"/>
-      <c r="L6" s="106" t="n"/>
+      <c r="B6" s="121" t="n"/>
+      <c r="C6" s="121" t="n"/>
+      <c r="D6" s="121" t="n"/>
+      <c r="E6" s="121" t="n"/>
+      <c r="F6" s="121" t="n"/>
+      <c r="G6" s="121" t="n"/>
+      <c r="H6" s="121" t="n"/>
+      <c r="I6" s="121" t="n"/>
+      <c r="J6" s="121" t="n"/>
+      <c r="K6" s="121" t="n"/>
+      <c r="L6" s="121" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="105" t="n">
+      <c r="A7" s="120" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="106" t="n"/>
-      <c r="C7" s="106" t="n"/>
-      <c r="D7" s="106" t="n"/>
-      <c r="E7" s="106" t="n"/>
-      <c r="F7" s="106" t="n"/>
-      <c r="G7" s="106" t="n"/>
-      <c r="H7" s="106" t="n"/>
-      <c r="I7" s="106" t="n"/>
-      <c r="J7" s="106" t="n"/>
-      <c r="K7" s="106" t="n"/>
-      <c r="L7" s="106" t="n"/>
+      <c r="B7" s="121" t="n"/>
+      <c r="C7" s="121" t="n"/>
+      <c r="D7" s="121" t="n"/>
+      <c r="E7" s="121" t="n"/>
+      <c r="F7" s="121" t="n"/>
+      <c r="G7" s="121" t="n"/>
+      <c r="H7" s="121" t="n"/>
+      <c r="I7" s="121" t="n"/>
+      <c r="J7" s="121" t="n"/>
+      <c r="K7" s="121" t="n"/>
+      <c r="L7" s="121" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="105" t="n">
+      <c r="A8" s="120" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="106" t="n"/>
-      <c r="C8" s="106" t="n"/>
-      <c r="D8" s="106" t="n"/>
-      <c r="E8" s="106" t="n"/>
-      <c r="F8" s="106" t="n"/>
-      <c r="G8" s="106" t="n"/>
-      <c r="H8" s="106" t="n"/>
-      <c r="I8" s="106" t="n"/>
-      <c r="J8" s="106" t="n"/>
-      <c r="K8" s="106" t="n"/>
-      <c r="L8" s="106" t="n"/>
+      <c r="B8" s="121" t="n"/>
+      <c r="C8" s="121" t="n"/>
+      <c r="D8" s="121" t="n"/>
+      <c r="E8" s="121" t="n"/>
+      <c r="F8" s="121" t="n"/>
+      <c r="G8" s="121" t="n"/>
+      <c r="H8" s="121" t="n"/>
+      <c r="I8" s="121" t="n"/>
+      <c r="J8" s="121" t="n"/>
+      <c r="K8" s="121" t="n"/>
+      <c r="L8" s="121" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="105" t="n">
+      <c r="A9" s="120" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="106" t="n"/>
-      <c r="C9" s="106" t="n"/>
-      <c r="D9" s="106" t="n"/>
-      <c r="E9" s="106" t="n"/>
-      <c r="F9" s="106" t="n"/>
-      <c r="G9" s="106" t="n"/>
-      <c r="H9" s="106" t="n"/>
-      <c r="I9" s="106" t="n"/>
-      <c r="J9" s="106" t="n"/>
-      <c r="K9" s="106" t="n"/>
-      <c r="L9" s="106" t="n"/>
+      <c r="B9" s="121" t="n"/>
+      <c r="C9" s="121" t="n"/>
+      <c r="D9" s="121" t="n"/>
+      <c r="E9" s="121" t="n"/>
+      <c r="F9" s="121" t="n"/>
+      <c r="G9" s="121" t="n"/>
+      <c r="H9" s="121" t="n"/>
+      <c r="I9" s="121" t="n"/>
+      <c r="J9" s="121" t="n"/>
+      <c r="K9" s="121" t="n"/>
+      <c r="L9" s="121" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="105" t="n">
+      <c r="A10" s="120" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="106" t="n"/>
-      <c r="C10" s="106" t="n"/>
-      <c r="D10" s="106" t="n"/>
-      <c r="E10" s="106" t="n"/>
-      <c r="F10" s="106" t="n"/>
-      <c r="G10" s="106" t="n"/>
-      <c r="H10" s="106" t="n"/>
-      <c r="I10" s="106" t="n"/>
-      <c r="J10" s="106" t="n"/>
-      <c r="K10" s="106" t="n"/>
-      <c r="L10" s="106" t="n"/>
+      <c r="B10" s="121" t="n"/>
+      <c r="C10" s="121" t="n"/>
+      <c r="D10" s="121" t="n"/>
+      <c r="E10" s="121" t="n"/>
+      <c r="F10" s="121" t="n"/>
+      <c r="G10" s="121" t="n"/>
+      <c r="H10" s="121" t="n"/>
+      <c r="I10" s="121" t="n"/>
+      <c r="J10" s="121" t="n"/>
+      <c r="K10" s="121" t="n"/>
+      <c r="L10" s="121" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="105" t="n">
+      <c r="A11" s="120" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="106" t="n"/>
-      <c r="C11" s="106" t="n"/>
-      <c r="D11" s="106" t="n"/>
-      <c r="E11" s="106" t="n"/>
-      <c r="F11" s="106" t="n"/>
-      <c r="G11" s="106" t="n"/>
-      <c r="H11" s="106" t="n"/>
-      <c r="I11" s="106" t="n"/>
-      <c r="J11" s="106" t="n"/>
-      <c r="K11" s="106" t="n"/>
-      <c r="L11" s="106" t="n"/>
+      <c r="B11" s="121" t="n"/>
+      <c r="C11" s="121" t="n"/>
+      <c r="D11" s="121" t="n"/>
+      <c r="E11" s="121" t="n"/>
+      <c r="F11" s="121" t="n"/>
+      <c r="G11" s="121" t="n"/>
+      <c r="H11" s="121" t="n"/>
+      <c r="I11" s="121" t="n"/>
+      <c r="J11" s="121" t="n"/>
+      <c r="K11" s="121" t="n"/>
+      <c r="L11" s="121" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="105" t="n">
+      <c r="A12" s="120" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="106" t="n"/>
-      <c r="C12" s="106" t="n"/>
-      <c r="D12" s="106" t="n"/>
-      <c r="E12" s="106" t="n"/>
-      <c r="F12" s="106" t="n"/>
-      <c r="G12" s="106" t="n"/>
-      <c r="H12" s="106" t="n"/>
-      <c r="I12" s="106" t="n"/>
-      <c r="J12" s="106" t="n"/>
-      <c r="K12" s="106" t="n"/>
-      <c r="L12" s="106" t="n"/>
+      <c r="B12" s="121" t="n"/>
+      <c r="C12" s="121" t="n"/>
+      <c r="D12" s="121" t="n"/>
+      <c r="E12" s="121" t="n"/>
+      <c r="F12" s="121" t="n"/>
+      <c r="G12" s="121" t="n"/>
+      <c r="H12" s="121" t="n"/>
+      <c r="I12" s="121" t="n"/>
+      <c r="J12" s="121" t="n"/>
+      <c r="K12" s="121" t="n"/>
+      <c r="L12" s="121" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="105" t="n">
+      <c r="A13" s="120" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="106" t="n"/>
-      <c r="C13" s="106" t="n"/>
-      <c r="D13" s="106" t="n"/>
-      <c r="E13" s="106" t="n"/>
-      <c r="F13" s="106" t="n"/>
-      <c r="G13" s="106" t="n"/>
-      <c r="H13" s="106" t="n"/>
-      <c r="I13" s="106" t="n"/>
-      <c r="J13" s="106" t="n"/>
-      <c r="K13" s="106" t="n"/>
-      <c r="L13" s="106" t="n"/>
+      <c r="B13" s="121" t="n"/>
+      <c r="C13" s="121" t="n"/>
+      <c r="D13" s="121" t="n"/>
+      <c r="E13" s="121" t="n"/>
+      <c r="F13" s="121" t="n"/>
+      <c r="G13" s="121" t="n"/>
+      <c r="H13" s="121" t="n"/>
+      <c r="I13" s="121" t="n"/>
+      <c r="J13" s="121" t="n"/>
+      <c r="K13" s="121" t="n"/>
+      <c r="L13" s="121" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="105" t="n">
+      <c r="A14" s="120" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="106" t="n"/>
-      <c r="C14" s="106" t="n"/>
-      <c r="D14" s="106" t="n"/>
-      <c r="E14" s="106" t="n"/>
-      <c r="F14" s="106" t="n"/>
-      <c r="G14" s="106" t="n"/>
-      <c r="H14" s="106" t="n"/>
-      <c r="I14" s="106" t="n"/>
-      <c r="J14" s="106" t="n"/>
-      <c r="K14" s="106" t="n"/>
-      <c r="L14" s="106" t="n"/>
+      <c r="B14" s="121" t="n"/>
+      <c r="C14" s="121" t="n"/>
+      <c r="D14" s="121" t="n"/>
+      <c r="E14" s="121" t="n"/>
+      <c r="F14" s="121" t="n"/>
+      <c r="G14" s="121" t="n"/>
+      <c r="H14" s="121" t="n"/>
+      <c r="I14" s="121" t="n"/>
+      <c r="J14" s="121" t="n"/>
+      <c r="K14" s="121" t="n"/>
+      <c r="L14" s="121" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="105" t="n">
+      <c r="A15" s="120" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="106" t="n"/>
-      <c r="C15" s="106" t="n"/>
-      <c r="D15" s="106" t="n"/>
-      <c r="E15" s="106" t="n"/>
-      <c r="F15" s="106" t="n"/>
-      <c r="G15" s="106" t="n"/>
-      <c r="H15" s="106" t="n"/>
-      <c r="I15" s="106" t="n"/>
-      <c r="J15" s="106" t="n"/>
-      <c r="K15" s="106" t="n"/>
-      <c r="L15" s="106" t="n"/>
+      <c r="B15" s="121" t="n"/>
+      <c r="C15" s="121" t="n"/>
+      <c r="D15" s="121" t="n"/>
+      <c r="E15" s="121" t="n"/>
+      <c r="F15" s="121" t="n"/>
+      <c r="G15" s="121" t="n"/>
+      <c r="H15" s="121" t="n"/>
+      <c r="I15" s="121" t="n"/>
+      <c r="J15" s="121" t="n"/>
+      <c r="K15" s="121" t="n"/>
+      <c r="L15" s="121" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="105" t="n">
+      <c r="A16" s="120" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="106" t="n"/>
-      <c r="C16" s="106" t="n"/>
-      <c r="D16" s="106" t="n"/>
-      <c r="E16" s="106" t="n"/>
-      <c r="F16" s="106" t="n"/>
-      <c r="G16" s="106" t="n"/>
-      <c r="H16" s="106" t="n"/>
-      <c r="I16" s="106" t="n"/>
-      <c r="J16" s="106" t="n"/>
-      <c r="K16" s="106" t="n"/>
-      <c r="L16" s="106" t="n"/>
+      <c r="B16" s="121" t="n"/>
+      <c r="C16" s="121" t="n"/>
+      <c r="D16" s="121" t="n"/>
+      <c r="E16" s="121" t="n"/>
+      <c r="F16" s="121" t="n"/>
+      <c r="G16" s="121" t="n"/>
+      <c r="H16" s="121" t="n"/>
+      <c r="I16" s="121" t="n"/>
+      <c r="J16" s="121" t="n"/>
+      <c r="K16" s="121" t="n"/>
+      <c r="L16" s="121" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
@@ -5374,1456 +9613,1456 @@
       <c r="N18" s="7" t="n"/>
     </row>
     <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="90" t="inlineStr">
+      <c r="A19" s="118" t="inlineStr">
         <is>
           <t>Tháng</t>
         </is>
       </c>
-      <c r="B19" s="90" t="inlineStr">
+      <c r="B19" s="118" t="inlineStr">
         <is>
           <t>Tuần</t>
         </is>
       </c>
-      <c r="C19" s="107" t="inlineStr">
+      <c r="C19" s="122" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="D19" s="104" t="inlineStr">
+      <c r="D19" s="119" t="inlineStr">
         <is>
           <t>Trang hoàn thành</t>
         </is>
       </c>
-      <c r="E19" s="104" t="inlineStr">
+      <c r="E19" s="119" t="inlineStr">
         <is>
           <t>Tính năng hoàn thành</t>
         </is>
       </c>
-      <c r="F19" s="104" t="inlineStr">
+      <c r="F19" s="119" t="inlineStr">
         <is>
           <t>Công việc HT trong kỳ</t>
         </is>
       </c>
-      <c r="G19" s="104" t="inlineStr">
+      <c r="G19" s="119" t="inlineStr">
         <is>
           <t>Lỗi phát hiện trong kỳ</t>
         </is>
       </c>
-      <c r="H19" s="104" t="inlineStr">
+      <c r="H19" s="119" t="inlineStr">
         <is>
           <t>Lỗi đã xử lý (lũy kế)</t>
         </is>
       </c>
-      <c r="I19" s="104" t="inlineStr">
+      <c r="I19" s="119" t="inlineStr">
         <is>
           <t>Số Trang đã xử lý</t>
         </is>
       </c>
-      <c r="J19" s="104" t="inlineStr">
+      <c r="J19" s="119" t="inlineStr">
         <is>
           <t>Số Tính năng đã xử lý</t>
         </is>
       </c>
-      <c r="K19" s="104" t="inlineStr">
+      <c r="K19" s="119" t="inlineStr">
         <is>
           <t>DB Doanh nghiệp</t>
         </is>
       </c>
-      <c r="L19" s="104" t="inlineStr">
+      <c r="L19" s="119" t="inlineStr">
         <is>
           <t>DB HR</t>
         </is>
       </c>
-      <c r="M19" s="104" t="inlineStr">
+      <c r="M19" s="119" t="inlineStr">
         <is>
           <t>DB Ứng viên</t>
         </is>
       </c>
-      <c r="N19" s="104" t="inlineStr">
+      <c r="N19" s="119" t="inlineStr">
         <is>
           <t>Tin tuyển dụng</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="108" t="n">
+      <c r="A20" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="108" t="n">
+      <c r="B20" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="109">
+      <c r="C20" s="124">
         <f>A20*10+B20</f>
         <v/>
       </c>
-      <c r="D20" s="106" t="n"/>
-      <c r="E20" s="106" t="n"/>
-      <c r="F20" s="106" t="n"/>
-      <c r="G20" s="106" t="n"/>
-      <c r="H20" s="106" t="n"/>
-      <c r="I20" s="106" t="n"/>
-      <c r="J20" s="106" t="n"/>
-      <c r="K20" s="106" t="n"/>
-      <c r="L20" s="106" t="n"/>
-      <c r="M20" s="106" t="n"/>
-      <c r="N20" s="106" t="n"/>
+      <c r="D20" s="121" t="n"/>
+      <c r="E20" s="121" t="n"/>
+      <c r="F20" s="121" t="n"/>
+      <c r="G20" s="121" t="n"/>
+      <c r="H20" s="121" t="n"/>
+      <c r="I20" s="121" t="n"/>
+      <c r="J20" s="121" t="n"/>
+      <c r="K20" s="121" t="n"/>
+      <c r="L20" s="121" t="n"/>
+      <c r="M20" s="121" t="n"/>
+      <c r="N20" s="121" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="108" t="n">
+      <c r="A21" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="108" t="n">
+      <c r="B21" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="109">
+      <c r="C21" s="124">
         <f>A21*10+B21</f>
         <v/>
       </c>
-      <c r="D21" s="106" t="n"/>
-      <c r="E21" s="106" t="n"/>
-      <c r="F21" s="106" t="n"/>
-      <c r="G21" s="106" t="n"/>
-      <c r="H21" s="106" t="n"/>
-      <c r="I21" s="106" t="n"/>
-      <c r="J21" s="106" t="n"/>
-      <c r="K21" s="106" t="n"/>
-      <c r="L21" s="106" t="n"/>
-      <c r="M21" s="106" t="n"/>
-      <c r="N21" s="106" t="n"/>
+      <c r="D21" s="121" t="n"/>
+      <c r="E21" s="121" t="n"/>
+      <c r="F21" s="121" t="n"/>
+      <c r="G21" s="121" t="n"/>
+      <c r="H21" s="121" t="n"/>
+      <c r="I21" s="121" t="n"/>
+      <c r="J21" s="121" t="n"/>
+      <c r="K21" s="121" t="n"/>
+      <c r="L21" s="121" t="n"/>
+      <c r="M21" s="121" t="n"/>
+      <c r="N21" s="121" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="108" t="n">
+      <c r="A22" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="108" t="n">
+      <c r="B22" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="C22" s="109">
+      <c r="C22" s="124">
         <f>A22*10+B22</f>
         <v/>
       </c>
-      <c r="D22" s="106" t="n"/>
-      <c r="E22" s="106" t="n"/>
-      <c r="F22" s="106" t="n"/>
-      <c r="G22" s="106" t="n"/>
-      <c r="H22" s="106" t="n"/>
-      <c r="I22" s="106" t="n"/>
-      <c r="J22" s="106" t="n"/>
-      <c r="K22" s="106" t="n"/>
-      <c r="L22" s="106" t="n"/>
-      <c r="M22" s="106" t="n"/>
-      <c r="N22" s="106" t="n"/>
+      <c r="D22" s="121" t="n"/>
+      <c r="E22" s="121" t="n"/>
+      <c r="F22" s="121" t="n"/>
+      <c r="G22" s="121" t="n"/>
+      <c r="H22" s="121" t="n"/>
+      <c r="I22" s="121" t="n"/>
+      <c r="J22" s="121" t="n"/>
+      <c r="K22" s="121" t="n"/>
+      <c r="L22" s="121" t="n"/>
+      <c r="M22" s="121" t="n"/>
+      <c r="N22" s="121" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="108" t="n">
+      <c r="A23" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="108" t="n">
+      <c r="B23" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="C23" s="109">
+      <c r="C23" s="124">
         <f>A23*10+B23</f>
         <v/>
       </c>
-      <c r="D23" s="106" t="n"/>
-      <c r="E23" s="106" t="n"/>
-      <c r="F23" s="106" t="n"/>
-      <c r="G23" s="106" t="n"/>
-      <c r="H23" s="106" t="n"/>
-      <c r="I23" s="106" t="n"/>
-      <c r="J23" s="106" t="n"/>
-      <c r="K23" s="106" t="n"/>
-      <c r="L23" s="106" t="n"/>
-      <c r="M23" s="106" t="n"/>
-      <c r="N23" s="106" t="n"/>
+      <c r="D23" s="121" t="n"/>
+      <c r="E23" s="121" t="n"/>
+      <c r="F23" s="121" t="n"/>
+      <c r="G23" s="121" t="n"/>
+      <c r="H23" s="121" t="n"/>
+      <c r="I23" s="121" t="n"/>
+      <c r="J23" s="121" t="n"/>
+      <c r="K23" s="121" t="n"/>
+      <c r="L23" s="121" t="n"/>
+      <c r="M23" s="121" t="n"/>
+      <c r="N23" s="121" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="108" t="n">
+      <c r="A24" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="108" t="n">
+      <c r="B24" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="C24" s="109">
+      <c r="C24" s="124">
         <f>A24*10+B24</f>
         <v/>
       </c>
-      <c r="D24" s="106" t="n"/>
-      <c r="E24" s="106" t="n"/>
-      <c r="F24" s="106" t="n"/>
-      <c r="G24" s="106" t="n"/>
-      <c r="H24" s="106" t="n"/>
-      <c r="I24" s="106" t="n"/>
-      <c r="J24" s="106" t="n"/>
-      <c r="K24" s="106" t="n"/>
-      <c r="L24" s="106" t="n"/>
-      <c r="M24" s="106" t="n"/>
-      <c r="N24" s="106" t="n"/>
+      <c r="D24" s="121" t="n"/>
+      <c r="E24" s="121" t="n"/>
+      <c r="F24" s="121" t="n"/>
+      <c r="G24" s="121" t="n"/>
+      <c r="H24" s="121" t="n"/>
+      <c r="I24" s="121" t="n"/>
+      <c r="J24" s="121" t="n"/>
+      <c r="K24" s="121" t="n"/>
+      <c r="L24" s="121" t="n"/>
+      <c r="M24" s="121" t="n"/>
+      <c r="N24" s="121" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="108" t="n">
+      <c r="A25" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="108" t="n">
+      <c r="B25" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="109">
+      <c r="C25" s="124">
         <f>A25*10+B25</f>
         <v/>
       </c>
-      <c r="D25" s="106" t="n"/>
-      <c r="E25" s="106" t="n"/>
-      <c r="F25" s="106" t="n"/>
-      <c r="G25" s="106" t="n"/>
-      <c r="H25" s="106" t="n"/>
-      <c r="I25" s="106" t="n"/>
-      <c r="J25" s="106" t="n"/>
-      <c r="K25" s="106" t="n"/>
-      <c r="L25" s="106" t="n"/>
-      <c r="M25" s="106" t="n"/>
-      <c r="N25" s="106" t="n"/>
+      <c r="D25" s="121" t="n"/>
+      <c r="E25" s="121" t="n"/>
+      <c r="F25" s="121" t="n"/>
+      <c r="G25" s="121" t="n"/>
+      <c r="H25" s="121" t="n"/>
+      <c r="I25" s="121" t="n"/>
+      <c r="J25" s="121" t="n"/>
+      <c r="K25" s="121" t="n"/>
+      <c r="L25" s="121" t="n"/>
+      <c r="M25" s="121" t="n"/>
+      <c r="N25" s="121" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="108" t="n">
+      <c r="A26" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="108" t="n">
+      <c r="B26" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="C26" s="109">
+      <c r="C26" s="124">
         <f>A26*10+B26</f>
         <v/>
       </c>
-      <c r="D26" s="106" t="n"/>
-      <c r="E26" s="106" t="n"/>
-      <c r="F26" s="106" t="n"/>
-      <c r="G26" s="106" t="n"/>
-      <c r="H26" s="106" t="n"/>
-      <c r="I26" s="106" t="n"/>
-      <c r="J26" s="106" t="n"/>
-      <c r="K26" s="106" t="n"/>
-      <c r="L26" s="106" t="n"/>
-      <c r="M26" s="106" t="n"/>
-      <c r="N26" s="106" t="n"/>
+      <c r="D26" s="121" t="n"/>
+      <c r="E26" s="121" t="n"/>
+      <c r="F26" s="121" t="n"/>
+      <c r="G26" s="121" t="n"/>
+      <c r="H26" s="121" t="n"/>
+      <c r="I26" s="121" t="n"/>
+      <c r="J26" s="121" t="n"/>
+      <c r="K26" s="121" t="n"/>
+      <c r="L26" s="121" t="n"/>
+      <c r="M26" s="121" t="n"/>
+      <c r="N26" s="121" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="108" t="n">
+      <c r="A27" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="108" t="n">
+      <c r="B27" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="109">
+      <c r="C27" s="124">
         <f>A27*10+B27</f>
         <v/>
       </c>
-      <c r="D27" s="106" t="n"/>
-      <c r="E27" s="106" t="n"/>
-      <c r="F27" s="106" t="n"/>
-      <c r="G27" s="106" t="n"/>
-      <c r="H27" s="106" t="n"/>
-      <c r="I27" s="106" t="n"/>
-      <c r="J27" s="106" t="n"/>
-      <c r="K27" s="106" t="n"/>
-      <c r="L27" s="106" t="n"/>
-      <c r="M27" s="106" t="n"/>
-      <c r="N27" s="106" t="n"/>
+      <c r="D27" s="121" t="n"/>
+      <c r="E27" s="121" t="n"/>
+      <c r="F27" s="121" t="n"/>
+      <c r="G27" s="121" t="n"/>
+      <c r="H27" s="121" t="n"/>
+      <c r="I27" s="121" t="n"/>
+      <c r="J27" s="121" t="n"/>
+      <c r="K27" s="121" t="n"/>
+      <c r="L27" s="121" t="n"/>
+      <c r="M27" s="121" t="n"/>
+      <c r="N27" s="121" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="108" t="n">
+      <c r="A28" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="108" t="n">
+      <c r="B28" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="109">
+      <c r="C28" s="124">
         <f>A28*10+B28</f>
         <v/>
       </c>
-      <c r="D28" s="106" t="n"/>
-      <c r="E28" s="106" t="n"/>
-      <c r="F28" s="106" t="n"/>
-      <c r="G28" s="106" t="n"/>
-      <c r="H28" s="106" t="n"/>
-      <c r="I28" s="106" t="n"/>
-      <c r="J28" s="106" t="n"/>
-      <c r="K28" s="106" t="n"/>
-      <c r="L28" s="106" t="n"/>
-      <c r="M28" s="106" t="n"/>
-      <c r="N28" s="106" t="n"/>
+      <c r="D28" s="121" t="n"/>
+      <c r="E28" s="121" t="n"/>
+      <c r="F28" s="121" t="n"/>
+      <c r="G28" s="121" t="n"/>
+      <c r="H28" s="121" t="n"/>
+      <c r="I28" s="121" t="n"/>
+      <c r="J28" s="121" t="n"/>
+      <c r="K28" s="121" t="n"/>
+      <c r="L28" s="121" t="n"/>
+      <c r="M28" s="121" t="n"/>
+      <c r="N28" s="121" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="108" t="n">
+      <c r="A29" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="108" t="n">
+      <c r="B29" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="C29" s="109">
+      <c r="C29" s="124">
         <f>A29*10+B29</f>
         <v/>
       </c>
-      <c r="D29" s="106" t="n"/>
-      <c r="E29" s="106" t="n"/>
-      <c r="F29" s="106" t="n"/>
-      <c r="G29" s="106" t="n"/>
-      <c r="H29" s="106" t="n"/>
-      <c r="I29" s="106" t="n"/>
-      <c r="J29" s="106" t="n"/>
-      <c r="K29" s="106" t="n"/>
-      <c r="L29" s="106" t="n"/>
-      <c r="M29" s="106" t="n"/>
-      <c r="N29" s="106" t="n"/>
+      <c r="D29" s="121" t="n"/>
+      <c r="E29" s="121" t="n"/>
+      <c r="F29" s="121" t="n"/>
+      <c r="G29" s="121" t="n"/>
+      <c r="H29" s="121" t="n"/>
+      <c r="I29" s="121" t="n"/>
+      <c r="J29" s="121" t="n"/>
+      <c r="K29" s="121" t="n"/>
+      <c r="L29" s="121" t="n"/>
+      <c r="M29" s="121" t="n"/>
+      <c r="N29" s="121" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="108" t="n">
+      <c r="A30" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="108" t="n">
+      <c r="B30" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="109">
+      <c r="C30" s="124">
         <f>A30*10+B30</f>
         <v/>
       </c>
-      <c r="D30" s="106" t="n"/>
-      <c r="E30" s="106" t="n"/>
-      <c r="F30" s="106" t="n"/>
-      <c r="G30" s="106" t="n"/>
-      <c r="H30" s="106" t="n"/>
-      <c r="I30" s="106" t="n"/>
-      <c r="J30" s="106" t="n"/>
-      <c r="K30" s="106" t="n"/>
-      <c r="L30" s="106" t="n"/>
-      <c r="M30" s="106" t="n"/>
-      <c r="N30" s="106" t="n"/>
+      <c r="D30" s="121" t="n"/>
+      <c r="E30" s="121" t="n"/>
+      <c r="F30" s="121" t="n"/>
+      <c r="G30" s="121" t="n"/>
+      <c r="H30" s="121" t="n"/>
+      <c r="I30" s="121" t="n"/>
+      <c r="J30" s="121" t="n"/>
+      <c r="K30" s="121" t="n"/>
+      <c r="L30" s="121" t="n"/>
+      <c r="M30" s="121" t="n"/>
+      <c r="N30" s="121" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="108" t="n">
+      <c r="A31" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="B31" s="108" t="n">
+      <c r="B31" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="109">
+      <c r="C31" s="124">
         <f>A31*10+B31</f>
         <v/>
       </c>
-      <c r="D31" s="106" t="n"/>
-      <c r="E31" s="106" t="n"/>
-      <c r="F31" s="106" t="n"/>
-      <c r="G31" s="106" t="n"/>
-      <c r="H31" s="106" t="n"/>
-      <c r="I31" s="106" t="n"/>
-      <c r="J31" s="106" t="n"/>
-      <c r="K31" s="106" t="n"/>
-      <c r="L31" s="106" t="n"/>
-      <c r="M31" s="106" t="n"/>
-      <c r="N31" s="106" t="n"/>
+      <c r="D31" s="121" t="n"/>
+      <c r="E31" s="121" t="n"/>
+      <c r="F31" s="121" t="n"/>
+      <c r="G31" s="121" t="n"/>
+      <c r="H31" s="121" t="n"/>
+      <c r="I31" s="121" t="n"/>
+      <c r="J31" s="121" t="n"/>
+      <c r="K31" s="121" t="n"/>
+      <c r="L31" s="121" t="n"/>
+      <c r="M31" s="121" t="n"/>
+      <c r="N31" s="121" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="108" t="n">
+      <c r="A32" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="108" t="n">
+      <c r="B32" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="109">
+      <c r="C32" s="124">
         <f>A32*10+B32</f>
         <v/>
       </c>
-      <c r="D32" s="106" t="n"/>
-      <c r="E32" s="106" t="n"/>
-      <c r="F32" s="106" t="n"/>
-      <c r="G32" s="106" t="n"/>
-      <c r="H32" s="106" t="n"/>
-      <c r="I32" s="106" t="n"/>
-      <c r="J32" s="106" t="n"/>
-      <c r="K32" s="106" t="n"/>
-      <c r="L32" s="106" t="n"/>
-      <c r="M32" s="106" t="n"/>
-      <c r="N32" s="106" t="n"/>
+      <c r="D32" s="121" t="n"/>
+      <c r="E32" s="121" t="n"/>
+      <c r="F32" s="121" t="n"/>
+      <c r="G32" s="121" t="n"/>
+      <c r="H32" s="121" t="n"/>
+      <c r="I32" s="121" t="n"/>
+      <c r="J32" s="121" t="n"/>
+      <c r="K32" s="121" t="n"/>
+      <c r="L32" s="121" t="n"/>
+      <c r="M32" s="121" t="n"/>
+      <c r="N32" s="121" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="108" t="n">
+      <c r="A33" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="B33" s="108" t="n">
+      <c r="B33" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="109">
+      <c r="C33" s="124">
         <f>A33*10+B33</f>
         <v/>
       </c>
-      <c r="D33" s="106" t="n"/>
-      <c r="E33" s="106" t="n"/>
-      <c r="F33" s="106" t="n"/>
-      <c r="G33" s="106" t="n"/>
-      <c r="H33" s="106" t="n"/>
-      <c r="I33" s="106" t="n"/>
-      <c r="J33" s="106" t="n"/>
-      <c r="K33" s="106" t="n"/>
-      <c r="L33" s="106" t="n"/>
-      <c r="M33" s="106" t="n"/>
-      <c r="N33" s="106" t="n"/>
+      <c r="D33" s="121" t="n"/>
+      <c r="E33" s="121" t="n"/>
+      <c r="F33" s="121" t="n"/>
+      <c r="G33" s="121" t="n"/>
+      <c r="H33" s="121" t="n"/>
+      <c r="I33" s="121" t="n"/>
+      <c r="J33" s="121" t="n"/>
+      <c r="K33" s="121" t="n"/>
+      <c r="L33" s="121" t="n"/>
+      <c r="M33" s="121" t="n"/>
+      <c r="N33" s="121" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="108" t="n">
+      <c r="A34" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="B34" s="108" t="n">
+      <c r="B34" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="C34" s="109">
+      <c r="C34" s="124">
         <f>A34*10+B34</f>
         <v/>
       </c>
-      <c r="D34" s="106" t="n"/>
-      <c r="E34" s="106" t="n"/>
-      <c r="F34" s="106" t="n"/>
-      <c r="G34" s="106" t="n"/>
-      <c r="H34" s="106" t="n"/>
-      <c r="I34" s="106" t="n"/>
-      <c r="J34" s="106" t="n"/>
-      <c r="K34" s="106" t="n"/>
-      <c r="L34" s="106" t="n"/>
-      <c r="M34" s="106" t="n"/>
-      <c r="N34" s="106" t="n"/>
+      <c r="D34" s="121" t="n"/>
+      <c r="E34" s="121" t="n"/>
+      <c r="F34" s="121" t="n"/>
+      <c r="G34" s="121" t="n"/>
+      <c r="H34" s="121" t="n"/>
+      <c r="I34" s="121" t="n"/>
+      <c r="J34" s="121" t="n"/>
+      <c r="K34" s="121" t="n"/>
+      <c r="L34" s="121" t="n"/>
+      <c r="M34" s="121" t="n"/>
+      <c r="N34" s="121" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="108" t="n">
+      <c r="A35" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="B35" s="108" t="n">
+      <c r="B35" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="109">
+      <c r="C35" s="124">
         <f>A35*10+B35</f>
         <v/>
       </c>
-      <c r="D35" s="106" t="n"/>
-      <c r="E35" s="106" t="n"/>
-      <c r="F35" s="106" t="n"/>
-      <c r="G35" s="106" t="n"/>
-      <c r="H35" s="106" t="n"/>
-      <c r="I35" s="106" t="n"/>
-      <c r="J35" s="106" t="n"/>
-      <c r="K35" s="106" t="n"/>
-      <c r="L35" s="106" t="n"/>
-      <c r="M35" s="106" t="n"/>
-      <c r="N35" s="106" t="n"/>
+      <c r="D35" s="121" t="n"/>
+      <c r="E35" s="121" t="n"/>
+      <c r="F35" s="121" t="n"/>
+      <c r="G35" s="121" t="n"/>
+      <c r="H35" s="121" t="n"/>
+      <c r="I35" s="121" t="n"/>
+      <c r="J35" s="121" t="n"/>
+      <c r="K35" s="121" t="n"/>
+      <c r="L35" s="121" t="n"/>
+      <c r="M35" s="121" t="n"/>
+      <c r="N35" s="121" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="108" t="n">
+      <c r="A36" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="B36" s="108" t="n">
+      <c r="B36" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="C36" s="109">
+      <c r="C36" s="124">
         <f>A36*10+B36</f>
         <v/>
       </c>
-      <c r="D36" s="106" t="n"/>
-      <c r="E36" s="106" t="n"/>
-      <c r="F36" s="106" t="n"/>
-      <c r="G36" s="106" t="n"/>
-      <c r="H36" s="106" t="n"/>
-      <c r="I36" s="106" t="n"/>
-      <c r="J36" s="106" t="n"/>
-      <c r="K36" s="106" t="n"/>
-      <c r="L36" s="106" t="n"/>
-      <c r="M36" s="106" t="n"/>
-      <c r="N36" s="106" t="n"/>
+      <c r="D36" s="121" t="n"/>
+      <c r="E36" s="121" t="n"/>
+      <c r="F36" s="121" t="n"/>
+      <c r="G36" s="121" t="n"/>
+      <c r="H36" s="121" t="n"/>
+      <c r="I36" s="121" t="n"/>
+      <c r="J36" s="121" t="n"/>
+      <c r="K36" s="121" t="n"/>
+      <c r="L36" s="121" t="n"/>
+      <c r="M36" s="121" t="n"/>
+      <c r="N36" s="121" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="108" t="n">
+      <c r="A37" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="B37" s="108" t="n">
+      <c r="B37" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="C37" s="109">
+      <c r="C37" s="124">
         <f>A37*10+B37</f>
         <v/>
       </c>
-      <c r="D37" s="106" t="n"/>
-      <c r="E37" s="106" t="n"/>
-      <c r="F37" s="106" t="n"/>
-      <c r="G37" s="106" t="n"/>
-      <c r="H37" s="106" t="n"/>
-      <c r="I37" s="106" t="n"/>
-      <c r="J37" s="106" t="n"/>
-      <c r="K37" s="106" t="n"/>
-      <c r="L37" s="106" t="n"/>
-      <c r="M37" s="106" t="n"/>
-      <c r="N37" s="106" t="n"/>
+      <c r="D37" s="121" t="n"/>
+      <c r="E37" s="121" t="n"/>
+      <c r="F37" s="121" t="n"/>
+      <c r="G37" s="121" t="n"/>
+      <c r="H37" s="121" t="n"/>
+      <c r="I37" s="121" t="n"/>
+      <c r="J37" s="121" t="n"/>
+      <c r="K37" s="121" t="n"/>
+      <c r="L37" s="121" t="n"/>
+      <c r="M37" s="121" t="n"/>
+      <c r="N37" s="121" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="108" t="n">
+      <c r="A38" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="B38" s="108" t="n">
+      <c r="B38" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="C38" s="109">
+      <c r="C38" s="124">
         <f>A38*10+B38</f>
         <v/>
       </c>
-      <c r="D38" s="106" t="n"/>
-      <c r="E38" s="106" t="n"/>
-      <c r="F38" s="106" t="n"/>
-      <c r="G38" s="106" t="n"/>
-      <c r="H38" s="106" t="n"/>
-      <c r="I38" s="106" t="n"/>
-      <c r="J38" s="106" t="n"/>
-      <c r="K38" s="106" t="n"/>
-      <c r="L38" s="106" t="n"/>
-      <c r="M38" s="106" t="n"/>
-      <c r="N38" s="106" t="n"/>
+      <c r="D38" s="121" t="n"/>
+      <c r="E38" s="121" t="n"/>
+      <c r="F38" s="121" t="n"/>
+      <c r="G38" s="121" t="n"/>
+      <c r="H38" s="121" t="n"/>
+      <c r="I38" s="121" t="n"/>
+      <c r="J38" s="121" t="n"/>
+      <c r="K38" s="121" t="n"/>
+      <c r="L38" s="121" t="n"/>
+      <c r="M38" s="121" t="n"/>
+      <c r="N38" s="121" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="108" t="n">
+      <c r="A39" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="B39" s="108" t="n">
+      <c r="B39" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="C39" s="109">
+      <c r="C39" s="124">
         <f>A39*10+B39</f>
         <v/>
       </c>
-      <c r="D39" s="106" t="n"/>
-      <c r="E39" s="106" t="n"/>
-      <c r="F39" s="106" t="n"/>
-      <c r="G39" s="106" t="n"/>
-      <c r="H39" s="106" t="n"/>
-      <c r="I39" s="106" t="n"/>
-      <c r="J39" s="106" t="n"/>
-      <c r="K39" s="106" t="n"/>
-      <c r="L39" s="106" t="n"/>
-      <c r="M39" s="106" t="n"/>
-      <c r="N39" s="106" t="n"/>
+      <c r="D39" s="121" t="n"/>
+      <c r="E39" s="121" t="n"/>
+      <c r="F39" s="121" t="n"/>
+      <c r="G39" s="121" t="n"/>
+      <c r="H39" s="121" t="n"/>
+      <c r="I39" s="121" t="n"/>
+      <c r="J39" s="121" t="n"/>
+      <c r="K39" s="121" t="n"/>
+      <c r="L39" s="121" t="n"/>
+      <c r="M39" s="121" t="n"/>
+      <c r="N39" s="121" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="108" t="n">
+      <c r="A40" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="B40" s="108" t="n">
+      <c r="B40" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="109">
+      <c r="C40" s="124">
         <f>A40*10+B40</f>
         <v/>
       </c>
-      <c r="D40" s="106" t="n"/>
-      <c r="E40" s="106" t="n"/>
-      <c r="F40" s="106" t="n"/>
-      <c r="G40" s="106" t="n"/>
-      <c r="H40" s="106" t="n"/>
-      <c r="I40" s="106" t="n"/>
-      <c r="J40" s="106" t="n"/>
-      <c r="K40" s="106" t="n"/>
-      <c r="L40" s="106" t="n"/>
-      <c r="M40" s="106" t="n"/>
-      <c r="N40" s="106" t="n"/>
+      <c r="D40" s="121" t="n"/>
+      <c r="E40" s="121" t="n"/>
+      <c r="F40" s="121" t="n"/>
+      <c r="G40" s="121" t="n"/>
+      <c r="H40" s="121" t="n"/>
+      <c r="I40" s="121" t="n"/>
+      <c r="J40" s="121" t="n"/>
+      <c r="K40" s="121" t="n"/>
+      <c r="L40" s="121" t="n"/>
+      <c r="M40" s="121" t="n"/>
+      <c r="N40" s="121" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="108" t="n">
+      <c r="A41" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="B41" s="108" t="n">
+      <c r="B41" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="109">
+      <c r="C41" s="124">
         <f>A41*10+B41</f>
         <v/>
       </c>
-      <c r="D41" s="106" t="n"/>
-      <c r="E41" s="106" t="n"/>
-      <c r="F41" s="106" t="n"/>
-      <c r="G41" s="106" t="n"/>
-      <c r="H41" s="106" t="n"/>
-      <c r="I41" s="106" t="n"/>
-      <c r="J41" s="106" t="n"/>
-      <c r="K41" s="106" t="n"/>
-      <c r="L41" s="106" t="n"/>
-      <c r="M41" s="106" t="n"/>
-      <c r="N41" s="106" t="n"/>
+      <c r="D41" s="121" t="n"/>
+      <c r="E41" s="121" t="n"/>
+      <c r="F41" s="121" t="n"/>
+      <c r="G41" s="121" t="n"/>
+      <c r="H41" s="121" t="n"/>
+      <c r="I41" s="121" t="n"/>
+      <c r="J41" s="121" t="n"/>
+      <c r="K41" s="121" t="n"/>
+      <c r="L41" s="121" t="n"/>
+      <c r="M41" s="121" t="n"/>
+      <c r="N41" s="121" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="108" t="n">
+      <c r="A42" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="B42" s="108" t="n">
+      <c r="B42" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="C42" s="109">
+      <c r="C42" s="124">
         <f>A42*10+B42</f>
         <v/>
       </c>
-      <c r="D42" s="106" t="n"/>
-      <c r="E42" s="106" t="n"/>
-      <c r="F42" s="106" t="n"/>
-      <c r="G42" s="106" t="n"/>
-      <c r="H42" s="106" t="n"/>
-      <c r="I42" s="106" t="n"/>
-      <c r="J42" s="106" t="n"/>
-      <c r="K42" s="106" t="n"/>
-      <c r="L42" s="106" t="n"/>
-      <c r="M42" s="106" t="n"/>
-      <c r="N42" s="106" t="n"/>
+      <c r="D42" s="121" t="n"/>
+      <c r="E42" s="121" t="n"/>
+      <c r="F42" s="121" t="n"/>
+      <c r="G42" s="121" t="n"/>
+      <c r="H42" s="121" t="n"/>
+      <c r="I42" s="121" t="n"/>
+      <c r="J42" s="121" t="n"/>
+      <c r="K42" s="121" t="n"/>
+      <c r="L42" s="121" t="n"/>
+      <c r="M42" s="121" t="n"/>
+      <c r="N42" s="121" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="108" t="n">
+      <c r="A43" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="B43" s="108" t="n">
+      <c r="B43" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="C43" s="109">
+      <c r="C43" s="124">
         <f>A43*10+B43</f>
         <v/>
       </c>
-      <c r="D43" s="106" t="n"/>
-      <c r="E43" s="106" t="n"/>
-      <c r="F43" s="106" t="n"/>
-      <c r="G43" s="106" t="n"/>
-      <c r="H43" s="106" t="n"/>
-      <c r="I43" s="106" t="n"/>
-      <c r="J43" s="106" t="n"/>
-      <c r="K43" s="106" t="n"/>
-      <c r="L43" s="106" t="n"/>
-      <c r="M43" s="106" t="n"/>
-      <c r="N43" s="106" t="n"/>
+      <c r="D43" s="121" t="n"/>
+      <c r="E43" s="121" t="n"/>
+      <c r="F43" s="121" t="n"/>
+      <c r="G43" s="121" t="n"/>
+      <c r="H43" s="121" t="n"/>
+      <c r="I43" s="121" t="n"/>
+      <c r="J43" s="121" t="n"/>
+      <c r="K43" s="121" t="n"/>
+      <c r="L43" s="121" t="n"/>
+      <c r="M43" s="121" t="n"/>
+      <c r="N43" s="121" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="108" t="n">
+      <c r="A44" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="B44" s="108" t="n">
+      <c r="B44" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="C44" s="109">
+      <c r="C44" s="124">
         <f>A44*10+B44</f>
         <v/>
       </c>
-      <c r="D44" s="106" t="n"/>
-      <c r="E44" s="106" t="n"/>
-      <c r="F44" s="106" t="n"/>
-      <c r="G44" s="106" t="n"/>
-      <c r="H44" s="106" t="n"/>
-      <c r="I44" s="106" t="n"/>
-      <c r="J44" s="106" t="n"/>
-      <c r="K44" s="106" t="n"/>
-      <c r="L44" s="106" t="n"/>
-      <c r="M44" s="106" t="n"/>
-      <c r="N44" s="106" t="n"/>
+      <c r="D44" s="121" t="n"/>
+      <c r="E44" s="121" t="n"/>
+      <c r="F44" s="121" t="n"/>
+      <c r="G44" s="121" t="n"/>
+      <c r="H44" s="121" t="n"/>
+      <c r="I44" s="121" t="n"/>
+      <c r="J44" s="121" t="n"/>
+      <c r="K44" s="121" t="n"/>
+      <c r="L44" s="121" t="n"/>
+      <c r="M44" s="121" t="n"/>
+      <c r="N44" s="121" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="108" t="n">
+      <c r="A45" s="123" t="n">
         <v>6</v>
       </c>
-      <c r="B45" s="108" t="n">
+      <c r="B45" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="109">
+      <c r="C45" s="124">
         <f>A45*10+B45</f>
         <v/>
       </c>
-      <c r="D45" s="106" t="n"/>
-      <c r="E45" s="106" t="n"/>
-      <c r="F45" s="106" t="n"/>
-      <c r="G45" s="106" t="n"/>
-      <c r="H45" s="106" t="n"/>
-      <c r="I45" s="106" t="n"/>
-      <c r="J45" s="106" t="n"/>
-      <c r="K45" s="106" t="n"/>
-      <c r="L45" s="106" t="n"/>
-      <c r="M45" s="106" t="n"/>
-      <c r="N45" s="106" t="n"/>
+      <c r="D45" s="121" t="n"/>
+      <c r="E45" s="121" t="n"/>
+      <c r="F45" s="121" t="n"/>
+      <c r="G45" s="121" t="n"/>
+      <c r="H45" s="121" t="n"/>
+      <c r="I45" s="121" t="n"/>
+      <c r="J45" s="121" t="n"/>
+      <c r="K45" s="121" t="n"/>
+      <c r="L45" s="121" t="n"/>
+      <c r="M45" s="121" t="n"/>
+      <c r="N45" s="121" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="108" t="n">
+      <c r="A46" s="123" t="n">
         <v>6</v>
       </c>
-      <c r="B46" s="108" t="n">
+      <c r="B46" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="C46" s="109">
+      <c r="C46" s="124">
         <f>A46*10+B46</f>
         <v/>
       </c>
-      <c r="D46" s="106" t="n"/>
-      <c r="E46" s="106" t="n"/>
-      <c r="F46" s="106" t="n"/>
-      <c r="G46" s="106" t="n"/>
-      <c r="H46" s="106" t="n"/>
-      <c r="I46" s="106" t="n"/>
-      <c r="J46" s="106" t="n"/>
-      <c r="K46" s="106" t="n"/>
-      <c r="L46" s="106" t="n"/>
-      <c r="M46" s="106" t="n"/>
-      <c r="N46" s="106" t="n"/>
+      <c r="D46" s="121" t="n"/>
+      <c r="E46" s="121" t="n"/>
+      <c r="F46" s="121" t="n"/>
+      <c r="G46" s="121" t="n"/>
+      <c r="H46" s="121" t="n"/>
+      <c r="I46" s="121" t="n"/>
+      <c r="J46" s="121" t="n"/>
+      <c r="K46" s="121" t="n"/>
+      <c r="L46" s="121" t="n"/>
+      <c r="M46" s="121" t="n"/>
+      <c r="N46" s="121" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="108" t="n">
+      <c r="A47" s="123" t="n">
         <v>6</v>
       </c>
-      <c r="B47" s="108" t="n">
+      <c r="B47" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="C47" s="109">
+      <c r="C47" s="124">
         <f>A47*10+B47</f>
         <v/>
       </c>
-      <c r="D47" s="106" t="n"/>
-      <c r="E47" s="106" t="n"/>
-      <c r="F47" s="106" t="n"/>
-      <c r="G47" s="106" t="n"/>
-      <c r="H47" s="106" t="n"/>
-      <c r="I47" s="106" t="n"/>
-      <c r="J47" s="106" t="n"/>
-      <c r="K47" s="106" t="n"/>
-      <c r="L47" s="106" t="n"/>
-      <c r="M47" s="106" t="n"/>
-      <c r="N47" s="106" t="n"/>
+      <c r="D47" s="121" t="n"/>
+      <c r="E47" s="121" t="n"/>
+      <c r="F47" s="121" t="n"/>
+      <c r="G47" s="121" t="n"/>
+      <c r="H47" s="121" t="n"/>
+      <c r="I47" s="121" t="n"/>
+      <c r="J47" s="121" t="n"/>
+      <c r="K47" s="121" t="n"/>
+      <c r="L47" s="121" t="n"/>
+      <c r="M47" s="121" t="n"/>
+      <c r="N47" s="121" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="108" t="n">
+      <c r="A48" s="123" t="n">
         <v>6</v>
       </c>
-      <c r="B48" s="108" t="n">
+      <c r="B48" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="C48" s="109">
+      <c r="C48" s="124">
         <f>A48*10+B48</f>
         <v/>
       </c>
-      <c r="D48" s="106" t="n"/>
-      <c r="E48" s="106" t="n"/>
-      <c r="F48" s="106" t="n"/>
-      <c r="G48" s="106" t="n"/>
-      <c r="H48" s="106" t="n"/>
-      <c r="I48" s="106" t="n"/>
-      <c r="J48" s="106" t="n"/>
-      <c r="K48" s="106" t="n"/>
-      <c r="L48" s="106" t="n"/>
-      <c r="M48" s="106" t="n"/>
-      <c r="N48" s="106" t="n"/>
+      <c r="D48" s="121" t="n"/>
+      <c r="E48" s="121" t="n"/>
+      <c r="F48" s="121" t="n"/>
+      <c r="G48" s="121" t="n"/>
+      <c r="H48" s="121" t="n"/>
+      <c r="I48" s="121" t="n"/>
+      <c r="J48" s="121" t="n"/>
+      <c r="K48" s="121" t="n"/>
+      <c r="L48" s="121" t="n"/>
+      <c r="M48" s="121" t="n"/>
+      <c r="N48" s="121" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="108" t="n">
+      <c r="A49" s="123" t="n">
         <v>6</v>
       </c>
-      <c r="B49" s="108" t="n">
+      <c r="B49" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="C49" s="109">
+      <c r="C49" s="124">
         <f>A49*10+B49</f>
         <v/>
       </c>
-      <c r="D49" s="106" t="n"/>
-      <c r="E49" s="106" t="n"/>
-      <c r="F49" s="106" t="n"/>
-      <c r="G49" s="106" t="n"/>
-      <c r="H49" s="106" t="n"/>
-      <c r="I49" s="106" t="n"/>
-      <c r="J49" s="106" t="n"/>
-      <c r="K49" s="106" t="n"/>
-      <c r="L49" s="106" t="n"/>
-      <c r="M49" s="106" t="n"/>
-      <c r="N49" s="106" t="n"/>
+      <c r="D49" s="121" t="n"/>
+      <c r="E49" s="121" t="n"/>
+      <c r="F49" s="121" t="n"/>
+      <c r="G49" s="121" t="n"/>
+      <c r="H49" s="121" t="n"/>
+      <c r="I49" s="121" t="n"/>
+      <c r="J49" s="121" t="n"/>
+      <c r="K49" s="121" t="n"/>
+      <c r="L49" s="121" t="n"/>
+      <c r="M49" s="121" t="n"/>
+      <c r="N49" s="121" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="108" t="n">
+      <c r="A50" s="123" t="n">
         <v>7</v>
       </c>
-      <c r="B50" s="108" t="n">
+      <c r="B50" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="C50" s="109">
+      <c r="C50" s="124">
         <f>A50*10+B50</f>
         <v/>
       </c>
-      <c r="D50" s="106" t="n"/>
-      <c r="E50" s="106" t="n"/>
-      <c r="F50" s="106" t="n"/>
-      <c r="G50" s="106" t="n"/>
-      <c r="H50" s="106" t="n"/>
-      <c r="I50" s="106" t="n"/>
-      <c r="J50" s="106" t="n"/>
-      <c r="K50" s="106" t="n"/>
-      <c r="L50" s="106" t="n"/>
-      <c r="M50" s="106" t="n"/>
-      <c r="N50" s="106" t="n"/>
+      <c r="D50" s="121" t="n"/>
+      <c r="E50" s="121" t="n"/>
+      <c r="F50" s="121" t="n"/>
+      <c r="G50" s="121" t="n"/>
+      <c r="H50" s="121" t="n"/>
+      <c r="I50" s="121" t="n"/>
+      <c r="J50" s="121" t="n"/>
+      <c r="K50" s="121" t="n"/>
+      <c r="L50" s="121" t="n"/>
+      <c r="M50" s="121" t="n"/>
+      <c r="N50" s="121" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="108" t="n">
+      <c r="A51" s="123" t="n">
         <v>7</v>
       </c>
-      <c r="B51" s="108" t="n">
+      <c r="B51" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="C51" s="109">
+      <c r="C51" s="124">
         <f>A51*10+B51</f>
         <v/>
       </c>
-      <c r="D51" s="106" t="n"/>
-      <c r="E51" s="106" t="n"/>
-      <c r="F51" s="106" t="n"/>
-      <c r="G51" s="106" t="n"/>
-      <c r="H51" s="106" t="n"/>
-      <c r="I51" s="106" t="n"/>
-      <c r="J51" s="106" t="n"/>
-      <c r="K51" s="106" t="n"/>
-      <c r="L51" s="106" t="n"/>
-      <c r="M51" s="106" t="n"/>
-      <c r="N51" s="106" t="n"/>
+      <c r="D51" s="121" t="n"/>
+      <c r="E51" s="121" t="n"/>
+      <c r="F51" s="121" t="n"/>
+      <c r="G51" s="121" t="n"/>
+      <c r="H51" s="121" t="n"/>
+      <c r="I51" s="121" t="n"/>
+      <c r="J51" s="121" t="n"/>
+      <c r="K51" s="121" t="n"/>
+      <c r="L51" s="121" t="n"/>
+      <c r="M51" s="121" t="n"/>
+      <c r="N51" s="121" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="108" t="n">
+      <c r="A52" s="123" t="n">
         <v>7</v>
       </c>
-      <c r="B52" s="108" t="n">
+      <c r="B52" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="C52" s="109">
+      <c r="C52" s="124">
         <f>A52*10+B52</f>
         <v/>
       </c>
-      <c r="D52" s="106" t="n"/>
-      <c r="E52" s="106" t="n"/>
-      <c r="F52" s="106" t="n"/>
-      <c r="G52" s="106" t="n"/>
-      <c r="H52" s="106" t="n"/>
-      <c r="I52" s="106" t="n"/>
-      <c r="J52" s="106" t="n"/>
-      <c r="K52" s="106" t="n"/>
-      <c r="L52" s="106" t="n"/>
-      <c r="M52" s="106" t="n"/>
-      <c r="N52" s="106" t="n"/>
+      <c r="D52" s="121" t="n"/>
+      <c r="E52" s="121" t="n"/>
+      <c r="F52" s="121" t="n"/>
+      <c r="G52" s="121" t="n"/>
+      <c r="H52" s="121" t="n"/>
+      <c r="I52" s="121" t="n"/>
+      <c r="J52" s="121" t="n"/>
+      <c r="K52" s="121" t="n"/>
+      <c r="L52" s="121" t="n"/>
+      <c r="M52" s="121" t="n"/>
+      <c r="N52" s="121" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="108" t="n">
+      <c r="A53" s="123" t="n">
         <v>7</v>
       </c>
-      <c r="B53" s="108" t="n">
+      <c r="B53" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="C53" s="109">
+      <c r="C53" s="124">
         <f>A53*10+B53</f>
         <v/>
       </c>
-      <c r="D53" s="106" t="n"/>
-      <c r="E53" s="106" t="n"/>
-      <c r="F53" s="106" t="n"/>
-      <c r="G53" s="106" t="n"/>
-      <c r="H53" s="106" t="n"/>
-      <c r="I53" s="106" t="n"/>
-      <c r="J53" s="106" t="n"/>
-      <c r="K53" s="106" t="n"/>
-      <c r="L53" s="106" t="n"/>
-      <c r="M53" s="106" t="n"/>
-      <c r="N53" s="106" t="n"/>
+      <c r="D53" s="121" t="n"/>
+      <c r="E53" s="121" t="n"/>
+      <c r="F53" s="121" t="n"/>
+      <c r="G53" s="121" t="n"/>
+      <c r="H53" s="121" t="n"/>
+      <c r="I53" s="121" t="n"/>
+      <c r="J53" s="121" t="n"/>
+      <c r="K53" s="121" t="n"/>
+      <c r="L53" s="121" t="n"/>
+      <c r="M53" s="121" t="n"/>
+      <c r="N53" s="121" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="108" t="n">
+      <c r="A54" s="123" t="n">
         <v>7</v>
       </c>
-      <c r="B54" s="108" t="n">
+      <c r="B54" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="C54" s="109">
+      <c r="C54" s="124">
         <f>A54*10+B54</f>
         <v/>
       </c>
-      <c r="D54" s="106" t="n"/>
-      <c r="E54" s="106" t="n"/>
-      <c r="F54" s="106" t="n"/>
-      <c r="G54" s="106" t="n"/>
-      <c r="H54" s="106" t="n"/>
-      <c r="I54" s="106" t="n"/>
-      <c r="J54" s="106" t="n"/>
-      <c r="K54" s="106" t="n"/>
-      <c r="L54" s="106" t="n"/>
-      <c r="M54" s="106" t="n"/>
-      <c r="N54" s="106" t="n"/>
+      <c r="D54" s="121" t="n"/>
+      <c r="E54" s="121" t="n"/>
+      <c r="F54" s="121" t="n"/>
+      <c r="G54" s="121" t="n"/>
+      <c r="H54" s="121" t="n"/>
+      <c r="I54" s="121" t="n"/>
+      <c r="J54" s="121" t="n"/>
+      <c r="K54" s="121" t="n"/>
+      <c r="L54" s="121" t="n"/>
+      <c r="M54" s="121" t="n"/>
+      <c r="N54" s="121" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="108" t="n">
+      <c r="A55" s="123" t="n">
         <v>8</v>
       </c>
-      <c r="B55" s="108" t="n">
+      <c r="B55" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="109">
+      <c r="C55" s="124">
         <f>A55*10+B55</f>
         <v/>
       </c>
-      <c r="D55" s="106" t="n"/>
-      <c r="E55" s="106" t="n"/>
-      <c r="F55" s="106" t="n"/>
-      <c r="G55" s="106" t="n"/>
-      <c r="H55" s="106" t="n"/>
-      <c r="I55" s="106" t="n"/>
-      <c r="J55" s="106" t="n"/>
-      <c r="K55" s="106" t="n"/>
-      <c r="L55" s="106" t="n"/>
-      <c r="M55" s="106" t="n"/>
-      <c r="N55" s="106" t="n"/>
+      <c r="D55" s="121" t="n"/>
+      <c r="E55" s="121" t="n"/>
+      <c r="F55" s="121" t="n"/>
+      <c r="G55" s="121" t="n"/>
+      <c r="H55" s="121" t="n"/>
+      <c r="I55" s="121" t="n"/>
+      <c r="J55" s="121" t="n"/>
+      <c r="K55" s="121" t="n"/>
+      <c r="L55" s="121" t="n"/>
+      <c r="M55" s="121" t="n"/>
+      <c r="N55" s="121" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="108" t="n">
+      <c r="A56" s="123" t="n">
         <v>8</v>
       </c>
-      <c r="B56" s="108" t="n">
+      <c r="B56" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="C56" s="109">
+      <c r="C56" s="124">
         <f>A56*10+B56</f>
         <v/>
       </c>
-      <c r="D56" s="106" t="n"/>
-      <c r="E56" s="106" t="n"/>
-      <c r="F56" s="106" t="n"/>
-      <c r="G56" s="106" t="n"/>
-      <c r="H56" s="106" t="n"/>
-      <c r="I56" s="106" t="n"/>
-      <c r="J56" s="106" t="n"/>
-      <c r="K56" s="106" t="n"/>
-      <c r="L56" s="106" t="n"/>
-      <c r="M56" s="106" t="n"/>
-      <c r="N56" s="106" t="n"/>
+      <c r="D56" s="121" t="n"/>
+      <c r="E56" s="121" t="n"/>
+      <c r="F56" s="121" t="n"/>
+      <c r="G56" s="121" t="n"/>
+      <c r="H56" s="121" t="n"/>
+      <c r="I56" s="121" t="n"/>
+      <c r="J56" s="121" t="n"/>
+      <c r="K56" s="121" t="n"/>
+      <c r="L56" s="121" t="n"/>
+      <c r="M56" s="121" t="n"/>
+      <c r="N56" s="121" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="108" t="n">
+      <c r="A57" s="123" t="n">
         <v>8</v>
       </c>
-      <c r="B57" s="108" t="n">
+      <c r="B57" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="C57" s="109">
+      <c r="C57" s="124">
         <f>A57*10+B57</f>
         <v/>
       </c>
-      <c r="D57" s="106" t="n"/>
-      <c r="E57" s="106" t="n"/>
-      <c r="F57" s="106" t="n"/>
-      <c r="G57" s="106" t="n"/>
-      <c r="H57" s="106" t="n"/>
-      <c r="I57" s="106" t="n"/>
-      <c r="J57" s="106" t="n"/>
-      <c r="K57" s="106" t="n"/>
-      <c r="L57" s="106" t="n"/>
-      <c r="M57" s="106" t="n"/>
-      <c r="N57" s="106" t="n"/>
+      <c r="D57" s="121" t="n"/>
+      <c r="E57" s="121" t="n"/>
+      <c r="F57" s="121" t="n"/>
+      <c r="G57" s="121" t="n"/>
+      <c r="H57" s="121" t="n"/>
+      <c r="I57" s="121" t="n"/>
+      <c r="J57" s="121" t="n"/>
+      <c r="K57" s="121" t="n"/>
+      <c r="L57" s="121" t="n"/>
+      <c r="M57" s="121" t="n"/>
+      <c r="N57" s="121" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="108" t="n">
+      <c r="A58" s="123" t="n">
         <v>8</v>
       </c>
-      <c r="B58" s="108" t="n">
+      <c r="B58" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="C58" s="109">
+      <c r="C58" s="124">
         <f>A58*10+B58</f>
         <v/>
       </c>
-      <c r="D58" s="106" t="n"/>
-      <c r="E58" s="106" t="n"/>
-      <c r="F58" s="106" t="n"/>
-      <c r="G58" s="106" t="n"/>
-      <c r="H58" s="106" t="n"/>
-      <c r="I58" s="106" t="n"/>
-      <c r="J58" s="106" t="n"/>
-      <c r="K58" s="106" t="n"/>
-      <c r="L58" s="106" t="n"/>
-      <c r="M58" s="106" t="n"/>
-      <c r="N58" s="106" t="n"/>
+      <c r="D58" s="121" t="n"/>
+      <c r="E58" s="121" t="n"/>
+      <c r="F58" s="121" t="n"/>
+      <c r="G58" s="121" t="n"/>
+      <c r="H58" s="121" t="n"/>
+      <c r="I58" s="121" t="n"/>
+      <c r="J58" s="121" t="n"/>
+      <c r="K58" s="121" t="n"/>
+      <c r="L58" s="121" t="n"/>
+      <c r="M58" s="121" t="n"/>
+      <c r="N58" s="121" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="108" t="n">
+      <c r="A59" s="123" t="n">
         <v>8</v>
       </c>
-      <c r="B59" s="108" t="n">
+      <c r="B59" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="C59" s="109">
+      <c r="C59" s="124">
         <f>A59*10+B59</f>
         <v/>
       </c>
-      <c r="D59" s="106" t="n"/>
-      <c r="E59" s="106" t="n"/>
-      <c r="F59" s="106" t="n"/>
-      <c r="G59" s="106" t="n"/>
-      <c r="H59" s="106" t="n"/>
-      <c r="I59" s="106" t="n"/>
-      <c r="J59" s="106" t="n"/>
-      <c r="K59" s="106" t="n"/>
-      <c r="L59" s="106" t="n"/>
-      <c r="M59" s="106" t="n"/>
-      <c r="N59" s="106" t="n"/>
+      <c r="D59" s="121" t="n"/>
+      <c r="E59" s="121" t="n"/>
+      <c r="F59" s="121" t="n"/>
+      <c r="G59" s="121" t="n"/>
+      <c r="H59" s="121" t="n"/>
+      <c r="I59" s="121" t="n"/>
+      <c r="J59" s="121" t="n"/>
+      <c r="K59" s="121" t="n"/>
+      <c r="L59" s="121" t="n"/>
+      <c r="M59" s="121" t="n"/>
+      <c r="N59" s="121" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="108" t="n">
+      <c r="A60" s="123" t="n">
         <v>9</v>
       </c>
-      <c r="B60" s="108" t="n">
+      <c r="B60" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="109">
+      <c r="C60" s="124">
         <f>A60*10+B60</f>
         <v/>
       </c>
-      <c r="D60" s="106" t="n"/>
-      <c r="E60" s="106" t="n"/>
-      <c r="F60" s="106" t="n"/>
-      <c r="G60" s="106" t="n"/>
-      <c r="H60" s="106" t="n"/>
-      <c r="I60" s="106" t="n"/>
-      <c r="J60" s="106" t="n"/>
-      <c r="K60" s="106" t="n"/>
-      <c r="L60" s="106" t="n"/>
-      <c r="M60" s="106" t="n"/>
-      <c r="N60" s="106" t="n"/>
+      <c r="D60" s="121" t="n"/>
+      <c r="E60" s="121" t="n"/>
+      <c r="F60" s="121" t="n"/>
+      <c r="G60" s="121" t="n"/>
+      <c r="H60" s="121" t="n"/>
+      <c r="I60" s="121" t="n"/>
+      <c r="J60" s="121" t="n"/>
+      <c r="K60" s="121" t="n"/>
+      <c r="L60" s="121" t="n"/>
+      <c r="M60" s="121" t="n"/>
+      <c r="N60" s="121" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="108" t="n">
+      <c r="A61" s="123" t="n">
         <v>9</v>
       </c>
-      <c r="B61" s="108" t="n">
+      <c r="B61" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="C61" s="109">
+      <c r="C61" s="124">
         <f>A61*10+B61</f>
         <v/>
       </c>
-      <c r="D61" s="106" t="n"/>
-      <c r="E61" s="106" t="n"/>
-      <c r="F61" s="106" t="n"/>
-      <c r="G61" s="106" t="n"/>
-      <c r="H61" s="106" t="n"/>
-      <c r="I61" s="106" t="n"/>
-      <c r="J61" s="106" t="n"/>
-      <c r="K61" s="106" t="n"/>
-      <c r="L61" s="106" t="n"/>
-      <c r="M61" s="106" t="n"/>
-      <c r="N61" s="106" t="n"/>
+      <c r="D61" s="121" t="n"/>
+      <c r="E61" s="121" t="n"/>
+      <c r="F61" s="121" t="n"/>
+      <c r="G61" s="121" t="n"/>
+      <c r="H61" s="121" t="n"/>
+      <c r="I61" s="121" t="n"/>
+      <c r="J61" s="121" t="n"/>
+      <c r="K61" s="121" t="n"/>
+      <c r="L61" s="121" t="n"/>
+      <c r="M61" s="121" t="n"/>
+      <c r="N61" s="121" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="108" t="n">
+      <c r="A62" s="123" t="n">
         <v>9</v>
       </c>
-      <c r="B62" s="108" t="n">
+      <c r="B62" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="C62" s="109">
+      <c r="C62" s="124">
         <f>A62*10+B62</f>
         <v/>
       </c>
-      <c r="D62" s="106" t="n"/>
-      <c r="E62" s="106" t="n"/>
-      <c r="F62" s="106" t="n"/>
-      <c r="G62" s="106" t="n"/>
-      <c r="H62" s="106" t="n"/>
-      <c r="I62" s="106" t="n"/>
-      <c r="J62" s="106" t="n"/>
-      <c r="K62" s="106" t="n"/>
-      <c r="L62" s="106" t="n"/>
-      <c r="M62" s="106" t="n"/>
-      <c r="N62" s="106" t="n"/>
+      <c r="D62" s="121" t="n"/>
+      <c r="E62" s="121" t="n"/>
+      <c r="F62" s="121" t="n"/>
+      <c r="G62" s="121" t="n"/>
+      <c r="H62" s="121" t="n"/>
+      <c r="I62" s="121" t="n"/>
+      <c r="J62" s="121" t="n"/>
+      <c r="K62" s="121" t="n"/>
+      <c r="L62" s="121" t="n"/>
+      <c r="M62" s="121" t="n"/>
+      <c r="N62" s="121" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="108" t="n">
+      <c r="A63" s="123" t="n">
         <v>9</v>
       </c>
-      <c r="B63" s="108" t="n">
+      <c r="B63" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="C63" s="109">
+      <c r="C63" s="124">
         <f>A63*10+B63</f>
         <v/>
       </c>
-      <c r="D63" s="106" t="n"/>
-      <c r="E63" s="106" t="n"/>
-      <c r="F63" s="106" t="n"/>
-      <c r="G63" s="106" t="n"/>
-      <c r="H63" s="106" t="n"/>
-      <c r="I63" s="106" t="n"/>
-      <c r="J63" s="106" t="n"/>
-      <c r="K63" s="106" t="n"/>
-      <c r="L63" s="106" t="n"/>
-      <c r="M63" s="106" t="n"/>
-      <c r="N63" s="106" t="n"/>
+      <c r="D63" s="121" t="n"/>
+      <c r="E63" s="121" t="n"/>
+      <c r="F63" s="121" t="n"/>
+      <c r="G63" s="121" t="n"/>
+      <c r="H63" s="121" t="n"/>
+      <c r="I63" s="121" t="n"/>
+      <c r="J63" s="121" t="n"/>
+      <c r="K63" s="121" t="n"/>
+      <c r="L63" s="121" t="n"/>
+      <c r="M63" s="121" t="n"/>
+      <c r="N63" s="121" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="108" t="n">
+      <c r="A64" s="123" t="n">
         <v>9</v>
       </c>
-      <c r="B64" s="108" t="n">
+      <c r="B64" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="C64" s="109">
+      <c r="C64" s="124">
         <f>A64*10+B64</f>
         <v/>
       </c>
-      <c r="D64" s="106" t="n"/>
-      <c r="E64" s="106" t="n"/>
-      <c r="F64" s="106" t="n"/>
-      <c r="G64" s="106" t="n"/>
-      <c r="H64" s="106" t="n"/>
-      <c r="I64" s="106" t="n"/>
-      <c r="J64" s="106" t="n"/>
-      <c r="K64" s="106" t="n"/>
-      <c r="L64" s="106" t="n"/>
-      <c r="M64" s="106" t="n"/>
-      <c r="N64" s="106" t="n"/>
+      <c r="D64" s="121" t="n"/>
+      <c r="E64" s="121" t="n"/>
+      <c r="F64" s="121" t="n"/>
+      <c r="G64" s="121" t="n"/>
+      <c r="H64" s="121" t="n"/>
+      <c r="I64" s="121" t="n"/>
+      <c r="J64" s="121" t="n"/>
+      <c r="K64" s="121" t="n"/>
+      <c r="L64" s="121" t="n"/>
+      <c r="M64" s="121" t="n"/>
+      <c r="N64" s="121" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="108" t="n">
+      <c r="A65" s="123" t="n">
         <v>10</v>
       </c>
-      <c r="B65" s="108" t="n">
+      <c r="B65" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="C65" s="109">
+      <c r="C65" s="124">
         <f>A65*10+B65</f>
         <v/>
       </c>
-      <c r="D65" s="106" t="n"/>
-      <c r="E65" s="106" t="n"/>
-      <c r="F65" s="106" t="n"/>
-      <c r="G65" s="106" t="n"/>
-      <c r="H65" s="106" t="n"/>
-      <c r="I65" s="106" t="n"/>
-      <c r="J65" s="106" t="n"/>
-      <c r="K65" s="106" t="n"/>
-      <c r="L65" s="106" t="n"/>
-      <c r="M65" s="106" t="n"/>
-      <c r="N65" s="106" t="n"/>
+      <c r="D65" s="121" t="n"/>
+      <c r="E65" s="121" t="n"/>
+      <c r="F65" s="121" t="n"/>
+      <c r="G65" s="121" t="n"/>
+      <c r="H65" s="121" t="n"/>
+      <c r="I65" s="121" t="n"/>
+      <c r="J65" s="121" t="n"/>
+      <c r="K65" s="121" t="n"/>
+      <c r="L65" s="121" t="n"/>
+      <c r="M65" s="121" t="n"/>
+      <c r="N65" s="121" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="108" t="n">
+      <c r="A66" s="123" t="n">
         <v>10</v>
       </c>
-      <c r="B66" s="108" t="n">
+      <c r="B66" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="C66" s="109">
+      <c r="C66" s="124">
         <f>A66*10+B66</f>
         <v/>
       </c>
-      <c r="D66" s="106" t="n"/>
-      <c r="E66" s="106" t="n"/>
-      <c r="F66" s="106" t="n"/>
-      <c r="G66" s="106" t="n"/>
-      <c r="H66" s="106" t="n"/>
-      <c r="I66" s="106" t="n"/>
-      <c r="J66" s="106" t="n"/>
-      <c r="K66" s="106" t="n"/>
-      <c r="L66" s="106" t="n"/>
-      <c r="M66" s="106" t="n"/>
-      <c r="N66" s="106" t="n"/>
+      <c r="D66" s="121" t="n"/>
+      <c r="E66" s="121" t="n"/>
+      <c r="F66" s="121" t="n"/>
+      <c r="G66" s="121" t="n"/>
+      <c r="H66" s="121" t="n"/>
+      <c r="I66" s="121" t="n"/>
+      <c r="J66" s="121" t="n"/>
+      <c r="K66" s="121" t="n"/>
+      <c r="L66" s="121" t="n"/>
+      <c r="M66" s="121" t="n"/>
+      <c r="N66" s="121" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="108" t="n">
+      <c r="A67" s="123" t="n">
         <v>10</v>
       </c>
-      <c r="B67" s="108" t="n">
+      <c r="B67" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="C67" s="109">
+      <c r="C67" s="124">
         <f>A67*10+B67</f>
         <v/>
       </c>
-      <c r="D67" s="106" t="n"/>
-      <c r="E67" s="106" t="n"/>
-      <c r="F67" s="106" t="n"/>
-      <c r="G67" s="106" t="n"/>
-      <c r="H67" s="106" t="n"/>
-      <c r="I67" s="106" t="n"/>
-      <c r="J67" s="106" t="n"/>
-      <c r="K67" s="106" t="n"/>
-      <c r="L67" s="106" t="n"/>
-      <c r="M67" s="106" t="n"/>
-      <c r="N67" s="106" t="n"/>
+      <c r="D67" s="121" t="n"/>
+      <c r="E67" s="121" t="n"/>
+      <c r="F67" s="121" t="n"/>
+      <c r="G67" s="121" t="n"/>
+      <c r="H67" s="121" t="n"/>
+      <c r="I67" s="121" t="n"/>
+      <c r="J67" s="121" t="n"/>
+      <c r="K67" s="121" t="n"/>
+      <c r="L67" s="121" t="n"/>
+      <c r="M67" s="121" t="n"/>
+      <c r="N67" s="121" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="108" t="n">
+      <c r="A68" s="123" t="n">
         <v>10</v>
       </c>
-      <c r="B68" s="108" t="n">
+      <c r="B68" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="C68" s="109">
+      <c r="C68" s="124">
         <f>A68*10+B68</f>
         <v/>
       </c>
-      <c r="D68" s="106" t="n"/>
-      <c r="E68" s="106" t="n"/>
-      <c r="F68" s="106" t="n"/>
-      <c r="G68" s="106" t="n"/>
-      <c r="H68" s="106" t="n"/>
-      <c r="I68" s="106" t="n"/>
-      <c r="J68" s="106" t="n"/>
-      <c r="K68" s="106" t="n"/>
-      <c r="L68" s="106" t="n"/>
-      <c r="M68" s="106" t="n"/>
-      <c r="N68" s="106" t="n"/>
+      <c r="D68" s="121" t="n"/>
+      <c r="E68" s="121" t="n"/>
+      <c r="F68" s="121" t="n"/>
+      <c r="G68" s="121" t="n"/>
+      <c r="H68" s="121" t="n"/>
+      <c r="I68" s="121" t="n"/>
+      <c r="J68" s="121" t="n"/>
+      <c r="K68" s="121" t="n"/>
+      <c r="L68" s="121" t="n"/>
+      <c r="M68" s="121" t="n"/>
+      <c r="N68" s="121" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="108" t="n">
+      <c r="A69" s="123" t="n">
         <v>10</v>
       </c>
-      <c r="B69" s="108" t="n">
+      <c r="B69" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="C69" s="109">
+      <c r="C69" s="124">
         <f>A69*10+B69</f>
         <v/>
       </c>
-      <c r="D69" s="106" t="n"/>
-      <c r="E69" s="106" t="n"/>
-      <c r="F69" s="106" t="n"/>
-      <c r="G69" s="106" t="n"/>
-      <c r="H69" s="106" t="n"/>
-      <c r="I69" s="106" t="n"/>
-      <c r="J69" s="106" t="n"/>
-      <c r="K69" s="106" t="n"/>
-      <c r="L69" s="106" t="n"/>
-      <c r="M69" s="106" t="n"/>
-      <c r="N69" s="106" t="n"/>
+      <c r="D69" s="121" t="n"/>
+      <c r="E69" s="121" t="n"/>
+      <c r="F69" s="121" t="n"/>
+      <c r="G69" s="121" t="n"/>
+      <c r="H69" s="121" t="n"/>
+      <c r="I69" s="121" t="n"/>
+      <c r="J69" s="121" t="n"/>
+      <c r="K69" s="121" t="n"/>
+      <c r="L69" s="121" t="n"/>
+      <c r="M69" s="121" t="n"/>
+      <c r="N69" s="121" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="108" t="n">
+      <c r="A70" s="123" t="n">
         <v>11</v>
       </c>
-      <c r="B70" s="108" t="n">
+      <c r="B70" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="C70" s="109">
+      <c r="C70" s="124">
         <f>A70*10+B70</f>
         <v/>
       </c>
-      <c r="D70" s="106" t="n"/>
-      <c r="E70" s="106" t="n"/>
-      <c r="F70" s="106" t="n"/>
-      <c r="G70" s="106" t="n"/>
-      <c r="H70" s="106" t="n"/>
-      <c r="I70" s="106" t="n"/>
-      <c r="J70" s="106" t="n"/>
-      <c r="K70" s="106" t="n"/>
-      <c r="L70" s="106" t="n"/>
-      <c r="M70" s="106" t="n"/>
-      <c r="N70" s="106" t="n"/>
+      <c r="D70" s="121" t="n"/>
+      <c r="E70" s="121" t="n"/>
+      <c r="F70" s="121" t="n"/>
+      <c r="G70" s="121" t="n"/>
+      <c r="H70" s="121" t="n"/>
+      <c r="I70" s="121" t="n"/>
+      <c r="J70" s="121" t="n"/>
+      <c r="K70" s="121" t="n"/>
+      <c r="L70" s="121" t="n"/>
+      <c r="M70" s="121" t="n"/>
+      <c r="N70" s="121" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="108" t="n">
+      <c r="A71" s="123" t="n">
         <v>11</v>
       </c>
-      <c r="B71" s="108" t="n">
+      <c r="B71" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="C71" s="109">
+      <c r="C71" s="124">
         <f>A71*10+B71</f>
         <v/>
       </c>
-      <c r="D71" s="106" t="n"/>
-      <c r="E71" s="106" t="n"/>
-      <c r="F71" s="106" t="n"/>
-      <c r="G71" s="106" t="n"/>
-      <c r="H71" s="106" t="n"/>
-      <c r="I71" s="106" t="n"/>
-      <c r="J71" s="106" t="n"/>
-      <c r="K71" s="106" t="n"/>
-      <c r="L71" s="106" t="n"/>
-      <c r="M71" s="106" t="n"/>
-      <c r="N71" s="106" t="n"/>
+      <c r="D71" s="121" t="n"/>
+      <c r="E71" s="121" t="n"/>
+      <c r="F71" s="121" t="n"/>
+      <c r="G71" s="121" t="n"/>
+      <c r="H71" s="121" t="n"/>
+      <c r="I71" s="121" t="n"/>
+      <c r="J71" s="121" t="n"/>
+      <c r="K71" s="121" t="n"/>
+      <c r="L71" s="121" t="n"/>
+      <c r="M71" s="121" t="n"/>
+      <c r="N71" s="121" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="108" t="n">
+      <c r="A72" s="123" t="n">
         <v>11</v>
       </c>
-      <c r="B72" s="108" t="n">
+      <c r="B72" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="C72" s="109">
+      <c r="C72" s="124">
         <f>A72*10+B72</f>
         <v/>
       </c>
-      <c r="D72" s="106" t="n"/>
-      <c r="E72" s="106" t="n"/>
-      <c r="F72" s="106" t="n"/>
-      <c r="G72" s="106" t="n"/>
-      <c r="H72" s="106" t="n"/>
-      <c r="I72" s="106" t="n"/>
-      <c r="J72" s="106" t="n"/>
-      <c r="K72" s="106" t="n"/>
-      <c r="L72" s="106" t="n"/>
-      <c r="M72" s="106" t="n"/>
-      <c r="N72" s="106" t="n"/>
+      <c r="D72" s="121" t="n"/>
+      <c r="E72" s="121" t="n"/>
+      <c r="F72" s="121" t="n"/>
+      <c r="G72" s="121" t="n"/>
+      <c r="H72" s="121" t="n"/>
+      <c r="I72" s="121" t="n"/>
+      <c r="J72" s="121" t="n"/>
+      <c r="K72" s="121" t="n"/>
+      <c r="L72" s="121" t="n"/>
+      <c r="M72" s="121" t="n"/>
+      <c r="N72" s="121" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="108" t="n">
+      <c r="A73" s="123" t="n">
         <v>11</v>
       </c>
-      <c r="B73" s="108" t="n">
+      <c r="B73" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="C73" s="109">
+      <c r="C73" s="124">
         <f>A73*10+B73</f>
         <v/>
       </c>
-      <c r="D73" s="106" t="n"/>
-      <c r="E73" s="106" t="n"/>
-      <c r="F73" s="106" t="n"/>
-      <c r="G73" s="106" t="n"/>
-      <c r="H73" s="106" t="n"/>
-      <c r="I73" s="106" t="n"/>
-      <c r="J73" s="106" t="n"/>
-      <c r="K73" s="106" t="n"/>
-      <c r="L73" s="106" t="n"/>
-      <c r="M73" s="106" t="n"/>
-      <c r="N73" s="106" t="n"/>
+      <c r="D73" s="121" t="n"/>
+      <c r="E73" s="121" t="n"/>
+      <c r="F73" s="121" t="n"/>
+      <c r="G73" s="121" t="n"/>
+      <c r="H73" s="121" t="n"/>
+      <c r="I73" s="121" t="n"/>
+      <c r="J73" s="121" t="n"/>
+      <c r="K73" s="121" t="n"/>
+      <c r="L73" s="121" t="n"/>
+      <c r="M73" s="121" t="n"/>
+      <c r="N73" s="121" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="108" t="n">
+      <c r="A74" s="123" t="n">
         <v>11</v>
       </c>
-      <c r="B74" s="108" t="n">
+      <c r="B74" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="C74" s="109">
+      <c r="C74" s="124">
         <f>A74*10+B74</f>
         <v/>
       </c>
-      <c r="D74" s="106" t="n"/>
-      <c r="E74" s="106" t="n"/>
-      <c r="F74" s="106" t="n"/>
-      <c r="G74" s="106" t="n"/>
-      <c r="H74" s="106" t="n"/>
-      <c r="I74" s="106" t="n"/>
-      <c r="J74" s="106" t="n"/>
-      <c r="K74" s="106" t="n"/>
-      <c r="L74" s="106" t="n"/>
-      <c r="M74" s="106" t="n"/>
-      <c r="N74" s="106" t="n"/>
+      <c r="D74" s="121" t="n"/>
+      <c r="E74" s="121" t="n"/>
+      <c r="F74" s="121" t="n"/>
+      <c r="G74" s="121" t="n"/>
+      <c r="H74" s="121" t="n"/>
+      <c r="I74" s="121" t="n"/>
+      <c r="J74" s="121" t="n"/>
+      <c r="K74" s="121" t="n"/>
+      <c r="L74" s="121" t="n"/>
+      <c r="M74" s="121" t="n"/>
+      <c r="N74" s="121" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="108" t="n">
+      <c r="A75" s="123" t="n">
         <v>12</v>
       </c>
-      <c r="B75" s="108" t="n">
+      <c r="B75" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="C75" s="109">
+      <c r="C75" s="124">
         <f>A75*10+B75</f>
         <v/>
       </c>
-      <c r="D75" s="106" t="n"/>
-      <c r="E75" s="106" t="n"/>
-      <c r="F75" s="106" t="n"/>
-      <c r="G75" s="106" t="n"/>
-      <c r="H75" s="106" t="n"/>
-      <c r="I75" s="106" t="n"/>
-      <c r="J75" s="106" t="n"/>
-      <c r="K75" s="106" t="n"/>
-      <c r="L75" s="106" t="n"/>
-      <c r="M75" s="106" t="n"/>
-      <c r="N75" s="106" t="n"/>
+      <c r="D75" s="121" t="n"/>
+      <c r="E75" s="121" t="n"/>
+      <c r="F75" s="121" t="n"/>
+      <c r="G75" s="121" t="n"/>
+      <c r="H75" s="121" t="n"/>
+      <c r="I75" s="121" t="n"/>
+      <c r="J75" s="121" t="n"/>
+      <c r="K75" s="121" t="n"/>
+      <c r="L75" s="121" t="n"/>
+      <c r="M75" s="121" t="n"/>
+      <c r="N75" s="121" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="108" t="n">
+      <c r="A76" s="123" t="n">
         <v>12</v>
       </c>
-      <c r="B76" s="108" t="n">
+      <c r="B76" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="C76" s="109">
+      <c r="C76" s="124">
         <f>A76*10+B76</f>
         <v/>
       </c>
-      <c r="D76" s="106" t="n"/>
-      <c r="E76" s="106" t="n"/>
-      <c r="F76" s="106" t="n"/>
-      <c r="G76" s="106" t="n"/>
-      <c r="H76" s="106" t="n"/>
-      <c r="I76" s="106" t="n"/>
-      <c r="J76" s="106" t="n"/>
-      <c r="K76" s="106" t="n"/>
-      <c r="L76" s="106" t="n"/>
-      <c r="M76" s="106" t="n"/>
-      <c r="N76" s="106" t="n"/>
+      <c r="D76" s="121" t="n"/>
+      <c r="E76" s="121" t="n"/>
+      <c r="F76" s="121" t="n"/>
+      <c r="G76" s="121" t="n"/>
+      <c r="H76" s="121" t="n"/>
+      <c r="I76" s="121" t="n"/>
+      <c r="J76" s="121" t="n"/>
+      <c r="K76" s="121" t="n"/>
+      <c r="L76" s="121" t="n"/>
+      <c r="M76" s="121" t="n"/>
+      <c r="N76" s="121" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="108" t="n">
+      <c r="A77" s="123" t="n">
         <v>12</v>
       </c>
-      <c r="B77" s="108" t="n">
+      <c r="B77" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="C77" s="109">
+      <c r="C77" s="124">
         <f>A77*10+B77</f>
         <v/>
       </c>
-      <c r="D77" s="106" t="n"/>
-      <c r="E77" s="106" t="n"/>
-      <c r="F77" s="106" t="n"/>
-      <c r="G77" s="106" t="n"/>
-      <c r="H77" s="106" t="n"/>
-      <c r="I77" s="106" t="n"/>
-      <c r="J77" s="106" t="n"/>
-      <c r="K77" s="106" t="n"/>
-      <c r="L77" s="106" t="n"/>
-      <c r="M77" s="106" t="n"/>
-      <c r="N77" s="106" t="n"/>
+      <c r="D77" s="121" t="n"/>
+      <c r="E77" s="121" t="n"/>
+      <c r="F77" s="121" t="n"/>
+      <c r="G77" s="121" t="n"/>
+      <c r="H77" s="121" t="n"/>
+      <c r="I77" s="121" t="n"/>
+      <c r="J77" s="121" t="n"/>
+      <c r="K77" s="121" t="n"/>
+      <c r="L77" s="121" t="n"/>
+      <c r="M77" s="121" t="n"/>
+      <c r="N77" s="121" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="108" t="n">
+      <c r="A78" s="123" t="n">
         <v>12</v>
       </c>
-      <c r="B78" s="108" t="n">
+      <c r="B78" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="C78" s="109">
+      <c r="C78" s="124">
         <f>A78*10+B78</f>
         <v/>
       </c>
-      <c r="D78" s="106" t="n"/>
-      <c r="E78" s="106" t="n"/>
-      <c r="F78" s="106" t="n"/>
-      <c r="G78" s="106" t="n"/>
-      <c r="H78" s="106" t="n"/>
-      <c r="I78" s="106" t="n"/>
-      <c r="J78" s="106" t="n"/>
-      <c r="K78" s="106" t="n"/>
-      <c r="L78" s="106" t="n"/>
-      <c r="M78" s="106" t="n"/>
-      <c r="N78" s="106" t="n"/>
+      <c r="D78" s="121" t="n"/>
+      <c r="E78" s="121" t="n"/>
+      <c r="F78" s="121" t="n"/>
+      <c r="G78" s="121" t="n"/>
+      <c r="H78" s="121" t="n"/>
+      <c r="I78" s="121" t="n"/>
+      <c r="J78" s="121" t="n"/>
+      <c r="K78" s="121" t="n"/>
+      <c r="L78" s="121" t="n"/>
+      <c r="M78" s="121" t="n"/>
+      <c r="N78" s="121" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="108" t="n">
+      <c r="A79" s="123" t="n">
         <v>12</v>
       </c>
-      <c r="B79" s="108" t="n">
+      <c r="B79" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="C79" s="109">
+      <c r="C79" s="124">
         <f>A79*10+B79</f>
         <v/>
       </c>
-      <c r="D79" s="106" t="n"/>
-      <c r="E79" s="106" t="n"/>
-      <c r="F79" s="106" t="n"/>
-      <c r="G79" s="106" t="n"/>
-      <c r="H79" s="106" t="n"/>
-      <c r="I79" s="106" t="n"/>
-      <c r="J79" s="106" t="n"/>
-      <c r="K79" s="106" t="n"/>
-      <c r="L79" s="106" t="n"/>
-      <c r="M79" s="106" t="n"/>
-      <c r="N79" s="106" t="n"/>
+      <c r="D79" s="121" t="n"/>
+      <c r="E79" s="121" t="n"/>
+      <c r="F79" s="121" t="n"/>
+      <c r="G79" s="121" t="n"/>
+      <c r="H79" s="121" t="n"/>
+      <c r="I79" s="121" t="n"/>
+      <c r="J79" s="121" t="n"/>
+      <c r="K79" s="121" t="n"/>
+      <c r="L79" s="121" t="n"/>
+      <c r="M79" s="121" t="n"/>
+      <c r="N79" s="121" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6886,7 +11125,7 @@
   <sheetData>
     <row r="1">
       <c r="A1">
-        <f>IMPORTRANGE('z_Config'!$B$1,"02_UI_UX!A4:R68")</f>
+        <f>IMPORTRANGE('z_Config'!$B$1,"02_UI_UX!A4:R200")</f>
         <v/>
       </c>
     </row>
@@ -6906,7 +11145,7 @@
   <sheetData>
     <row r="1">
       <c r="A1">
-        <f>IMPORTRANGE('z_Config'!$B$1,"03_Tính_năng!A4:T92")</f>
+        <f>IMPORTRANGE('z_Config'!$B$1,"03_Tính_năng!A4:T200")</f>
         <v/>
       </c>
     </row>

--- a/BaoCao_BGD_TimViec123.xlsx
+++ b/BaoCao_BGD_TimViec123.xlsx
@@ -35,7 +35,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="36">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -209,19 +209,36 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C62828"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001155CC"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001A1A1A"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -287,7 +304,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -309,11 +326,55 @@
         <color rgb="00C9D6E5"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C9D6E5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C9D6E5"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9D6E5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C9D6E5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D6E5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C9D6E5"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9D6E5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D6E5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -543,14 +604,45 @@
     <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -559,10 +651,7 @@
     <xf numFmtId="3" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="22" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -571,26 +660,52 @@
     <xf numFmtId="3" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -599,19 +714,54 @@
     <xf numFmtId="3" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="002E7D32"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D9F0DD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00C62828"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FBE3E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00B8860B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF3CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1066,7 +1216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1238,41 +1388,40 @@
       <c r="E14" s="14" t="n"/>
       <c r="F14" s="14" t="n"/>
     </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Nghiệm thu theo người dùng: hành trình ĐẠT khi mọi bước Pass và không có lỗi Critical/High đang mở; vai trò ĐẠT khi mọi hành trình ĐẠT.</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>KÍCH HOẠT KẾT NỐI (làm 1 lần)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>① File làm việc QA</t>
-        </is>
-      </c>
-      <c r="B17" s="16">
-        <f>IMPORTRANGE('z_Config'!$B$1,"05_Lỗi_Tester!E4")</f>
-        <v/>
-      </c>
-      <c r="C17" s="17" t="n"/>
-      <c r="D17" s="17" t="n"/>
-      <c r="E17" s="17" t="n"/>
-      <c r="F17" s="17" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>② File Database</t>
+          <t>① File làm việc QA</t>
         </is>
       </c>
       <c r="B18" s="16">
-        <f>IMPORTRANGE('z_Config'!$B$3,"'HS DN'!D3")</f>
+        <f>IMPORTRANGE('z_Config'!$B$1,"05_Lỗi_Tester!E4")</f>
         <v/>
       </c>
       <c r="C18" s="17" t="n"/>
@@ -1280,70 +1429,69 @@
       <c r="E18" s="17" t="n"/>
       <c r="F18" s="17" t="n"/>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>② File Database</t>
+        </is>
+      </c>
+      <c r="B19" s="16">
+        <f>IMPORTRANGE('z_Config'!$B$3,"'HS DN'!D3")</f>
+        <v/>
+      </c>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>→ Nếu ô ① hoặc ② báo #REF!: bấm vào ô đó → "Cho phép truy cập / Allow access". Làm 1 lần cho mỗi ô.</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Trạng thái kết nối</t>
         </is>
       </c>
-      <c r="B20" s="20">
+      <c r="B21" s="20">
         <f>IF(ISERROR('z_Trang'!$B$1),"⚠ Chưa kết nối file làm việc","✔ Đã kết nối")&amp;"   |   "&amp;IF(ISERROR('z_DB_DN'!$A:$A),"⚠ Chưa kết nối Database","✔ Database OK")</f>
         <v/>
       </c>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="14" t="n"/>
-      <c r="F20" s="14" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>LIÊN KẾT</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>File làm việc (QA)</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1J2A_OiWz7IeYsgafLDY3mIfZsG-xCNGhkNaSQkhicHg/edit</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="14" t="n"/>
-      <c r="E23" s="14" t="n"/>
-      <c r="F23" s="14" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>File Database (Hồ sơ)</t>
+          <t>File làm việc (QA)</t>
         </is>
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1i7-xLYiLHg60EqmCpfeA9B4Y0T-8YsgXk-_0qJ4eACo/edit</t>
+          <t>https://docs.google.com/spreadsheets/d/1J2A_OiWz7IeYsgafLDY3mIfZsG-xCNGhkNaSQkhicHg/edit</t>
         </is>
       </c>
       <c r="C24" s="14" t="n"/>
@@ -1351,31 +1499,48 @@
       <c r="E24" s="14" t="n"/>
       <c r="F24" s="14" t="n"/>
     </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>File Database (Hồ sơ)</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1i7-xLYiLHg60EqmCpfeA9B4Y0T-8YsgXk-_0qJ4eACo/edit</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="14" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="A16:F16"/>
+  <mergeCells count="25">
+    <mergeCell ref="B25:F25"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="B21:F21"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="B11:F11"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="C6:F6"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="B14:F14"/>
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="C5:F5"/>
-    <mergeCell ref="B17:F17"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="A19:F19"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="B19:F19"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4737,23 +4902,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:N114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>BIÊN BẢN / CHECKLIST NGHIỆM THU</t>
+          <t>BIÊN BẢN NGHIỆM THU THEO NGƯỜI DÙNG — WEBSITE TIMVIEC123</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -4763,11 +4934,17 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="22" t="inlineStr">
-        <is>
-          <t>Cột Kết luận &amp; Người duyệt do người duyệt điền.</t>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>Nghiệm thu theo góc nhìn người dùng: mỗi VAI TRÒ phải đi hết được các HÀNH TRÌNH chính. Tester chỉ nhập ô nền vàng ở mục IV; mục I–III tự tính. Mức độ/trạng thái lỗi tra live từ 05_Lỗi_Tester theo BUG_ID.</t>
         </is>
       </c>
       <c r="B2" s="5" t="n"/>
@@ -4777,6 +4954,12 @@
       <c r="F2" s="5" t="n"/>
       <c r="G2" s="5" t="n"/>
       <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="43" t="inlineStr">
@@ -4798,237 +4981,4158 @@
         <f>TODAY()</f>
         <v/>
       </c>
-      <c r="E4" s="88" t="n"/>
-      <c r="F4" s="43" t="inlineStr">
+      <c r="E4" s="43" t="inlineStr">
         <is>
           <t>Người lập</t>
         </is>
       </c>
-      <c r="G4" s="89" t="inlineStr"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="90" t="inlineStr">
+      <c r="F4" s="88" t="inlineStr"/>
+      <c r="G4" s="89" t="n"/>
+      <c r="H4" s="89" t="n"/>
+      <c r="I4" s="43" t="inlineStr">
+        <is>
+          <t>Môi trường</t>
+        </is>
+      </c>
+      <c r="J4" s="88" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="K4" s="89" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>I. TỔNG HỢP THEO VAI TRÒ NGƯỜI DÙNG (tự tính từ mục III–IV)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
+      <c r="K6" s="7" t="n"/>
+      <c r="L6" s="7" t="n"/>
+      <c r="M6" s="7" t="n"/>
+      <c r="N6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="90" t="inlineStr">
+        <is>
+          <t>Vai trò</t>
+        </is>
+      </c>
+      <c r="B7" s="90" t="inlineStr">
+        <is>
+          <t>Số hành trình</t>
+        </is>
+      </c>
+      <c r="C7" s="90" t="inlineStr">
+        <is>
+          <t>Hành trình ĐẠT</t>
+        </is>
+      </c>
+      <c r="D7" s="90" t="inlineStr">
+        <is>
+          <t>Tổng số bước</t>
+        </is>
+      </c>
+      <c r="E7" s="90" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F7" s="90" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G7" s="90" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H7" s="90" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="I7" s="90" t="inlineStr">
+        <is>
+          <t>% Pass</t>
+        </is>
+      </c>
+      <c r="J7" s="90" t="inlineStr">
+        <is>
+          <t>Lỗi C/H đang chặn</t>
+        </is>
+      </c>
+      <c r="K7" s="90" t="inlineStr">
+        <is>
+          <t>Kết luận</t>
+        </is>
+      </c>
+      <c r="L7" s="90" t="inlineStr">
+        <is>
+          <t>Ghi chú / Người duyệt</t>
+        </is>
+      </c>
+      <c r="M7" s="91" t="n"/>
+      <c r="N7" s="91" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="74" t="inlineStr">
+        <is>
+          <t>Khách vãng lai</t>
+        </is>
+      </c>
+      <c r="B8" s="52">
+        <f>COUNTIF($B$35:$B$49,$A8)</f>
+        <v/>
+      </c>
+      <c r="C8" s="92">
+        <f>COUNTIFS($B$35:$B$49,$A8,$K$35:$K$49,"ĐẠT")</f>
+        <v/>
+      </c>
+      <c r="D8" s="52">
+        <f>COUNTIFS($C$54:$C$114,$A8,$A$54:$A$114,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="E8" s="52">
+        <f>COUNTIFS($C$54:$C$114,$A8,$G$54:$G$114,"Pass")</f>
+        <v/>
+      </c>
+      <c r="F8" s="52">
+        <f>COUNTIFS($C$54:$C$114,$A8,$G$54:$G$114,"Fail")</f>
+        <v/>
+      </c>
+      <c r="G8" s="52">
+        <f>COUNTIFS($C$54:$C$114,$A8,$G$54:$G$114,"Blocked")</f>
+        <v/>
+      </c>
+      <c r="H8" s="52">
+        <f>D8-E8-F8-G8</f>
+        <v/>
+      </c>
+      <c r="I8" s="53">
+        <f>IF(D8=0,"",E8/D8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="93">
+        <f>COUNTIFS($C$54:$C$114,$A8,$K$54:$K$114,"CHẶN")</f>
+        <v/>
+      </c>
+      <c r="K8" s="34">
+        <f>IF(B8=0,"—",IF(AND(C8=B8,J8=0),"ĐẠT",IF(OR(F8+G8&gt;0,J8&gt;0),"CHƯA ĐẠT","ĐANG TEST")))</f>
+        <v/>
+      </c>
+      <c r="L8" s="94" t="inlineStr"/>
+      <c r="M8" s="89" t="n"/>
+      <c r="N8" s="89" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="76" t="inlineStr">
+        <is>
+          <t>Ứng viên</t>
+        </is>
+      </c>
+      <c r="B9" s="49">
+        <f>COUNTIF($B$35:$B$49,$A9)</f>
+        <v/>
+      </c>
+      <c r="C9" s="95">
+        <f>COUNTIFS($B$35:$B$49,$A9,$K$35:$K$49,"ĐẠT")</f>
+        <v/>
+      </c>
+      <c r="D9" s="49">
+        <f>COUNTIFS($C$54:$C$114,$A9,$A$54:$A$114,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="E9" s="49">
+        <f>COUNTIFS($C$54:$C$114,$A9,$G$54:$G$114,"Pass")</f>
+        <v/>
+      </c>
+      <c r="F9" s="49">
+        <f>COUNTIFS($C$54:$C$114,$A9,$G$54:$G$114,"Fail")</f>
+        <v/>
+      </c>
+      <c r="G9" s="49">
+        <f>COUNTIFS($C$54:$C$114,$A9,$G$54:$G$114,"Blocked")</f>
+        <v/>
+      </c>
+      <c r="H9" s="49">
+        <f>D9-E9-F9-G9</f>
+        <v/>
+      </c>
+      <c r="I9" s="50">
+        <f>IF(D9=0,"",E9/D9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="96">
+        <f>COUNTIFS($C$54:$C$114,$A9,$K$54:$K$114,"CHẶN")</f>
+        <v/>
+      </c>
+      <c r="K9" s="40">
+        <f>IF(B9=0,"—",IF(AND(C9=B9,J9=0),"ĐẠT",IF(OR(F9+G9&gt;0,J9&gt;0),"CHƯA ĐẠT","ĐANG TEST")))</f>
+        <v/>
+      </c>
+      <c r="L9" s="94" t="inlineStr"/>
+      <c r="M9" s="89" t="n"/>
+      <c r="N9" s="89" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="74" t="inlineStr">
+        <is>
+          <t>Nhà tuyển dụng (DN)</t>
+        </is>
+      </c>
+      <c r="B10" s="52">
+        <f>COUNTIF($B$35:$B$49,$A10)</f>
+        <v/>
+      </c>
+      <c r="C10" s="92">
+        <f>COUNTIFS($B$35:$B$49,$A10,$K$35:$K$49,"ĐẠT")</f>
+        <v/>
+      </c>
+      <c r="D10" s="52">
+        <f>COUNTIFS($C$54:$C$114,$A10,$A$54:$A$114,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="E10" s="52">
+        <f>COUNTIFS($C$54:$C$114,$A10,$G$54:$G$114,"Pass")</f>
+        <v/>
+      </c>
+      <c r="F10" s="52">
+        <f>COUNTIFS($C$54:$C$114,$A10,$G$54:$G$114,"Fail")</f>
+        <v/>
+      </c>
+      <c r="G10" s="52">
+        <f>COUNTIFS($C$54:$C$114,$A10,$G$54:$G$114,"Blocked")</f>
+        <v/>
+      </c>
+      <c r="H10" s="52">
+        <f>D10-E10-F10-G10</f>
+        <v/>
+      </c>
+      <c r="I10" s="53">
+        <f>IF(D10=0,"",E10/D10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="93">
+        <f>COUNTIFS($C$54:$C$114,$A10,$K$54:$K$114,"CHẶN")</f>
+        <v/>
+      </c>
+      <c r="K10" s="34">
+        <f>IF(B10=0,"—",IF(AND(C10=B10,J10=0),"ĐẠT",IF(OR(F10+G10&gt;0,J10&gt;0),"CHƯA ĐẠT","ĐANG TEST")))</f>
+        <v/>
+      </c>
+      <c r="L10" s="94" t="inlineStr"/>
+      <c r="M10" s="89" t="n"/>
+      <c r="N10" s="89" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="76" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="B11" s="49">
+        <f>COUNTIF($B$35:$B$49,$A11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="95">
+        <f>COUNTIFS($B$35:$B$49,$A11,$K$35:$K$49,"ĐẠT")</f>
+        <v/>
+      </c>
+      <c r="D11" s="49">
+        <f>COUNTIFS($C$54:$C$114,$A11,$A$54:$A$114,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="E11" s="49">
+        <f>COUNTIFS($C$54:$C$114,$A11,$G$54:$G$114,"Pass")</f>
+        <v/>
+      </c>
+      <c r="F11" s="49">
+        <f>COUNTIFS($C$54:$C$114,$A11,$G$54:$G$114,"Fail")</f>
+        <v/>
+      </c>
+      <c r="G11" s="49">
+        <f>COUNTIFS($C$54:$C$114,$A11,$G$54:$G$114,"Blocked")</f>
+        <v/>
+      </c>
+      <c r="H11" s="49">
+        <f>D11-E11-F11-G11</f>
+        <v/>
+      </c>
+      <c r="I11" s="50">
+        <f>IF(D11=0,"",E11/D11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="96">
+        <f>COUNTIFS($C$54:$C$114,$A11,$K$54:$K$114,"CHẶN")</f>
+        <v/>
+      </c>
+      <c r="K11" s="40">
+        <f>IF(B11=0,"—",IF(AND(C11=B11,J11=0),"ĐẠT",IF(OR(F11+G11&gt;0,J11&gt;0),"CHƯA ĐẠT","ĐANG TEST")))</f>
+        <v/>
+      </c>
+      <c r="L11" s="94" t="inlineStr"/>
+      <c r="M11" s="89" t="n"/>
+      <c r="N11" s="89" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="74" t="inlineStr">
+        <is>
+          <t>Quản trị viên</t>
+        </is>
+      </c>
+      <c r="B12" s="52">
+        <f>COUNTIF($B$35:$B$49,$A12)</f>
+        <v/>
+      </c>
+      <c r="C12" s="92">
+        <f>COUNTIFS($B$35:$B$49,$A12,$K$35:$K$49,"ĐẠT")</f>
+        <v/>
+      </c>
+      <c r="D12" s="52">
+        <f>COUNTIFS($C$54:$C$114,$A12,$A$54:$A$114,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="E12" s="52">
+        <f>COUNTIFS($C$54:$C$114,$A12,$G$54:$G$114,"Pass")</f>
+        <v/>
+      </c>
+      <c r="F12" s="52">
+        <f>COUNTIFS($C$54:$C$114,$A12,$G$54:$G$114,"Fail")</f>
+        <v/>
+      </c>
+      <c r="G12" s="52">
+        <f>COUNTIFS($C$54:$C$114,$A12,$G$54:$G$114,"Blocked")</f>
+        <v/>
+      </c>
+      <c r="H12" s="52">
+        <f>D12-E12-F12-G12</f>
+        <v/>
+      </c>
+      <c r="I12" s="53">
+        <f>IF(D12=0,"",E12/D12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="93">
+        <f>COUNTIFS($C$54:$C$114,$A12,$K$54:$K$114,"CHẶN")</f>
+        <v/>
+      </c>
+      <c r="K12" s="34">
+        <f>IF(B12=0,"—",IF(AND(C12=B12,J12=0),"ĐẠT",IF(OR(F12+G12&gt;0,J12&gt;0),"CHƯA ĐẠT","ĐANG TEST")))</f>
+        <v/>
+      </c>
+      <c r="L12" s="94" t="inlineStr"/>
+      <c r="M12" s="89" t="n"/>
+      <c r="N12" s="89" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="B13" s="97">
+        <f>SUM(B8:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="97">
+        <f>SUM(C8:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="97">
+        <f>SUM(D8:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="97">
+        <f>SUM(E8:E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="97">
+        <f>SUM(F8:F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="97">
+        <f>SUM(G8:G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="97">
+        <f>SUM(H8:H12)</f>
+        <v/>
+      </c>
+      <c r="I13" s="98">
+        <f>IF(D13=0,"",E13/D13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="97">
+        <f>SUM(J8:J12)</f>
+        <v/>
+      </c>
+      <c r="K13" s="81">
+        <f>IF(B13=0,"—",IF(AND(C13=B13,J13=0),"ĐẠT",IF(OR(F13+G13&gt;0,J13&gt;0),"CHƯA ĐẠT","ĐANG TEST")))</f>
+        <v/>
+      </c>
+      <c r="L13" s="29" t="inlineStr"/>
+      <c r="M13" s="29" t="n"/>
+      <c r="N13" s="29" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="73" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (tự động)</t>
+        </is>
+      </c>
+      <c r="B15" s="60" t="n"/>
+      <c r="C15" s="99">
+        <f>IF(B13=0,"Chưa có hành trình nghiệm thu",IF(K13="ĐẠT","✔ ĐỦ ĐIỀU KIỆN NGHIỆM THU — "&amp;C13&amp;"/"&amp;B13&amp;" hành trình đạt, không còn lỗi Critical/High chặn","✖ CHƯA ĐỦ ĐIỀU KIỆN — "&amp;C13&amp;"/"&amp;B13&amp;" hành trình đạt; "&amp;F13&amp;" bước Fail, "&amp;G13&amp;" Blocked, "&amp;H13&amp;" chưa test; "&amp;J13&amp;" lỗi Critical/High đang chặn"))</f>
+        <v/>
+      </c>
+      <c r="D15" s="63" t="n"/>
+      <c r="E15" s="63" t="n"/>
+      <c r="F15" s="63" t="n"/>
+      <c r="G15" s="63" t="n"/>
+      <c r="H15" s="63" t="n"/>
+      <c r="I15" s="63" t="n"/>
+      <c r="J15" s="63" t="n"/>
+      <c r="K15" s="63" t="n"/>
+      <c r="L15" s="63" t="n"/>
+      <c r="M15" s="63" t="n"/>
+      <c r="N15" s="63" t="n"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="73" t="inlineStr">
+        <is>
+          <t>QUYẾT ĐỊNH BGD</t>
+        </is>
+      </c>
+      <c r="B16" s="60" t="n"/>
+      <c r="C16" s="100" t="inlineStr"/>
+      <c r="D16" s="89" t="n"/>
+      <c r="E16" s="89" t="n"/>
+      <c r="F16" s="101" t="inlineStr">
+        <is>
+          <t>Điều kiện / ngoại lệ</t>
+        </is>
+      </c>
+      <c r="G16" s="60" t="n"/>
+      <c r="H16" s="94" t="inlineStr"/>
+      <c r="I16" s="89" t="n"/>
+      <c r="J16" s="89" t="n"/>
+      <c r="K16" s="89" t="n"/>
+      <c r="L16" s="89" t="n"/>
+      <c r="M16" s="89" t="n"/>
+      <c r="N16" s="89" t="n"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>Điều kiện ĐẠT: mọi bước của hành trình là Pass và không có BUG_ID mức Critical/High còn Open/Chưa gửi Dev. Ngoại lệ phải ghi rõ lý do và người duyệt.</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>II. CHẤT LƯỢNG KỸ THUẬT (live từ file QA)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
+      <c r="K19" s="7" t="n"/>
+      <c r="L19" s="7" t="n"/>
+      <c r="M19" s="7" t="n"/>
+      <c r="N19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="90" t="inlineStr">
         <is>
           <t>Hạng mục</t>
         </is>
       </c>
-      <c r="B6" s="90" t="inlineStr">
+      <c r="B20" s="90" t="inlineStr">
         <is>
           <t>Phạm vi</t>
         </is>
       </c>
-      <c r="C6" s="90" t="inlineStr">
+      <c r="C20" s="90" t="inlineStr">
         <is>
           <t>Tổng</t>
         </is>
       </c>
-      <c r="D6" s="90" t="inlineStr">
+      <c r="D20" s="90" t="inlineStr">
         <is>
           <t>Hoàn thành</t>
         </is>
       </c>
-      <c r="E6" s="90" t="inlineStr">
+      <c r="E20" s="90" t="inlineStr">
         <is>
           <t>Tỷ lệ</t>
         </is>
       </c>
-      <c r="F6" s="90" t="inlineStr">
+      <c r="F20" s="90" t="inlineStr">
         <is>
           <t>Critical/High mở</t>
         </is>
       </c>
-      <c r="G6" s="90" t="inlineStr">
+      <c r="G20" s="90" t="inlineStr">
         <is>
           <t>Kết luận</t>
         </is>
       </c>
-      <c r="H6" s="90" t="inlineStr">
+      <c r="H20" s="90" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="74" t="inlineStr">
+      <c r="I20" s="91" t="n"/>
+      <c r="J20" s="91" t="n"/>
+      <c r="K20" s="91" t="n"/>
+      <c r="L20" s="91" t="n"/>
+      <c r="M20" s="91" t="n"/>
+      <c r="N20" s="91" t="n"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="74" t="inlineStr">
         <is>
           <t>UI/UX</t>
         </is>
       </c>
-      <c r="B7" s="91" t="inlineStr">
+      <c r="B21" s="102" t="inlineStr">
         <is>
           <t>Trang website</t>
         </is>
       </c>
-      <c r="C7" s="52">
+      <c r="C21" s="52">
         <f>'z_Trang'!$B$1</f>
         <v/>
       </c>
-      <c r="D7" s="92">
+      <c r="D21" s="103">
         <f>'z_Trang'!$D$1</f>
         <v/>
       </c>
-      <c r="E7" s="33">
+      <c r="E21" s="33">
         <f>'z_Trang'!$F$1</f>
         <v/>
       </c>
-      <c r="F7" s="93">
+      <c r="F21" s="93">
         <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"High")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"High"))</f>
         <v/>
       </c>
-      <c r="G7" s="94" t="inlineStr">
-        <is>
-          <t>Chưa nghiệm thu</t>
-        </is>
-      </c>
-      <c r="H7" s="79" t="inlineStr"/>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="76" t="inlineStr">
+      <c r="G21" s="104" t="inlineStr"/>
+      <c r="H21" s="94" t="inlineStr"/>
+      <c r="I21" s="89" t="n"/>
+      <c r="J21" s="89" t="n"/>
+      <c r="K21" s="89" t="n"/>
+      <c r="L21" s="89" t="n"/>
+      <c r="M21" s="89" t="n"/>
+      <c r="N21" s="89" t="n"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="76" t="inlineStr">
         <is>
           <t>Chức năng</t>
         </is>
       </c>
-      <c r="B8" s="95" t="inlineStr">
+      <c r="B22" s="105" t="inlineStr">
         <is>
           <t>88 tính năng</t>
         </is>
       </c>
-      <c r="C8" s="49">
+      <c r="C22" s="49">
         <f>'z_TinhNang'!$B$1</f>
         <v/>
       </c>
-      <c r="D8" s="96">
+      <c r="D22" s="106">
         <f>'z_TinhNang'!$D$1</f>
         <v/>
       </c>
-      <c r="E8" s="39">
+      <c r="E22" s="39">
         <f>'z_TinhNang'!$F$1</f>
         <v/>
       </c>
-      <c r="F8" s="97">
+      <c r="F22" s="96">
         <f>(COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Open",'z_Loi'!$L:$L,"High")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"Critical")+COUNTIFS('z_Loi'!$U:$U,"Chưa gửi Dev",'z_Loi'!$L:$L,"High"))</f>
         <v/>
       </c>
-      <c r="G8" s="98" t="inlineStr">
-        <is>
-          <t>Chưa nghiệm thu</t>
-        </is>
-      </c>
-      <c r="H8" s="99" t="inlineStr"/>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="74" t="inlineStr">
+      <c r="G22" s="104" t="inlineStr"/>
+      <c r="H22" s="94" t="inlineStr"/>
+      <c r="I22" s="89" t="n"/>
+      <c r="J22" s="89" t="n"/>
+      <c r="K22" s="89" t="n"/>
+      <c r="L22" s="89" t="n"/>
+      <c r="M22" s="89" t="n"/>
+      <c r="N22" s="89" t="n"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="74" t="inlineStr">
         <is>
           <t>Responsive</t>
         </is>
       </c>
-      <c r="B9" s="91" t="inlineStr">
+      <c r="B23" s="102" t="inlineStr">
         <is>
           <t>YC_87 + lỗi responsive</t>
         </is>
       </c>
-      <c r="C9" s="52" t="inlineStr"/>
-      <c r="D9" s="92" t="inlineStr"/>
-      <c r="E9" s="59" t="inlineStr"/>
-      <c r="F9" s="93">
+      <c r="C23" s="52" t="inlineStr"/>
+      <c r="D23" s="103" t="inlineStr"/>
+      <c r="E23" s="59" t="inlineStr"/>
+      <c r="F23" s="93">
         <f>COUNTIF('z_Loi'!$K:$K,"*Responsive*")</f>
         <v/>
       </c>
-      <c r="G9" s="94" t="inlineStr">
-        <is>
-          <t>Chưa nghiệm thu</t>
-        </is>
-      </c>
-      <c r="H9" s="79" t="inlineStr"/>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="76" t="inlineStr">
+      <c r="G23" s="104" t="inlineStr"/>
+      <c r="H23" s="94" t="inlineStr"/>
+      <c r="I23" s="89" t="n"/>
+      <c r="J23" s="89" t="n"/>
+      <c r="K23" s="89" t="n"/>
+      <c r="L23" s="89" t="n"/>
+      <c r="M23" s="89" t="n"/>
+      <c r="N23" s="89" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="76" t="inlineStr">
         <is>
           <t>Bảo mật</t>
         </is>
       </c>
-      <c r="B10" s="95" t="inlineStr">
+      <c r="B24" s="105" t="inlineStr">
         <is>
           <t>Test Case Security</t>
         </is>
       </c>
-      <c r="C10" s="49" t="inlineStr"/>
-      <c r="D10" s="96" t="inlineStr"/>
-      <c r="E10" s="54" t="inlineStr"/>
-      <c r="F10" s="97">
+      <c r="C24" s="49" t="inlineStr"/>
+      <c r="D24" s="106" t="inlineStr"/>
+      <c r="E24" s="54" t="inlineStr"/>
+      <c r="F24" s="96">
         <f>COUNTIF('z_Loi'!$K:$K,"*Security*")</f>
         <v/>
       </c>
-      <c r="G10" s="98" t="inlineStr">
-        <is>
-          <t>Chưa nghiệm thu</t>
-        </is>
-      </c>
-      <c r="H10" s="99" t="inlineStr"/>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="74" t="inlineStr">
+      <c r="G24" s="104" t="inlineStr"/>
+      <c r="H24" s="94" t="inlineStr"/>
+      <c r="I24" s="89" t="n"/>
+      <c r="J24" s="89" t="n"/>
+      <c r="K24" s="89" t="n"/>
+      <c r="L24" s="89" t="n"/>
+      <c r="M24" s="89" t="n"/>
+      <c r="N24" s="89" t="n"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="74" t="inlineStr">
         <is>
           <t>Dữ liệu</t>
         </is>
       </c>
-      <c r="B11" s="91" t="inlineStr">
+      <c r="B25" s="102" t="inlineStr">
         <is>
           <t>Test Case API/Database</t>
         </is>
       </c>
-      <c r="C11" s="52" t="inlineStr"/>
-      <c r="D11" s="92" t="inlineStr"/>
-      <c r="E11" s="59" t="inlineStr"/>
-      <c r="F11" s="100" t="inlineStr"/>
-      <c r="G11" s="94" t="inlineStr">
-        <is>
-          <t>Chưa nghiệm thu</t>
-        </is>
-      </c>
-      <c r="H11" s="79" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="73" t="inlineStr">
-        <is>
-          <t>KẾT LUẬN CHUNG</t>
-        </is>
-      </c>
-      <c r="B13" s="60" t="n"/>
-      <c r="C13" s="101" t="inlineStr">
-        <is>
-          <t>Chưa nghiệm thu</t>
-        </is>
-      </c>
-      <c r="D13" s="63" t="n"/>
-      <c r="E13" s="63" t="n"/>
-      <c r="F13" s="63" t="n"/>
-      <c r="G13" s="63" t="n"/>
-      <c r="H13" s="63" t="n"/>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="102" t="inlineStr">
-        <is>
-          <t>Điều kiện khuyến nghị: không còn Critical/High chưa được phê duyệt; phạm vi và bằng chứng đầy đủ; ngoại lệ phải có người duyệt và lý do rõ ràng.</t>
-        </is>
-      </c>
-      <c r="B14" s="103" t="n"/>
-      <c r="C14" s="103" t="n"/>
-      <c r="D14" s="103" t="n"/>
-      <c r="E14" s="103" t="n"/>
-      <c r="F14" s="103" t="n"/>
-      <c r="G14" s="103" t="n"/>
-      <c r="H14" s="103" t="n"/>
+      <c r="C25" s="52" t="inlineStr"/>
+      <c r="D25" s="103" t="inlineStr"/>
+      <c r="E25" s="59" t="inlineStr"/>
+      <c r="F25" s="107" t="inlineStr"/>
+      <c r="G25" s="104" t="inlineStr"/>
+      <c r="H25" s="94" t="inlineStr"/>
+      <c r="I25" s="89" t="n"/>
+      <c r="J25" s="89" t="n"/>
+      <c r="K25" s="89" t="n"/>
+      <c r="L25" s="89" t="n"/>
+      <c r="M25" s="89" t="n"/>
+      <c r="N25" s="89" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>NGƯỜI LẬP (Tester)</t>
+        </is>
+      </c>
+      <c r="B27" s="60" t="n"/>
+      <c r="C27" s="60" t="n"/>
+      <c r="D27" s="43" t="inlineStr">
+        <is>
+          <t>QA LEAD</t>
+        </is>
+      </c>
+      <c r="E27" s="60" t="n"/>
+      <c r="F27" s="43" t="inlineStr">
+        <is>
+          <t>ĐẠI DIỆN DEV</t>
+        </is>
+      </c>
+      <c r="G27" s="60" t="n"/>
+      <c r="H27" s="60" t="n"/>
+      <c r="I27" s="60" t="n"/>
+      <c r="J27" s="60" t="n"/>
+      <c r="K27" s="43" t="inlineStr">
+        <is>
+          <t>BAN GIÁM ĐỐC</t>
+        </is>
+      </c>
+      <c r="L27" s="60" t="n"/>
+      <c r="M27" s="60" t="n"/>
+      <c r="N27" s="60" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="108" t="inlineStr">
+        <is>
+          <t>(Ký, ghi rõ họ tên)</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="108" t="inlineStr">
+        <is>
+          <t>(Ký, ghi rõ họ tên)</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="108" t="inlineStr">
+        <is>
+          <t>(Ký, ghi rõ họ tên)</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="108" t="inlineStr">
+        <is>
+          <t>(Ký, ghi rõ họ tên)</t>
+        </is>
+      </c>
+      <c r="L28" s="14" t="n"/>
+      <c r="M28" s="14" t="n"/>
+      <c r="N28" s="14" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="n"/>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="14" t="n"/>
+      <c r="J29" s="14" t="n"/>
+      <c r="K29" s="14" t="n"/>
+      <c r="L29" s="14" t="n"/>
+      <c r="M29" s="14" t="n"/>
+      <c r="N29" s="14" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="n"/>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="14" t="n"/>
+      <c r="K30" s="14" t="n"/>
+      <c r="L30" s="14" t="n"/>
+      <c r="M30" s="14" t="n"/>
+      <c r="N30" s="14" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>III. DANH SÁCH HÀNH TRÌNH NGƯỜI DÙNG (kết luận tự tính từ mục IV)</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="7" t="n"/>
+      <c r="J32" s="7" t="n"/>
+      <c r="K32" s="7" t="n"/>
+      <c r="L32" s="7" t="n"/>
+      <c r="M32" s="7" t="n"/>
+      <c r="N32" s="7" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>Thêm hành trình mới vào các dòng trống (nhập Mã HT, Vai trò, Tên). Mã HT phải khớp với cột Mã HT ở mục IV.</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="90" t="inlineStr">
+        <is>
+          <t>Mã HT</t>
+        </is>
+      </c>
+      <c r="B34" s="90" t="inlineStr">
+        <is>
+          <t>Vai trò</t>
+        </is>
+      </c>
+      <c r="C34" s="90" t="inlineStr">
+        <is>
+          <t>Tên hành trình</t>
+        </is>
+      </c>
+      <c r="D34" s="91" t="n"/>
+      <c r="E34" s="90" t="inlineStr">
+        <is>
+          <t>Số bước</t>
+        </is>
+      </c>
+      <c r="F34" s="90" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G34" s="90" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="H34" s="90" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="I34" s="90" t="inlineStr">
+        <is>
+          <t>% Pass</t>
+        </is>
+      </c>
+      <c r="J34" s="90" t="inlineStr">
+        <is>
+          <t>Lỗi C/H chặn</t>
+        </is>
+      </c>
+      <c r="K34" s="90" t="inlineStr">
+        <is>
+          <t>Kết luận</t>
+        </is>
+      </c>
+      <c r="L34" s="90" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+      <c r="M34" s="91" t="n"/>
+      <c r="N34" s="91" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="86" t="inlineStr">
+        <is>
+          <t>KV-01</t>
+        </is>
+      </c>
+      <c r="B35" s="94" t="inlineStr">
+        <is>
+          <t>Khách vãng lai</t>
+        </is>
+      </c>
+      <c r="C35" s="109" t="inlineStr">
+        <is>
+          <t>Tìm &amp; xem việc làm khi chưa đăng nhập</t>
+        </is>
+      </c>
+      <c r="D35" s="89" t="n"/>
+      <c r="E35" s="110">
+        <f>IF($A35="","",COUNTIF($A$54:$A$114,$A35))</f>
+        <v/>
+      </c>
+      <c r="F35" s="110">
+        <f>IF($A35="","",COUNTIFS($A$54:$A$114,$A35,$G$54:$G$114,"Pass"))</f>
+        <v/>
+      </c>
+      <c r="G35" s="110">
+        <f>IF($A35="","",COUNTIFS($A$54:$A$114,$A35,$G$54:$G$114,"Fail"))</f>
+        <v/>
+      </c>
+      <c r="H35" s="110">
+        <f>IF($A35="","",COUNTIFS($A$54:$A$114,$A35,$G$54:$G$114,"Blocked"))</f>
+        <v/>
+      </c>
+      <c r="I35" s="111">
+        <f>IF(OR($A35="",N(E35)=0),"",F35/E35)</f>
+        <v/>
+      </c>
+      <c r="J35" s="112">
+        <f>IF($A35="","",COUNTIFS($A$54:$A$114,$A35,$K$54:$K$114,"CHẶN"))</f>
+        <v/>
+      </c>
+      <c r="K35" s="113">
+        <f>IF($A35="","",IF(E35=0,"Chưa có bước",IF(J35&gt;0,"CHƯA ĐẠT",IF(F35=E35,"ĐẠT",IF(G35+H35&gt;0,"CHƯA ĐẠT","ĐANG TEST")))))</f>
+        <v/>
+      </c>
+      <c r="L35" s="94" t="inlineStr"/>
+      <c r="M35" s="89" t="n"/>
+      <c r="N35" s="89" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="86" t="inlineStr">
+        <is>
+          <t>UV-01</t>
+        </is>
+      </c>
+      <c r="B36" s="94" t="inlineStr">
+        <is>
+          <t>Ứng viên</t>
+        </is>
+      </c>
+      <c r="C36" s="109" t="inlineStr">
+        <is>
+          <t>Đăng ký &amp; đăng nhập</t>
+        </is>
+      </c>
+      <c r="D36" s="89" t="n"/>
+      <c r="E36" s="110">
+        <f>IF($A36="","",COUNTIF($A$54:$A$114,$A36))</f>
+        <v/>
+      </c>
+      <c r="F36" s="110">
+        <f>IF($A36="","",COUNTIFS($A$54:$A$114,$A36,$G$54:$G$114,"Pass"))</f>
+        <v/>
+      </c>
+      <c r="G36" s="110">
+        <f>IF($A36="","",COUNTIFS($A$54:$A$114,$A36,$G$54:$G$114,"Fail"))</f>
+        <v/>
+      </c>
+      <c r="H36" s="110">
+        <f>IF($A36="","",COUNTIFS($A$54:$A$114,$A36,$G$54:$G$114,"Blocked"))</f>
+        <v/>
+      </c>
+      <c r="I36" s="111">
+        <f>IF(OR($A36="",N(E36)=0),"",F36/E36)</f>
+        <v/>
+      </c>
+      <c r="J36" s="112">
+        <f>IF($A36="","",COUNTIFS($A$54:$A$114,$A36,$K$54:$K$114,"CHẶN"))</f>
+        <v/>
+      </c>
+      <c r="K36" s="113">
+        <f>IF($A36="","",IF(E36=0,"Chưa có bước",IF(J36&gt;0,"CHƯA ĐẠT",IF(F36=E36,"ĐẠT",IF(G36+H36&gt;0,"CHƯA ĐẠT","ĐANG TEST")))))</f>
+        <v/>
+      </c>
+      <c r="L36" s="94" t="inlineStr"/>
+      <c r="M36" s="89" t="n"/>
+      <c r="N36" s="89" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="86" t="inlineStr">
+        <is>
+          <t>UV-02</t>
+        </is>
+      </c>
+      <c r="B37" s="94" t="inlineStr">
+        <is>
+          <t>Ứng viên</t>
+        </is>
+      </c>
+      <c r="C37" s="109" t="inlineStr">
+        <is>
+          <t>Tạo hồ sơ &amp; CV</t>
+        </is>
+      </c>
+      <c r="D37" s="89" t="n"/>
+      <c r="E37" s="110">
+        <f>IF($A37="","",COUNTIF($A$54:$A$114,$A37))</f>
+        <v/>
+      </c>
+      <c r="F37" s="110">
+        <f>IF($A37="","",COUNTIFS($A$54:$A$114,$A37,$G$54:$G$114,"Pass"))</f>
+        <v/>
+      </c>
+      <c r="G37" s="110">
+        <f>IF($A37="","",COUNTIFS($A$54:$A$114,$A37,$G$54:$G$114,"Fail"))</f>
+        <v/>
+      </c>
+      <c r="H37" s="110">
+        <f>IF($A37="","",COUNTIFS($A$54:$A$114,$A37,$G$54:$G$114,"Blocked"))</f>
+        <v/>
+      </c>
+      <c r="I37" s="111">
+        <f>IF(OR($A37="",N(E37)=0),"",F37/E37)</f>
+        <v/>
+      </c>
+      <c r="J37" s="112">
+        <f>IF($A37="","",COUNTIFS($A$54:$A$114,$A37,$K$54:$K$114,"CHẶN"))</f>
+        <v/>
+      </c>
+      <c r="K37" s="113">
+        <f>IF($A37="","",IF(E37=0,"Chưa có bước",IF(J37&gt;0,"CHƯA ĐẠT",IF(F37=E37,"ĐẠT",IF(G37+H37&gt;0,"CHƯA ĐẠT","ĐANG TEST")))))</f>
+        <v/>
+      </c>
+      <c r="L37" s="94" t="inlineStr"/>
+      <c r="M37" s="89" t="n"/>
+      <c r="N37" s="89" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="86" t="inlineStr">
+        <is>
+          <t>UV-03</t>
+        </is>
+      </c>
+      <c r="B38" s="94" t="inlineStr">
+        <is>
+          <t>Ứng viên</t>
+        </is>
+      </c>
+      <c r="C38" s="109" t="inlineStr">
+        <is>
+          <t>Tìm việc &amp; ứng tuyển</t>
+        </is>
+      </c>
+      <c r="D38" s="89" t="n"/>
+      <c r="E38" s="110">
+        <f>IF($A38="","",COUNTIF($A$54:$A$114,$A38))</f>
+        <v/>
+      </c>
+      <c r="F38" s="110">
+        <f>IF($A38="","",COUNTIFS($A$54:$A$114,$A38,$G$54:$G$114,"Pass"))</f>
+        <v/>
+      </c>
+      <c r="G38" s="110">
+        <f>IF($A38="","",COUNTIFS($A$54:$A$114,$A38,$G$54:$G$114,"Fail"))</f>
+        <v/>
+      </c>
+      <c r="H38" s="110">
+        <f>IF($A38="","",COUNTIFS($A$54:$A$114,$A38,$G$54:$G$114,"Blocked"))</f>
+        <v/>
+      </c>
+      <c r="I38" s="111">
+        <f>IF(OR($A38="",N(E38)=0),"",F38/E38)</f>
+        <v/>
+      </c>
+      <c r="J38" s="112">
+        <f>IF($A38="","",COUNTIFS($A$54:$A$114,$A38,$K$54:$K$114,"CHẶN"))</f>
+        <v/>
+      </c>
+      <c r="K38" s="113">
+        <f>IF($A38="","",IF(E38=0,"Chưa có bước",IF(J38&gt;0,"CHƯA ĐẠT",IF(F38=E38,"ĐẠT",IF(G38+H38&gt;0,"CHƯA ĐẠT","ĐANG TEST")))))</f>
+        <v/>
+      </c>
+      <c r="L38" s="94" t="inlineStr"/>
+      <c r="M38" s="89" t="n"/>
+      <c r="N38" s="89" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="86" t="inlineStr">
+        <is>
+          <t>NTD-01</t>
+        </is>
+      </c>
+      <c r="B39" s="94" t="inlineStr">
+        <is>
+          <t>Nhà tuyển dụng (DN)</t>
+        </is>
+      </c>
+      <c r="C39" s="109" t="inlineStr">
+        <is>
+          <t>Đăng ký doanh nghiệp &amp; xác thực</t>
+        </is>
+      </c>
+      <c r="D39" s="89" t="n"/>
+      <c r="E39" s="110">
+        <f>IF($A39="","",COUNTIF($A$54:$A$114,$A39))</f>
+        <v/>
+      </c>
+      <c r="F39" s="110">
+        <f>IF($A39="","",COUNTIFS($A$54:$A$114,$A39,$G$54:$G$114,"Pass"))</f>
+        <v/>
+      </c>
+      <c r="G39" s="110">
+        <f>IF($A39="","",COUNTIFS($A$54:$A$114,$A39,$G$54:$G$114,"Fail"))</f>
+        <v/>
+      </c>
+      <c r="H39" s="110">
+        <f>IF($A39="","",COUNTIFS($A$54:$A$114,$A39,$G$54:$G$114,"Blocked"))</f>
+        <v/>
+      </c>
+      <c r="I39" s="111">
+        <f>IF(OR($A39="",N(E39)=0),"",F39/E39)</f>
+        <v/>
+      </c>
+      <c r="J39" s="112">
+        <f>IF($A39="","",COUNTIFS($A$54:$A$114,$A39,$K$54:$K$114,"CHẶN"))</f>
+        <v/>
+      </c>
+      <c r="K39" s="113">
+        <f>IF($A39="","",IF(E39=0,"Chưa có bước",IF(J39&gt;0,"CHƯA ĐẠT",IF(F39=E39,"ĐẠT",IF(G39+H39&gt;0,"CHƯA ĐẠT","ĐANG TEST")))))</f>
+        <v/>
+      </c>
+      <c r="L39" s="94" t="inlineStr"/>
+      <c r="M39" s="89" t="n"/>
+      <c r="N39" s="89" t="n"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="86" t="inlineStr">
+        <is>
+          <t>NTD-02</t>
+        </is>
+      </c>
+      <c r="B40" s="94" t="inlineStr">
+        <is>
+          <t>Nhà tuyển dụng (DN)</t>
+        </is>
+      </c>
+      <c r="C40" s="109" t="inlineStr">
+        <is>
+          <t>Đăng &amp; quản lý tin tuyển dụng</t>
+        </is>
+      </c>
+      <c r="D40" s="89" t="n"/>
+      <c r="E40" s="110">
+        <f>IF($A40="","",COUNTIF($A$54:$A$114,$A40))</f>
+        <v/>
+      </c>
+      <c r="F40" s="110">
+        <f>IF($A40="","",COUNTIFS($A$54:$A$114,$A40,$G$54:$G$114,"Pass"))</f>
+        <v/>
+      </c>
+      <c r="G40" s="110">
+        <f>IF($A40="","",COUNTIFS($A$54:$A$114,$A40,$G$54:$G$114,"Fail"))</f>
+        <v/>
+      </c>
+      <c r="H40" s="110">
+        <f>IF($A40="","",COUNTIFS($A$54:$A$114,$A40,$G$54:$G$114,"Blocked"))</f>
+        <v/>
+      </c>
+      <c r="I40" s="111">
+        <f>IF(OR($A40="",N(E40)=0),"",F40/E40)</f>
+        <v/>
+      </c>
+      <c r="J40" s="112">
+        <f>IF($A40="","",COUNTIFS($A$54:$A$114,$A40,$K$54:$K$114,"CHẶN"))</f>
+        <v/>
+      </c>
+      <c r="K40" s="113">
+        <f>IF($A40="","",IF(E40=0,"Chưa có bước",IF(J40&gt;0,"CHƯA ĐẠT",IF(F40=E40,"ĐẠT",IF(G40+H40&gt;0,"CHƯA ĐẠT","ĐANG TEST")))))</f>
+        <v/>
+      </c>
+      <c r="L40" s="94" t="inlineStr"/>
+      <c r="M40" s="89" t="n"/>
+      <c r="N40" s="89" t="n"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="86" t="inlineStr">
+        <is>
+          <t>NTD-03</t>
+        </is>
+      </c>
+      <c r="B41" s="94" t="inlineStr">
+        <is>
+          <t>Nhà tuyển dụng (DN)</t>
+        </is>
+      </c>
+      <c r="C41" s="109" t="inlineStr">
+        <is>
+          <t>Nhận &amp; xử lý hồ sơ ứng viên</t>
+        </is>
+      </c>
+      <c r="D41" s="89" t="n"/>
+      <c r="E41" s="110">
+        <f>IF($A41="","",COUNTIF($A$54:$A$114,$A41))</f>
+        <v/>
+      </c>
+      <c r="F41" s="110">
+        <f>IF($A41="","",COUNTIFS($A$54:$A$114,$A41,$G$54:$G$114,"Pass"))</f>
+        <v/>
+      </c>
+      <c r="G41" s="110">
+        <f>IF($A41="","",COUNTIFS($A$54:$A$114,$A41,$G$54:$G$114,"Fail"))</f>
+        <v/>
+      </c>
+      <c r="H41" s="110">
+        <f>IF($A41="","",COUNTIFS($A$54:$A$114,$A41,$G$54:$G$114,"Blocked"))</f>
+        <v/>
+      </c>
+      <c r="I41" s="111">
+        <f>IF(OR($A41="",N(E41)=0),"",F41/E41)</f>
+        <v/>
+      </c>
+      <c r="J41" s="112">
+        <f>IF($A41="","",COUNTIFS($A$54:$A$114,$A41,$K$54:$K$114,"CHẶN"))</f>
+        <v/>
+      </c>
+      <c r="K41" s="113">
+        <f>IF($A41="","",IF(E41=0,"Chưa có bước",IF(J41&gt;0,"CHƯA ĐẠT",IF(F41=E41,"ĐẠT",IF(G41+H41&gt;0,"CHƯA ĐẠT","ĐANG TEST")))))</f>
+        <v/>
+      </c>
+      <c r="L41" s="94" t="inlineStr"/>
+      <c r="M41" s="89" t="n"/>
+      <c r="N41" s="89" t="n"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="86" t="inlineStr">
+        <is>
+          <t>HR-01</t>
+        </is>
+      </c>
+      <c r="B42" s="94" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C42" s="109" t="inlineStr">
+        <is>
+          <t>Tài khoản HR của doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="D42" s="89" t="n"/>
+      <c r="E42" s="110">
+        <f>IF($A42="","",COUNTIF($A$54:$A$114,$A42))</f>
+        <v/>
+      </c>
+      <c r="F42" s="110">
+        <f>IF($A42="","",COUNTIFS($A$54:$A$114,$A42,$G$54:$G$114,"Pass"))</f>
+        <v/>
+      </c>
+      <c r="G42" s="110">
+        <f>IF($A42="","",COUNTIFS($A$54:$A$114,$A42,$G$54:$G$114,"Fail"))</f>
+        <v/>
+      </c>
+      <c r="H42" s="110">
+        <f>IF($A42="","",COUNTIFS($A$54:$A$114,$A42,$G$54:$G$114,"Blocked"))</f>
+        <v/>
+      </c>
+      <c r="I42" s="111">
+        <f>IF(OR($A42="",N(E42)=0),"",F42/E42)</f>
+        <v/>
+      </c>
+      <c r="J42" s="112">
+        <f>IF($A42="","",COUNTIFS($A$54:$A$114,$A42,$K$54:$K$114,"CHẶN"))</f>
+        <v/>
+      </c>
+      <c r="K42" s="113">
+        <f>IF($A42="","",IF(E42=0,"Chưa có bước",IF(J42&gt;0,"CHƯA ĐẠT",IF(F42=E42,"ĐẠT",IF(G42+H42&gt;0,"CHƯA ĐẠT","ĐANG TEST")))))</f>
+        <v/>
+      </c>
+      <c r="L42" s="94" t="inlineStr"/>
+      <c r="M42" s="89" t="n"/>
+      <c r="N42" s="89" t="n"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="86" t="inlineStr">
+        <is>
+          <t>AD-01</t>
+        </is>
+      </c>
+      <c r="B43" s="94" t="inlineStr">
+        <is>
+          <t>Quản trị viên</t>
+        </is>
+      </c>
+      <c r="C43" s="109" t="inlineStr">
+        <is>
+          <t>Kiểm duyệt &amp; vận hành</t>
+        </is>
+      </c>
+      <c r="D43" s="89" t="n"/>
+      <c r="E43" s="110">
+        <f>IF($A43="","",COUNTIF($A$54:$A$114,$A43))</f>
+        <v/>
+      </c>
+      <c r="F43" s="110">
+        <f>IF($A43="","",COUNTIFS($A$54:$A$114,$A43,$G$54:$G$114,"Pass"))</f>
+        <v/>
+      </c>
+      <c r="G43" s="110">
+        <f>IF($A43="","",COUNTIFS($A$54:$A$114,$A43,$G$54:$G$114,"Fail"))</f>
+        <v/>
+      </c>
+      <c r="H43" s="110">
+        <f>IF($A43="","",COUNTIFS($A$54:$A$114,$A43,$G$54:$G$114,"Blocked"))</f>
+        <v/>
+      </c>
+      <c r="I43" s="111">
+        <f>IF(OR($A43="",N(E43)=0),"",F43/E43)</f>
+        <v/>
+      </c>
+      <c r="J43" s="112">
+        <f>IF($A43="","",COUNTIFS($A$54:$A$114,$A43,$K$54:$K$114,"CHẶN"))</f>
+        <v/>
+      </c>
+      <c r="K43" s="113">
+        <f>IF($A43="","",IF(E43=0,"Chưa có bước",IF(J43&gt;0,"CHƯA ĐẠT",IF(F43=E43,"ĐẠT",IF(G43+H43&gt;0,"CHƯA ĐẠT","ĐANG TEST")))))</f>
+        <v/>
+      </c>
+      <c r="L43" s="94" t="inlineStr"/>
+      <c r="M43" s="89" t="n"/>
+      <c r="N43" s="89" t="n"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="86" t="n"/>
+      <c r="B44" s="94" t="n"/>
+      <c r="C44" s="109" t="n"/>
+      <c r="D44" s="89" t="n"/>
+      <c r="E44" s="110">
+        <f>IF($A44="","",COUNTIF($A$54:$A$114,$A44))</f>
+        <v/>
+      </c>
+      <c r="F44" s="110">
+        <f>IF($A44="","",COUNTIFS($A$54:$A$114,$A44,$G$54:$G$114,"Pass"))</f>
+        <v/>
+      </c>
+      <c r="G44" s="110">
+        <f>IF($A44="","",COUNTIFS($A$54:$A$114,$A44,$G$54:$G$114,"Fail"))</f>
+        <v/>
+      </c>
+      <c r="H44" s="110">
+        <f>IF($A44="","",COUNTIFS($A$54:$A$114,$A44,$G$54:$G$114,"Blocked"))</f>
+        <v/>
+      </c>
+      <c r="I44" s="111">
+        <f>IF(OR($A44="",N(E44)=0),"",F44/E44)</f>
+        <v/>
+      </c>
+      <c r="J44" s="112">
+        <f>IF($A44="","",COUNTIFS($A$54:$A$114,$A44,$K$54:$K$114,"CHẶN"))</f>
+        <v/>
+      </c>
+      <c r="K44" s="113">
+        <f>IF($A44="","",IF(E44=0,"Chưa có bước",IF(J44&gt;0,"CHƯA ĐẠT",IF(F44=E44,"ĐẠT",IF(G44+H44&gt;0,"CHƯA ĐẠT","ĐANG TEST")))))</f>
+        <v/>
+      </c>
+      <c r="L44" s="94" t="inlineStr"/>
+      <c r="M44" s="89" t="n"/>
+      <c r="N44" s="89" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="86" t="n"/>
+      <c r="B45" s="94" t="n"/>
+      <c r="C45" s="109" t="n"/>
+      <c r="D45" s="89" t="n"/>
+      <c r="E45" s="110">
+        <f>IF($A45="","",COUNTIF($A$54:$A$114,$A45))</f>
+        <v/>
+      </c>
+      <c r="F45" s="110">
+        <f>IF($A45="","",COUNTIFS($A$54:$A$114,$A45,$G$54:$G$114,"Pass"))</f>
+        <v/>
+      </c>
+      <c r="G45" s="110">
+        <f>IF($A45="","",COUNTIFS($A$54:$A$114,$A45,$G$54:$G$114,"Fail"))</f>
+        <v/>
+      </c>
+      <c r="H45" s="110">
+        <f>IF($A45="","",COUNTIFS($A$54:$A$114,$A45,$G$54:$G$114,"Blocked"))</f>
+        <v/>
+      </c>
+      <c r="I45" s="111">
+        <f>IF(OR($A45="",N(E45)=0),"",F45/E45)</f>
+        <v/>
+      </c>
+      <c r="J45" s="112">
+        <f>IF($A45="","",COUNTIFS($A$54:$A$114,$A45,$K$54:$K$114,"CHẶN"))</f>
+        <v/>
+      </c>
+      <c r="K45" s="113">
+        <f>IF($A45="","",IF(E45=0,"Chưa có bước",IF(J45&gt;0,"CHƯA ĐẠT",IF(F45=E45,"ĐẠT",IF(G45+H45&gt;0,"CHƯA ĐẠT","ĐANG TEST")))))</f>
+        <v/>
+      </c>
+      <c r="L45" s="94" t="inlineStr"/>
+      <c r="M45" s="89" t="n"/>
+      <c r="N45" s="89" t="n"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="86" t="n"/>
+      <c r="B46" s="94" t="n"/>
+      <c r="C46" s="109" t="n"/>
+      <c r="D46" s="89" t="n"/>
+      <c r="E46" s="110">
+        <f>IF($A46="","",COUNTIF($A$54:$A$114,$A46))</f>
+        <v/>
+      </c>
+      <c r="F46" s="110">
+        <f>IF($A46="","",COUNTIFS($A$54:$A$114,$A46,$G$54:$G$114,"Pass"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="110">
+        <f>IF($A46="","",COUNTIFS($A$54:$A$114,$A46,$G$54:$G$114,"Fail"))</f>
+        <v/>
+      </c>
+      <c r="H46" s="110">
+        <f>IF($A46="","",COUNTIFS($A$54:$A$114,$A46,$G$54:$G$114,"Blocked"))</f>
+        <v/>
+      </c>
+      <c r="I46" s="111">
+        <f>IF(OR($A46="",N(E46)=0),"",F46/E46)</f>
+        <v/>
+      </c>
+      <c r="J46" s="112">
+        <f>IF($A46="","",COUNTIFS($A$54:$A$114,$A46,$K$54:$K$114,"CHẶN"))</f>
+        <v/>
+      </c>
+      <c r="K46" s="113">
+        <f>IF($A46="","",IF(E46=0,"Chưa có bước",IF(J46&gt;0,"CHƯA ĐẠT",IF(F46=E46,"ĐẠT",IF(G46+H46&gt;0,"CHƯA ĐẠT","ĐANG TEST")))))</f>
+        <v/>
+      </c>
+      <c r="L46" s="94" t="inlineStr"/>
+      <c r="M46" s="89" t="n"/>
+      <c r="N46" s="89" t="n"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="86" t="n"/>
+      <c r="B47" s="94" t="n"/>
+      <c r="C47" s="109" t="n"/>
+      <c r="D47" s="89" t="n"/>
+      <c r="E47" s="110">
+        <f>IF($A47="","",COUNTIF($A$54:$A$114,$A47))</f>
+        <v/>
+      </c>
+      <c r="F47" s="110">
+        <f>IF($A47="","",COUNTIFS($A$54:$A$114,$A47,$G$54:$G$114,"Pass"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="110">
+        <f>IF($A47="","",COUNTIFS($A$54:$A$114,$A47,$G$54:$G$114,"Fail"))</f>
+        <v/>
+      </c>
+      <c r="H47" s="110">
+        <f>IF($A47="","",COUNTIFS($A$54:$A$114,$A47,$G$54:$G$114,"Blocked"))</f>
+        <v/>
+      </c>
+      <c r="I47" s="111">
+        <f>IF(OR($A47="",N(E47)=0),"",F47/E47)</f>
+        <v/>
+      </c>
+      <c r="J47" s="112">
+        <f>IF($A47="","",COUNTIFS($A$54:$A$114,$A47,$K$54:$K$114,"CHẶN"))</f>
+        <v/>
+      </c>
+      <c r="K47" s="113">
+        <f>IF($A47="","",IF(E47=0,"Chưa có bước",IF(J47&gt;0,"CHƯA ĐẠT",IF(F47=E47,"ĐẠT",IF(G47+H47&gt;0,"CHƯA ĐẠT","ĐANG TEST")))))</f>
+        <v/>
+      </c>
+      <c r="L47" s="94" t="inlineStr"/>
+      <c r="M47" s="89" t="n"/>
+      <c r="N47" s="89" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="86" t="n"/>
+      <c r="B48" s="94" t="n"/>
+      <c r="C48" s="109" t="n"/>
+      <c r="D48" s="89" t="n"/>
+      <c r="E48" s="110">
+        <f>IF($A48="","",COUNTIF($A$54:$A$114,$A48))</f>
+        <v/>
+      </c>
+      <c r="F48" s="110">
+        <f>IF($A48="","",COUNTIFS($A$54:$A$114,$A48,$G$54:$G$114,"Pass"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="110">
+        <f>IF($A48="","",COUNTIFS($A$54:$A$114,$A48,$G$54:$G$114,"Fail"))</f>
+        <v/>
+      </c>
+      <c r="H48" s="110">
+        <f>IF($A48="","",COUNTIFS($A$54:$A$114,$A48,$G$54:$G$114,"Blocked"))</f>
+        <v/>
+      </c>
+      <c r="I48" s="111">
+        <f>IF(OR($A48="",N(E48)=0),"",F48/E48)</f>
+        <v/>
+      </c>
+      <c r="J48" s="112">
+        <f>IF($A48="","",COUNTIFS($A$54:$A$114,$A48,$K$54:$K$114,"CHẶN"))</f>
+        <v/>
+      </c>
+      <c r="K48" s="113">
+        <f>IF($A48="","",IF(E48=0,"Chưa có bước",IF(J48&gt;0,"CHƯA ĐẠT",IF(F48=E48,"ĐẠT",IF(G48+H48&gt;0,"CHƯA ĐẠT","ĐANG TEST")))))</f>
+        <v/>
+      </c>
+      <c r="L48" s="94" t="inlineStr"/>
+      <c r="M48" s="89" t="n"/>
+      <c r="N48" s="89" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="86" t="n"/>
+      <c r="B49" s="94" t="n"/>
+      <c r="C49" s="109" t="n"/>
+      <c r="D49" s="89" t="n"/>
+      <c r="E49" s="110">
+        <f>IF($A49="","",COUNTIF($A$54:$A$114,$A49))</f>
+        <v/>
+      </c>
+      <c r="F49" s="110">
+        <f>IF($A49="","",COUNTIFS($A$54:$A$114,$A49,$G$54:$G$114,"Pass"))</f>
+        <v/>
+      </c>
+      <c r="G49" s="110">
+        <f>IF($A49="","",COUNTIFS($A$54:$A$114,$A49,$G$54:$G$114,"Fail"))</f>
+        <v/>
+      </c>
+      <c r="H49" s="110">
+        <f>IF($A49="","",COUNTIFS($A$54:$A$114,$A49,$G$54:$G$114,"Blocked"))</f>
+        <v/>
+      </c>
+      <c r="I49" s="111">
+        <f>IF(OR($A49="",N(E49)=0),"",F49/E49)</f>
+        <v/>
+      </c>
+      <c r="J49" s="112">
+        <f>IF($A49="","",COUNTIFS($A$54:$A$114,$A49,$K$54:$K$114,"CHẶN"))</f>
+        <v/>
+      </c>
+      <c r="K49" s="113">
+        <f>IF($A49="","",IF(E49=0,"Chưa có bước",IF(J49&gt;0,"CHƯA ĐẠT",IF(F49=E49,"ĐẠT",IF(G49+H49&gt;0,"CHƯA ĐẠT","ĐANG TEST")))))</f>
+        <v/>
+      </c>
+      <c r="L49" s="94" t="inlineStr"/>
+      <c r="M49" s="89" t="n"/>
+      <c r="N49" s="89" t="n"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>IV. CHECKLIST CHI TIẾT TỪNG BƯỚC (Tester nhập ô nền vàng)</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="7" t="n"/>
+      <c r="E51" s="7" t="n"/>
+      <c r="F51" s="7" t="n"/>
+      <c r="G51" s="7" t="n"/>
+      <c r="H51" s="7" t="n"/>
+      <c r="I51" s="7" t="n"/>
+      <c r="J51" s="7" t="n"/>
+      <c r="K51" s="7" t="n"/>
+      <c r="L51" s="7" t="n"/>
+      <c r="M51" s="7" t="n"/>
+      <c r="N51" s="7" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>Kết quả: Pass / Fail / Blocked / Chưa test. Bước Fail hoặc Blocked phải ghi BUG_ID (khớp cột BUG_ID ở 05_Lỗi_Tester) → Mức độ, Trạng thái lỗi, Chặn? tự điền. Bằng chứng: link ảnh/video.</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="n"/>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="90" t="inlineStr">
+        <is>
+          <t>Mã HT</t>
+        </is>
+      </c>
+      <c r="B53" s="90" t="inlineStr">
+        <is>
+          <t>Bước</t>
+        </is>
+      </c>
+      <c r="C53" s="90" t="inlineStr">
+        <is>
+          <t>Vai trò (tự điền)</t>
+        </is>
+      </c>
+      <c r="D53" s="90" t="inlineStr">
+        <is>
+          <t>Thao tác</t>
+        </is>
+      </c>
+      <c r="E53" s="90" t="inlineStr">
+        <is>
+          <t>Kết quả mong đợi</t>
+        </is>
+      </c>
+      <c r="F53" s="90" t="inlineStr">
+        <is>
+          <t>TC_ID</t>
+        </is>
+      </c>
+      <c r="G53" s="90" t="inlineStr">
+        <is>
+          <t>Kết quả</t>
+        </is>
+      </c>
+      <c r="H53" s="90" t="inlineStr">
+        <is>
+          <t>BUG_ID</t>
+        </is>
+      </c>
+      <c r="I53" s="90" t="inlineStr">
+        <is>
+          <t>Mức độ lỗi</t>
+        </is>
+      </c>
+      <c r="J53" s="90" t="inlineStr">
+        <is>
+          <t>Trạng thái lỗi</t>
+        </is>
+      </c>
+      <c r="K53" s="90" t="inlineStr">
+        <is>
+          <t>Chặn?</t>
+        </is>
+      </c>
+      <c r="L53" s="90" t="inlineStr">
+        <is>
+          <t>Bằng chứng</t>
+        </is>
+      </c>
+      <c r="M53" s="90" t="inlineStr">
+        <is>
+          <t>Người test</t>
+        </is>
+      </c>
+      <c r="N53" s="90" t="inlineStr">
+        <is>
+          <t>Ngày test</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="114" t="inlineStr">
+        <is>
+          <t>KV-01</t>
+        </is>
+      </c>
+      <c r="B54" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="115">
+        <f>IF($A54="","",IFERROR(VLOOKUP($A54,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D54" s="94" t="inlineStr">
+        <is>
+          <t>Truy cập trang chủ</t>
+        </is>
+      </c>
+      <c r="E54" s="94" t="inlineStr">
+        <is>
+          <t>Trang tải đủ, không lỗi hiển thị (PC + Mobile)</t>
+        </is>
+      </c>
+      <c r="F54" s="104" t="n"/>
+      <c r="G54" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H54" s="104" t="n"/>
+      <c r="I54" s="116">
+        <f>IF($H54="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H54,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J54" s="116">
+        <f>IF($H54="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H54,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K54" s="117">
+        <f>IF($H54="","",IF(AND(OR(I54="Critical",I54="High"),OR(J54="Open",J54="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L54" s="118" t="n"/>
+      <c r="M54" s="119" t="n"/>
+      <c r="N54" s="120" t="n"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="114" t="inlineStr">
+        <is>
+          <t>KV-01</t>
+        </is>
+      </c>
+      <c r="B55" s="104" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" s="115">
+        <f>IF($A55="","",IFERROR(VLOOKUP($A55,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D55" s="94" t="inlineStr">
+        <is>
+          <t>Tìm việc theo từ khóa / ngành / địa điểm</t>
+        </is>
+      </c>
+      <c r="E55" s="94" t="inlineStr">
+        <is>
+          <t>Trả về danh sách tin đúng điều kiện</t>
+        </is>
+      </c>
+      <c r="F55" s="104" t="n"/>
+      <c r="G55" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H55" s="104" t="n"/>
+      <c r="I55" s="116">
+        <f>IF($H55="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H55,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J55" s="116">
+        <f>IF($H55="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H55,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K55" s="117">
+        <f>IF($H55="","",IF(AND(OR(I55="Critical",I55="High"),OR(J55="Open",J55="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L55" s="118" t="n"/>
+      <c r="M55" s="119" t="n"/>
+      <c r="N55" s="120" t="n"/>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="114" t="inlineStr">
+        <is>
+          <t>KV-01</t>
+        </is>
+      </c>
+      <c r="B56" s="104" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" s="115">
+        <f>IF($A56="","",IFERROR(VLOOKUP($A56,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D56" s="94" t="inlineStr">
+        <is>
+          <t>Lọc &amp; sắp xếp kết quả</t>
+        </is>
+      </c>
+      <c r="E56" s="94" t="inlineStr">
+        <is>
+          <t>Bộ lọc lương, kinh nghiệm, hình thức hoạt động đúng</t>
+        </is>
+      </c>
+      <c r="F56" s="104" t="n"/>
+      <c r="G56" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H56" s="104" t="n"/>
+      <c r="I56" s="116">
+        <f>IF($H56="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H56,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J56" s="116">
+        <f>IF($H56="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H56,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K56" s="117">
+        <f>IF($H56="","",IF(AND(OR(I56="Critical",I56="High"),OR(J56="Open",J56="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L56" s="118" t="n"/>
+      <c r="M56" s="119" t="n"/>
+      <c r="N56" s="120" t="n"/>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="114" t="inlineStr">
+        <is>
+          <t>KV-01</t>
+        </is>
+      </c>
+      <c r="B57" s="104" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" s="115">
+        <f>IF($A57="","",IFERROR(VLOOKUP($A57,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D57" s="94" t="inlineStr">
+        <is>
+          <t>Xem chi tiết tin tuyển dụng</t>
+        </is>
+      </c>
+      <c r="E57" s="94" t="inlineStr">
+        <is>
+          <t>Hiển thị đủ mô tả, quyền lợi, thông tin công ty</t>
+        </is>
+      </c>
+      <c r="F57" s="104" t="n"/>
+      <c r="G57" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H57" s="104" t="n"/>
+      <c r="I57" s="116">
+        <f>IF($H57="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H57,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J57" s="116">
+        <f>IF($H57="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H57,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K57" s="117">
+        <f>IF($H57="","",IF(AND(OR(I57="Critical",I57="High"),OR(J57="Open",J57="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L57" s="118" t="n"/>
+      <c r="M57" s="119" t="n"/>
+      <c r="N57" s="120" t="n"/>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="114" t="inlineStr">
+        <is>
+          <t>KV-01</t>
+        </is>
+      </c>
+      <c r="B58" s="104" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" s="115">
+        <f>IF($A58="","",IFERROR(VLOOKUP($A58,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D58" s="94" t="inlineStr">
+        <is>
+          <t>Bấm Ứng tuyển khi chưa đăng nhập</t>
+        </is>
+      </c>
+      <c r="E58" s="94" t="inlineStr">
+        <is>
+          <t>Chuyển sang đăng nhập/đăng ký, quay lại đúng tin</t>
+        </is>
+      </c>
+      <c r="F58" s="104" t="n"/>
+      <c r="G58" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H58" s="104" t="n"/>
+      <c r="I58" s="116">
+        <f>IF($H58="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H58,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J58" s="116">
+        <f>IF($H58="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H58,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K58" s="117">
+        <f>IF($H58="","",IF(AND(OR(I58="Critical",I58="High"),OR(J58="Open",J58="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L58" s="118" t="n"/>
+      <c r="M58" s="119" t="n"/>
+      <c r="N58" s="120" t="n"/>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="114" t="inlineStr">
+        <is>
+          <t>UV-01</t>
+        </is>
+      </c>
+      <c r="B59" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="115">
+        <f>IF($A59="","",IFERROR(VLOOKUP($A59,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D59" s="94" t="inlineStr">
+        <is>
+          <t>Đăng ký tài khoản ứng viên</t>
+        </is>
+      </c>
+      <c r="E59" s="94" t="inlineStr">
+        <is>
+          <t>Tạo tài khoản thành công, validate dữ liệu đúng</t>
+        </is>
+      </c>
+      <c r="F59" s="104" t="n"/>
+      <c r="G59" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H59" s="104" t="n"/>
+      <c r="I59" s="116">
+        <f>IF($H59="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H59,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J59" s="116">
+        <f>IF($H59="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H59,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K59" s="117">
+        <f>IF($H59="","",IF(AND(OR(I59="Critical",I59="High"),OR(J59="Open",J59="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L59" s="118" t="n"/>
+      <c r="M59" s="119" t="n"/>
+      <c r="N59" s="120" t="n"/>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="114" t="inlineStr">
+        <is>
+          <t>UV-01</t>
+        </is>
+      </c>
+      <c r="B60" s="104" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" s="115">
+        <f>IF($A60="","",IFERROR(VLOOKUP($A60,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D60" s="94" t="inlineStr">
+        <is>
+          <t>Xác thực email / OTP</t>
+        </is>
+      </c>
+      <c r="E60" s="94" t="inlineStr">
+        <is>
+          <t>Nhận mã, xác thực thành công</t>
+        </is>
+      </c>
+      <c r="F60" s="104" t="n"/>
+      <c r="G60" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H60" s="104" t="n"/>
+      <c r="I60" s="116">
+        <f>IF($H60="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H60,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J60" s="116">
+        <f>IF($H60="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H60,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K60" s="117">
+        <f>IF($H60="","",IF(AND(OR(I60="Critical",I60="High"),OR(J60="Open",J60="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L60" s="118" t="n"/>
+      <c r="M60" s="119" t="n"/>
+      <c r="N60" s="120" t="n"/>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="114" t="inlineStr">
+        <is>
+          <t>UV-01</t>
+        </is>
+      </c>
+      <c r="B61" s="104" t="n">
+        <v>3</v>
+      </c>
+      <c r="C61" s="115">
+        <f>IF($A61="","",IFERROR(VLOOKUP($A61,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D61" s="94" t="inlineStr">
+        <is>
+          <t>Đăng nhập / đăng xuất</t>
+        </is>
+      </c>
+      <c r="E61" s="94" t="inlineStr">
+        <is>
+          <t>Đăng nhập đúng quyền ứng viên</t>
+        </is>
+      </c>
+      <c r="F61" s="104" t="n"/>
+      <c r="G61" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H61" s="104" t="n"/>
+      <c r="I61" s="116">
+        <f>IF($H61="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H61,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J61" s="116">
+        <f>IF($H61="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H61,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K61" s="117">
+        <f>IF($H61="","",IF(AND(OR(I61="Critical",I61="High"),OR(J61="Open",J61="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L61" s="118" t="n"/>
+      <c r="M61" s="119" t="n"/>
+      <c r="N61" s="120" t="n"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="114" t="inlineStr">
+        <is>
+          <t>UV-01</t>
+        </is>
+      </c>
+      <c r="B62" s="104" t="n">
+        <v>4</v>
+      </c>
+      <c r="C62" s="115">
+        <f>IF($A62="","",IFERROR(VLOOKUP($A62,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D62" s="94" t="inlineStr">
+        <is>
+          <t>Quên mật khẩu</t>
+        </is>
+      </c>
+      <c r="E62" s="94" t="inlineStr">
+        <is>
+          <t>Nhận link/OTP, đổi mật khẩu thành công</t>
+        </is>
+      </c>
+      <c r="F62" s="104" t="n"/>
+      <c r="G62" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H62" s="104" t="n"/>
+      <c r="I62" s="116">
+        <f>IF($H62="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H62,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J62" s="116">
+        <f>IF($H62="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H62,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K62" s="117">
+        <f>IF($H62="","",IF(AND(OR(I62="Critical",I62="High"),OR(J62="Open",J62="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L62" s="118" t="n"/>
+      <c r="M62" s="119" t="n"/>
+      <c r="N62" s="120" t="n"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="114" t="inlineStr">
+        <is>
+          <t>UV-02</t>
+        </is>
+      </c>
+      <c r="B63" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="115">
+        <f>IF($A63="","",IFERROR(VLOOKUP($A63,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D63" s="94" t="inlineStr">
+        <is>
+          <t>Cập nhật thông tin cá nhân</t>
+        </is>
+      </c>
+      <c r="E63" s="94" t="inlineStr">
+        <is>
+          <t>Lưu đúng, hiển thị lại đúng</t>
+        </is>
+      </c>
+      <c r="F63" s="104" t="n"/>
+      <c r="G63" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H63" s="104" t="n"/>
+      <c r="I63" s="116">
+        <f>IF($H63="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H63,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J63" s="116">
+        <f>IF($H63="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H63,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K63" s="117">
+        <f>IF($H63="","",IF(AND(OR(I63="Critical",I63="High"),OR(J63="Open",J63="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L63" s="118" t="n"/>
+      <c r="M63" s="119" t="n"/>
+      <c r="N63" s="120" t="n"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="114" t="inlineStr">
+        <is>
+          <t>UV-02</t>
+        </is>
+      </c>
+      <c r="B64" s="104" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" s="115">
+        <f>IF($A64="","",IFERROR(VLOOKUP($A64,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D64" s="94" t="inlineStr">
+        <is>
+          <t>Tạo CV từ mẫu có sẵn</t>
+        </is>
+      </c>
+      <c r="E64" s="94" t="inlineStr">
+        <is>
+          <t>Tạo/sửa/xem trước/tải PDF được</t>
+        </is>
+      </c>
+      <c r="F64" s="104" t="n"/>
+      <c r="G64" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H64" s="104" t="n"/>
+      <c r="I64" s="116">
+        <f>IF($H64="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H64,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J64" s="116">
+        <f>IF($H64="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H64,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K64" s="117">
+        <f>IF($H64="","",IF(AND(OR(I64="Critical",I64="High"),OR(J64="Open",J64="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L64" s="118" t="n"/>
+      <c r="M64" s="119" t="n"/>
+      <c r="N64" s="120" t="n"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="114" t="inlineStr">
+        <is>
+          <t>UV-02</t>
+        </is>
+      </c>
+      <c r="B65" s="104" t="n">
+        <v>3</v>
+      </c>
+      <c r="C65" s="115">
+        <f>IF($A65="","",IFERROR(VLOOKUP($A65,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D65" s="94" t="inlineStr">
+        <is>
+          <t>Tải CV có sẵn lên</t>
+        </is>
+      </c>
+      <c r="E65" s="94" t="inlineStr">
+        <is>
+          <t>Nhận đúng định dạng &amp; dung lượng cho phép</t>
+        </is>
+      </c>
+      <c r="F65" s="104" t="n"/>
+      <c r="G65" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H65" s="104" t="n"/>
+      <c r="I65" s="116">
+        <f>IF($H65="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H65,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J65" s="116">
+        <f>IF($H65="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H65,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K65" s="117">
+        <f>IF($H65="","",IF(AND(OR(I65="Critical",I65="High"),OR(J65="Open",J65="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L65" s="118" t="n"/>
+      <c r="M65" s="119" t="n"/>
+      <c r="N65" s="120" t="n"/>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="114" t="inlineStr">
+        <is>
+          <t>UV-02</t>
+        </is>
+      </c>
+      <c r="B66" s="104" t="n">
+        <v>4</v>
+      </c>
+      <c r="C66" s="115">
+        <f>IF($A66="","",IFERROR(VLOOKUP($A66,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D66" s="94" t="inlineStr">
+        <is>
+          <t>Bật trạng thái tìm việc / công khai hồ sơ</t>
+        </is>
+      </c>
+      <c r="E66" s="94" t="inlineStr">
+        <is>
+          <t>NTD tìm thấy hồ sơ theo cài đặt</t>
+        </is>
+      </c>
+      <c r="F66" s="104" t="n"/>
+      <c r="G66" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H66" s="104" t="n"/>
+      <c r="I66" s="116">
+        <f>IF($H66="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H66,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J66" s="116">
+        <f>IF($H66="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H66,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K66" s="117">
+        <f>IF($H66="","",IF(AND(OR(I66="Critical",I66="High"),OR(J66="Open",J66="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L66" s="118" t="n"/>
+      <c r="M66" s="119" t="n"/>
+      <c r="N66" s="120" t="n"/>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="114" t="inlineStr">
+        <is>
+          <t>UV-03</t>
+        </is>
+      </c>
+      <c r="B67" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="115">
+        <f>IF($A67="","",IFERROR(VLOOKUP($A67,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D67" s="94" t="inlineStr">
+        <is>
+          <t>Tìm và lưu tin yêu thích</t>
+        </is>
+      </c>
+      <c r="E67" s="94" t="inlineStr">
+        <is>
+          <t>Tin được lưu, xem lại trong danh sách</t>
+        </is>
+      </c>
+      <c r="F67" s="104" t="n"/>
+      <c r="G67" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H67" s="104" t="n"/>
+      <c r="I67" s="116">
+        <f>IF($H67="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H67,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J67" s="116">
+        <f>IF($H67="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H67,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K67" s="117">
+        <f>IF($H67="","",IF(AND(OR(I67="Critical",I67="High"),OR(J67="Open",J67="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L67" s="118" t="n"/>
+      <c r="M67" s="119" t="n"/>
+      <c r="N67" s="120" t="n"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="114" t="inlineStr">
+        <is>
+          <t>UV-03</t>
+        </is>
+      </c>
+      <c r="B68" s="104" t="n">
+        <v>2</v>
+      </c>
+      <c r="C68" s="115">
+        <f>IF($A68="","",IFERROR(VLOOKUP($A68,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D68" s="94" t="inlineStr">
+        <is>
+          <t>Ứng tuyển bằng CV</t>
+        </is>
+      </c>
+      <c r="E68" s="94" t="inlineStr">
+        <is>
+          <t>Nộp thành công, NTD nhận được hồ sơ</t>
+        </is>
+      </c>
+      <c r="F68" s="104" t="n"/>
+      <c r="G68" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H68" s="104" t="n"/>
+      <c r="I68" s="116">
+        <f>IF($H68="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H68,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J68" s="116">
+        <f>IF($H68="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H68,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K68" s="117">
+        <f>IF($H68="","",IF(AND(OR(I68="Critical",I68="High"),OR(J68="Open",J68="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L68" s="118" t="n"/>
+      <c r="M68" s="119" t="n"/>
+      <c r="N68" s="120" t="n"/>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="114" t="inlineStr">
+        <is>
+          <t>UV-03</t>
+        </is>
+      </c>
+      <c r="B69" s="104" t="n">
+        <v>3</v>
+      </c>
+      <c r="C69" s="115">
+        <f>IF($A69="","",IFERROR(VLOOKUP($A69,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D69" s="94" t="inlineStr">
+        <is>
+          <t>Xem lịch sử ứng tuyển</t>
+        </is>
+      </c>
+      <c r="E69" s="94" t="inlineStr">
+        <is>
+          <t>Hiển thị đúng tin &amp; trạng thái hồ sơ</t>
+        </is>
+      </c>
+      <c r="F69" s="104" t="n"/>
+      <c r="G69" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H69" s="104" t="n"/>
+      <c r="I69" s="116">
+        <f>IF($H69="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H69,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J69" s="116">
+        <f>IF($H69="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H69,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K69" s="117">
+        <f>IF($H69="","",IF(AND(OR(I69="Critical",I69="High"),OR(J69="Open",J69="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L69" s="118" t="n"/>
+      <c r="M69" s="119" t="n"/>
+      <c r="N69" s="120" t="n"/>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="114" t="inlineStr">
+        <is>
+          <t>UV-03</t>
+        </is>
+      </c>
+      <c r="B70" s="104" t="n">
+        <v>4</v>
+      </c>
+      <c r="C70" s="115">
+        <f>IF($A70="","",IFERROR(VLOOKUP($A70,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D70" s="94" t="inlineStr">
+        <is>
+          <t>Nhận thông báo khi NTD xem / phản hồi</t>
+        </is>
+      </c>
+      <c r="E70" s="94" t="inlineStr">
+        <is>
+          <t>Thông báo/email đến đúng lúc, đúng nội dung</t>
+        </is>
+      </c>
+      <c r="F70" s="104" t="n"/>
+      <c r="G70" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H70" s="104" t="n"/>
+      <c r="I70" s="116">
+        <f>IF($H70="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H70,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J70" s="116">
+        <f>IF($H70="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H70,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K70" s="117">
+        <f>IF($H70="","",IF(AND(OR(I70="Critical",I70="High"),OR(J70="Open",J70="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L70" s="118" t="n"/>
+      <c r="M70" s="119" t="n"/>
+      <c r="N70" s="120" t="n"/>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="114" t="inlineStr">
+        <is>
+          <t>NTD-01</t>
+        </is>
+      </c>
+      <c r="B71" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" s="115">
+        <f>IF($A71="","",IFERROR(VLOOKUP($A71,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D71" s="94" t="inlineStr">
+        <is>
+          <t>Đăng ký tài khoản nhà tuyển dụng</t>
+        </is>
+      </c>
+      <c r="E71" s="94" t="inlineStr">
+        <is>
+          <t>Tạo tài khoản thành công</t>
+        </is>
+      </c>
+      <c r="F71" s="104" t="n"/>
+      <c r="G71" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H71" s="104" t="n"/>
+      <c r="I71" s="116">
+        <f>IF($H71="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H71,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J71" s="116">
+        <f>IF($H71="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H71,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K71" s="117">
+        <f>IF($H71="","",IF(AND(OR(I71="Critical",I71="High"),OR(J71="Open",J71="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L71" s="118" t="n"/>
+      <c r="M71" s="119" t="n"/>
+      <c r="N71" s="120" t="n"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="114" t="inlineStr">
+        <is>
+          <t>NTD-01</t>
+        </is>
+      </c>
+      <c r="B72" s="104" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" s="115">
+        <f>IF($A72="","",IFERROR(VLOOKUP($A72,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D72" s="94" t="inlineStr">
+        <is>
+          <t>Cập nhật thông tin công ty</t>
+        </is>
+      </c>
+      <c r="E72" s="94" t="inlineStr">
+        <is>
+          <t>Logo, giới thiệu, địa chỉ hiển thị đúng</t>
+        </is>
+      </c>
+      <c r="F72" s="104" t="n"/>
+      <c r="G72" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H72" s="104" t="n"/>
+      <c r="I72" s="116">
+        <f>IF($H72="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H72,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J72" s="116">
+        <f>IF($H72="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H72,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K72" s="117">
+        <f>IF($H72="","",IF(AND(OR(I72="Critical",I72="High"),OR(J72="Open",J72="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L72" s="118" t="n"/>
+      <c r="M72" s="119" t="n"/>
+      <c r="N72" s="120" t="n"/>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="114" t="inlineStr">
+        <is>
+          <t>NTD-01</t>
+        </is>
+      </c>
+      <c r="B73" s="104" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" s="115">
+        <f>IF($A73="","",IFERROR(VLOOKUP($A73,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D73" s="94" t="inlineStr">
+        <is>
+          <t>Gửi giấy tờ xác thực</t>
+        </is>
+      </c>
+      <c r="E73" s="94" t="inlineStr">
+        <is>
+          <t>Upload thành công, chờ duyệt</t>
+        </is>
+      </c>
+      <c r="F73" s="104" t="n"/>
+      <c r="G73" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H73" s="104" t="n"/>
+      <c r="I73" s="116">
+        <f>IF($H73="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H73,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J73" s="116">
+        <f>IF($H73="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H73,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K73" s="117">
+        <f>IF($H73="","",IF(AND(OR(I73="Critical",I73="High"),OR(J73="Open",J73="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L73" s="118" t="n"/>
+      <c r="M73" s="119" t="n"/>
+      <c r="N73" s="120" t="n"/>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="114" t="inlineStr">
+        <is>
+          <t>NTD-01</t>
+        </is>
+      </c>
+      <c r="B74" s="104" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" s="115">
+        <f>IF($A74="","",IFERROR(VLOOKUP($A74,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D74" s="94" t="inlineStr">
+        <is>
+          <t>Nhận kết quả duyệt</t>
+        </is>
+      </c>
+      <c r="E74" s="94" t="inlineStr">
+        <is>
+          <t>Trạng thái xác thực cập nhật, có thông báo</t>
+        </is>
+      </c>
+      <c r="F74" s="104" t="n"/>
+      <c r="G74" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H74" s="104" t="n"/>
+      <c r="I74" s="116">
+        <f>IF($H74="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H74,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J74" s="116">
+        <f>IF($H74="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H74,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K74" s="117">
+        <f>IF($H74="","",IF(AND(OR(I74="Critical",I74="High"),OR(J74="Open",J74="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L74" s="118" t="n"/>
+      <c r="M74" s="119" t="n"/>
+      <c r="N74" s="120" t="n"/>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="114" t="inlineStr">
+        <is>
+          <t>NTD-02</t>
+        </is>
+      </c>
+      <c r="B75" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" s="115">
+        <f>IF($A75="","",IFERROR(VLOOKUP($A75,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D75" s="94" t="inlineStr">
+        <is>
+          <t>Tạo tin tuyển dụng</t>
+        </is>
+      </c>
+      <c r="E75" s="94" t="inlineStr">
+        <is>
+          <t>Nhập đủ trường, validate đúng</t>
+        </is>
+      </c>
+      <c r="F75" s="104" t="n"/>
+      <c r="G75" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H75" s="104" t="n"/>
+      <c r="I75" s="116">
+        <f>IF($H75="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H75,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J75" s="116">
+        <f>IF($H75="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H75,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K75" s="117">
+        <f>IF($H75="","",IF(AND(OR(I75="Critical",I75="High"),OR(J75="Open",J75="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L75" s="118" t="n"/>
+      <c r="M75" s="119" t="n"/>
+      <c r="N75" s="120" t="n"/>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="114" t="inlineStr">
+        <is>
+          <t>NTD-02</t>
+        </is>
+      </c>
+      <c r="B76" s="104" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" s="115">
+        <f>IF($A76="","",IFERROR(VLOOKUP($A76,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D76" s="94" t="inlineStr">
+        <is>
+          <t>Xem trước &amp; đăng tin</t>
+        </is>
+      </c>
+      <c r="E76" s="94" t="inlineStr">
+        <is>
+          <t>Tin gửi duyệt / đăng thành công</t>
+        </is>
+      </c>
+      <c r="F76" s="104" t="n"/>
+      <c r="G76" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H76" s="104" t="n"/>
+      <c r="I76" s="116">
+        <f>IF($H76="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H76,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J76" s="116">
+        <f>IF($H76="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H76,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K76" s="117">
+        <f>IF($H76="","",IF(AND(OR(I76="Critical",I76="High"),OR(J76="Open",J76="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L76" s="118" t="n"/>
+      <c r="M76" s="119" t="n"/>
+      <c r="N76" s="120" t="n"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="114" t="inlineStr">
+        <is>
+          <t>NTD-02</t>
+        </is>
+      </c>
+      <c r="B77" s="104" t="n">
+        <v>3</v>
+      </c>
+      <c r="C77" s="115">
+        <f>IF($A77="","",IFERROR(VLOOKUP($A77,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D77" s="94" t="inlineStr">
+        <is>
+          <t>Tin hiển thị trên trang tìm việc</t>
+        </is>
+      </c>
+      <c r="E77" s="94" t="inlineStr">
+        <is>
+          <t>Ứng viên tìm thấy tin đúng ngành/địa điểm</t>
+        </is>
+      </c>
+      <c r="F77" s="104" t="n"/>
+      <c r="G77" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H77" s="104" t="n"/>
+      <c r="I77" s="116">
+        <f>IF($H77="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H77,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J77" s="116">
+        <f>IF($H77="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H77,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K77" s="117">
+        <f>IF($H77="","",IF(AND(OR(I77="Critical",I77="High"),OR(J77="Open",J77="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L77" s="118" t="n"/>
+      <c r="M77" s="119" t="n"/>
+      <c r="N77" s="120" t="n"/>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="114" t="inlineStr">
+        <is>
+          <t>NTD-02</t>
+        </is>
+      </c>
+      <c r="B78" s="104" t="n">
+        <v>4</v>
+      </c>
+      <c r="C78" s="115">
+        <f>IF($A78="","",IFERROR(VLOOKUP($A78,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D78" s="94" t="inlineStr">
+        <is>
+          <t>Sửa / ẩn / gia hạn tin</t>
+        </is>
+      </c>
+      <c r="E78" s="94" t="inlineStr">
+        <is>
+          <t>Thay đổi áp dụng ngay, đúng trạng thái</t>
+        </is>
+      </c>
+      <c r="F78" s="104" t="n"/>
+      <c r="G78" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H78" s="104" t="n"/>
+      <c r="I78" s="116">
+        <f>IF($H78="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H78,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J78" s="116">
+        <f>IF($H78="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H78,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K78" s="117">
+        <f>IF($H78="","",IF(AND(OR(I78="Critical",I78="High"),OR(J78="Open",J78="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L78" s="118" t="n"/>
+      <c r="M78" s="119" t="n"/>
+      <c r="N78" s="120" t="n"/>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="114" t="inlineStr">
+        <is>
+          <t>NTD-03</t>
+        </is>
+      </c>
+      <c r="B79" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="115">
+        <f>IF($A79="","",IFERROR(VLOOKUP($A79,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D79" s="94" t="inlineStr">
+        <is>
+          <t>Nhận hồ sơ ứng tuyển</t>
+        </is>
+      </c>
+      <c r="E79" s="94" t="inlineStr">
+        <is>
+          <t>Hồ sơ xuất hiện đúng tin, có thông báo</t>
+        </is>
+      </c>
+      <c r="F79" s="104" t="n"/>
+      <c r="G79" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H79" s="104" t="n"/>
+      <c r="I79" s="116">
+        <f>IF($H79="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H79,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J79" s="116">
+        <f>IF($H79="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H79,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K79" s="117">
+        <f>IF($H79="","",IF(AND(OR(I79="Critical",I79="High"),OR(J79="Open",J79="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L79" s="118" t="n"/>
+      <c r="M79" s="119" t="n"/>
+      <c r="N79" s="120" t="n"/>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="114" t="inlineStr">
+        <is>
+          <t>NTD-03</t>
+        </is>
+      </c>
+      <c r="B80" s="104" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" s="115">
+        <f>IF($A80="","",IFERROR(VLOOKUP($A80,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D80" s="94" t="inlineStr">
+        <is>
+          <t>Xem / tải CV ứng viên</t>
+        </is>
+      </c>
+      <c r="E80" s="94" t="inlineStr">
+        <is>
+          <t>Mở và tải CV được</t>
+        </is>
+      </c>
+      <c r="F80" s="104" t="n"/>
+      <c r="G80" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H80" s="104" t="n"/>
+      <c r="I80" s="116">
+        <f>IF($H80="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H80,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J80" s="116">
+        <f>IF($H80="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H80,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K80" s="117">
+        <f>IF($H80="","",IF(AND(OR(I80="Critical",I80="High"),OR(J80="Open",J80="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L80" s="118" t="n"/>
+      <c r="M80" s="119" t="n"/>
+      <c r="N80" s="120" t="n"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="114" t="inlineStr">
+        <is>
+          <t>NTD-03</t>
+        </is>
+      </c>
+      <c r="B81" s="104" t="n">
+        <v>3</v>
+      </c>
+      <c r="C81" s="115">
+        <f>IF($A81="","",IFERROR(VLOOKUP($A81,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D81" s="94" t="inlineStr">
+        <is>
+          <t>Lọc, đánh giá, đổi trạng thái hồ sơ</t>
+        </is>
+      </c>
+      <c r="E81" s="94" t="inlineStr">
+        <is>
+          <t>Trạng thái lưu đúng, ứng viên được thông báo</t>
+        </is>
+      </c>
+      <c r="F81" s="104" t="n"/>
+      <c r="G81" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H81" s="104" t="n"/>
+      <c r="I81" s="116">
+        <f>IF($H81="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H81,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J81" s="116">
+        <f>IF($H81="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H81,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K81" s="117">
+        <f>IF($H81="","",IF(AND(OR(I81="Critical",I81="High"),OR(J81="Open",J81="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L81" s="118" t="n"/>
+      <c r="M81" s="119" t="n"/>
+      <c r="N81" s="120" t="n"/>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="114" t="inlineStr">
+        <is>
+          <t>NTD-03</t>
+        </is>
+      </c>
+      <c r="B82" s="104" t="n">
+        <v>4</v>
+      </c>
+      <c r="C82" s="115">
+        <f>IF($A82="","",IFERROR(VLOOKUP($A82,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D82" s="94" t="inlineStr">
+        <is>
+          <t>Liên hệ / hẹn phỏng vấn ứng viên</t>
+        </is>
+      </c>
+      <c r="E82" s="94" t="inlineStr">
+        <is>
+          <t>Gửi được liên hệ, ứng viên nhận được</t>
+        </is>
+      </c>
+      <c r="F82" s="104" t="n"/>
+      <c r="G82" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H82" s="104" t="n"/>
+      <c r="I82" s="116">
+        <f>IF($H82="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H82,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J82" s="116">
+        <f>IF($H82="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H82,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K82" s="117">
+        <f>IF($H82="","",IF(AND(OR(I82="Critical",I82="High"),OR(J82="Open",J82="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L82" s="118" t="n"/>
+      <c r="M82" s="119" t="n"/>
+      <c r="N82" s="120" t="n"/>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="114" t="inlineStr">
+        <is>
+          <t>HR-01</t>
+        </is>
+      </c>
+      <c r="B83" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" s="115">
+        <f>IF($A83="","",IFERROR(VLOOKUP($A83,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D83" s="94" t="inlineStr">
+        <is>
+          <t>DN tạo / mời tài khoản HR</t>
+        </is>
+      </c>
+      <c r="E83" s="94" t="inlineStr">
+        <is>
+          <t>HR nhận lời mời, kích hoạt được</t>
+        </is>
+      </c>
+      <c r="F83" s="104" t="n"/>
+      <c r="G83" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H83" s="104" t="n"/>
+      <c r="I83" s="116">
+        <f>IF($H83="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H83,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J83" s="116">
+        <f>IF($H83="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H83,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K83" s="117">
+        <f>IF($H83="","",IF(AND(OR(I83="Critical",I83="High"),OR(J83="Open",J83="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L83" s="118" t="n"/>
+      <c r="M83" s="119" t="n"/>
+      <c r="N83" s="120" t="n"/>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="114" t="inlineStr">
+        <is>
+          <t>HR-01</t>
+        </is>
+      </c>
+      <c r="B84" s="104" t="n">
+        <v>2</v>
+      </c>
+      <c r="C84" s="115">
+        <f>IF($A84="","",IFERROR(VLOOKUP($A84,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D84" s="94" t="inlineStr">
+        <is>
+          <t>HR đăng nhập</t>
+        </is>
+      </c>
+      <c r="E84" s="94" t="inlineStr">
+        <is>
+          <t>Vào đúng doanh nghiệp, đúng phân quyền</t>
+        </is>
+      </c>
+      <c r="F84" s="104" t="n"/>
+      <c r="G84" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H84" s="104" t="n"/>
+      <c r="I84" s="116">
+        <f>IF($H84="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H84,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J84" s="116">
+        <f>IF($H84="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H84,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K84" s="117">
+        <f>IF($H84="","",IF(AND(OR(I84="Critical",I84="High"),OR(J84="Open",J84="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L84" s="118" t="n"/>
+      <c r="M84" s="119" t="n"/>
+      <c r="N84" s="120" t="n"/>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="114" t="inlineStr">
+        <is>
+          <t>HR-01</t>
+        </is>
+      </c>
+      <c r="B85" s="104" t="n">
+        <v>3</v>
+      </c>
+      <c r="C85" s="115">
+        <f>IF($A85="","",IFERROR(VLOOKUP($A85,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D85" s="94" t="inlineStr">
+        <is>
+          <t>HR đăng tin &amp; xử lý hồ sơ thay DN</t>
+        </is>
+      </c>
+      <c r="E85" s="94" t="inlineStr">
+        <is>
+          <t>Thao tác thành công, DN xem được lịch sử</t>
+        </is>
+      </c>
+      <c r="F85" s="104" t="n"/>
+      <c r="G85" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H85" s="104" t="n"/>
+      <c r="I85" s="116">
+        <f>IF($H85="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H85,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J85" s="116">
+        <f>IF($H85="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H85,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K85" s="117">
+        <f>IF($H85="","",IF(AND(OR(I85="Critical",I85="High"),OR(J85="Open",J85="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L85" s="118" t="n"/>
+      <c r="M85" s="119" t="n"/>
+      <c r="N85" s="120" t="n"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="114" t="inlineStr">
+        <is>
+          <t>AD-01</t>
+        </is>
+      </c>
+      <c r="B86" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="115">
+        <f>IF($A86="","",IFERROR(VLOOKUP($A86,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D86" s="94" t="inlineStr">
+        <is>
+          <t>Duyệt doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="E86" s="94" t="inlineStr">
+        <is>
+          <t>Duyệt/từ chối, DN nhận thông báo</t>
+        </is>
+      </c>
+      <c r="F86" s="104" t="n"/>
+      <c r="G86" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H86" s="104" t="n"/>
+      <c r="I86" s="116">
+        <f>IF($H86="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H86,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J86" s="116">
+        <f>IF($H86="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H86,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K86" s="117">
+        <f>IF($H86="","",IF(AND(OR(I86="Critical",I86="High"),OR(J86="Open",J86="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L86" s="118" t="n"/>
+      <c r="M86" s="119" t="n"/>
+      <c r="N86" s="120" t="n"/>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="114" t="inlineStr">
+        <is>
+          <t>AD-01</t>
+        </is>
+      </c>
+      <c r="B87" s="104" t="n">
+        <v>2</v>
+      </c>
+      <c r="C87" s="115">
+        <f>IF($A87="","",IFERROR(VLOOKUP($A87,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D87" s="94" t="inlineStr">
+        <is>
+          <t>Duyệt tin tuyển dụng</t>
+        </is>
+      </c>
+      <c r="E87" s="94" t="inlineStr">
+        <is>
+          <t>Tin duyệt mới hiển thị công khai</t>
+        </is>
+      </c>
+      <c r="F87" s="104" t="n"/>
+      <c r="G87" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H87" s="104" t="n"/>
+      <c r="I87" s="116">
+        <f>IF($H87="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H87,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J87" s="116">
+        <f>IF($H87="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H87,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K87" s="117">
+        <f>IF($H87="","",IF(AND(OR(I87="Critical",I87="High"),OR(J87="Open",J87="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L87" s="118" t="n"/>
+      <c r="M87" s="119" t="n"/>
+      <c r="N87" s="120" t="n"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="114" t="inlineStr">
+        <is>
+          <t>AD-01</t>
+        </is>
+      </c>
+      <c r="B88" s="104" t="n">
+        <v>3</v>
+      </c>
+      <c r="C88" s="115">
+        <f>IF($A88="","",IFERROR(VLOOKUP($A88,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D88" s="94" t="inlineStr">
+        <is>
+          <t>Khóa tài khoản / tin vi phạm</t>
+        </is>
+      </c>
+      <c r="E88" s="94" t="inlineStr">
+        <is>
+          <t>Khóa có hiệu lực ngay</t>
+        </is>
+      </c>
+      <c r="F88" s="104" t="n"/>
+      <c r="G88" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H88" s="104" t="n"/>
+      <c r="I88" s="116">
+        <f>IF($H88="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H88,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J88" s="116">
+        <f>IF($H88="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H88,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K88" s="117">
+        <f>IF($H88="","",IF(AND(OR(I88="Critical",I88="High"),OR(J88="Open",J88="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L88" s="118" t="n"/>
+      <c r="M88" s="119" t="n"/>
+      <c r="N88" s="120" t="n"/>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="114" t="inlineStr">
+        <is>
+          <t>AD-01</t>
+        </is>
+      </c>
+      <c r="B89" s="104" t="n">
+        <v>4</v>
+      </c>
+      <c r="C89" s="115">
+        <f>IF($A89="","",IFERROR(VLOOKUP($A89,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D89" s="94" t="inlineStr">
+        <is>
+          <t>Xem thống kê DN / HR / Ứng viên / Tin</t>
+        </is>
+      </c>
+      <c r="E89" s="94" t="inlineStr">
+        <is>
+          <t>Số liệu khớp Database</t>
+        </is>
+      </c>
+      <c r="F89" s="104" t="n"/>
+      <c r="G89" s="114" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="H89" s="104" t="n"/>
+      <c r="I89" s="116">
+        <f>IF($H89="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H89,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J89" s="116">
+        <f>IF($H89="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H89,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K89" s="117">
+        <f>IF($H89="","",IF(AND(OR(I89="Critical",I89="High"),OR(J89="Open",J89="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L89" s="118" t="n"/>
+      <c r="M89" s="119" t="n"/>
+      <c r="N89" s="120" t="n"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="114" t="n"/>
+      <c r="B90" s="104" t="n"/>
+      <c r="C90" s="115">
+        <f>IF($A90="","",IFERROR(VLOOKUP($A90,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D90" s="94" t="n"/>
+      <c r="E90" s="94" t="n"/>
+      <c r="F90" s="104" t="n"/>
+      <c r="G90" s="114" t="n"/>
+      <c r="H90" s="104" t="n"/>
+      <c r="I90" s="116">
+        <f>IF($H90="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H90,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J90" s="116">
+        <f>IF($H90="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H90,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K90" s="117">
+        <f>IF($H90="","",IF(AND(OR(I90="Critical",I90="High"),OR(J90="Open",J90="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L90" s="118" t="n"/>
+      <c r="M90" s="119" t="n"/>
+      <c r="N90" s="120" t="n"/>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="114" t="n"/>
+      <c r="B91" s="104" t="n"/>
+      <c r="C91" s="115">
+        <f>IF($A91="","",IFERROR(VLOOKUP($A91,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D91" s="94" t="n"/>
+      <c r="E91" s="94" t="n"/>
+      <c r="F91" s="104" t="n"/>
+      <c r="G91" s="114" t="n"/>
+      <c r="H91" s="104" t="n"/>
+      <c r="I91" s="116">
+        <f>IF($H91="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H91,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J91" s="116">
+        <f>IF($H91="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H91,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K91" s="117">
+        <f>IF($H91="","",IF(AND(OR(I91="Critical",I91="High"),OR(J91="Open",J91="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L91" s="118" t="n"/>
+      <c r="M91" s="119" t="n"/>
+      <c r="N91" s="120" t="n"/>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="114" t="n"/>
+      <c r="B92" s="104" t="n"/>
+      <c r="C92" s="115">
+        <f>IF($A92="","",IFERROR(VLOOKUP($A92,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D92" s="94" t="n"/>
+      <c r="E92" s="94" t="n"/>
+      <c r="F92" s="104" t="n"/>
+      <c r="G92" s="114" t="n"/>
+      <c r="H92" s="104" t="n"/>
+      <c r="I92" s="116">
+        <f>IF($H92="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H92,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J92" s="116">
+        <f>IF($H92="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H92,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K92" s="117">
+        <f>IF($H92="","",IF(AND(OR(I92="Critical",I92="High"),OR(J92="Open",J92="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L92" s="118" t="n"/>
+      <c r="M92" s="119" t="n"/>
+      <c r="N92" s="120" t="n"/>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="114" t="n"/>
+      <c r="B93" s="104" t="n"/>
+      <c r="C93" s="115">
+        <f>IF($A93="","",IFERROR(VLOOKUP($A93,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D93" s="94" t="n"/>
+      <c r="E93" s="94" t="n"/>
+      <c r="F93" s="104" t="n"/>
+      <c r="G93" s="114" t="n"/>
+      <c r="H93" s="104" t="n"/>
+      <c r="I93" s="116">
+        <f>IF($H93="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H93,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J93" s="116">
+        <f>IF($H93="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H93,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K93" s="117">
+        <f>IF($H93="","",IF(AND(OR(I93="Critical",I93="High"),OR(J93="Open",J93="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L93" s="118" t="n"/>
+      <c r="M93" s="119" t="n"/>
+      <c r="N93" s="120" t="n"/>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="114" t="n"/>
+      <c r="B94" s="104" t="n"/>
+      <c r="C94" s="115">
+        <f>IF($A94="","",IFERROR(VLOOKUP($A94,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D94" s="94" t="n"/>
+      <c r="E94" s="94" t="n"/>
+      <c r="F94" s="104" t="n"/>
+      <c r="G94" s="114" t="n"/>
+      <c r="H94" s="104" t="n"/>
+      <c r="I94" s="116">
+        <f>IF($H94="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H94,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J94" s="116">
+        <f>IF($H94="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H94,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K94" s="117">
+        <f>IF($H94="","",IF(AND(OR(I94="Critical",I94="High"),OR(J94="Open",J94="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L94" s="118" t="n"/>
+      <c r="M94" s="119" t="n"/>
+      <c r="N94" s="120" t="n"/>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="114" t="n"/>
+      <c r="B95" s="104" t="n"/>
+      <c r="C95" s="115">
+        <f>IF($A95="","",IFERROR(VLOOKUP($A95,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D95" s="94" t="n"/>
+      <c r="E95" s="94" t="n"/>
+      <c r="F95" s="104" t="n"/>
+      <c r="G95" s="114" t="n"/>
+      <c r="H95" s="104" t="n"/>
+      <c r="I95" s="116">
+        <f>IF($H95="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H95,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J95" s="116">
+        <f>IF($H95="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H95,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K95" s="117">
+        <f>IF($H95="","",IF(AND(OR(I95="Critical",I95="High"),OR(J95="Open",J95="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L95" s="118" t="n"/>
+      <c r="M95" s="119" t="n"/>
+      <c r="N95" s="120" t="n"/>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="114" t="n"/>
+      <c r="B96" s="104" t="n"/>
+      <c r="C96" s="115">
+        <f>IF($A96="","",IFERROR(VLOOKUP($A96,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D96" s="94" t="n"/>
+      <c r="E96" s="94" t="n"/>
+      <c r="F96" s="104" t="n"/>
+      <c r="G96" s="114" t="n"/>
+      <c r="H96" s="104" t="n"/>
+      <c r="I96" s="116">
+        <f>IF($H96="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H96,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J96" s="116">
+        <f>IF($H96="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H96,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K96" s="117">
+        <f>IF($H96="","",IF(AND(OR(I96="Critical",I96="High"),OR(J96="Open",J96="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L96" s="118" t="n"/>
+      <c r="M96" s="119" t="n"/>
+      <c r="N96" s="120" t="n"/>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="114" t="n"/>
+      <c r="B97" s="104" t="n"/>
+      <c r="C97" s="115">
+        <f>IF($A97="","",IFERROR(VLOOKUP($A97,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D97" s="94" t="n"/>
+      <c r="E97" s="94" t="n"/>
+      <c r="F97" s="104" t="n"/>
+      <c r="G97" s="114" t="n"/>
+      <c r="H97" s="104" t="n"/>
+      <c r="I97" s="116">
+        <f>IF($H97="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H97,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J97" s="116">
+        <f>IF($H97="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H97,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K97" s="117">
+        <f>IF($H97="","",IF(AND(OR(I97="Critical",I97="High"),OR(J97="Open",J97="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L97" s="118" t="n"/>
+      <c r="M97" s="119" t="n"/>
+      <c r="N97" s="120" t="n"/>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="114" t="n"/>
+      <c r="B98" s="104" t="n"/>
+      <c r="C98" s="115">
+        <f>IF($A98="","",IFERROR(VLOOKUP($A98,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D98" s="94" t="n"/>
+      <c r="E98" s="94" t="n"/>
+      <c r="F98" s="104" t="n"/>
+      <c r="G98" s="114" t="n"/>
+      <c r="H98" s="104" t="n"/>
+      <c r="I98" s="116">
+        <f>IF($H98="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H98,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J98" s="116">
+        <f>IF($H98="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H98,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K98" s="117">
+        <f>IF($H98="","",IF(AND(OR(I98="Critical",I98="High"),OR(J98="Open",J98="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L98" s="118" t="n"/>
+      <c r="M98" s="119" t="n"/>
+      <c r="N98" s="120" t="n"/>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="114" t="n"/>
+      <c r="B99" s="104" t="n"/>
+      <c r="C99" s="115">
+        <f>IF($A99="","",IFERROR(VLOOKUP($A99,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D99" s="94" t="n"/>
+      <c r="E99" s="94" t="n"/>
+      <c r="F99" s="104" t="n"/>
+      <c r="G99" s="114" t="n"/>
+      <c r="H99" s="104" t="n"/>
+      <c r="I99" s="116">
+        <f>IF($H99="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H99,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J99" s="116">
+        <f>IF($H99="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H99,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K99" s="117">
+        <f>IF($H99="","",IF(AND(OR(I99="Critical",I99="High"),OR(J99="Open",J99="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L99" s="118" t="n"/>
+      <c r="M99" s="119" t="n"/>
+      <c r="N99" s="120" t="n"/>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="114" t="n"/>
+      <c r="B100" s="104" t="n"/>
+      <c r="C100" s="115">
+        <f>IF($A100="","",IFERROR(VLOOKUP($A100,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D100" s="94" t="n"/>
+      <c r="E100" s="94" t="n"/>
+      <c r="F100" s="104" t="n"/>
+      <c r="G100" s="114" t="n"/>
+      <c r="H100" s="104" t="n"/>
+      <c r="I100" s="116">
+        <f>IF($H100="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H100,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J100" s="116">
+        <f>IF($H100="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H100,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K100" s="117">
+        <f>IF($H100="","",IF(AND(OR(I100="Critical",I100="High"),OR(J100="Open",J100="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L100" s="118" t="n"/>
+      <c r="M100" s="119" t="n"/>
+      <c r="N100" s="120" t="n"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="114" t="n"/>
+      <c r="B101" s="104" t="n"/>
+      <c r="C101" s="115">
+        <f>IF($A101="","",IFERROR(VLOOKUP($A101,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D101" s="94" t="n"/>
+      <c r="E101" s="94" t="n"/>
+      <c r="F101" s="104" t="n"/>
+      <c r="G101" s="114" t="n"/>
+      <c r="H101" s="104" t="n"/>
+      <c r="I101" s="116">
+        <f>IF($H101="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H101,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J101" s="116">
+        <f>IF($H101="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H101,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K101" s="117">
+        <f>IF($H101="","",IF(AND(OR(I101="Critical",I101="High"),OR(J101="Open",J101="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L101" s="118" t="n"/>
+      <c r="M101" s="119" t="n"/>
+      <c r="N101" s="120" t="n"/>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="114" t="n"/>
+      <c r="B102" s="104" t="n"/>
+      <c r="C102" s="115">
+        <f>IF($A102="","",IFERROR(VLOOKUP($A102,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D102" s="94" t="n"/>
+      <c r="E102" s="94" t="n"/>
+      <c r="F102" s="104" t="n"/>
+      <c r="G102" s="114" t="n"/>
+      <c r="H102" s="104" t="n"/>
+      <c r="I102" s="116">
+        <f>IF($H102="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H102,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J102" s="116">
+        <f>IF($H102="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H102,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K102" s="117">
+        <f>IF($H102="","",IF(AND(OR(I102="Critical",I102="High"),OR(J102="Open",J102="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L102" s="118" t="n"/>
+      <c r="M102" s="119" t="n"/>
+      <c r="N102" s="120" t="n"/>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="114" t="n"/>
+      <c r="B103" s="104" t="n"/>
+      <c r="C103" s="115">
+        <f>IF($A103="","",IFERROR(VLOOKUP($A103,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D103" s="94" t="n"/>
+      <c r="E103" s="94" t="n"/>
+      <c r="F103" s="104" t="n"/>
+      <c r="G103" s="114" t="n"/>
+      <c r="H103" s="104" t="n"/>
+      <c r="I103" s="116">
+        <f>IF($H103="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H103,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J103" s="116">
+        <f>IF($H103="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H103,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K103" s="117">
+        <f>IF($H103="","",IF(AND(OR(I103="Critical",I103="High"),OR(J103="Open",J103="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L103" s="118" t="n"/>
+      <c r="M103" s="119" t="n"/>
+      <c r="N103" s="120" t="n"/>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="114" t="n"/>
+      <c r="B104" s="104" t="n"/>
+      <c r="C104" s="115">
+        <f>IF($A104="","",IFERROR(VLOOKUP($A104,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D104" s="94" t="n"/>
+      <c r="E104" s="94" t="n"/>
+      <c r="F104" s="104" t="n"/>
+      <c r="G104" s="114" t="n"/>
+      <c r="H104" s="104" t="n"/>
+      <c r="I104" s="116">
+        <f>IF($H104="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H104,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J104" s="116">
+        <f>IF($H104="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H104,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K104" s="117">
+        <f>IF($H104="","",IF(AND(OR(I104="Critical",I104="High"),OR(J104="Open",J104="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L104" s="118" t="n"/>
+      <c r="M104" s="119" t="n"/>
+      <c r="N104" s="120" t="n"/>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="114" t="n"/>
+      <c r="B105" s="104" t="n"/>
+      <c r="C105" s="115">
+        <f>IF($A105="","",IFERROR(VLOOKUP($A105,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D105" s="94" t="n"/>
+      <c r="E105" s="94" t="n"/>
+      <c r="F105" s="104" t="n"/>
+      <c r="G105" s="114" t="n"/>
+      <c r="H105" s="104" t="n"/>
+      <c r="I105" s="116">
+        <f>IF($H105="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H105,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J105" s="116">
+        <f>IF($H105="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H105,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K105" s="117">
+        <f>IF($H105="","",IF(AND(OR(I105="Critical",I105="High"),OR(J105="Open",J105="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L105" s="118" t="n"/>
+      <c r="M105" s="119" t="n"/>
+      <c r="N105" s="120" t="n"/>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="114" t="n"/>
+      <c r="B106" s="104" t="n"/>
+      <c r="C106" s="115">
+        <f>IF($A106="","",IFERROR(VLOOKUP($A106,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D106" s="94" t="n"/>
+      <c r="E106" s="94" t="n"/>
+      <c r="F106" s="104" t="n"/>
+      <c r="G106" s="114" t="n"/>
+      <c r="H106" s="104" t="n"/>
+      <c r="I106" s="116">
+        <f>IF($H106="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H106,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J106" s="116">
+        <f>IF($H106="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H106,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K106" s="117">
+        <f>IF($H106="","",IF(AND(OR(I106="Critical",I106="High"),OR(J106="Open",J106="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L106" s="118" t="n"/>
+      <c r="M106" s="119" t="n"/>
+      <c r="N106" s="120" t="n"/>
+    </row>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="114" t="n"/>
+      <c r="B107" s="104" t="n"/>
+      <c r="C107" s="115">
+        <f>IF($A107="","",IFERROR(VLOOKUP($A107,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D107" s="94" t="n"/>
+      <c r="E107" s="94" t="n"/>
+      <c r="F107" s="104" t="n"/>
+      <c r="G107" s="114" t="n"/>
+      <c r="H107" s="104" t="n"/>
+      <c r="I107" s="116">
+        <f>IF($H107="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H107,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J107" s="116">
+        <f>IF($H107="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H107,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K107" s="117">
+        <f>IF($H107="","",IF(AND(OR(I107="Critical",I107="High"),OR(J107="Open",J107="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L107" s="118" t="n"/>
+      <c r="M107" s="119" t="n"/>
+      <c r="N107" s="120" t="n"/>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="114" t="n"/>
+      <c r="B108" s="104" t="n"/>
+      <c r="C108" s="115">
+        <f>IF($A108="","",IFERROR(VLOOKUP($A108,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D108" s="94" t="n"/>
+      <c r="E108" s="94" t="n"/>
+      <c r="F108" s="104" t="n"/>
+      <c r="G108" s="114" t="n"/>
+      <c r="H108" s="104" t="n"/>
+      <c r="I108" s="116">
+        <f>IF($H108="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H108,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J108" s="116">
+        <f>IF($H108="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H108,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K108" s="117">
+        <f>IF($H108="","",IF(AND(OR(I108="Critical",I108="High"),OR(J108="Open",J108="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L108" s="118" t="n"/>
+      <c r="M108" s="119" t="n"/>
+      <c r="N108" s="120" t="n"/>
+    </row>
+    <row r="109" ht="30" customHeight="1">
+      <c r="A109" s="114" t="n"/>
+      <c r="B109" s="104" t="n"/>
+      <c r="C109" s="115">
+        <f>IF($A109="","",IFERROR(VLOOKUP($A109,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D109" s="94" t="n"/>
+      <c r="E109" s="94" t="n"/>
+      <c r="F109" s="104" t="n"/>
+      <c r="G109" s="114" t="n"/>
+      <c r="H109" s="104" t="n"/>
+      <c r="I109" s="116">
+        <f>IF($H109="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H109,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J109" s="116">
+        <f>IF($H109="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H109,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K109" s="117">
+        <f>IF($H109="","",IF(AND(OR(I109="Critical",I109="High"),OR(J109="Open",J109="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L109" s="118" t="n"/>
+      <c r="M109" s="119" t="n"/>
+      <c r="N109" s="120" t="n"/>
+    </row>
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="114" t="n"/>
+      <c r="B110" s="104" t="n"/>
+      <c r="C110" s="115">
+        <f>IF($A110="","",IFERROR(VLOOKUP($A110,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D110" s="94" t="n"/>
+      <c r="E110" s="94" t="n"/>
+      <c r="F110" s="104" t="n"/>
+      <c r="G110" s="114" t="n"/>
+      <c r="H110" s="104" t="n"/>
+      <c r="I110" s="116">
+        <f>IF($H110="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H110,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J110" s="116">
+        <f>IF($H110="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H110,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K110" s="117">
+        <f>IF($H110="","",IF(AND(OR(I110="Critical",I110="High"),OR(J110="Open",J110="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L110" s="118" t="n"/>
+      <c r="M110" s="119" t="n"/>
+      <c r="N110" s="120" t="n"/>
+    </row>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" s="114" t="n"/>
+      <c r="B111" s="104" t="n"/>
+      <c r="C111" s="115">
+        <f>IF($A111="","",IFERROR(VLOOKUP($A111,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D111" s="94" t="n"/>
+      <c r="E111" s="94" t="n"/>
+      <c r="F111" s="104" t="n"/>
+      <c r="G111" s="114" t="n"/>
+      <c r="H111" s="104" t="n"/>
+      <c r="I111" s="116">
+        <f>IF($H111="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H111,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J111" s="116">
+        <f>IF($H111="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H111,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K111" s="117">
+        <f>IF($H111="","",IF(AND(OR(I111="Critical",I111="High"),OR(J111="Open",J111="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L111" s="118" t="n"/>
+      <c r="M111" s="119" t="n"/>
+      <c r="N111" s="120" t="n"/>
+    </row>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="114" t="n"/>
+      <c r="B112" s="104" t="n"/>
+      <c r="C112" s="115">
+        <f>IF($A112="","",IFERROR(VLOOKUP($A112,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D112" s="94" t="n"/>
+      <c r="E112" s="94" t="n"/>
+      <c r="F112" s="104" t="n"/>
+      <c r="G112" s="114" t="n"/>
+      <c r="H112" s="104" t="n"/>
+      <c r="I112" s="116">
+        <f>IF($H112="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H112,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J112" s="116">
+        <f>IF($H112="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H112,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K112" s="117">
+        <f>IF($H112="","",IF(AND(OR(I112="Critical",I112="High"),OR(J112="Open",J112="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L112" s="118" t="n"/>
+      <c r="M112" s="119" t="n"/>
+      <c r="N112" s="120" t="n"/>
+    </row>
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" s="114" t="n"/>
+      <c r="B113" s="104" t="n"/>
+      <c r="C113" s="115">
+        <f>IF($A113="","",IFERROR(VLOOKUP($A113,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D113" s="94" t="n"/>
+      <c r="E113" s="94" t="n"/>
+      <c r="F113" s="104" t="n"/>
+      <c r="G113" s="114" t="n"/>
+      <c r="H113" s="104" t="n"/>
+      <c r="I113" s="116">
+        <f>IF($H113="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H113,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J113" s="116">
+        <f>IF($H113="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H113,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K113" s="117">
+        <f>IF($H113="","",IF(AND(OR(I113="Critical",I113="High"),OR(J113="Open",J113="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L113" s="118" t="n"/>
+      <c r="M113" s="119" t="n"/>
+      <c r="N113" s="120" t="n"/>
+    </row>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="114" t="n"/>
+      <c r="B114" s="104" t="n"/>
+      <c r="C114" s="115">
+        <f>IF($A114="","",IFERROR(VLOOKUP($A114,$A$35:$B$49,2,0),"⚠ Sai Mã HT"))</f>
+        <v/>
+      </c>
+      <c r="D114" s="94" t="n"/>
+      <c r="E114" s="94" t="n"/>
+      <c r="F114" s="104" t="n"/>
+      <c r="G114" s="114" t="n"/>
+      <c r="H114" s="104" t="n"/>
+      <c r="I114" s="116">
+        <f>IF($H114="","",IFERROR(INDEX('z_Loi'!$L:$L,MATCH($H114,'z_Loi'!$E:$E,0)),"Không tìm thấy"))</f>
+        <v/>
+      </c>
+      <c r="J114" s="116">
+        <f>IF($H114="","",IFERROR(INDEX('z_Loi'!$U:$U,MATCH($H114,'z_Loi'!$E:$E,0)),""))</f>
+        <v/>
+      </c>
+      <c r="K114" s="117">
+        <f>IF($H114="","",IF(AND(OR(I114="Critical",I114="High"),OR(J114="Open",J114="Chưa gửi Dev")),"CHẶN",""))</f>
+        <v/>
+      </c>
+      <c r="L114" s="118" t="n"/>
+      <c r="M114" s="119" t="n"/>
+      <c r="N114" s="120" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="70">
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="L42:N42"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="L45:N45"/>
+    <mergeCell ref="A51:N51"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A6:N6"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="K28:N30"/>
+    <mergeCell ref="L41:N41"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="L44:N44"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="L40:N40"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="L46:N46"/>
+    <mergeCell ref="L49:N49"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="A33:N33"/>
+    <mergeCell ref="D28:E30"/>
+    <mergeCell ref="A28:C30"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="A32:N32"/>
+    <mergeCell ref="L48:N48"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="F27:J27"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A17:N17"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C15:N15"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="F28:J30"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="A52:N52"/>
+    <mergeCell ref="L47:N47"/>
+    <mergeCell ref="A19:N19"/>
+    <mergeCell ref="L43:N43"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="C49:D49"/>
   </mergeCells>
+  <conditionalFormatting sqref="K8:K13">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>K8="ĐẠT"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>K8="CHƯA ĐẠT"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>K8="ĐANG TEST"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K35:K49">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>K35="ĐẠT"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="1">
+      <formula>K35="CHƯA ĐẠT"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2">
+      <formula>K35="ĐANG TEST"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G54:G114">
+    <cfRule type="expression" priority="7" dxfId="0">
+      <formula>G54="Pass"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="1">
+      <formula>G54="Fail"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" dxfId="2">
+      <formula>G54="Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K54:K114">
+    <cfRule type="expression" priority="10" dxfId="1">
+      <formula>K54="CHẶN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15">
+    <cfRule type="expression" priority="11" dxfId="0">
+      <formula>LEFT(C15,1)="✔"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="1">
+      <formula>LEFT(C15,1)="✖"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="5">
+    <dataValidation sqref="C16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Đồng ý nghiệm thu,Nghiệm thu có điều kiện,Chưa nghiệm thu"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G21:G25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Đạt,Chưa đạt,Đạt có điều kiện"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B35:B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Khách vãng lai,Ứng viên,Nhà tuyển dụng (DN),HR,Quản trị viên"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G54:G114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pass,Fail,Blocked,Chưa test"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N54:N114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+      <formula1>1</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5100,258 +9204,258 @@
       <c r="N3" s="7" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="90" t="inlineStr">
+      <c r="A4" s="121" t="inlineStr">
         <is>
           <t>Tháng</t>
         </is>
       </c>
-      <c r="B4" s="104" t="inlineStr">
+      <c r="B4" s="122" t="inlineStr">
         <is>
           <t>Trang hoàn thành</t>
         </is>
       </c>
-      <c r="C4" s="104" t="inlineStr">
+      <c r="C4" s="122" t="inlineStr">
         <is>
           <t>Tính năng hoàn thành</t>
         </is>
       </c>
-      <c r="D4" s="104" t="inlineStr">
+      <c r="D4" s="122" t="inlineStr">
         <is>
           <t>Công việc HT trong kỳ</t>
         </is>
       </c>
-      <c r="E4" s="104" t="inlineStr">
+      <c r="E4" s="122" t="inlineStr">
         <is>
           <t>Lỗi phát hiện trong kỳ</t>
         </is>
       </c>
-      <c r="F4" s="104" t="inlineStr">
+      <c r="F4" s="122" t="inlineStr">
         <is>
           <t>Lỗi đã xử lý (lũy kế)</t>
         </is>
       </c>
-      <c r="G4" s="104" t="inlineStr">
+      <c r="G4" s="122" t="inlineStr">
         <is>
           <t>Số Trang đã xử lý</t>
         </is>
       </c>
-      <c r="H4" s="104" t="inlineStr">
+      <c r="H4" s="122" t="inlineStr">
         <is>
           <t>Số Tính năng đã xử lý</t>
         </is>
       </c>
-      <c r="I4" s="104" t="inlineStr">
+      <c r="I4" s="122" t="inlineStr">
         <is>
           <t>DB Doanh nghiệp</t>
         </is>
       </c>
-      <c r="J4" s="104" t="inlineStr">
+      <c r="J4" s="122" t="inlineStr">
         <is>
           <t>DB HR</t>
         </is>
       </c>
-      <c r="K4" s="104" t="inlineStr">
+      <c r="K4" s="122" t="inlineStr">
         <is>
           <t>DB Ứng viên</t>
         </is>
       </c>
-      <c r="L4" s="104" t="inlineStr">
+      <c r="L4" s="122" t="inlineStr">
         <is>
           <t>Tin tuyển dụng</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="105" t="n">
+      <c r="A5" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="106" t="n"/>
-      <c r="C5" s="106" t="n"/>
-      <c r="D5" s="106" t="n"/>
-      <c r="E5" s="106" t="n"/>
-      <c r="F5" s="106" t="n"/>
-      <c r="G5" s="106" t="n"/>
-      <c r="H5" s="106" t="n"/>
-      <c r="I5" s="106" t="n"/>
-      <c r="J5" s="106" t="n"/>
-      <c r="K5" s="106" t="n"/>
-      <c r="L5" s="106" t="n"/>
+      <c r="B5" s="124" t="n"/>
+      <c r="C5" s="124" t="n"/>
+      <c r="D5" s="124" t="n"/>
+      <c r="E5" s="124" t="n"/>
+      <c r="F5" s="124" t="n"/>
+      <c r="G5" s="124" t="n"/>
+      <c r="H5" s="124" t="n"/>
+      <c r="I5" s="124" t="n"/>
+      <c r="J5" s="124" t="n"/>
+      <c r="K5" s="124" t="n"/>
+      <c r="L5" s="124" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="105" t="n">
+      <c r="A6" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="106" t="n"/>
-      <c r="C6" s="106" t="n"/>
-      <c r="D6" s="106" t="n"/>
-      <c r="E6" s="106" t="n"/>
-      <c r="F6" s="106" t="n"/>
-      <c r="G6" s="106" t="n"/>
-      <c r="H6" s="106" t="n"/>
-      <c r="I6" s="106" t="n"/>
-      <c r="J6" s="106" t="n"/>
-      <c r="K6" s="106" t="n"/>
-      <c r="L6" s="106" t="n"/>
+      <c r="B6" s="124" t="n"/>
+      <c r="C6" s="124" t="n"/>
+      <c r="D6" s="124" t="n"/>
+      <c r="E6" s="124" t="n"/>
+      <c r="F6" s="124" t="n"/>
+      <c r="G6" s="124" t="n"/>
+      <c r="H6" s="124" t="n"/>
+      <c r="I6" s="124" t="n"/>
+      <c r="J6" s="124" t="n"/>
+      <c r="K6" s="124" t="n"/>
+      <c r="L6" s="124" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="105" t="n">
+      <c r="A7" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="106" t="n"/>
-      <c r="C7" s="106" t="n"/>
-      <c r="D7" s="106" t="n"/>
-      <c r="E7" s="106" t="n"/>
-      <c r="F7" s="106" t="n"/>
-      <c r="G7" s="106" t="n"/>
-      <c r="H7" s="106" t="n"/>
-      <c r="I7" s="106" t="n"/>
-      <c r="J7" s="106" t="n"/>
-      <c r="K7" s="106" t="n"/>
-      <c r="L7" s="106" t="n"/>
+      <c r="B7" s="124" t="n"/>
+      <c r="C7" s="124" t="n"/>
+      <c r="D7" s="124" t="n"/>
+      <c r="E7" s="124" t="n"/>
+      <c r="F7" s="124" t="n"/>
+      <c r="G7" s="124" t="n"/>
+      <c r="H7" s="124" t="n"/>
+      <c r="I7" s="124" t="n"/>
+      <c r="J7" s="124" t="n"/>
+      <c r="K7" s="124" t="n"/>
+      <c r="L7" s="124" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="105" t="n">
+      <c r="A8" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="106" t="n"/>
-      <c r="C8" s="106" t="n"/>
-      <c r="D8" s="106" t="n"/>
-      <c r="E8" s="106" t="n"/>
-      <c r="F8" s="106" t="n"/>
-      <c r="G8" s="106" t="n"/>
-      <c r="H8" s="106" t="n"/>
-      <c r="I8" s="106" t="n"/>
-      <c r="J8" s="106" t="n"/>
-      <c r="K8" s="106" t="n"/>
-      <c r="L8" s="106" t="n"/>
+      <c r="B8" s="124" t="n"/>
+      <c r="C8" s="124" t="n"/>
+      <c r="D8" s="124" t="n"/>
+      <c r="E8" s="124" t="n"/>
+      <c r="F8" s="124" t="n"/>
+      <c r="G8" s="124" t="n"/>
+      <c r="H8" s="124" t="n"/>
+      <c r="I8" s="124" t="n"/>
+      <c r="J8" s="124" t="n"/>
+      <c r="K8" s="124" t="n"/>
+      <c r="L8" s="124" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="105" t="n">
+      <c r="A9" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="106" t="n"/>
-      <c r="C9" s="106" t="n"/>
-      <c r="D9" s="106" t="n"/>
-      <c r="E9" s="106" t="n"/>
-      <c r="F9" s="106" t="n"/>
-      <c r="G9" s="106" t="n"/>
-      <c r="H9" s="106" t="n"/>
-      <c r="I9" s="106" t="n"/>
-      <c r="J9" s="106" t="n"/>
-      <c r="K9" s="106" t="n"/>
-      <c r="L9" s="106" t="n"/>
+      <c r="B9" s="124" t="n"/>
+      <c r="C9" s="124" t="n"/>
+      <c r="D9" s="124" t="n"/>
+      <c r="E9" s="124" t="n"/>
+      <c r="F9" s="124" t="n"/>
+      <c r="G9" s="124" t="n"/>
+      <c r="H9" s="124" t="n"/>
+      <c r="I9" s="124" t="n"/>
+      <c r="J9" s="124" t="n"/>
+      <c r="K9" s="124" t="n"/>
+      <c r="L9" s="124" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="105" t="n">
+      <c r="A10" s="123" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="106" t="n"/>
-      <c r="C10" s="106" t="n"/>
-      <c r="D10" s="106" t="n"/>
-      <c r="E10" s="106" t="n"/>
-      <c r="F10" s="106" t="n"/>
-      <c r="G10" s="106" t="n"/>
-      <c r="H10" s="106" t="n"/>
-      <c r="I10" s="106" t="n"/>
-      <c r="J10" s="106" t="n"/>
-      <c r="K10" s="106" t="n"/>
-      <c r="L10" s="106" t="n"/>
+      <c r="B10" s="124" t="n"/>
+      <c r="C10" s="124" t="n"/>
+      <c r="D10" s="124" t="n"/>
+      <c r="E10" s="124" t="n"/>
+      <c r="F10" s="124" t="n"/>
+      <c r="G10" s="124" t="n"/>
+      <c r="H10" s="124" t="n"/>
+      <c r="I10" s="124" t="n"/>
+      <c r="J10" s="124" t="n"/>
+      <c r="K10" s="124" t="n"/>
+      <c r="L10" s="124" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="105" t="n">
+      <c r="A11" s="123" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="106" t="n"/>
-      <c r="C11" s="106" t="n"/>
-      <c r="D11" s="106" t="n"/>
-      <c r="E11" s="106" t="n"/>
-      <c r="F11" s="106" t="n"/>
-      <c r="G11" s="106" t="n"/>
-      <c r="H11" s="106" t="n"/>
-      <c r="I11" s="106" t="n"/>
-      <c r="J11" s="106" t="n"/>
-      <c r="K11" s="106" t="n"/>
-      <c r="L11" s="106" t="n"/>
+      <c r="B11" s="124" t="n"/>
+      <c r="C11" s="124" t="n"/>
+      <c r="D11" s="124" t="n"/>
+      <c r="E11" s="124" t="n"/>
+      <c r="F11" s="124" t="n"/>
+      <c r="G11" s="124" t="n"/>
+      <c r="H11" s="124" t="n"/>
+      <c r="I11" s="124" t="n"/>
+      <c r="J11" s="124" t="n"/>
+      <c r="K11" s="124" t="n"/>
+      <c r="L11" s="124" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="105" t="n">
+      <c r="A12" s="123" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="106" t="n"/>
-      <c r="C12" s="106" t="n"/>
-      <c r="D12" s="106" t="n"/>
-      <c r="E12" s="106" t="n"/>
-      <c r="F12" s="106" t="n"/>
-      <c r="G12" s="106" t="n"/>
-      <c r="H12" s="106" t="n"/>
-      <c r="I12" s="106" t="n"/>
-      <c r="J12" s="106" t="n"/>
-      <c r="K12" s="106" t="n"/>
-      <c r="L12" s="106" t="n"/>
+      <c r="B12" s="124" t="n"/>
+      <c r="C12" s="124" t="n"/>
+      <c r="D12" s="124" t="n"/>
+      <c r="E12" s="124" t="n"/>
+      <c r="F12" s="124" t="n"/>
+      <c r="G12" s="124" t="n"/>
+      <c r="H12" s="124" t="n"/>
+      <c r="I12" s="124" t="n"/>
+      <c r="J12" s="124" t="n"/>
+      <c r="K12" s="124" t="n"/>
+      <c r="L12" s="124" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="105" t="n">
+      <c r="A13" s="123" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="106" t="n"/>
-      <c r="C13" s="106" t="n"/>
-      <c r="D13" s="106" t="n"/>
-      <c r="E13" s="106" t="n"/>
-      <c r="F13" s="106" t="n"/>
-      <c r="G13" s="106" t="n"/>
-      <c r="H13" s="106" t="n"/>
-      <c r="I13" s="106" t="n"/>
-      <c r="J13" s="106" t="n"/>
-      <c r="K13" s="106" t="n"/>
-      <c r="L13" s="106" t="n"/>
+      <c r="B13" s="124" t="n"/>
+      <c r="C13" s="124" t="n"/>
+      <c r="D13" s="124" t="n"/>
+      <c r="E13" s="124" t="n"/>
+      <c r="F13" s="124" t="n"/>
+      <c r="G13" s="124" t="n"/>
+      <c r="H13" s="124" t="n"/>
+      <c r="I13" s="124" t="n"/>
+      <c r="J13" s="124" t="n"/>
+      <c r="K13" s="124" t="n"/>
+      <c r="L13" s="124" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="105" t="n">
+      <c r="A14" s="123" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="106" t="n"/>
-      <c r="C14" s="106" t="n"/>
-      <c r="D14" s="106" t="n"/>
-      <c r="E14" s="106" t="n"/>
-      <c r="F14" s="106" t="n"/>
-      <c r="G14" s="106" t="n"/>
-      <c r="H14" s="106" t="n"/>
-      <c r="I14" s="106" t="n"/>
-      <c r="J14" s="106" t="n"/>
-      <c r="K14" s="106" t="n"/>
-      <c r="L14" s="106" t="n"/>
+      <c r="B14" s="124" t="n"/>
+      <c r="C14" s="124" t="n"/>
+      <c r="D14" s="124" t="n"/>
+      <c r="E14" s="124" t="n"/>
+      <c r="F14" s="124" t="n"/>
+      <c r="G14" s="124" t="n"/>
+      <c r="H14" s="124" t="n"/>
+      <c r="I14" s="124" t="n"/>
+      <c r="J14" s="124" t="n"/>
+      <c r="K14" s="124" t="n"/>
+      <c r="L14" s="124" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="105" t="n">
+      <c r="A15" s="123" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="106" t="n"/>
-      <c r="C15" s="106" t="n"/>
-      <c r="D15" s="106" t="n"/>
-      <c r="E15" s="106" t="n"/>
-      <c r="F15" s="106" t="n"/>
-      <c r="G15" s="106" t="n"/>
-      <c r="H15" s="106" t="n"/>
-      <c r="I15" s="106" t="n"/>
-      <c r="J15" s="106" t="n"/>
-      <c r="K15" s="106" t="n"/>
-      <c r="L15" s="106" t="n"/>
+      <c r="B15" s="124" t="n"/>
+      <c r="C15" s="124" t="n"/>
+      <c r="D15" s="124" t="n"/>
+      <c r="E15" s="124" t="n"/>
+      <c r="F15" s="124" t="n"/>
+      <c r="G15" s="124" t="n"/>
+      <c r="H15" s="124" t="n"/>
+      <c r="I15" s="124" t="n"/>
+      <c r="J15" s="124" t="n"/>
+      <c r="K15" s="124" t="n"/>
+      <c r="L15" s="124" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="105" t="n">
+      <c r="A16" s="123" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="106" t="n"/>
-      <c r="C16" s="106" t="n"/>
-      <c r="D16" s="106" t="n"/>
-      <c r="E16" s="106" t="n"/>
-      <c r="F16" s="106" t="n"/>
-      <c r="G16" s="106" t="n"/>
-      <c r="H16" s="106" t="n"/>
-      <c r="I16" s="106" t="n"/>
-      <c r="J16" s="106" t="n"/>
-      <c r="K16" s="106" t="n"/>
-      <c r="L16" s="106" t="n"/>
+      <c r="B16" s="124" t="n"/>
+      <c r="C16" s="124" t="n"/>
+      <c r="D16" s="124" t="n"/>
+      <c r="E16" s="124" t="n"/>
+      <c r="F16" s="124" t="n"/>
+      <c r="G16" s="124" t="n"/>
+      <c r="H16" s="124" t="n"/>
+      <c r="I16" s="124" t="n"/>
+      <c r="J16" s="124" t="n"/>
+      <c r="K16" s="124" t="n"/>
+      <c r="L16" s="124" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
@@ -5374,1456 +9478,1456 @@
       <c r="N18" s="7" t="n"/>
     </row>
     <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="90" t="inlineStr">
+      <c r="A19" s="121" t="inlineStr">
         <is>
           <t>Tháng</t>
         </is>
       </c>
-      <c r="B19" s="90" t="inlineStr">
+      <c r="B19" s="121" t="inlineStr">
         <is>
           <t>Tuần</t>
         </is>
       </c>
-      <c r="C19" s="107" t="inlineStr">
+      <c r="C19" s="125" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="D19" s="104" t="inlineStr">
+      <c r="D19" s="122" t="inlineStr">
         <is>
           <t>Trang hoàn thành</t>
         </is>
       </c>
-      <c r="E19" s="104" t="inlineStr">
+      <c r="E19" s="122" t="inlineStr">
         <is>
           <t>Tính năng hoàn thành</t>
         </is>
       </c>
-      <c r="F19" s="104" t="inlineStr">
+      <c r="F19" s="122" t="inlineStr">
         <is>
           <t>Công việc HT trong kỳ</t>
         </is>
       </c>
-      <c r="G19" s="104" t="inlineStr">
+      <c r="G19" s="122" t="inlineStr">
         <is>
           <t>Lỗi phát hiện trong kỳ</t>
         </is>
       </c>
-      <c r="H19" s="104" t="inlineStr">
+      <c r="H19" s="122" t="inlineStr">
         <is>
           <t>Lỗi đã xử lý (lũy kế)</t>
         </is>
       </c>
-      <c r="I19" s="104" t="inlineStr">
+      <c r="I19" s="122" t="inlineStr">
         <is>
           <t>Số Trang đã xử lý</t>
         </is>
       </c>
-      <c r="J19" s="104" t="inlineStr">
+      <c r="J19" s="122" t="inlineStr">
         <is>
           <t>Số Tính năng đã xử lý</t>
         </is>
       </c>
-      <c r="K19" s="104" t="inlineStr">
+      <c r="K19" s="122" t="inlineStr">
         <is>
           <t>DB Doanh nghiệp</t>
         </is>
       </c>
-      <c r="L19" s="104" t="inlineStr">
+      <c r="L19" s="122" t="inlineStr">
         <is>
           <t>DB HR</t>
         </is>
       </c>
-      <c r="M19" s="104" t="inlineStr">
+      <c r="M19" s="122" t="inlineStr">
         <is>
           <t>DB Ứng viên</t>
         </is>
       </c>
-      <c r="N19" s="104" t="inlineStr">
+      <c r="N19" s="122" t="inlineStr">
         <is>
           <t>Tin tuyển dụng</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="108" t="n">
+      <c r="A20" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="108" t="n">
+      <c r="B20" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="109">
+      <c r="C20" s="127">
         <f>A20*10+B20</f>
         <v/>
       </c>
-      <c r="D20" s="106" t="n"/>
-      <c r="E20" s="106" t="n"/>
-      <c r="F20" s="106" t="n"/>
-      <c r="G20" s="106" t="n"/>
-      <c r="H20" s="106" t="n"/>
-      <c r="I20" s="106" t="n"/>
-      <c r="J20" s="106" t="n"/>
-      <c r="K20" s="106" t="n"/>
-      <c r="L20" s="106" t="n"/>
-      <c r="M20" s="106" t="n"/>
-      <c r="N20" s="106" t="n"/>
+      <c r="D20" s="124" t="n"/>
+      <c r="E20" s="124" t="n"/>
+      <c r="F20" s="124" t="n"/>
+      <c r="G20" s="124" t="n"/>
+      <c r="H20" s="124" t="n"/>
+      <c r="I20" s="124" t="n"/>
+      <c r="J20" s="124" t="n"/>
+      <c r="K20" s="124" t="n"/>
+      <c r="L20" s="124" t="n"/>
+      <c r="M20" s="124" t="n"/>
+      <c r="N20" s="124" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="108" t="n">
+      <c r="A21" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="108" t="n">
+      <c r="B21" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="109">
+      <c r="C21" s="127">
         <f>A21*10+B21</f>
         <v/>
       </c>
-      <c r="D21" s="106" t="n"/>
-      <c r="E21" s="106" t="n"/>
-      <c r="F21" s="106" t="n"/>
-      <c r="G21" s="106" t="n"/>
-      <c r="H21" s="106" t="n"/>
-      <c r="I21" s="106" t="n"/>
-      <c r="J21" s="106" t="n"/>
-      <c r="K21" s="106" t="n"/>
-      <c r="L21" s="106" t="n"/>
-      <c r="M21" s="106" t="n"/>
-      <c r="N21" s="106" t="n"/>
+      <c r="D21" s="124" t="n"/>
+      <c r="E21" s="124" t="n"/>
+      <c r="F21" s="124" t="n"/>
+      <c r="G21" s="124" t="n"/>
+      <c r="H21" s="124" t="n"/>
+      <c r="I21" s="124" t="n"/>
+      <c r="J21" s="124" t="n"/>
+      <c r="K21" s="124" t="n"/>
+      <c r="L21" s="124" t="n"/>
+      <c r="M21" s="124" t="n"/>
+      <c r="N21" s="124" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="108" t="n">
+      <c r="A22" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="108" t="n">
+      <c r="B22" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="C22" s="109">
+      <c r="C22" s="127">
         <f>A22*10+B22</f>
         <v/>
       </c>
-      <c r="D22" s="106" t="n"/>
-      <c r="E22" s="106" t="n"/>
-      <c r="F22" s="106" t="n"/>
-      <c r="G22" s="106" t="n"/>
-      <c r="H22" s="106" t="n"/>
-      <c r="I22" s="106" t="n"/>
-      <c r="J22" s="106" t="n"/>
-      <c r="K22" s="106" t="n"/>
-      <c r="L22" s="106" t="n"/>
-      <c r="M22" s="106" t="n"/>
-      <c r="N22" s="106" t="n"/>
+      <c r="D22" s="124" t="n"/>
+      <c r="E22" s="124" t="n"/>
+      <c r="F22" s="124" t="n"/>
+      <c r="G22" s="124" t="n"/>
+      <c r="H22" s="124" t="n"/>
+      <c r="I22" s="124" t="n"/>
+      <c r="J22" s="124" t="n"/>
+      <c r="K22" s="124" t="n"/>
+      <c r="L22" s="124" t="n"/>
+      <c r="M22" s="124" t="n"/>
+      <c r="N22" s="124" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="108" t="n">
+      <c r="A23" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="108" t="n">
+      <c r="B23" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="C23" s="109">
+      <c r="C23" s="127">
         <f>A23*10+B23</f>
         <v/>
       </c>
-      <c r="D23" s="106" t="n"/>
-      <c r="E23" s="106" t="n"/>
-      <c r="F23" s="106" t="n"/>
-      <c r="G23" s="106" t="n"/>
-      <c r="H23" s="106" t="n"/>
-      <c r="I23" s="106" t="n"/>
-      <c r="J23" s="106" t="n"/>
-      <c r="K23" s="106" t="n"/>
-      <c r="L23" s="106" t="n"/>
-      <c r="M23" s="106" t="n"/>
-      <c r="N23" s="106" t="n"/>
+      <c r="D23" s="124" t="n"/>
+      <c r="E23" s="124" t="n"/>
+      <c r="F23" s="124" t="n"/>
+      <c r="G23" s="124" t="n"/>
+      <c r="H23" s="124" t="n"/>
+      <c r="I23" s="124" t="n"/>
+      <c r="J23" s="124" t="n"/>
+      <c r="K23" s="124" t="n"/>
+      <c r="L23" s="124" t="n"/>
+      <c r="M23" s="124" t="n"/>
+      <c r="N23" s="124" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="108" t="n">
+      <c r="A24" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="108" t="n">
+      <c r="B24" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="C24" s="109">
+      <c r="C24" s="127">
         <f>A24*10+B24</f>
         <v/>
       </c>
-      <c r="D24" s="106" t="n"/>
-      <c r="E24" s="106" t="n"/>
-      <c r="F24" s="106" t="n"/>
-      <c r="G24" s="106" t="n"/>
-      <c r="H24" s="106" t="n"/>
-      <c r="I24" s="106" t="n"/>
-      <c r="J24" s="106" t="n"/>
-      <c r="K24" s="106" t="n"/>
-      <c r="L24" s="106" t="n"/>
-      <c r="M24" s="106" t="n"/>
-      <c r="N24" s="106" t="n"/>
+      <c r="D24" s="124" t="n"/>
+      <c r="E24" s="124" t="n"/>
+      <c r="F24" s="124" t="n"/>
+      <c r="G24" s="124" t="n"/>
+      <c r="H24" s="124" t="n"/>
+      <c r="I24" s="124" t="n"/>
+      <c r="J24" s="124" t="n"/>
+      <c r="K24" s="124" t="n"/>
+      <c r="L24" s="124" t="n"/>
+      <c r="M24" s="124" t="n"/>
+      <c r="N24" s="124" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="108" t="n">
+      <c r="A25" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="108" t="n">
+      <c r="B25" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="109">
+      <c r="C25" s="127">
         <f>A25*10+B25</f>
         <v/>
       </c>
-      <c r="D25" s="106" t="n"/>
-      <c r="E25" s="106" t="n"/>
-      <c r="F25" s="106" t="n"/>
-      <c r="G25" s="106" t="n"/>
-      <c r="H25" s="106" t="n"/>
-      <c r="I25" s="106" t="n"/>
-      <c r="J25" s="106" t="n"/>
-      <c r="K25" s="106" t="n"/>
-      <c r="L25" s="106" t="n"/>
-      <c r="M25" s="106" t="n"/>
-      <c r="N25" s="106" t="n"/>
+      <c r="D25" s="124" t="n"/>
+      <c r="E25" s="124" t="n"/>
+      <c r="F25" s="124" t="n"/>
+      <c r="G25" s="124" t="n"/>
+      <c r="H25" s="124" t="n"/>
+      <c r="I25" s="124" t="n"/>
+      <c r="J25" s="124" t="n"/>
+      <c r="K25" s="124" t="n"/>
+      <c r="L25" s="124" t="n"/>
+      <c r="M25" s="124" t="n"/>
+      <c r="N25" s="124" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="108" t="n">
+      <c r="A26" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="108" t="n">
+      <c r="B26" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="C26" s="109">
+      <c r="C26" s="127">
         <f>A26*10+B26</f>
         <v/>
       </c>
-      <c r="D26" s="106" t="n"/>
-      <c r="E26" s="106" t="n"/>
-      <c r="F26" s="106" t="n"/>
-      <c r="G26" s="106" t="n"/>
-      <c r="H26" s="106" t="n"/>
-      <c r="I26" s="106" t="n"/>
-      <c r="J26" s="106" t="n"/>
-      <c r="K26" s="106" t="n"/>
-      <c r="L26" s="106" t="n"/>
-      <c r="M26" s="106" t="n"/>
-      <c r="N26" s="106" t="n"/>
+      <c r="D26" s="124" t="n"/>
+      <c r="E26" s="124" t="n"/>
+      <c r="F26" s="124" t="n"/>
+      <c r="G26" s="124" t="n"/>
+      <c r="H26" s="124" t="n"/>
+      <c r="I26" s="124" t="n"/>
+      <c r="J26" s="124" t="n"/>
+      <c r="K26" s="124" t="n"/>
+      <c r="L26" s="124" t="n"/>
+      <c r="M26" s="124" t="n"/>
+      <c r="N26" s="124" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="108" t="n">
+      <c r="A27" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="108" t="n">
+      <c r="B27" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="109">
+      <c r="C27" s="127">
         <f>A27*10+B27</f>
         <v/>
       </c>
-      <c r="D27" s="106" t="n"/>
-      <c r="E27" s="106" t="n"/>
-      <c r="F27" s="106" t="n"/>
-      <c r="G27" s="106" t="n"/>
-      <c r="H27" s="106" t="n"/>
-      <c r="I27" s="106" t="n"/>
-      <c r="J27" s="106" t="n"/>
-      <c r="K27" s="106" t="n"/>
-      <c r="L27" s="106" t="n"/>
-      <c r="M27" s="106" t="n"/>
-      <c r="N27" s="106" t="n"/>
+      <c r="D27" s="124" t="n"/>
+      <c r="E27" s="124" t="n"/>
+      <c r="F27" s="124" t="n"/>
+      <c r="G27" s="124" t="n"/>
+      <c r="H27" s="124" t="n"/>
+      <c r="I27" s="124" t="n"/>
+      <c r="J27" s="124" t="n"/>
+      <c r="K27" s="124" t="n"/>
+      <c r="L27" s="124" t="n"/>
+      <c r="M27" s="124" t="n"/>
+      <c r="N27" s="124" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="108" t="n">
+      <c r="A28" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="108" t="n">
+      <c r="B28" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="109">
+      <c r="C28" s="127">
         <f>A28*10+B28</f>
         <v/>
       </c>
-      <c r="D28" s="106" t="n"/>
-      <c r="E28" s="106" t="n"/>
-      <c r="F28" s="106" t="n"/>
-      <c r="G28" s="106" t="n"/>
-      <c r="H28" s="106" t="n"/>
-      <c r="I28" s="106" t="n"/>
-      <c r="J28" s="106" t="n"/>
-      <c r="K28" s="106" t="n"/>
-      <c r="L28" s="106" t="n"/>
-      <c r="M28" s="106" t="n"/>
-      <c r="N28" s="106" t="n"/>
+      <c r="D28" s="124" t="n"/>
+      <c r="E28" s="124" t="n"/>
+      <c r="F28" s="124" t="n"/>
+      <c r="G28" s="124" t="n"/>
+      <c r="H28" s="124" t="n"/>
+      <c r="I28" s="124" t="n"/>
+      <c r="J28" s="124" t="n"/>
+      <c r="K28" s="124" t="n"/>
+      <c r="L28" s="124" t="n"/>
+      <c r="M28" s="124" t="n"/>
+      <c r="N28" s="124" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="108" t="n">
+      <c r="A29" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="108" t="n">
+      <c r="B29" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="C29" s="109">
+      <c r="C29" s="127">
         <f>A29*10+B29</f>
         <v/>
       </c>
-      <c r="D29" s="106" t="n"/>
-      <c r="E29" s="106" t="n"/>
-      <c r="F29" s="106" t="n"/>
-      <c r="G29" s="106" t="n"/>
-      <c r="H29" s="106" t="n"/>
-      <c r="I29" s="106" t="n"/>
-      <c r="J29" s="106" t="n"/>
-      <c r="K29" s="106" t="n"/>
-      <c r="L29" s="106" t="n"/>
-      <c r="M29" s="106" t="n"/>
-      <c r="N29" s="106" t="n"/>
+      <c r="D29" s="124" t="n"/>
+      <c r="E29" s="124" t="n"/>
+      <c r="F29" s="124" t="n"/>
+      <c r="G29" s="124" t="n"/>
+      <c r="H29" s="124" t="n"/>
+      <c r="I29" s="124" t="n"/>
+      <c r="J29" s="124" t="n"/>
+      <c r="K29" s="124" t="n"/>
+      <c r="L29" s="124" t="n"/>
+      <c r="M29" s="124" t="n"/>
+      <c r="N29" s="124" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="108" t="n">
+      <c r="A30" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="108" t="n">
+      <c r="B30" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="109">
+      <c r="C30" s="127">
         <f>A30*10+B30</f>
         <v/>
       </c>
-      <c r="D30" s="106" t="n"/>
-      <c r="E30" s="106" t="n"/>
-      <c r="F30" s="106" t="n"/>
-      <c r="G30" s="106" t="n"/>
-      <c r="H30" s="106" t="n"/>
-      <c r="I30" s="106" t="n"/>
-      <c r="J30" s="106" t="n"/>
-      <c r="K30" s="106" t="n"/>
-      <c r="L30" s="106" t="n"/>
-      <c r="M30" s="106" t="n"/>
-      <c r="N30" s="106" t="n"/>
+      <c r="D30" s="124" t="n"/>
+      <c r="E30" s="124" t="n"/>
+      <c r="F30" s="124" t="n"/>
+      <c r="G30" s="124" t="n"/>
+      <c r="H30" s="124" t="n"/>
+      <c r="I30" s="124" t="n"/>
+      <c r="J30" s="124" t="n"/>
+      <c r="K30" s="124" t="n"/>
+      <c r="L30" s="124" t="n"/>
+      <c r="M30" s="124" t="n"/>
+      <c r="N30" s="124" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="108" t="n">
+      <c r="A31" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="B31" s="108" t="n">
+      <c r="B31" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="109">
+      <c r="C31" s="127">
         <f>A31*10+B31</f>
         <v/>
       </c>
-      <c r="D31" s="106" t="n"/>
-      <c r="E31" s="106" t="n"/>
-      <c r="F31" s="106" t="n"/>
-      <c r="G31" s="106" t="n"/>
-      <c r="H31" s="106" t="n"/>
-      <c r="I31" s="106" t="n"/>
-      <c r="J31" s="106" t="n"/>
-      <c r="K31" s="106" t="n"/>
-      <c r="L31" s="106" t="n"/>
-      <c r="M31" s="106" t="n"/>
-      <c r="N31" s="106" t="n"/>
+      <c r="D31" s="124" t="n"/>
+      <c r="E31" s="124" t="n"/>
+      <c r="F31" s="124" t="n"/>
+      <c r="G31" s="124" t="n"/>
+      <c r="H31" s="124" t="n"/>
+      <c r="I31" s="124" t="n"/>
+      <c r="J31" s="124" t="n"/>
+      <c r="K31" s="124" t="n"/>
+      <c r="L31" s="124" t="n"/>
+      <c r="M31" s="124" t="n"/>
+      <c r="N31" s="124" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="108" t="n">
+      <c r="A32" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="108" t="n">
+      <c r="B32" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="109">
+      <c r="C32" s="127">
         <f>A32*10+B32</f>
         <v/>
       </c>
-      <c r="D32" s="106" t="n"/>
-      <c r="E32" s="106" t="n"/>
-      <c r="F32" s="106" t="n"/>
-      <c r="G32" s="106" t="n"/>
-      <c r="H32" s="106" t="n"/>
-      <c r="I32" s="106" t="n"/>
-      <c r="J32" s="106" t="n"/>
-      <c r="K32" s="106" t="n"/>
-      <c r="L32" s="106" t="n"/>
-      <c r="M32" s="106" t="n"/>
-      <c r="N32" s="106" t="n"/>
+      <c r="D32" s="124" t="n"/>
+      <c r="E32" s="124" t="n"/>
+      <c r="F32" s="124" t="n"/>
+      <c r="G32" s="124" t="n"/>
+      <c r="H32" s="124" t="n"/>
+      <c r="I32" s="124" t="n"/>
+      <c r="J32" s="124" t="n"/>
+      <c r="K32" s="124" t="n"/>
+      <c r="L32" s="124" t="n"/>
+      <c r="M32" s="124" t="n"/>
+      <c r="N32" s="124" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="108" t="n">
+      <c r="A33" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="B33" s="108" t="n">
+      <c r="B33" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="109">
+      <c r="C33" s="127">
         <f>A33*10+B33</f>
         <v/>
       </c>
-      <c r="D33" s="106" t="n"/>
-      <c r="E33" s="106" t="n"/>
-      <c r="F33" s="106" t="n"/>
-      <c r="G33" s="106" t="n"/>
-      <c r="H33" s="106" t="n"/>
-      <c r="I33" s="106" t="n"/>
-      <c r="J33" s="106" t="n"/>
-      <c r="K33" s="106" t="n"/>
-      <c r="L33" s="106" t="n"/>
-      <c r="M33" s="106" t="n"/>
-      <c r="N33" s="106" t="n"/>
+      <c r="D33" s="124" t="n"/>
+      <c r="E33" s="124" t="n"/>
+      <c r="F33" s="124" t="n"/>
+      <c r="G33" s="124" t="n"/>
+      <c r="H33" s="124" t="n"/>
+      <c r="I33" s="124" t="n"/>
+      <c r="J33" s="124" t="n"/>
+      <c r="K33" s="124" t="n"/>
+      <c r="L33" s="124" t="n"/>
+      <c r="M33" s="124" t="n"/>
+      <c r="N33" s="124" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="108" t="n">
+      <c r="A34" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="B34" s="108" t="n">
+      <c r="B34" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="C34" s="109">
+      <c r="C34" s="127">
         <f>A34*10+B34</f>
         <v/>
       </c>
-      <c r="D34" s="106" t="n"/>
-      <c r="E34" s="106" t="n"/>
-      <c r="F34" s="106" t="n"/>
-      <c r="G34" s="106" t="n"/>
-      <c r="H34" s="106" t="n"/>
-      <c r="I34" s="106" t="n"/>
-      <c r="J34" s="106" t="n"/>
-      <c r="K34" s="106" t="n"/>
-      <c r="L34" s="106" t="n"/>
-      <c r="M34" s="106" t="n"/>
-      <c r="N34" s="106" t="n"/>
+      <c r="D34" s="124" t="n"/>
+      <c r="E34" s="124" t="n"/>
+      <c r="F34" s="124" t="n"/>
+      <c r="G34" s="124" t="n"/>
+      <c r="H34" s="124" t="n"/>
+      <c r="I34" s="124" t="n"/>
+      <c r="J34" s="124" t="n"/>
+      <c r="K34" s="124" t="n"/>
+      <c r="L34" s="124" t="n"/>
+      <c r="M34" s="124" t="n"/>
+      <c r="N34" s="124" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="108" t="n">
+      <c r="A35" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="B35" s="108" t="n">
+      <c r="B35" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="109">
+      <c r="C35" s="127">
         <f>A35*10+B35</f>
         <v/>
       </c>
-      <c r="D35" s="106" t="n"/>
-      <c r="E35" s="106" t="n"/>
-      <c r="F35" s="106" t="n"/>
-      <c r="G35" s="106" t="n"/>
-      <c r="H35" s="106" t="n"/>
-      <c r="I35" s="106" t="n"/>
-      <c r="J35" s="106" t="n"/>
-      <c r="K35" s="106" t="n"/>
-      <c r="L35" s="106" t="n"/>
-      <c r="M35" s="106" t="n"/>
-      <c r="N35" s="106" t="n"/>
+      <c r="D35" s="124" t="n"/>
+      <c r="E35" s="124" t="n"/>
+      <c r="F35" s="124" t="n"/>
+      <c r="G35" s="124" t="n"/>
+      <c r="H35" s="124" t="n"/>
+      <c r="I35" s="124" t="n"/>
+      <c r="J35" s="124" t="n"/>
+      <c r="K35" s="124" t="n"/>
+      <c r="L35" s="124" t="n"/>
+      <c r="M35" s="124" t="n"/>
+      <c r="N35" s="124" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="108" t="n">
+      <c r="A36" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="B36" s="108" t="n">
+      <c r="B36" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="C36" s="109">
+      <c r="C36" s="127">
         <f>A36*10+B36</f>
         <v/>
       </c>
-      <c r="D36" s="106" t="n"/>
-      <c r="E36" s="106" t="n"/>
-      <c r="F36" s="106" t="n"/>
-      <c r="G36" s="106" t="n"/>
-      <c r="H36" s="106" t="n"/>
-      <c r="I36" s="106" t="n"/>
-      <c r="J36" s="106" t="n"/>
-      <c r="K36" s="106" t="n"/>
-      <c r="L36" s="106" t="n"/>
-      <c r="M36" s="106" t="n"/>
-      <c r="N36" s="106" t="n"/>
+      <c r="D36" s="124" t="n"/>
+      <c r="E36" s="124" t="n"/>
+      <c r="F36" s="124" t="n"/>
+      <c r="G36" s="124" t="n"/>
+      <c r="H36" s="124" t="n"/>
+      <c r="I36" s="124" t="n"/>
+      <c r="J36" s="124" t="n"/>
+      <c r="K36" s="124" t="n"/>
+      <c r="L36" s="124" t="n"/>
+      <c r="M36" s="124" t="n"/>
+      <c r="N36" s="124" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="108" t="n">
+      <c r="A37" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="B37" s="108" t="n">
+      <c r="B37" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="C37" s="109">
+      <c r="C37" s="127">
         <f>A37*10+B37</f>
         <v/>
       </c>
-      <c r="D37" s="106" t="n"/>
-      <c r="E37" s="106" t="n"/>
-      <c r="F37" s="106" t="n"/>
-      <c r="G37" s="106" t="n"/>
-      <c r="H37" s="106" t="n"/>
-      <c r="I37" s="106" t="n"/>
-      <c r="J37" s="106" t="n"/>
-      <c r="K37" s="106" t="n"/>
-      <c r="L37" s="106" t="n"/>
-      <c r="M37" s="106" t="n"/>
-      <c r="N37" s="106" t="n"/>
+      <c r="D37" s="124" t="n"/>
+      <c r="E37" s="124" t="n"/>
+      <c r="F37" s="124" t="n"/>
+      <c r="G37" s="124" t="n"/>
+      <c r="H37" s="124" t="n"/>
+      <c r="I37" s="124" t="n"/>
+      <c r="J37" s="124" t="n"/>
+      <c r="K37" s="124" t="n"/>
+      <c r="L37" s="124" t="n"/>
+      <c r="M37" s="124" t="n"/>
+      <c r="N37" s="124" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="108" t="n">
+      <c r="A38" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="B38" s="108" t="n">
+      <c r="B38" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="C38" s="109">
+      <c r="C38" s="127">
         <f>A38*10+B38</f>
         <v/>
       </c>
-      <c r="D38" s="106" t="n"/>
-      <c r="E38" s="106" t="n"/>
-      <c r="F38" s="106" t="n"/>
-      <c r="G38" s="106" t="n"/>
-      <c r="H38" s="106" t="n"/>
-      <c r="I38" s="106" t="n"/>
-      <c r="J38" s="106" t="n"/>
-      <c r="K38" s="106" t="n"/>
-      <c r="L38" s="106" t="n"/>
-      <c r="M38" s="106" t="n"/>
-      <c r="N38" s="106" t="n"/>
+      <c r="D38" s="124" t="n"/>
+      <c r="E38" s="124" t="n"/>
+      <c r="F38" s="124" t="n"/>
+      <c r="G38" s="124" t="n"/>
+      <c r="H38" s="124" t="n"/>
+      <c r="I38" s="124" t="n"/>
+      <c r="J38" s="124" t="n"/>
+      <c r="K38" s="124" t="n"/>
+      <c r="L38" s="124" t="n"/>
+      <c r="M38" s="124" t="n"/>
+      <c r="N38" s="124" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="108" t="n">
+      <c r="A39" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="B39" s="108" t="n">
+      <c r="B39" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="C39" s="109">
+      <c r="C39" s="127">
         <f>A39*10+B39</f>
         <v/>
       </c>
-      <c r="D39" s="106" t="n"/>
-      <c r="E39" s="106" t="n"/>
-      <c r="F39" s="106" t="n"/>
-      <c r="G39" s="106" t="n"/>
-      <c r="H39" s="106" t="n"/>
-      <c r="I39" s="106" t="n"/>
-      <c r="J39" s="106" t="n"/>
-      <c r="K39" s="106" t="n"/>
-      <c r="L39" s="106" t="n"/>
-      <c r="M39" s="106" t="n"/>
-      <c r="N39" s="106" t="n"/>
+      <c r="D39" s="124" t="n"/>
+      <c r="E39" s="124" t="n"/>
+      <c r="F39" s="124" t="n"/>
+      <c r="G39" s="124" t="n"/>
+      <c r="H39" s="124" t="n"/>
+      <c r="I39" s="124" t="n"/>
+      <c r="J39" s="124" t="n"/>
+      <c r="K39" s="124" t="n"/>
+      <c r="L39" s="124" t="n"/>
+      <c r="M39" s="124" t="n"/>
+      <c r="N39" s="124" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="108" t="n">
+      <c r="A40" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="B40" s="108" t="n">
+      <c r="B40" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="109">
+      <c r="C40" s="127">
         <f>A40*10+B40</f>
         <v/>
       </c>
-      <c r="D40" s="106" t="n"/>
-      <c r="E40" s="106" t="n"/>
-      <c r="F40" s="106" t="n"/>
-      <c r="G40" s="106" t="n"/>
-      <c r="H40" s="106" t="n"/>
-      <c r="I40" s="106" t="n"/>
-      <c r="J40" s="106" t="n"/>
-      <c r="K40" s="106" t="n"/>
-      <c r="L40" s="106" t="n"/>
-      <c r="M40" s="106" t="n"/>
-      <c r="N40" s="106" t="n"/>
+      <c r="D40" s="124" t="n"/>
+      <c r="E40" s="124" t="n"/>
+      <c r="F40" s="124" t="n"/>
+      <c r="G40" s="124" t="n"/>
+      <c r="H40" s="124" t="n"/>
+      <c r="I40" s="124" t="n"/>
+      <c r="J40" s="124" t="n"/>
+      <c r="K40" s="124" t="n"/>
+      <c r="L40" s="124" t="n"/>
+      <c r="M40" s="124" t="n"/>
+      <c r="N40" s="124" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="108" t="n">
+      <c r="A41" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="B41" s="108" t="n">
+      <c r="B41" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="109">
+      <c r="C41" s="127">
         <f>A41*10+B41</f>
         <v/>
       </c>
-      <c r="D41" s="106" t="n"/>
-      <c r="E41" s="106" t="n"/>
-      <c r="F41" s="106" t="n"/>
-      <c r="G41" s="106" t="n"/>
-      <c r="H41" s="106" t="n"/>
-      <c r="I41" s="106" t="n"/>
-      <c r="J41" s="106" t="n"/>
-      <c r="K41" s="106" t="n"/>
-      <c r="L41" s="106" t="n"/>
-      <c r="M41" s="106" t="n"/>
-      <c r="N41" s="106" t="n"/>
+      <c r="D41" s="124" t="n"/>
+      <c r="E41" s="124" t="n"/>
+      <c r="F41" s="124" t="n"/>
+      <c r="G41" s="124" t="n"/>
+      <c r="H41" s="124" t="n"/>
+      <c r="I41" s="124" t="n"/>
+      <c r="J41" s="124" t="n"/>
+      <c r="K41" s="124" t="n"/>
+      <c r="L41" s="124" t="n"/>
+      <c r="M41" s="124" t="n"/>
+      <c r="N41" s="124" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="108" t="n">
+      <c r="A42" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="B42" s="108" t="n">
+      <c r="B42" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="C42" s="109">
+      <c r="C42" s="127">
         <f>A42*10+B42</f>
         <v/>
       </c>
-      <c r="D42" s="106" t="n"/>
-      <c r="E42" s="106" t="n"/>
-      <c r="F42" s="106" t="n"/>
-      <c r="G42" s="106" t="n"/>
-      <c r="H42" s="106" t="n"/>
-      <c r="I42" s="106" t="n"/>
-      <c r="J42" s="106" t="n"/>
-      <c r="K42" s="106" t="n"/>
-      <c r="L42" s="106" t="n"/>
-      <c r="M42" s="106" t="n"/>
-      <c r="N42" s="106" t="n"/>
+      <c r="D42" s="124" t="n"/>
+      <c r="E42" s="124" t="n"/>
+      <c r="F42" s="124" t="n"/>
+      <c r="G42" s="124" t="n"/>
+      <c r="H42" s="124" t="n"/>
+      <c r="I42" s="124" t="n"/>
+      <c r="J42" s="124" t="n"/>
+      <c r="K42" s="124" t="n"/>
+      <c r="L42" s="124" t="n"/>
+      <c r="M42" s="124" t="n"/>
+      <c r="N42" s="124" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="108" t="n">
+      <c r="A43" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="B43" s="108" t="n">
+      <c r="B43" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="C43" s="109">
+      <c r="C43" s="127">
         <f>A43*10+B43</f>
         <v/>
       </c>
-      <c r="D43" s="106" t="n"/>
-      <c r="E43" s="106" t="n"/>
-      <c r="F43" s="106" t="n"/>
-      <c r="G43" s="106" t="n"/>
-      <c r="H43" s="106" t="n"/>
-      <c r="I43" s="106" t="n"/>
-      <c r="J43" s="106" t="n"/>
-      <c r="K43" s="106" t="n"/>
-      <c r="L43" s="106" t="n"/>
-      <c r="M43" s="106" t="n"/>
-      <c r="N43" s="106" t="n"/>
+      <c r="D43" s="124" t="n"/>
+      <c r="E43" s="124" t="n"/>
+      <c r="F43" s="124" t="n"/>
+      <c r="G43" s="124" t="n"/>
+      <c r="H43" s="124" t="n"/>
+      <c r="I43" s="124" t="n"/>
+      <c r="J43" s="124" t="n"/>
+      <c r="K43" s="124" t="n"/>
+      <c r="L43" s="124" t="n"/>
+      <c r="M43" s="124" t="n"/>
+      <c r="N43" s="124" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="108" t="n">
+      <c r="A44" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="B44" s="108" t="n">
+      <c r="B44" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="C44" s="109">
+      <c r="C44" s="127">
         <f>A44*10+B44</f>
         <v/>
       </c>
-      <c r="D44" s="106" t="n"/>
-      <c r="E44" s="106" t="n"/>
-      <c r="F44" s="106" t="n"/>
-      <c r="G44" s="106" t="n"/>
-      <c r="H44" s="106" t="n"/>
-      <c r="I44" s="106" t="n"/>
-      <c r="J44" s="106" t="n"/>
-      <c r="K44" s="106" t="n"/>
-      <c r="L44" s="106" t="n"/>
-      <c r="M44" s="106" t="n"/>
-      <c r="N44" s="106" t="n"/>
+      <c r="D44" s="124" t="n"/>
+      <c r="E44" s="124" t="n"/>
+      <c r="F44" s="124" t="n"/>
+      <c r="G44" s="124" t="n"/>
+      <c r="H44" s="124" t="n"/>
+      <c r="I44" s="124" t="n"/>
+      <c r="J44" s="124" t="n"/>
+      <c r="K44" s="124" t="n"/>
+      <c r="L44" s="124" t="n"/>
+      <c r="M44" s="124" t="n"/>
+      <c r="N44" s="124" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="108" t="n">
+      <c r="A45" s="126" t="n">
         <v>6</v>
       </c>
-      <c r="B45" s="108" t="n">
+      <c r="B45" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="109">
+      <c r="C45" s="127">
         <f>A45*10+B45</f>
         <v/>
       </c>
-      <c r="D45" s="106" t="n"/>
-      <c r="E45" s="106" t="n"/>
-      <c r="F45" s="106" t="n"/>
-      <c r="G45" s="106" t="n"/>
-      <c r="H45" s="106" t="n"/>
-      <c r="I45" s="106" t="n"/>
-      <c r="J45" s="106" t="n"/>
-      <c r="K45" s="106" t="n"/>
-      <c r="L45" s="106" t="n"/>
-      <c r="M45" s="106" t="n"/>
-      <c r="N45" s="106" t="n"/>
+      <c r="D45" s="124" t="n"/>
+      <c r="E45" s="124" t="n"/>
+      <c r="F45" s="124" t="n"/>
+      <c r="G45" s="124" t="n"/>
+      <c r="H45" s="124" t="n"/>
+      <c r="I45" s="124" t="n"/>
+      <c r="J45" s="124" t="n"/>
+      <c r="K45" s="124" t="n"/>
+      <c r="L45" s="124" t="n"/>
+      <c r="M45" s="124" t="n"/>
+      <c r="N45" s="124" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="108" t="n">
+      <c r="A46" s="126" t="n">
         <v>6</v>
       </c>
-      <c r="B46" s="108" t="n">
+      <c r="B46" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="C46" s="109">
+      <c r="C46" s="127">
         <f>A46*10+B46</f>
         <v/>
       </c>
-      <c r="D46" s="106" t="n"/>
-      <c r="E46" s="106" t="n"/>
-      <c r="F46" s="106" t="n"/>
-      <c r="G46" s="106" t="n"/>
-      <c r="H46" s="106" t="n"/>
-      <c r="I46" s="106" t="n"/>
-      <c r="J46" s="106" t="n"/>
-      <c r="K46" s="106" t="n"/>
-      <c r="L46" s="106" t="n"/>
-      <c r="M46" s="106" t="n"/>
-      <c r="N46" s="106" t="n"/>
+      <c r="D46" s="124" t="n"/>
+      <c r="E46" s="124" t="n"/>
+      <c r="F46" s="124" t="n"/>
+      <c r="G46" s="124" t="n"/>
+      <c r="H46" s="124" t="n"/>
+      <c r="I46" s="124" t="n"/>
+      <c r="J46" s="124" t="n"/>
+      <c r="K46" s="124" t="n"/>
+      <c r="L46" s="124" t="n"/>
+      <c r="M46" s="124" t="n"/>
+      <c r="N46" s="124" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="108" t="n">
+      <c r="A47" s="126" t="n">
         <v>6</v>
       </c>
-      <c r="B47" s="108" t="n">
+      <c r="B47" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="C47" s="109">
+      <c r="C47" s="127">
         <f>A47*10+B47</f>
         <v/>
       </c>
-      <c r="D47" s="106" t="n"/>
-      <c r="E47" s="106" t="n"/>
-      <c r="F47" s="106" t="n"/>
-      <c r="G47" s="106" t="n"/>
-      <c r="H47" s="106" t="n"/>
-      <c r="I47" s="106" t="n"/>
-      <c r="J47" s="106" t="n"/>
-      <c r="K47" s="106" t="n"/>
-      <c r="L47" s="106" t="n"/>
-      <c r="M47" s="106" t="n"/>
-      <c r="N47" s="106" t="n"/>
+      <c r="D47" s="124" t="n"/>
+      <c r="E47" s="124" t="n"/>
+      <c r="F47" s="124" t="n"/>
+      <c r="G47" s="124" t="n"/>
+      <c r="H47" s="124" t="n"/>
+      <c r="I47" s="124" t="n"/>
+      <c r="J47" s="124" t="n"/>
+      <c r="K47" s="124" t="n"/>
+      <c r="L47" s="124" t="n"/>
+      <c r="M47" s="124" t="n"/>
+      <c r="N47" s="124" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="108" t="n">
+      <c r="A48" s="126" t="n">
         <v>6</v>
       </c>
-      <c r="B48" s="108" t="n">
+      <c r="B48" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="C48" s="109">
+      <c r="C48" s="127">
         <f>A48*10+B48</f>
         <v/>
       </c>
-      <c r="D48" s="106" t="n"/>
-      <c r="E48" s="106" t="n"/>
-      <c r="F48" s="106" t="n"/>
-      <c r="G48" s="106" t="n"/>
-      <c r="H48" s="106" t="n"/>
-      <c r="I48" s="106" t="n"/>
-      <c r="J48" s="106" t="n"/>
-      <c r="K48" s="106" t="n"/>
-      <c r="L48" s="106" t="n"/>
-      <c r="M48" s="106" t="n"/>
-      <c r="N48" s="106" t="n"/>
+      <c r="D48" s="124" t="n"/>
+      <c r="E48" s="124" t="n"/>
+      <c r="F48" s="124" t="n"/>
+      <c r="G48" s="124" t="n"/>
+      <c r="H48" s="124" t="n"/>
+      <c r="I48" s="124" t="n"/>
+      <c r="J48" s="124" t="n"/>
+      <c r="K48" s="124" t="n"/>
+      <c r="L48" s="124" t="n"/>
+      <c r="M48" s="124" t="n"/>
+      <c r="N48" s="124" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="108" t="n">
+      <c r="A49" s="126" t="n">
         <v>6</v>
       </c>
-      <c r="B49" s="108" t="n">
+      <c r="B49" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="C49" s="109">
+      <c r="C49" s="127">
         <f>A49*10+B49</f>
         <v/>
       </c>
-      <c r="D49" s="106" t="n"/>
-      <c r="E49" s="106" t="n"/>
-      <c r="F49" s="106" t="n"/>
-      <c r="G49" s="106" t="n"/>
-      <c r="H49" s="106" t="n"/>
-      <c r="I49" s="106" t="n"/>
-      <c r="J49" s="106" t="n"/>
-      <c r="K49" s="106" t="n"/>
-      <c r="L49" s="106" t="n"/>
-      <c r="M49" s="106" t="n"/>
-      <c r="N49" s="106" t="n"/>
+      <c r="D49" s="124" t="n"/>
+      <c r="E49" s="124" t="n"/>
+      <c r="F49" s="124" t="n"/>
+      <c r="G49" s="124" t="n"/>
+      <c r="H49" s="124" t="n"/>
+      <c r="I49" s="124" t="n"/>
+      <c r="J49" s="124" t="n"/>
+      <c r="K49" s="124" t="n"/>
+      <c r="L49" s="124" t="n"/>
+      <c r="M49" s="124" t="n"/>
+      <c r="N49" s="124" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="108" t="n">
+      <c r="A50" s="126" t="n">
         <v>7</v>
       </c>
-      <c r="B50" s="108" t="n">
+      <c r="B50" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="C50" s="109">
+      <c r="C50" s="127">
         <f>A50*10+B50</f>
         <v/>
       </c>
-      <c r="D50" s="106" t="n"/>
-      <c r="E50" s="106" t="n"/>
-      <c r="F50" s="106" t="n"/>
-      <c r="G50" s="106" t="n"/>
-      <c r="H50" s="106" t="n"/>
-      <c r="I50" s="106" t="n"/>
-      <c r="J50" s="106" t="n"/>
-      <c r="K50" s="106" t="n"/>
-      <c r="L50" s="106" t="n"/>
-      <c r="M50" s="106" t="n"/>
-      <c r="N50" s="106" t="n"/>
+      <c r="D50" s="124" t="n"/>
+      <c r="E50" s="124" t="n"/>
+      <c r="F50" s="124" t="n"/>
+      <c r="G50" s="124" t="n"/>
+      <c r="H50" s="124" t="n"/>
+      <c r="I50" s="124" t="n"/>
+      <c r="J50" s="124" t="n"/>
+      <c r="K50" s="124" t="n"/>
+      <c r="L50" s="124" t="n"/>
+      <c r="M50" s="124" t="n"/>
+      <c r="N50" s="124" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="108" t="n">
+      <c r="A51" s="126" t="n">
         <v>7</v>
       </c>
-      <c r="B51" s="108" t="n">
+      <c r="B51" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="C51" s="109">
+      <c r="C51" s="127">
         <f>A51*10+B51</f>
         <v/>
       </c>
-      <c r="D51" s="106" t="n"/>
-      <c r="E51" s="106" t="n"/>
-      <c r="F51" s="106" t="n"/>
-      <c r="G51" s="106" t="n"/>
-      <c r="H51" s="106" t="n"/>
-      <c r="I51" s="106" t="n"/>
-      <c r="J51" s="106" t="n"/>
-      <c r="K51" s="106" t="n"/>
-      <c r="L51" s="106" t="n"/>
-      <c r="M51" s="106" t="n"/>
-      <c r="N51" s="106" t="n"/>
+      <c r="D51" s="124" t="n"/>
+      <c r="E51" s="124" t="n"/>
+      <c r="F51" s="124" t="n"/>
+      <c r="G51" s="124" t="n"/>
+      <c r="H51" s="124" t="n"/>
+      <c r="I51" s="124" t="n"/>
+      <c r="J51" s="124" t="n"/>
+      <c r="K51" s="124" t="n"/>
+      <c r="L51" s="124" t="n"/>
+      <c r="M51" s="124" t="n"/>
+      <c r="N51" s="124" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="108" t="n">
+      <c r="A52" s="126" t="n">
         <v>7</v>
       </c>
-      <c r="B52" s="108" t="n">
+      <c r="B52" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="C52" s="109">
+      <c r="C52" s="127">
         <f>A52*10+B52</f>
         <v/>
       </c>
-      <c r="D52" s="106" t="n"/>
-      <c r="E52" s="106" t="n"/>
-      <c r="F52" s="106" t="n"/>
-      <c r="G52" s="106" t="n"/>
-      <c r="H52" s="106" t="n"/>
-      <c r="I52" s="106" t="n"/>
-      <c r="J52" s="106" t="n"/>
-      <c r="K52" s="106" t="n"/>
-      <c r="L52" s="106" t="n"/>
-      <c r="M52" s="106" t="n"/>
-      <c r="N52" s="106" t="n"/>
+      <c r="D52" s="124" t="n"/>
+      <c r="E52" s="124" t="n"/>
+      <c r="F52" s="124" t="n"/>
+      <c r="G52" s="124" t="n"/>
+      <c r="H52" s="124" t="n"/>
+      <c r="I52" s="124" t="n"/>
+      <c r="J52" s="124" t="n"/>
+      <c r="K52" s="124" t="n"/>
+      <c r="L52" s="124" t="n"/>
+      <c r="M52" s="124" t="n"/>
+      <c r="N52" s="124" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="108" t="n">
+      <c r="A53" s="126" t="n">
         <v>7</v>
       </c>
-      <c r="B53" s="108" t="n">
+      <c r="B53" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="C53" s="109">
+      <c r="C53" s="127">
         <f>A53*10+B53</f>
         <v/>
       </c>
-      <c r="D53" s="106" t="n"/>
-      <c r="E53" s="106" t="n"/>
-      <c r="F53" s="106" t="n"/>
-      <c r="G53" s="106" t="n"/>
-      <c r="H53" s="106" t="n"/>
-      <c r="I53" s="106" t="n"/>
-      <c r="J53" s="106" t="n"/>
-      <c r="K53" s="106" t="n"/>
-      <c r="L53" s="106" t="n"/>
-      <c r="M53" s="106" t="n"/>
-      <c r="N53" s="106" t="n"/>
+      <c r="D53" s="124" t="n"/>
+      <c r="E53" s="124" t="n"/>
+      <c r="F53" s="124" t="n"/>
+      <c r="G53" s="124" t="n"/>
+      <c r="H53" s="124" t="n"/>
+      <c r="I53" s="124" t="n"/>
+      <c r="J53" s="124" t="n"/>
+      <c r="K53" s="124" t="n"/>
+      <c r="L53" s="124" t="n"/>
+      <c r="M53" s="124" t="n"/>
+      <c r="N53" s="124" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="108" t="n">
+      <c r="A54" s="126" t="n">
         <v>7</v>
       </c>
-      <c r="B54" s="108" t="n">
+      <c r="B54" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="C54" s="109">
+      <c r="C54" s="127">
         <f>A54*10+B54</f>
         <v/>
       </c>
-      <c r="D54" s="106" t="n"/>
-      <c r="E54" s="106" t="n"/>
-      <c r="F54" s="106" t="n"/>
-      <c r="G54" s="106" t="n"/>
-      <c r="H54" s="106" t="n"/>
-      <c r="I54" s="106" t="n"/>
-      <c r="J54" s="106" t="n"/>
-      <c r="K54" s="106" t="n"/>
-      <c r="L54" s="106" t="n"/>
-      <c r="M54" s="106" t="n"/>
-      <c r="N54" s="106" t="n"/>
+      <c r="D54" s="124" t="n"/>
+      <c r="E54" s="124" t="n"/>
+      <c r="F54" s="124" t="n"/>
+      <c r="G54" s="124" t="n"/>
+      <c r="H54" s="124" t="n"/>
+      <c r="I54" s="124" t="n"/>
+      <c r="J54" s="124" t="n"/>
+      <c r="K54" s="124" t="n"/>
+      <c r="L54" s="124" t="n"/>
+      <c r="M54" s="124" t="n"/>
+      <c r="N54" s="124" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="108" t="n">
+      <c r="A55" s="126" t="n">
         <v>8</v>
       </c>
-      <c r="B55" s="108" t="n">
+      <c r="B55" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="109">
+      <c r="C55" s="127">
         <f>A55*10+B55</f>
         <v/>
       </c>
-      <c r="D55" s="106" t="n"/>
-      <c r="E55" s="106" t="n"/>
-      <c r="F55" s="106" t="n"/>
-      <c r="G55" s="106" t="n"/>
-      <c r="H55" s="106" t="n"/>
-      <c r="I55" s="106" t="n"/>
-      <c r="J55" s="106" t="n"/>
-      <c r="K55" s="106" t="n"/>
-      <c r="L55" s="106" t="n"/>
-      <c r="M55" s="106" t="n"/>
-      <c r="N55" s="106" t="n"/>
+      <c r="D55" s="124" t="n"/>
+      <c r="E55" s="124" t="n"/>
+      <c r="F55" s="124" t="n"/>
+      <c r="G55" s="124" t="n"/>
+      <c r="H55" s="124" t="n"/>
+      <c r="I55" s="124" t="n"/>
+      <c r="J55" s="124" t="n"/>
+      <c r="K55" s="124" t="n"/>
+      <c r="L55" s="124" t="n"/>
+      <c r="M55" s="124" t="n"/>
+      <c r="N55" s="124" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="108" t="n">
+      <c r="A56" s="126" t="n">
         <v>8</v>
       </c>
-      <c r="B56" s="108" t="n">
+      <c r="B56" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="C56" s="109">
+      <c r="C56" s="127">
         <f>A56*10+B56</f>
         <v/>
       </c>
-      <c r="D56" s="106" t="n"/>
-      <c r="E56" s="106" t="n"/>
-      <c r="F56" s="106" t="n"/>
-      <c r="G56" s="106" t="n"/>
-      <c r="H56" s="106" t="n"/>
-      <c r="I56" s="106" t="n"/>
-      <c r="J56" s="106" t="n"/>
-      <c r="K56" s="106" t="n"/>
-      <c r="L56" s="106" t="n"/>
-      <c r="M56" s="106" t="n"/>
-      <c r="N56" s="106" t="n"/>
+      <c r="D56" s="124" t="n"/>
+      <c r="E56" s="124" t="n"/>
+      <c r="F56" s="124" t="n"/>
+      <c r="G56" s="124" t="n"/>
+      <c r="H56" s="124" t="n"/>
+      <c r="I56" s="124" t="n"/>
+      <c r="J56" s="124" t="n"/>
+      <c r="K56" s="124" t="n"/>
+      <c r="L56" s="124" t="n"/>
+      <c r="M56" s="124" t="n"/>
+      <c r="N56" s="124" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="108" t="n">
+      <c r="A57" s="126" t="n">
         <v>8</v>
       </c>
-      <c r="B57" s="108" t="n">
+      <c r="B57" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="C57" s="109">
+      <c r="C57" s="127">
         <f>A57*10+B57</f>
         <v/>
       </c>
-      <c r="D57" s="106" t="n"/>
-      <c r="E57" s="106" t="n"/>
-      <c r="F57" s="106" t="n"/>
-      <c r="G57" s="106" t="n"/>
-      <c r="H57" s="106" t="n"/>
-      <c r="I57" s="106" t="n"/>
-      <c r="J57" s="106" t="n"/>
-      <c r="K57" s="106" t="n"/>
-      <c r="L57" s="106" t="n"/>
-      <c r="M57" s="106" t="n"/>
-      <c r="N57" s="106" t="n"/>
+      <c r="D57" s="124" t="n"/>
+      <c r="E57" s="124" t="n"/>
+      <c r="F57" s="124" t="n"/>
+      <c r="G57" s="124" t="n"/>
+      <c r="H57" s="124" t="n"/>
+      <c r="I57" s="124" t="n"/>
+      <c r="J57" s="124" t="n"/>
+      <c r="K57" s="124" t="n"/>
+      <c r="L57" s="124" t="n"/>
+      <c r="M57" s="124" t="n"/>
+      <c r="N57" s="124" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="108" t="n">
+      <c r="A58" s="126" t="n">
         <v>8</v>
       </c>
-      <c r="B58" s="108" t="n">
+      <c r="B58" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="C58" s="109">
+      <c r="C58" s="127">
         <f>A58*10+B58</f>
         <v/>
       </c>
-      <c r="D58" s="106" t="n"/>
-      <c r="E58" s="106" t="n"/>
-      <c r="F58" s="106" t="n"/>
-      <c r="G58" s="106" t="n"/>
-      <c r="H58" s="106" t="n"/>
-      <c r="I58" s="106" t="n"/>
-      <c r="J58" s="106" t="n"/>
-      <c r="K58" s="106" t="n"/>
-      <c r="L58" s="106" t="n"/>
-      <c r="M58" s="106" t="n"/>
-      <c r="N58" s="106" t="n"/>
+      <c r="D58" s="124" t="n"/>
+      <c r="E58" s="124" t="n"/>
+      <c r="F58" s="124" t="n"/>
+      <c r="G58" s="124" t="n"/>
+      <c r="H58" s="124" t="n"/>
+      <c r="I58" s="124" t="n"/>
+      <c r="J58" s="124" t="n"/>
+      <c r="K58" s="124" t="n"/>
+      <c r="L58" s="124" t="n"/>
+      <c r="M58" s="124" t="n"/>
+      <c r="N58" s="124" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="108" t="n">
+      <c r="A59" s="126" t="n">
         <v>8</v>
       </c>
-      <c r="B59" s="108" t="n">
+      <c r="B59" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="C59" s="109">
+      <c r="C59" s="127">
         <f>A59*10+B59</f>
         <v/>
       </c>
-      <c r="D59" s="106" t="n"/>
-      <c r="E59" s="106" t="n"/>
-      <c r="F59" s="106" t="n"/>
-      <c r="G59" s="106" t="n"/>
-      <c r="H59" s="106" t="n"/>
-      <c r="I59" s="106" t="n"/>
-      <c r="J59" s="106" t="n"/>
-      <c r="K59" s="106" t="n"/>
-      <c r="L59" s="106" t="n"/>
-      <c r="M59" s="106" t="n"/>
-      <c r="N59" s="106" t="n"/>
+      <c r="D59" s="124" t="n"/>
+      <c r="E59" s="124" t="n"/>
+      <c r="F59" s="124" t="n"/>
+      <c r="G59" s="124" t="n"/>
+      <c r="H59" s="124" t="n"/>
+      <c r="I59" s="124" t="n"/>
+      <c r="J59" s="124" t="n"/>
+      <c r="K59" s="124" t="n"/>
+      <c r="L59" s="124" t="n"/>
+      <c r="M59" s="124" t="n"/>
+      <c r="N59" s="124" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="108" t="n">
+      <c r="A60" s="126" t="n">
         <v>9</v>
       </c>
-      <c r="B60" s="108" t="n">
+      <c r="B60" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="109">
+      <c r="C60" s="127">
         <f>A60*10+B60</f>
         <v/>
       </c>
-      <c r="D60" s="106" t="n"/>
-      <c r="E60" s="106" t="n"/>
-      <c r="F60" s="106" t="n"/>
-      <c r="G60" s="106" t="n"/>
-      <c r="H60" s="106" t="n"/>
-      <c r="I60" s="106" t="n"/>
-      <c r="J60" s="106" t="n"/>
-      <c r="K60" s="106" t="n"/>
-      <c r="L60" s="106" t="n"/>
-      <c r="M60" s="106" t="n"/>
-      <c r="N60" s="106" t="n"/>
+      <c r="D60" s="124" t="n"/>
+      <c r="E60" s="124" t="n"/>
+      <c r="F60" s="124" t="n"/>
+      <c r="G60" s="124" t="n"/>
+      <c r="H60" s="124" t="n"/>
+      <c r="I60" s="124" t="n"/>
+      <c r="J60" s="124" t="n"/>
+      <c r="K60" s="124" t="n"/>
+      <c r="L60" s="124" t="n"/>
+      <c r="M60" s="124" t="n"/>
+      <c r="N60" s="124" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="108" t="n">
+      <c r="A61" s="126" t="n">
         <v>9</v>
       </c>
-      <c r="B61" s="108" t="n">
+      <c r="B61" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="C61" s="109">
+      <c r="C61" s="127">
         <f>A61*10+B61</f>
         <v/>
       </c>
-      <c r="D61" s="106" t="n"/>
-      <c r="E61" s="106" t="n"/>
-      <c r="F61" s="106" t="n"/>
-      <c r="G61" s="106" t="n"/>
-      <c r="H61" s="106" t="n"/>
-      <c r="I61" s="106" t="n"/>
-      <c r="J61" s="106" t="n"/>
-      <c r="K61" s="106" t="n"/>
-      <c r="L61" s="106" t="n"/>
-      <c r="M61" s="106" t="n"/>
-      <c r="N61" s="106" t="n"/>
+      <c r="D61" s="124" t="n"/>
+      <c r="E61" s="124" t="n"/>
+      <c r="F61" s="124" t="n"/>
+      <c r="G61" s="124" t="n"/>
+      <c r="H61" s="124" t="n"/>
+      <c r="I61" s="124" t="n"/>
+      <c r="J61" s="124" t="n"/>
+      <c r="K61" s="124" t="n"/>
+      <c r="L61" s="124" t="n"/>
+      <c r="M61" s="124" t="n"/>
+      <c r="N61" s="124" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="108" t="n">
+      <c r="A62" s="126" t="n">
         <v>9</v>
       </c>
-      <c r="B62" s="108" t="n">
+      <c r="B62" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="C62" s="109">
+      <c r="C62" s="127">
         <f>A62*10+B62</f>
         <v/>
       </c>
-      <c r="D62" s="106" t="n"/>
-      <c r="E62" s="106" t="n"/>
-      <c r="F62" s="106" t="n"/>
-      <c r="G62" s="106" t="n"/>
-      <c r="H62" s="106" t="n"/>
-      <c r="I62" s="106" t="n"/>
-      <c r="J62" s="106" t="n"/>
-      <c r="K62" s="106" t="n"/>
-      <c r="L62" s="106" t="n"/>
-      <c r="M62" s="106" t="n"/>
-      <c r="N62" s="106" t="n"/>
+      <c r="D62" s="124" t="n"/>
+      <c r="E62" s="124" t="n"/>
+      <c r="F62" s="124" t="n"/>
+      <c r="G62" s="124" t="n"/>
+      <c r="H62" s="124" t="n"/>
+      <c r="I62" s="124" t="n"/>
+      <c r="J62" s="124" t="n"/>
+      <c r="K62" s="124" t="n"/>
+      <c r="L62" s="124" t="n"/>
+      <c r="M62" s="124" t="n"/>
+      <c r="N62" s="124" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="108" t="n">
+      <c r="A63" s="126" t="n">
         <v>9</v>
       </c>
-      <c r="B63" s="108" t="n">
+      <c r="B63" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="C63" s="109">
+      <c r="C63" s="127">
         <f>A63*10+B63</f>
         <v/>
       </c>
-      <c r="D63" s="106" t="n"/>
-      <c r="E63" s="106" t="n"/>
-      <c r="F63" s="106" t="n"/>
-      <c r="G63" s="106" t="n"/>
-      <c r="H63" s="106" t="n"/>
-      <c r="I63" s="106" t="n"/>
-      <c r="J63" s="106" t="n"/>
-      <c r="K63" s="106" t="n"/>
-      <c r="L63" s="106" t="n"/>
-      <c r="M63" s="106" t="n"/>
-      <c r="N63" s="106" t="n"/>
+      <c r="D63" s="124" t="n"/>
+      <c r="E63" s="124" t="n"/>
+      <c r="F63" s="124" t="n"/>
+      <c r="G63" s="124" t="n"/>
+      <c r="H63" s="124" t="n"/>
+      <c r="I63" s="124" t="n"/>
+      <c r="J63" s="124" t="n"/>
+      <c r="K63" s="124" t="n"/>
+      <c r="L63" s="124" t="n"/>
+      <c r="M63" s="124" t="n"/>
+      <c r="N63" s="124" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="108" t="n">
+      <c r="A64" s="126" t="n">
         <v>9</v>
       </c>
-      <c r="B64" s="108" t="n">
+      <c r="B64" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="C64" s="109">
+      <c r="C64" s="127">
         <f>A64*10+B64</f>
         <v/>
       </c>
-      <c r="D64" s="106" t="n"/>
-      <c r="E64" s="106" t="n"/>
-      <c r="F64" s="106" t="n"/>
-      <c r="G64" s="106" t="n"/>
-      <c r="H64" s="106" t="n"/>
-      <c r="I64" s="106" t="n"/>
-      <c r="J64" s="106" t="n"/>
-      <c r="K64" s="106" t="n"/>
-      <c r="L64" s="106" t="n"/>
-      <c r="M64" s="106" t="n"/>
-      <c r="N64" s="106" t="n"/>
+      <c r="D64" s="124" t="n"/>
+      <c r="E64" s="124" t="n"/>
+      <c r="F64" s="124" t="n"/>
+      <c r="G64" s="124" t="n"/>
+      <c r="H64" s="124" t="n"/>
+      <c r="I64" s="124" t="n"/>
+      <c r="J64" s="124" t="n"/>
+      <c r="K64" s="124" t="n"/>
+      <c r="L64" s="124" t="n"/>
+      <c r="M64" s="124" t="n"/>
+      <c r="N64" s="124" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="108" t="n">
+      <c r="A65" s="126" t="n">
         <v>10</v>
       </c>
-      <c r="B65" s="108" t="n">
+      <c r="B65" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="C65" s="109">
+      <c r="C65" s="127">
         <f>A65*10+B65</f>
         <v/>
       </c>
-      <c r="D65" s="106" t="n"/>
-      <c r="E65" s="106" t="n"/>
-      <c r="F65" s="106" t="n"/>
-      <c r="G65" s="106" t="n"/>
-      <c r="H65" s="106" t="n"/>
-      <c r="I65" s="106" t="n"/>
-      <c r="J65" s="106" t="n"/>
-      <c r="K65" s="106" t="n"/>
-      <c r="L65" s="106" t="n"/>
-      <c r="M65" s="106" t="n"/>
-      <c r="N65" s="106" t="n"/>
+      <c r="D65" s="124" t="n"/>
+      <c r="E65" s="124" t="n"/>
+      <c r="F65" s="124" t="n"/>
+      <c r="G65" s="124" t="n"/>
+      <c r="H65" s="124" t="n"/>
+      <c r="I65" s="124" t="n"/>
+      <c r="J65" s="124" t="n"/>
+      <c r="K65" s="124" t="n"/>
+      <c r="L65" s="124" t="n"/>
+      <c r="M65" s="124" t="n"/>
+      <c r="N65" s="124" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="108" t="n">
+      <c r="A66" s="126" t="n">
         <v>10</v>
       </c>
-      <c r="B66" s="108" t="n">
+      <c r="B66" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="C66" s="109">
+      <c r="C66" s="127">
         <f>A66*10+B66</f>
         <v/>
       </c>
-      <c r="D66" s="106" t="n"/>
-      <c r="E66" s="106" t="n"/>
-      <c r="F66" s="106" t="n"/>
-      <c r="G66" s="106" t="n"/>
-      <c r="H66" s="106" t="n"/>
-      <c r="I66" s="106" t="n"/>
-      <c r="J66" s="106" t="n"/>
-      <c r="K66" s="106" t="n"/>
-      <c r="L66" s="106" t="n"/>
-      <c r="M66" s="106" t="n"/>
-      <c r="N66" s="106" t="n"/>
+      <c r="D66" s="124" t="n"/>
+      <c r="E66" s="124" t="n"/>
+      <c r="F66" s="124" t="n"/>
+      <c r="G66" s="124" t="n"/>
+      <c r="H66" s="124" t="n"/>
+      <c r="I66" s="124" t="n"/>
+      <c r="J66" s="124" t="n"/>
+      <c r="K66" s="124" t="n"/>
+      <c r="L66" s="124" t="n"/>
+      <c r="M66" s="124" t="n"/>
+      <c r="N66" s="124" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="108" t="n">
+      <c r="A67" s="126" t="n">
         <v>10</v>
       </c>
-      <c r="B67" s="108" t="n">
+      <c r="B67" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="C67" s="109">
+      <c r="C67" s="127">
         <f>A67*10+B67</f>
         <v/>
       </c>
-      <c r="D67" s="106" t="n"/>
-      <c r="E67" s="106" t="n"/>
-      <c r="F67" s="106" t="n"/>
-      <c r="G67" s="106" t="n"/>
-      <c r="H67" s="106" t="n"/>
-      <c r="I67" s="106" t="n"/>
-      <c r="J67" s="106" t="n"/>
-      <c r="K67" s="106" t="n"/>
-      <c r="L67" s="106" t="n"/>
-      <c r="M67" s="106" t="n"/>
-      <c r="N67" s="106" t="n"/>
+      <c r="D67" s="124" t="n"/>
+      <c r="E67" s="124" t="n"/>
+      <c r="F67" s="124" t="n"/>
+      <c r="G67" s="124" t="n"/>
+      <c r="H67" s="124" t="n"/>
+      <c r="I67" s="124" t="n"/>
+      <c r="J67" s="124" t="n"/>
+      <c r="K67" s="124" t="n"/>
+      <c r="L67" s="124" t="n"/>
+      <c r="M67" s="124" t="n"/>
+      <c r="N67" s="124" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="108" t="n">
+      <c r="A68" s="126" t="n">
         <v>10</v>
       </c>
-      <c r="B68" s="108" t="n">
+      <c r="B68" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="C68" s="109">
+      <c r="C68" s="127">
         <f>A68*10+B68</f>
         <v/>
       </c>
-      <c r="D68" s="106" t="n"/>
-      <c r="E68" s="106" t="n"/>
-      <c r="F68" s="106" t="n"/>
-      <c r="G68" s="106" t="n"/>
-      <c r="H68" s="106" t="n"/>
-      <c r="I68" s="106" t="n"/>
-      <c r="J68" s="106" t="n"/>
-      <c r="K68" s="106" t="n"/>
-      <c r="L68" s="106" t="n"/>
-      <c r="M68" s="106" t="n"/>
-      <c r="N68" s="106" t="n"/>
+      <c r="D68" s="124" t="n"/>
+      <c r="E68" s="124" t="n"/>
+      <c r="F68" s="124" t="n"/>
+      <c r="G68" s="124" t="n"/>
+      <c r="H68" s="124" t="n"/>
+      <c r="I68" s="124" t="n"/>
+      <c r="J68" s="124" t="n"/>
+      <c r="K68" s="124" t="n"/>
+      <c r="L68" s="124" t="n"/>
+      <c r="M68" s="124" t="n"/>
+      <c r="N68" s="124" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="108" t="n">
+      <c r="A69" s="126" t="n">
         <v>10</v>
       </c>
-      <c r="B69" s="108" t="n">
+      <c r="B69" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="C69" s="109">
+      <c r="C69" s="127">
         <f>A69*10+B69</f>
         <v/>
       </c>
-      <c r="D69" s="106" t="n"/>
-      <c r="E69" s="106" t="n"/>
-      <c r="F69" s="106" t="n"/>
-      <c r="G69" s="106" t="n"/>
-      <c r="H69" s="106" t="n"/>
-      <c r="I69" s="106" t="n"/>
-      <c r="J69" s="106" t="n"/>
-      <c r="K69" s="106" t="n"/>
-      <c r="L69" s="106" t="n"/>
-      <c r="M69" s="106" t="n"/>
-      <c r="N69" s="106" t="n"/>
+      <c r="D69" s="124" t="n"/>
+      <c r="E69" s="124" t="n"/>
+      <c r="F69" s="124" t="n"/>
+      <c r="G69" s="124" t="n"/>
+      <c r="H69" s="124" t="n"/>
+      <c r="I69" s="124" t="n"/>
+      <c r="J69" s="124" t="n"/>
+      <c r="K69" s="124" t="n"/>
+      <c r="L69" s="124" t="n"/>
+      <c r="M69" s="124" t="n"/>
+      <c r="N69" s="124" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="108" t="n">
+      <c r="A70" s="126" t="n">
         <v>11</v>
       </c>
-      <c r="B70" s="108" t="n">
+      <c r="B70" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="C70" s="109">
+      <c r="C70" s="127">
         <f>A70*10+B70</f>
         <v/>
       </c>
-      <c r="D70" s="106" t="n"/>
-      <c r="E70" s="106" t="n"/>
-      <c r="F70" s="106" t="n"/>
-      <c r="G70" s="106" t="n"/>
-      <c r="H70" s="106" t="n"/>
-      <c r="I70" s="106" t="n"/>
-      <c r="J70" s="106" t="n"/>
-      <c r="K70" s="106" t="n"/>
-      <c r="L70" s="106" t="n"/>
-      <c r="M70" s="106" t="n"/>
-      <c r="N70" s="106" t="n"/>
+      <c r="D70" s="124" t="n"/>
+      <c r="E70" s="124" t="n"/>
+      <c r="F70" s="124" t="n"/>
+      <c r="G70" s="124" t="n"/>
+      <c r="H70" s="124" t="n"/>
+      <c r="I70" s="124" t="n"/>
+      <c r="J70" s="124" t="n"/>
+      <c r="K70" s="124" t="n"/>
+      <c r="L70" s="124" t="n"/>
+      <c r="M70" s="124" t="n"/>
+      <c r="N70" s="124" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="108" t="n">
+      <c r="A71" s="126" t="n">
         <v>11</v>
       </c>
-      <c r="B71" s="108" t="n">
+      <c r="B71" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="C71" s="109">
+      <c r="C71" s="127">
         <f>A71*10+B71</f>
         <v/>
       </c>
-      <c r="D71" s="106" t="n"/>
-      <c r="E71" s="106" t="n"/>
-      <c r="F71" s="106" t="n"/>
-      <c r="G71" s="106" t="n"/>
-      <c r="H71" s="106" t="n"/>
-      <c r="I71" s="106" t="n"/>
-      <c r="J71" s="106" t="n"/>
-      <c r="K71" s="106" t="n"/>
-      <c r="L71" s="106" t="n"/>
-      <c r="M71" s="106" t="n"/>
-      <c r="N71" s="106" t="n"/>
+      <c r="D71" s="124" t="n"/>
+      <c r="E71" s="124" t="n"/>
+      <c r="F71" s="124" t="n"/>
+      <c r="G71" s="124" t="n"/>
+      <c r="H71" s="124" t="n"/>
+      <c r="I71" s="124" t="n"/>
+      <c r="J71" s="124" t="n"/>
+      <c r="K71" s="124" t="n"/>
+      <c r="L71" s="124" t="n"/>
+      <c r="M71" s="124" t="n"/>
+      <c r="N71" s="124" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="108" t="n">
+      <c r="A72" s="126" t="n">
         <v>11</v>
       </c>
-      <c r="B72" s="108" t="n">
+      <c r="B72" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="C72" s="109">
+      <c r="C72" s="127">
         <f>A72*10+B72</f>
         <v/>
       </c>
-      <c r="D72" s="106" t="n"/>
-      <c r="E72" s="106" t="n"/>
-      <c r="F72" s="106" t="n"/>
-      <c r="G72" s="106" t="n"/>
-      <c r="H72" s="106" t="n"/>
-      <c r="I72" s="106" t="n"/>
-      <c r="J72" s="106" t="n"/>
-      <c r="K72" s="106" t="n"/>
-      <c r="L72" s="106" t="n"/>
-      <c r="M72" s="106" t="n"/>
-      <c r="N72" s="106" t="n"/>
+      <c r="D72" s="124" t="n"/>
+      <c r="E72" s="124" t="n"/>
+      <c r="F72" s="124" t="n"/>
+      <c r="G72" s="124" t="n"/>
+      <c r="H72" s="124" t="n"/>
+      <c r="I72" s="124" t="n"/>
+      <c r="J72" s="124" t="n"/>
+      <c r="K72" s="124" t="n"/>
+      <c r="L72" s="124" t="n"/>
+      <c r="M72" s="124" t="n"/>
+      <c r="N72" s="124" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="108" t="n">
+      <c r="A73" s="126" t="n">
         <v>11</v>
       </c>
-      <c r="B73" s="108" t="n">
+      <c r="B73" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="C73" s="109">
+      <c r="C73" s="127">
         <f>A73*10+B73</f>
         <v/>
       </c>
-      <c r="D73" s="106" t="n"/>
-      <c r="E73" s="106" t="n"/>
-      <c r="F73" s="106" t="n"/>
-      <c r="G73" s="106" t="n"/>
-      <c r="H73" s="106" t="n"/>
-      <c r="I73" s="106" t="n"/>
-      <c r="J73" s="106" t="n"/>
-      <c r="K73" s="106" t="n"/>
-      <c r="L73" s="106" t="n"/>
-      <c r="M73" s="106" t="n"/>
-      <c r="N73" s="106" t="n"/>
+      <c r="D73" s="124" t="n"/>
+      <c r="E73" s="124" t="n"/>
+      <c r="F73" s="124" t="n"/>
+      <c r="G73" s="124" t="n"/>
+      <c r="H73" s="124" t="n"/>
+      <c r="I73" s="124" t="n"/>
+      <c r="J73" s="124" t="n"/>
+      <c r="K73" s="124" t="n"/>
+      <c r="L73" s="124" t="n"/>
+      <c r="M73" s="124" t="n"/>
+      <c r="N73" s="124" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="108" t="n">
+      <c r="A74" s="126" t="n">
         <v>11</v>
       </c>
-      <c r="B74" s="108" t="n">
+      <c r="B74" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="C74" s="109">
+      <c r="C74" s="127">
         <f>A74*10+B74</f>
         <v/>
       </c>
-      <c r="D74" s="106" t="n"/>
-      <c r="E74" s="106" t="n"/>
-      <c r="F74" s="106" t="n"/>
-      <c r="G74" s="106" t="n"/>
-      <c r="H74" s="106" t="n"/>
-      <c r="I74" s="106" t="n"/>
-      <c r="J74" s="106" t="n"/>
-      <c r="K74" s="106" t="n"/>
-      <c r="L74" s="106" t="n"/>
-      <c r="M74" s="106" t="n"/>
-      <c r="N74" s="106" t="n"/>
+      <c r="D74" s="124" t="n"/>
+      <c r="E74" s="124" t="n"/>
+      <c r="F74" s="124" t="n"/>
+      <c r="G74" s="124" t="n"/>
+      <c r="H74" s="124" t="n"/>
+      <c r="I74" s="124" t="n"/>
+      <c r="J74" s="124" t="n"/>
+      <c r="K74" s="124" t="n"/>
+      <c r="L74" s="124" t="n"/>
+      <c r="M74" s="124" t="n"/>
+      <c r="N74" s="124" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="108" t="n">
+      <c r="A75" s="126" t="n">
         <v>12</v>
       </c>
-      <c r="B75" s="108" t="n">
+      <c r="B75" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="C75" s="109">
+      <c r="C75" s="127">
         <f>A75*10+B75</f>
         <v/>
       </c>
-      <c r="D75" s="106" t="n"/>
-      <c r="E75" s="106" t="n"/>
-      <c r="F75" s="106" t="n"/>
-      <c r="G75" s="106" t="n"/>
-      <c r="H75" s="106" t="n"/>
-      <c r="I75" s="106" t="n"/>
-      <c r="J75" s="106" t="n"/>
-      <c r="K75" s="106" t="n"/>
-      <c r="L75" s="106" t="n"/>
-      <c r="M75" s="106" t="n"/>
-      <c r="N75" s="106" t="n"/>
+      <c r="D75" s="124" t="n"/>
+      <c r="E75" s="124" t="n"/>
+      <c r="F75" s="124" t="n"/>
+      <c r="G75" s="124" t="n"/>
+      <c r="H75" s="124" t="n"/>
+      <c r="I75" s="124" t="n"/>
+      <c r="J75" s="124" t="n"/>
+      <c r="K75" s="124" t="n"/>
+      <c r="L75" s="124" t="n"/>
+      <c r="M75" s="124" t="n"/>
+      <c r="N75" s="124" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="108" t="n">
+      <c r="A76" s="126" t="n">
         <v>12</v>
       </c>
-      <c r="B76" s="108" t="n">
+      <c r="B76" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="C76" s="109">
+      <c r="C76" s="127">
         <f>A76*10+B76</f>
         <v/>
       </c>
-      <c r="D76" s="106" t="n"/>
-      <c r="E76" s="106" t="n"/>
-      <c r="F76" s="106" t="n"/>
-      <c r="G76" s="106" t="n"/>
-      <c r="H76" s="106" t="n"/>
-      <c r="I76" s="106" t="n"/>
-      <c r="J76" s="106" t="n"/>
-      <c r="K76" s="106" t="n"/>
-      <c r="L76" s="106" t="n"/>
-      <c r="M76" s="106" t="n"/>
-      <c r="N76" s="106" t="n"/>
+      <c r="D76" s="124" t="n"/>
+      <c r="E76" s="124" t="n"/>
+      <c r="F76" s="124" t="n"/>
+      <c r="G76" s="124" t="n"/>
+      <c r="H76" s="124" t="n"/>
+      <c r="I76" s="124" t="n"/>
+      <c r="J76" s="124" t="n"/>
+      <c r="K76" s="124" t="n"/>
+      <c r="L76" s="124" t="n"/>
+      <c r="M76" s="124" t="n"/>
+      <c r="N76" s="124" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="108" t="n">
+      <c r="A77" s="126" t="n">
         <v>12</v>
       </c>
-      <c r="B77" s="108" t="n">
+      <c r="B77" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="C77" s="109">
+      <c r="C77" s="127">
         <f>A77*10+B77</f>
         <v/>
       </c>
-      <c r="D77" s="106" t="n"/>
-      <c r="E77" s="106" t="n"/>
-      <c r="F77" s="106" t="n"/>
-      <c r="G77" s="106" t="n"/>
-      <c r="H77" s="106" t="n"/>
-      <c r="I77" s="106" t="n"/>
-      <c r="J77" s="106" t="n"/>
-      <c r="K77" s="106" t="n"/>
-      <c r="L77" s="106" t="n"/>
-      <c r="M77" s="106" t="n"/>
-      <c r="N77" s="106" t="n"/>
+      <c r="D77" s="124" t="n"/>
+      <c r="E77" s="124" t="n"/>
+      <c r="F77" s="124" t="n"/>
+      <c r="G77" s="124" t="n"/>
+      <c r="H77" s="124" t="n"/>
+      <c r="I77" s="124" t="n"/>
+      <c r="J77" s="124" t="n"/>
+      <c r="K77" s="124" t="n"/>
+      <c r="L77" s="124" t="n"/>
+      <c r="M77" s="124" t="n"/>
+      <c r="N77" s="124" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="108" t="n">
+      <c r="A78" s="126" t="n">
         <v>12</v>
       </c>
-      <c r="B78" s="108" t="n">
+      <c r="B78" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="C78" s="109">
+      <c r="C78" s="127">
         <f>A78*10+B78</f>
         <v/>
       </c>
-      <c r="D78" s="106" t="n"/>
-      <c r="E78" s="106" t="n"/>
-      <c r="F78" s="106" t="n"/>
-      <c r="G78" s="106" t="n"/>
-      <c r="H78" s="106" t="n"/>
-      <c r="I78" s="106" t="n"/>
-      <c r="J78" s="106" t="n"/>
-      <c r="K78" s="106" t="n"/>
-      <c r="L78" s="106" t="n"/>
-      <c r="M78" s="106" t="n"/>
-      <c r="N78" s="106" t="n"/>
+      <c r="D78" s="124" t="n"/>
+      <c r="E78" s="124" t="n"/>
+      <c r="F78" s="124" t="n"/>
+      <c r="G78" s="124" t="n"/>
+      <c r="H78" s="124" t="n"/>
+      <c r="I78" s="124" t="n"/>
+      <c r="J78" s="124" t="n"/>
+      <c r="K78" s="124" t="n"/>
+      <c r="L78" s="124" t="n"/>
+      <c r="M78" s="124" t="n"/>
+      <c r="N78" s="124" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="108" t="n">
+      <c r="A79" s="126" t="n">
         <v>12</v>
       </c>
-      <c r="B79" s="108" t="n">
+      <c r="B79" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="C79" s="109">
+      <c r="C79" s="127">
         <f>A79*10+B79</f>
         <v/>
       </c>
-      <c r="D79" s="106" t="n"/>
-      <c r="E79" s="106" t="n"/>
-      <c r="F79" s="106" t="n"/>
-      <c r="G79" s="106" t="n"/>
-      <c r="H79" s="106" t="n"/>
-      <c r="I79" s="106" t="n"/>
-      <c r="J79" s="106" t="n"/>
-      <c r="K79" s="106" t="n"/>
-      <c r="L79" s="106" t="n"/>
-      <c r="M79" s="106" t="n"/>
-      <c r="N79" s="106" t="n"/>
+      <c r="D79" s="124" t="n"/>
+      <c r="E79" s="124" t="n"/>
+      <c r="F79" s="124" t="n"/>
+      <c r="G79" s="124" t="n"/>
+      <c r="H79" s="124" t="n"/>
+      <c r="I79" s="124" t="n"/>
+      <c r="J79" s="124" t="n"/>
+      <c r="K79" s="124" t="n"/>
+      <c r="L79" s="124" t="n"/>
+      <c r="M79" s="124" t="n"/>
+      <c r="N79" s="124" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
